--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecuworldwide-my.sharepoint.com/personal/daniel_calle_am_eculine_net/Documents/Documentos/ASIAPAC/COTIZADOR GITHUB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="267" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{092D7B1A-144B-469F-86B0-08B499F39627}"/>
+  <xr:revisionPtr revIDLastSave="280" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6ADDF8E-3523-4D45-8F5F-16C02D552E8C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="95">
   <si>
     <t>POD</t>
   </si>
@@ -311,6 +311,24 @@
   <si>
     <t xml:space="preserve">BUSAN </t>
   </si>
+  <si>
+    <t>KEELUNG</t>
+  </si>
+  <si>
+    <t>TAOYUAN</t>
+  </si>
+  <si>
+    <t>COSCO</t>
+  </si>
+  <si>
+    <t>TAICHUNG</t>
+  </si>
+  <si>
+    <t>TAIPEI</t>
+  </si>
+  <si>
+    <t>KAOHSIUNG</t>
+  </si>
 </sst>
 </file>
 
@@ -319,7 +337,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="0\ &quot;DÍAS&quot;"/>
-    <numFmt numFmtId="167" formatCode="[$USD]\ #,##0"/>
+    <numFmt numFmtId="166" formatCode="[$USD]\ #,##0"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -453,10 +471,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -837,7 +855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}">
-  <dimension ref="A1:I1307"/>
+  <dimension ref="A1:I1309"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
@@ -2576,97 +2594,202 @@
         <v>38</v>
       </c>
     </row>
-    <row r="65" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>94</v>
+      </c>
+      <c r="B65" t="s">
+        <v>12</v>
+      </c>
       <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
-      <c r="G65" s="7"/>
-    </row>
-    <row r="66" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D65" s="9">
+        <v>7930</v>
+      </c>
+      <c r="E65" s="9">
+        <v>8180</v>
+      </c>
+      <c r="F65" t="s">
+        <v>40</v>
+      </c>
+      <c r="G65" s="7">
+        <v>17</v>
+      </c>
+      <c r="H65" t="s">
+        <v>91</v>
+      </c>
+      <c r="I65" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>92</v>
+      </c>
+      <c r="B66" t="s">
+        <v>12</v>
+      </c>
       <c r="C66" s="9"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="9"/>
-      <c r="G66" s="7"/>
-    </row>
-    <row r="67" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D66" s="9">
+        <v>7930</v>
+      </c>
+      <c r="E66" s="9">
+        <v>8180</v>
+      </c>
+      <c r="F66" t="s">
+        <v>40</v>
+      </c>
+      <c r="G66" s="7">
+        <v>17</v>
+      </c>
+      <c r="H66" t="s">
+        <v>91</v>
+      </c>
+      <c r="I66" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>93</v>
+      </c>
+      <c r="B67" t="s">
+        <v>12</v>
+      </c>
       <c r="C67" s="9"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="9"/>
-      <c r="G67" s="7"/>
-    </row>
-    <row r="68" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D67" s="9">
+        <v>7930</v>
+      </c>
+      <c r="E67" s="9">
+        <v>8180</v>
+      </c>
+      <c r="F67" t="s">
+        <v>40</v>
+      </c>
+      <c r="G67" s="7">
+        <v>17</v>
+      </c>
+      <c r="H67" t="s">
+        <v>91</v>
+      </c>
+      <c r="I67" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>89</v>
+      </c>
+      <c r="B68" t="s">
+        <v>12</v>
+      </c>
       <c r="C68" s="9"/>
-      <c r="D68" s="9"/>
-      <c r="E68" s="9"/>
-      <c r="G68" s="7"/>
-    </row>
-    <row r="69" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D68" s="9">
+        <v>8030</v>
+      </c>
+      <c r="E68" s="9">
+        <v>8330</v>
+      </c>
+      <c r="F68" t="s">
+        <v>40</v>
+      </c>
+      <c r="G68" s="7">
+        <v>17</v>
+      </c>
+      <c r="H68" t="s">
+        <v>91</v>
+      </c>
+      <c r="I68" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>90</v>
+      </c>
+      <c r="B69" t="s">
+        <v>12</v>
+      </c>
       <c r="C69" s="9"/>
-      <c r="D69" s="9"/>
-      <c r="E69" s="9"/>
-      <c r="G69" s="7"/>
-    </row>
-    <row r="70" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D69" s="9">
+        <v>8130</v>
+      </c>
+      <c r="E69" s="9">
+        <v>8480</v>
+      </c>
+      <c r="F69" t="s">
+        <v>40</v>
+      </c>
+      <c r="G69" s="7">
+        <v>17</v>
+      </c>
+      <c r="H69" t="s">
+        <v>91</v>
+      </c>
+      <c r="I69" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C70" s="9"/>
       <c r="D70" s="9"/>
       <c r="E70" s="9"/>
       <c r="G70" s="7"/>
     </row>
-    <row r="71" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C71" s="9"/>
       <c r="D71" s="9"/>
       <c r="E71" s="9"/>
       <c r="G71" s="7"/>
     </row>
-    <row r="72" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C72" s="9"/>
       <c r="D72" s="9"/>
       <c r="E72" s="9"/>
       <c r="G72" s="7"/>
     </row>
-    <row r="73" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C73" s="9"/>
       <c r="D73" s="9"/>
       <c r="E73" s="9"/>
       <c r="G73" s="7"/>
     </row>
-    <row r="74" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C74" s="9"/>
       <c r="D74" s="9"/>
       <c r="E74" s="9"/>
       <c r="G74" s="7"/>
     </row>
-    <row r="75" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C75" s="9"/>
       <c r="D75" s="9"/>
       <c r="E75" s="9"/>
       <c r="G75" s="7"/>
     </row>
-    <row r="76" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C76" s="9"/>
       <c r="D76" s="9"/>
       <c r="E76" s="9"/>
       <c r="G76" s="7"/>
     </row>
-    <row r="77" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C77" s="9"/>
       <c r="D77" s="9"/>
       <c r="E77" s="9"/>
       <c r="G77" s="7"/>
     </row>
-    <row r="78" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C78" s="9"/>
       <c r="D78" s="9"/>
       <c r="E78" s="9"/>
       <c r="G78" s="7"/>
     </row>
-    <row r="79" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C79" s="9"/>
       <c r="D79" s="9"/>
       <c r="E79" s="9"/>
       <c r="G79" s="7"/>
     </row>
-    <row r="80" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C80" s="9"/>
       <c r="D80" s="9"/>
       <c r="E80" s="9"/>
@@ -10033,6 +10156,18 @@
       <c r="D1307" s="9"/>
       <c r="E1307" s="9"/>
       <c r="G1307" s="7"/>
+    </row>
+    <row r="1308" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C1308" s="9"/>
+      <c r="D1308" s="9"/>
+      <c r="E1308" s="9"/>
+      <c r="G1308" s="7"/>
+    </row>
+    <row r="1309" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C1309" s="9"/>
+      <c r="D1309" s="9"/>
+      <c r="E1309" s="9"/>
+      <c r="G1309" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}"/>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecuworldwide-my.sharepoint.com/personal/daniel_calle_am_eculine_net/Documents/Documentos/ASIAPAC/COTIZADOR GITHUB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="280" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6ADDF8E-3523-4D45-8F5F-16C02D552E8C}"/>
+  <xr:revisionPtr revIDLastSave="295" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20BD53D9-6CAD-45FA-AB9E-FE0214B882C4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="101">
   <si>
     <t>POD</t>
   </si>
@@ -328,6 +328,24 @@
   </si>
   <si>
     <t>KAOHSIUNG</t>
+  </si>
+  <si>
+    <t>CALLAO</t>
+  </si>
+  <si>
+    <t>1 al 30 de septiembre</t>
+  </si>
+  <si>
+    <t>PIL</t>
+  </si>
+  <si>
+    <t>SPX</t>
+  </si>
+  <si>
+    <t>ONE</t>
+  </si>
+  <si>
+    <t>TPSAC</t>
   </si>
 </sst>
 </file>
@@ -2730,16 +2748,54 @@
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>95</v>
+      </c>
+      <c r="B70" t="s">
+        <v>12</v>
+      </c>
       <c r="C70" s="9"/>
       <c r="D70" s="9"/>
-      <c r="E70" s="9"/>
-      <c r="G70" s="7"/>
+      <c r="E70" s="9">
+        <v>440</v>
+      </c>
+      <c r="F70" t="s">
+        <v>96</v>
+      </c>
+      <c r="G70" s="7">
+        <v>14</v>
+      </c>
+      <c r="H70" t="s">
+        <v>97</v>
+      </c>
+      <c r="I70" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>95</v>
+      </c>
+      <c r="B71" t="s">
+        <v>12</v>
+      </c>
       <c r="C71" s="9"/>
       <c r="D71" s="9"/>
-      <c r="E71" s="9"/>
-      <c r="G71" s="7"/>
+      <c r="E71" s="9">
+        <v>390</v>
+      </c>
+      <c r="F71" t="s">
+        <v>96</v>
+      </c>
+      <c r="G71" s="7">
+        <v>15</v>
+      </c>
+      <c r="H71" t="s">
+        <v>99</v>
+      </c>
+      <c r="I71" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C72" s="9"/>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecuworldwide-my.sharepoint.com/personal/daniel_calle_am_eculine_net/Documents/Documentos/ASIAPAC/COTIZADOR GITHUB/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DOCS EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="295" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20BD53D9-6CAD-45FA-AB9E-FE0214B882C4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A777C19-4956-430B-A2CB-9655F49E6BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="109">
   <si>
     <t>POD</t>
   </si>
@@ -126,48 +126,12 @@
     <t>OWS MAS DE 18TN EQUIPO DE 20 A CRITERIO NAVIERA</t>
   </si>
   <si>
-    <t xml:space="preserve"> SHENZHEN </t>
-  </si>
-  <si>
-    <t xml:space="preserve">HONGKONG </t>
-  </si>
-  <si>
     <t xml:space="preserve">SHANGHAI </t>
   </si>
   <si>
-    <t xml:space="preserve">NINGBO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">QINGDAO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">XINGANG </t>
-  </si>
-  <si>
-    <t xml:space="preserve">XIAMEN </t>
-  </si>
-  <si>
-    <t xml:space="preserve">DALIAN </t>
-  </si>
-  <si>
-    <t>1 al 6 de septiembre</t>
-  </si>
-  <si>
-    <t>MSC</t>
-  </si>
-  <si>
-    <t>Z</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
-    <t xml:space="preserve">SHENZHEN </t>
-  </si>
-  <si>
-    <t>1 al 7 de septiembre</t>
-  </si>
-  <si>
     <t>EMC</t>
   </si>
   <si>
@@ -312,24 +276,9 @@
     <t xml:space="preserve">BUSAN </t>
   </si>
   <si>
-    <t>KEELUNG</t>
-  </si>
-  <si>
-    <t>TAOYUAN</t>
-  </si>
-  <si>
     <t>COSCO</t>
   </si>
   <si>
-    <t>TAICHUNG</t>
-  </si>
-  <si>
-    <t>TAIPEI</t>
-  </si>
-  <si>
-    <t>KAOHSIUNG</t>
-  </si>
-  <si>
     <t>CALLAO</t>
   </si>
   <si>
@@ -346,6 +295,81 @@
   </si>
   <si>
     <t>TPSAC</t>
+  </si>
+  <si>
+    <t>NINGBO</t>
+  </si>
+  <si>
+    <t>QINGDAO</t>
+  </si>
+  <si>
+    <t>SHEKOU</t>
+  </si>
+  <si>
+    <t>YANTIAN</t>
+  </si>
+  <si>
+    <t>XIAMEN</t>
+  </si>
+  <si>
+    <t>KAOSHIUNG/BUSAN</t>
+  </si>
+  <si>
+    <t>XINGANG</t>
+  </si>
+  <si>
+    <t>8 al 14 de septiembre</t>
+  </si>
+  <si>
+    <t>21 DRY / 14 NOR</t>
+  </si>
+  <si>
+    <t>Z-HF</t>
+  </si>
+  <si>
+    <t>DALIAN</t>
+  </si>
+  <si>
+    <t>17 DRY / 14 NOR</t>
+  </si>
+  <si>
+    <t>HUANGPU/NANSHA</t>
+  </si>
+  <si>
+    <t>JIANGMEN</t>
+  </si>
+  <si>
+    <t>ZHONGSHAN</t>
+  </si>
+  <si>
+    <t>ZHUHAI</t>
+  </si>
+  <si>
+    <t>RONGQI</t>
+  </si>
+  <si>
+    <t>SHANTOU</t>
+  </si>
+  <si>
+    <t>18 DRY / 14 NOR</t>
+  </si>
+  <si>
+    <t>OOCL</t>
+  </si>
+  <si>
+    <t>OOCL 20GP ≥ 18TN AGREGAR OWS $250</t>
+  </si>
+  <si>
+    <t>SHANGHAI</t>
+  </si>
+  <si>
+    <t>SHENZHEN</t>
+  </si>
+  <si>
+    <t>15 al 21 de septiembre</t>
+  </si>
+  <si>
+    <t>Z-J</t>
   </si>
 </sst>
 </file>
@@ -873,7 +897,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}">
-  <dimension ref="A1:I1309"/>
+  <dimension ref="A1:I1288"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
@@ -913,1703 +937,1723 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9">
-        <v>8080</v>
+        <v>6890</v>
       </c>
       <c r="E2" s="9">
-        <v>8980</v>
+        <v>7090</v>
       </c>
       <c r="F2" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="G2" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H2" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="I2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="9">
-        <v>8080</v>
+        <v>7090</v>
       </c>
       <c r="E3" s="9">
-        <v>8980</v>
+        <v>7490</v>
       </c>
       <c r="F3" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="G3" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="I3" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="9">
-        <v>8080</v>
+        <v>6890</v>
       </c>
       <c r="E4" s="9">
-        <v>8980</v>
+        <v>7090</v>
       </c>
       <c r="F4" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="G4" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="I4" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9">
-        <v>8080</v>
+        <v>6890</v>
       </c>
       <c r="E5" s="9">
-        <v>8980</v>
+        <v>7090</v>
       </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="G5" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="I5" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9">
-        <v>8080</v>
+        <v>6890</v>
       </c>
       <c r="E6" s="9">
-        <v>8980</v>
+        <v>7090</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="G6" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H6" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="I6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9">
-        <v>8080</v>
+        <v>6090</v>
       </c>
       <c r="E7" s="9">
-        <v>8980</v>
+        <v>6990</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="G7" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H7" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="I7" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9">
-        <v>8080</v>
+        <v>6090</v>
       </c>
       <c r="E8" s="9">
-        <v>8980</v>
+        <v>6990</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="G8" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H8" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="I8" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9">
-        <v>8080</v>
+        <v>6590</v>
       </c>
       <c r="E9" s="9">
-        <v>8980</v>
+        <v>7290</v>
       </c>
       <c r="F9" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="G9" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H9" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="I9" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9">
-        <v>7900</v>
+        <v>6090</v>
       </c>
       <c r="E10" s="9">
-        <v>8650</v>
+        <v>6990</v>
       </c>
       <c r="F10" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="G10" s="7">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H10" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="I10" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9">
-        <v>7900</v>
+        <v>6090</v>
       </c>
       <c r="E11" s="9">
-        <v>8650</v>
+        <v>6990</v>
       </c>
       <c r="F11" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="G11" s="7">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H11" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="I11" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9">
-        <v>7900</v>
+        <v>6090</v>
       </c>
       <c r="E12" s="9">
-        <v>8650</v>
+        <v>6990</v>
       </c>
       <c r="F12" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="G12" s="7">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H12" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="I12" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9">
-        <v>7900</v>
+        <v>6090</v>
       </c>
       <c r="E13" s="9">
-        <v>8650</v>
+        <v>6990</v>
       </c>
       <c r="F13" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="G13" s="7">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H13" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="I13" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9">
-        <v>7950</v>
+        <v>6090</v>
       </c>
       <c r="E14" s="9">
-        <v>8750</v>
+        <v>6990</v>
       </c>
       <c r="F14" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="G14" s="7">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H14" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="I14" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9">
-        <v>7950</v>
+        <v>6090</v>
       </c>
       <c r="E15" s="9">
-        <v>8750</v>
+        <v>6990</v>
       </c>
       <c r="F15" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="G15" s="7">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H15" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="I15" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9">
-        <v>8000</v>
+        <v>6090</v>
       </c>
       <c r="E16" s="9">
-        <v>8850</v>
+        <v>6990</v>
       </c>
       <c r="F16" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="G16" s="7">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H16" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="I16" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9">
-        <v>7950</v>
+        <v>6090</v>
       </c>
       <c r="E17" s="9">
-        <v>8750</v>
+        <v>6990</v>
       </c>
       <c r="F17" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="G17" s="7">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H17" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="I17" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9">
-        <v>6890</v>
+        <v>6090</v>
       </c>
       <c r="E18" s="9">
-        <v>7090</v>
+        <v>6990</v>
       </c>
       <c r="F18" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G18" s="7">
         <v>18</v>
       </c>
       <c r="H18" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I18" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9">
-        <v>7090</v>
+        <v>6590</v>
       </c>
       <c r="E19" s="9">
-        <v>7490</v>
+        <v>7290</v>
       </c>
       <c r="F19" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G19" s="7">
         <v>18</v>
       </c>
       <c r="H19" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I19" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B20" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9">
-        <v>6890</v>
+        <v>6090</v>
       </c>
       <c r="E20" s="9">
-        <v>7090</v>
+        <v>6990</v>
       </c>
       <c r="F20" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G20" s="7">
         <v>18</v>
       </c>
       <c r="H20" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I20" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B21" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9">
-        <v>6890</v>
+        <v>6090</v>
       </c>
       <c r="E21" s="9">
-        <v>7090</v>
+        <v>6990</v>
       </c>
       <c r="F21" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G21" s="7">
         <v>18</v>
       </c>
       <c r="H21" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I21" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9">
-        <v>6890</v>
+        <v>6140</v>
       </c>
       <c r="E22" s="9">
-        <v>7090</v>
+        <v>6590</v>
       </c>
       <c r="F22" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G22" s="7">
         <v>18</v>
       </c>
       <c r="H22" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I22" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B23" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9">
-        <v>6090</v>
+        <v>6140</v>
       </c>
       <c r="E23" s="9">
-        <v>6990</v>
+        <v>6590</v>
       </c>
       <c r="F23" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G23" s="7">
         <v>18</v>
       </c>
       <c r="H23" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I23" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B24" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9">
-        <v>6090</v>
+        <v>6140</v>
       </c>
       <c r="E24" s="9">
-        <v>6990</v>
+        <v>6590</v>
       </c>
       <c r="F24" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G24" s="7">
         <v>18</v>
       </c>
       <c r="H24" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I24" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B25" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9">
+        <v>6140</v>
+      </c>
+      <c r="E25" s="9">
         <v>6590</v>
       </c>
-      <c r="E25" s="9">
-        <v>7290</v>
-      </c>
       <c r="F25" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G25" s="7">
         <v>18</v>
       </c>
       <c r="H25" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I25" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B26" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9">
-        <v>6090</v>
+        <v>6140</v>
       </c>
       <c r="E26" s="9">
-        <v>6990</v>
+        <v>6590</v>
       </c>
       <c r="F26" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G26" s="7">
         <v>18</v>
       </c>
       <c r="H26" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I26" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B27" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9">
-        <v>6090</v>
+        <v>6340</v>
       </c>
       <c r="E27" s="9">
-        <v>6990</v>
+        <v>6890</v>
       </c>
       <c r="F27" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G27" s="7">
         <v>18</v>
       </c>
       <c r="H27" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I27" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B28" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9">
-        <v>6090</v>
+        <v>6340</v>
       </c>
       <c r="E28" s="9">
-        <v>6990</v>
+        <v>6890</v>
       </c>
       <c r="F28" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G28" s="7">
         <v>18</v>
       </c>
       <c r="H28" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I28" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="B29" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9">
-        <v>6090</v>
+        <v>6990</v>
       </c>
       <c r="E29" s="9">
-        <v>6990</v>
+        <v>7390</v>
       </c>
       <c r="F29" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G29" s="7">
         <v>18</v>
       </c>
       <c r="H29" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I29" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B30" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9">
-        <v>6090</v>
+        <v>6990</v>
       </c>
       <c r="E30" s="9">
-        <v>6990</v>
+        <v>7090</v>
       </c>
       <c r="F30" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G30" s="7">
         <v>18</v>
       </c>
       <c r="H30" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I30" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B31" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9">
-        <v>6090</v>
+        <v>6990</v>
       </c>
       <c r="E31" s="9">
-        <v>6990</v>
+        <v>7090</v>
       </c>
       <c r="F31" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G31" s="7">
         <v>18</v>
       </c>
       <c r="H31" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I31" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B32" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9">
-        <v>6090</v>
+        <v>6990</v>
       </c>
       <c r="E32" s="9">
-        <v>6990</v>
+        <v>7090</v>
       </c>
       <c r="F32" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G32" s="7">
         <v>18</v>
       </c>
       <c r="H32" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I32" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B33" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9">
-        <v>6090</v>
+        <v>7240</v>
       </c>
       <c r="E33" s="9">
-        <v>6990</v>
+        <v>7590</v>
       </c>
       <c r="F33" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G33" s="7">
         <v>18</v>
       </c>
       <c r="H33" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I33" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B34" t="s">
         <v>12</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9">
-        <v>6090</v>
+        <v>7290</v>
       </c>
       <c r="E34" s="9">
-        <v>6990</v>
+        <v>7390</v>
       </c>
       <c r="F34" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G34" s="7">
         <v>18</v>
       </c>
       <c r="H34" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I34" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B35" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9">
-        <v>6590</v>
+        <v>6290</v>
       </c>
       <c r="E35" s="9">
-        <v>7290</v>
+        <v>6690</v>
       </c>
       <c r="F35" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G35" s="7">
         <v>18</v>
       </c>
       <c r="H35" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I35" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B36" t="s">
         <v>12</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9">
-        <v>6090</v>
+        <v>6290</v>
       </c>
       <c r="E36" s="9">
-        <v>6990</v>
+        <v>6690</v>
       </c>
       <c r="F36" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G36" s="7">
         <v>18</v>
       </c>
       <c r="H36" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I36" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B37" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9">
-        <v>6090</v>
+        <v>6290</v>
       </c>
       <c r="E37" s="9">
-        <v>6990</v>
+        <v>6690</v>
       </c>
       <c r="F37" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G37" s="7">
         <v>18</v>
       </c>
       <c r="H37" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I37" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B38" t="s">
         <v>12</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9">
-        <v>6140</v>
+        <v>6590</v>
       </c>
       <c r="E38" s="9">
-        <v>6590</v>
+        <v>6890</v>
       </c>
       <c r="F38" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G38" s="7">
         <v>18</v>
       </c>
       <c r="H38" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I38" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B39" t="s">
         <v>12</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9">
-        <v>6140</v>
+        <v>7190</v>
       </c>
       <c r="E39" s="9">
-        <v>6590</v>
+        <v>7590</v>
       </c>
       <c r="F39" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G39" s="7">
         <v>18</v>
       </c>
       <c r="H39" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I39" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B40" t="s">
         <v>12</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9">
-        <v>6140</v>
+        <v>6590</v>
       </c>
       <c r="E40" s="9">
-        <v>6590</v>
+        <v>6890</v>
       </c>
       <c r="F40" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G40" s="7">
         <v>18</v>
       </c>
       <c r="H40" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I40" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B41" t="s">
         <v>12</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9">
-        <v>6140</v>
+        <v>6590</v>
       </c>
       <c r="E41" s="9">
-        <v>6590</v>
+        <v>6890</v>
       </c>
       <c r="F41" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G41" s="7">
         <v>18</v>
       </c>
       <c r="H41" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I41" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B42" t="s">
         <v>12</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="9">
-        <v>6140</v>
+        <v>6590</v>
       </c>
       <c r="E42" s="9">
-        <v>6590</v>
+        <v>6890</v>
       </c>
       <c r="F42" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G42" s="7">
         <v>18</v>
       </c>
       <c r="H42" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I42" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B43" t="s">
         <v>12</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9">
-        <v>6340</v>
+        <v>6800</v>
       </c>
       <c r="E43" s="9">
-        <v>6890</v>
+        <v>7100</v>
       </c>
       <c r="F43" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G43" s="7">
         <v>18</v>
       </c>
       <c r="H43" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I43" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B44" t="s">
         <v>12</v>
       </c>
       <c r="C44" s="9"/>
       <c r="D44" s="9">
-        <v>6340</v>
+        <v>6390</v>
       </c>
       <c r="E44" s="9">
-        <v>6890</v>
+        <v>6690</v>
       </c>
       <c r="F44" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G44" s="7">
         <v>18</v>
       </c>
       <c r="H44" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I44" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="B45" t="s">
         <v>12</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="9">
-        <v>6990</v>
+        <v>6390</v>
       </c>
       <c r="E45" s="9">
-        <v>7390</v>
+        <v>6690</v>
       </c>
       <c r="F45" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G45" s="7">
         <v>18</v>
       </c>
       <c r="H45" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I45" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B46" t="s">
         <v>12</v>
       </c>
       <c r="C46" s="9"/>
       <c r="D46" s="9">
-        <v>6990</v>
+        <v>5990</v>
       </c>
       <c r="E46" s="9">
-        <v>7090</v>
+        <v>6690</v>
       </c>
       <c r="F46" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G46" s="7">
         <v>18</v>
       </c>
       <c r="H46" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I46" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B47" t="s">
         <v>12</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="9">
-        <v>6990</v>
+        <v>6190</v>
       </c>
       <c r="E47" s="9">
-        <v>7090</v>
+        <v>6690</v>
       </c>
       <c r="F47" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G47" s="7">
         <v>18</v>
       </c>
       <c r="H47" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I47" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B48" t="s">
         <v>12</v>
       </c>
       <c r="C48" s="9"/>
       <c r="D48" s="9">
-        <v>6990</v>
+        <v>5890</v>
       </c>
       <c r="E48" s="9">
-        <v>7090</v>
+        <v>6390</v>
       </c>
       <c r="F48" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G48" s="7">
         <v>18</v>
       </c>
       <c r="H48" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I48" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B49" t="s">
         <v>12</v>
       </c>
       <c r="C49" s="9"/>
-      <c r="D49" s="9">
-        <v>7240</v>
-      </c>
+      <c r="D49" s="9"/>
       <c r="E49" s="9">
-        <v>7590</v>
+        <v>440</v>
       </c>
       <c r="F49" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="G49" s="7">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H49" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="I49" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B50" t="s">
         <v>12</v>
       </c>
       <c r="C50" s="9"/>
-      <c r="D50" s="9">
-        <v>7290</v>
-      </c>
+      <c r="D50" s="9"/>
       <c r="E50" s="9">
-        <v>7390</v>
+        <v>390</v>
       </c>
       <c r="F50" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="G50" s="7">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H50" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="I50" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="B51" t="s">
         <v>12</v>
       </c>
-      <c r="C51" s="9"/>
+      <c r="C51" s="9">
+        <v>6450</v>
+      </c>
       <c r="D51" s="9">
-        <v>6290</v>
+        <v>7450</v>
       </c>
       <c r="E51" s="9">
-        <v>6690</v>
+        <v>7650</v>
       </c>
       <c r="F51" t="s">
-        <v>86</v>
-      </c>
-      <c r="G51" s="7">
-        <v>18</v>
+        <v>91</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="H51" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="I51" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="B52" t="s">
         <v>12</v>
       </c>
-      <c r="C52" s="9"/>
+      <c r="C52" s="9">
+        <v>6430</v>
+      </c>
       <c r="D52" s="9">
-        <v>6290</v>
+        <v>7450</v>
       </c>
       <c r="E52" s="9">
-        <v>6690</v>
+        <v>7650</v>
       </c>
       <c r="F52" t="s">
-        <v>86</v>
-      </c>
-      <c r="G52" s="7">
-        <v>18</v>
+        <v>91</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="H52" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="I52" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="B53" t="s">
         <v>12</v>
       </c>
-      <c r="C53" s="9"/>
+      <c r="C53" s="9">
+        <v>6430</v>
+      </c>
       <c r="D53" s="9">
-        <v>6290</v>
+        <v>7450</v>
       </c>
       <c r="E53" s="9">
-        <v>6690</v>
+        <v>7650</v>
       </c>
       <c r="F53" t="s">
-        <v>86</v>
-      </c>
-      <c r="G53" s="7">
-        <v>18</v>
+        <v>91</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="H53" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="I53" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="B54" t="s">
         <v>12</v>
       </c>
-      <c r="C54" s="9"/>
+      <c r="C54" s="9">
+        <v>6430</v>
+      </c>
       <c r="D54" s="9">
-        <v>6590</v>
+        <v>7450</v>
       </c>
       <c r="E54" s="9">
-        <v>6890</v>
+        <v>7650</v>
       </c>
       <c r="F54" t="s">
-        <v>86</v>
-      </c>
-      <c r="G54" s="7">
-        <v>18</v>
+        <v>91</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="H54" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="I54" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="B55" t="s">
         <v>12</v>
       </c>
-      <c r="C55" s="9"/>
+      <c r="C55" s="9">
+        <v>6430</v>
+      </c>
       <c r="D55" s="9">
-        <v>7190</v>
+        <v>7450</v>
       </c>
       <c r="E55" s="9">
-        <v>7590</v>
+        <v>7650</v>
       </c>
       <c r="F55" t="s">
-        <v>86</v>
-      </c>
-      <c r="G55" s="7">
-        <v>18</v>
+        <v>91</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="H55" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="I55" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="B56" t="s">
         <v>12</v>
       </c>
-      <c r="C56" s="9"/>
+      <c r="C56" s="9">
+        <v>6430</v>
+      </c>
       <c r="D56" s="9">
-        <v>6590</v>
+        <v>7450</v>
       </c>
       <c r="E56" s="9">
-        <v>6890</v>
+        <v>7650</v>
       </c>
       <c r="F56" t="s">
-        <v>86</v>
-      </c>
-      <c r="G56" s="7">
-        <v>18</v>
+        <v>91</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="H56" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="I56" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B57" t="s">
         <v>12</v>
       </c>
-      <c r="C57" s="9"/>
+      <c r="C57" s="9">
+        <v>6430</v>
+      </c>
       <c r="D57" s="9">
-        <v>6590</v>
+        <v>7450</v>
       </c>
       <c r="E57" s="9">
-        <v>6890</v>
+        <v>7650</v>
       </c>
       <c r="F57" t="s">
-        <v>86</v>
-      </c>
-      <c r="G57" s="7">
-        <v>18</v>
+        <v>91</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="H57" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="I57" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="B58" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="9"/>
       <c r="D58" s="9">
-        <v>6590</v>
+        <v>7550</v>
       </c>
       <c r="E58" s="9">
-        <v>6890</v>
+        <v>7850</v>
       </c>
       <c r="F58" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G58" s="7">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H58" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="I58" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B59" t="s">
         <v>12</v>
       </c>
-      <c r="C59" s="9"/>
+      <c r="C59" s="9">
+        <v>6410</v>
+      </c>
       <c r="D59" s="9">
-        <v>6800</v>
+        <v>7210</v>
       </c>
       <c r="E59" s="9">
-        <v>7100</v>
+        <v>7410</v>
       </c>
       <c r="F59" t="s">
-        <v>86</v>
-      </c>
-      <c r="G59" s="7">
-        <v>18</v>
+        <v>91</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="H59" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="I59" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="B60" t="s">
         <v>12</v>
       </c>
-      <c r="C60" s="9"/>
+      <c r="C60" s="9">
+        <v>6410</v>
+      </c>
       <c r="D60" s="9">
-        <v>6390</v>
+        <v>7210</v>
       </c>
       <c r="E60" s="9">
-        <v>6690</v>
+        <v>7410</v>
       </c>
       <c r="F60" t="s">
-        <v>86</v>
-      </c>
-      <c r="G60" s="7">
-        <v>18</v>
+        <v>91</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="H60" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="I60" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B61" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="9">
-        <v>6390</v>
+        <v>7210</v>
       </c>
       <c r="E61" s="9">
-        <v>6690</v>
+        <v>7410</v>
       </c>
       <c r="F61" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G61" s="7">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H61" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="I61" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B62" t="s">
         <v>12</v>
       </c>
-      <c r="C62" s="9"/>
+      <c r="C62" s="9">
+        <v>6410</v>
+      </c>
       <c r="D62" s="9">
-        <v>5990</v>
+        <v>7210</v>
       </c>
       <c r="E62" s="9">
-        <v>6690</v>
+        <v>7410</v>
       </c>
       <c r="F62" t="s">
-        <v>86</v>
-      </c>
-      <c r="G62" s="7">
-        <v>18</v>
+        <v>91</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="H62" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="I62" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B63" t="s">
         <v>12</v>
       </c>
-      <c r="C63" s="9"/>
+      <c r="C63" s="9">
+        <v>6410</v>
+      </c>
       <c r="D63" s="9">
-        <v>6190</v>
+        <v>7210</v>
       </c>
       <c r="E63" s="9">
-        <v>6690</v>
+        <v>7410</v>
       </c>
       <c r="F63" t="s">
-        <v>86</v>
-      </c>
-      <c r="G63" s="7">
-        <v>18</v>
+        <v>91</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="H63" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="I63" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B64" t="s">
         <v>12</v>
       </c>
-      <c r="C64" s="9"/>
+      <c r="C64" s="9">
+        <v>6410</v>
+      </c>
       <c r="D64" s="9">
-        <v>5890</v>
+        <v>7210</v>
       </c>
       <c r="E64" s="9">
-        <v>6390</v>
+        <v>7410</v>
       </c>
       <c r="F64" t="s">
-        <v>86</v>
-      </c>
-      <c r="G64" s="7">
-        <v>18</v>
+        <v>91</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="H64" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="I64" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
@@ -2619,237 +2663,440 @@
       <c r="B65" t="s">
         <v>12</v>
       </c>
-      <c r="C65" s="9"/>
+      <c r="C65" s="9">
+        <v>6510</v>
+      </c>
       <c r="D65" s="9">
-        <v>7930</v>
+        <v>7310</v>
       </c>
       <c r="E65" s="9">
-        <v>8180</v>
+        <v>7610</v>
       </c>
       <c r="F65" t="s">
-        <v>40</v>
-      </c>
-      <c r="G65" s="7">
-        <v>17</v>
+        <v>91</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="H65" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="I65" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B66" t="s">
         <v>12</v>
       </c>
-      <c r="C66" s="9"/>
+      <c r="C66" s="9">
+        <v>6510</v>
+      </c>
       <c r="D66" s="9">
-        <v>7930</v>
+        <v>7310</v>
       </c>
       <c r="E66" s="9">
-        <v>8180</v>
+        <v>7610</v>
       </c>
       <c r="F66" t="s">
-        <v>40</v>
-      </c>
-      <c r="G66" s="7">
-        <v>17</v>
+        <v>91</v>
+      </c>
+      <c r="G66" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="H66" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="I66" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="B67" t="s">
         <v>12</v>
       </c>
-      <c r="C67" s="9"/>
+      <c r="C67" s="9">
+        <v>5830</v>
+      </c>
       <c r="D67" s="9">
-        <v>7930</v>
+        <v>7030</v>
       </c>
       <c r="E67" s="9">
-        <v>8180</v>
+        <v>7230</v>
       </c>
       <c r="F67" t="s">
-        <v>40</v>
-      </c>
-      <c r="G67" s="7">
-        <v>17</v>
+        <v>91</v>
+      </c>
+      <c r="G67" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="H67" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="I67" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B68" t="s">
         <v>12</v>
       </c>
-      <c r="C68" s="9"/>
+      <c r="C68" s="9">
+        <v>5830</v>
+      </c>
       <c r="D68" s="9">
-        <v>8030</v>
+        <v>7030</v>
       </c>
       <c r="E68" s="9">
-        <v>8330</v>
+        <v>7230</v>
       </c>
       <c r="F68" t="s">
-        <v>40</v>
-      </c>
-      <c r="G68" s="7">
-        <v>17</v>
+        <v>91</v>
+      </c>
+      <c r="G68" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="H68" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="I68" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B69" t="s">
         <v>12</v>
       </c>
-      <c r="C69" s="9"/>
+      <c r="C69" s="9">
+        <v>5830</v>
+      </c>
       <c r="D69" s="9">
-        <v>8130</v>
+        <v>7030</v>
       </c>
       <c r="E69" s="9">
-        <v>8480</v>
+        <v>7230</v>
       </c>
       <c r="F69" t="s">
-        <v>40</v>
-      </c>
-      <c r="G69" s="7">
-        <v>17</v>
+        <v>91</v>
+      </c>
+      <c r="G69" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="H69" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="I69" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B70" t="s">
         <v>12</v>
       </c>
       <c r="C70" s="9"/>
-      <c r="D70" s="9"/>
+      <c r="D70" s="9">
+        <v>7080</v>
+      </c>
       <c r="E70" s="9">
-        <v>440</v>
+        <v>7330</v>
       </c>
       <c r="F70" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="G70" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H70" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I70" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B71" t="s">
         <v>12</v>
       </c>
       <c r="C71" s="9"/>
-      <c r="D71" s="9"/>
+      <c r="D71" s="9">
+        <v>7150</v>
+      </c>
       <c r="E71" s="9">
-        <v>390</v>
+        <v>7380</v>
       </c>
       <c r="F71" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="G71" s="7">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H71" t="s">
+        <v>103</v>
+      </c>
+      <c r="I71" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>98</v>
+      </c>
+      <c r="B72" t="s">
+        <v>12</v>
+      </c>
+      <c r="C72" s="9"/>
+      <c r="D72" s="9">
+        <v>7090</v>
+      </c>
+      <c r="E72" s="9">
+        <v>7380</v>
+      </c>
+      <c r="F72" t="s">
+        <v>91</v>
+      </c>
+      <c r="G72" s="7">
+        <v>18</v>
+      </c>
+      <c r="H72" t="s">
+        <v>103</v>
+      </c>
+      <c r="I72" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>99</v>
       </c>
-      <c r="I71" t="s">
+      <c r="B73" t="s">
+        <v>12</v>
+      </c>
+      <c r="C73" s="9"/>
+      <c r="D73" s="9">
+        <v>7090</v>
+      </c>
+      <c r="E73" s="9">
+        <v>7380</v>
+      </c>
+      <c r="F73" t="s">
+        <v>91</v>
+      </c>
+      <c r="G73" s="7">
+        <v>18</v>
+      </c>
+      <c r="H73" t="s">
+        <v>103</v>
+      </c>
+      <c r="I73" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C72" s="9"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="9"/>
-      <c r="G72" s="7"/>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C73" s="9"/>
-      <c r="D73" s="9"/>
-      <c r="E73" s="9"/>
-      <c r="G73" s="7"/>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B74" t="s">
+        <v>12</v>
+      </c>
       <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
-      <c r="G74" s="7"/>
+      <c r="D74" s="9">
+        <v>7090</v>
+      </c>
+      <c r="E74" s="9">
+        <v>7380</v>
+      </c>
+      <c r="F74" t="s">
+        <v>91</v>
+      </c>
+      <c r="G74" s="7">
+        <v>18</v>
+      </c>
+      <c r="H74" t="s">
+        <v>103</v>
+      </c>
+      <c r="I74" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>101</v>
+      </c>
+      <c r="B75" t="s">
+        <v>12</v>
+      </c>
       <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="9"/>
-      <c r="G75" s="7"/>
+      <c r="D75" s="9">
+        <v>7150</v>
+      </c>
+      <c r="E75" s="9">
+        <v>7430</v>
+      </c>
+      <c r="F75" t="s">
+        <v>91</v>
+      </c>
+      <c r="G75" s="7">
+        <v>18</v>
+      </c>
+      <c r="H75" t="s">
+        <v>103</v>
+      </c>
+      <c r="I75" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>105</v>
+      </c>
+      <c r="B76" t="s">
+        <v>12</v>
+      </c>
       <c r="C76" s="9"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="9"/>
-      <c r="G76" s="7"/>
+      <c r="D76" s="9">
+        <v>6780</v>
+      </c>
+      <c r="E76" s="9">
+        <v>6980</v>
+      </c>
+      <c r="F76" t="s">
+        <v>107</v>
+      </c>
+      <c r="G76" s="7">
+        <v>20</v>
+      </c>
+      <c r="H76" t="s">
+        <v>80</v>
+      </c>
+      <c r="I76" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>84</v>
+      </c>
+      <c r="B77" t="s">
+        <v>12</v>
+      </c>
       <c r="C77" s="9"/>
-      <c r="D77" s="9"/>
-      <c r="E77" s="9"/>
-      <c r="G77" s="7"/>
+      <c r="D77" s="9">
+        <v>6780</v>
+      </c>
+      <c r="E77" s="9">
+        <v>6980</v>
+      </c>
+      <c r="F77" t="s">
+        <v>107</v>
+      </c>
+      <c r="G77" s="7">
+        <v>18</v>
+      </c>
+      <c r="H77" t="s">
+        <v>80</v>
+      </c>
+      <c r="I77" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>106</v>
+      </c>
+      <c r="B78" t="s">
+        <v>12</v>
+      </c>
       <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="G78" s="7"/>
+      <c r="D78" s="9">
+        <v>6780</v>
+      </c>
+      <c r="E78" s="9">
+        <v>6980</v>
+      </c>
+      <c r="F78" t="s">
+        <v>107</v>
+      </c>
+      <c r="G78" s="7">
+        <v>20</v>
+      </c>
+      <c r="H78" t="s">
+        <v>80</v>
+      </c>
+      <c r="I78" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>86</v>
+      </c>
+      <c r="B79" t="s">
+        <v>12</v>
+      </c>
       <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="G79" s="7"/>
+      <c r="D79" s="9">
+        <v>6780</v>
+      </c>
+      <c r="E79" s="9">
+        <v>6980</v>
+      </c>
+      <c r="F79" t="s">
+        <v>107</v>
+      </c>
+      <c r="G79" s="7">
+        <v>20</v>
+      </c>
+      <c r="H79" t="s">
+        <v>80</v>
+      </c>
+      <c r="I79" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>85</v>
+      </c>
+      <c r="B80" t="s">
+        <v>12</v>
+      </c>
       <c r="C80" s="9"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
-      <c r="G80" s="7"/>
+      <c r="D80" s="9">
+        <v>6780</v>
+      </c>
+      <c r="E80" s="9">
+        <v>6980</v>
+      </c>
+      <c r="F80" t="s">
+        <v>107</v>
+      </c>
+      <c r="G80" s="7">
+        <v>20</v>
+      </c>
+      <c r="H80" t="s">
+        <v>80</v>
+      </c>
+      <c r="I80" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="81" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C81" s="9"/>
@@ -10098,132 +10345,6 @@
       <c r="D1288" s="9"/>
       <c r="E1288" s="9"/>
       <c r="G1288" s="7"/>
-    </row>
-    <row r="1289" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1289" s="9"/>
-      <c r="D1289" s="9"/>
-      <c r="E1289" s="9"/>
-      <c r="G1289" s="7"/>
-    </row>
-    <row r="1290" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1290" s="9"/>
-      <c r="D1290" s="9"/>
-      <c r="E1290" s="9"/>
-      <c r="G1290" s="7"/>
-    </row>
-    <row r="1291" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1291" s="9"/>
-      <c r="D1291" s="9"/>
-      <c r="E1291" s="9"/>
-      <c r="G1291" s="7"/>
-    </row>
-    <row r="1292" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1292" s="9"/>
-      <c r="D1292" s="9"/>
-      <c r="E1292" s="9"/>
-      <c r="G1292" s="7"/>
-    </row>
-    <row r="1293" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1293" s="9"/>
-      <c r="D1293" s="9"/>
-      <c r="E1293" s="9"/>
-      <c r="G1293" s="7"/>
-    </row>
-    <row r="1294" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1294" s="9"/>
-      <c r="D1294" s="9"/>
-      <c r="E1294" s="9"/>
-      <c r="G1294" s="7"/>
-    </row>
-    <row r="1295" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1295" s="9"/>
-      <c r="D1295" s="9"/>
-      <c r="E1295" s="9"/>
-      <c r="G1295" s="7"/>
-    </row>
-    <row r="1296" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1296" s="9"/>
-      <c r="D1296" s="9"/>
-      <c r="E1296" s="9"/>
-      <c r="G1296" s="7"/>
-    </row>
-    <row r="1297" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1297" s="9"/>
-      <c r="D1297" s="9"/>
-      <c r="E1297" s="9"/>
-      <c r="G1297" s="7"/>
-    </row>
-    <row r="1298" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1298" s="9"/>
-      <c r="D1298" s="9"/>
-      <c r="E1298" s="9"/>
-      <c r="G1298" s="7"/>
-    </row>
-    <row r="1299" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1299" s="9"/>
-      <c r="D1299" s="9"/>
-      <c r="E1299" s="9"/>
-      <c r="G1299" s="7"/>
-    </row>
-    <row r="1300" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1300" s="9"/>
-      <c r="D1300" s="9"/>
-      <c r="E1300" s="9"/>
-      <c r="G1300" s="7"/>
-    </row>
-    <row r="1301" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1301" s="9"/>
-      <c r="D1301" s="9"/>
-      <c r="E1301" s="9"/>
-      <c r="G1301" s="7"/>
-    </row>
-    <row r="1302" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1302" s="9"/>
-      <c r="D1302" s="9"/>
-      <c r="E1302" s="9"/>
-      <c r="G1302" s="7"/>
-    </row>
-    <row r="1303" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1303" s="9"/>
-      <c r="D1303" s="9"/>
-      <c r="E1303" s="9"/>
-      <c r="G1303" s="7"/>
-    </row>
-    <row r="1304" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1304" s="9"/>
-      <c r="D1304" s="9"/>
-      <c r="E1304" s="9"/>
-      <c r="G1304" s="7"/>
-    </row>
-    <row r="1305" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1305" s="9"/>
-      <c r="D1305" s="9"/>
-      <c r="E1305" s="9"/>
-      <c r="G1305" s="7"/>
-    </row>
-    <row r="1306" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1306" s="9"/>
-      <c r="D1306" s="9"/>
-      <c r="E1306" s="9"/>
-      <c r="G1306" s="7"/>
-    </row>
-    <row r="1307" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1307" s="9"/>
-      <c r="D1307" s="9"/>
-      <c r="E1307" s="9"/>
-      <c r="G1307" s="7"/>
-    </row>
-    <row r="1308" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1308" s="9"/>
-      <c r="D1308" s="9"/>
-      <c r="E1308" s="9"/>
-      <c r="G1308" s="7"/>
-    </row>
-    <row r="1309" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1309" s="9"/>
-      <c r="D1309" s="9"/>
-      <c r="E1309" s="9"/>
-      <c r="G1309" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}"/>
@@ -10319,7 +10440,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3805A486-29BF-4244-AD2E-4DBCFFE9D0EA}">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -10352,6 +10473,11 @@
         <v>26</v>
       </c>
     </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DOCS EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A777C19-4956-430B-A2CB-9655F49E6BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0247A70C-45B9-4079-966B-068F73523BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="111">
   <si>
     <t>POD</t>
   </si>
@@ -370,6 +370,12 @@
   </si>
   <si>
     <t>Z-J</t>
+  </si>
+  <si>
+    <t>20 al 30 de septiembre</t>
+  </si>
+  <si>
+    <t>Z-ES</t>
   </si>
 </sst>
 </file>
@@ -897,7 +903,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}">
-  <dimension ref="A1:I1288"/>
+  <dimension ref="A1:I1286"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
@@ -3098,97 +3104,265 @@
         <v>108</v>
       </c>
     </row>
-    <row r="81" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>106</v>
+      </c>
+      <c r="B81" t="s">
+        <v>12</v>
+      </c>
       <c r="C81" s="9"/>
-      <c r="D81" s="9"/>
-      <c r="E81" s="9"/>
-      <c r="G81" s="7"/>
-    </row>
-    <row r="82" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D81" s="9">
+        <v>6110</v>
+      </c>
+      <c r="E81" s="9">
+        <v>6710</v>
+      </c>
+      <c r="F81" t="s">
+        <v>109</v>
+      </c>
+      <c r="G81" s="7">
+        <v>17</v>
+      </c>
+      <c r="H81" t="s">
+        <v>77</v>
+      </c>
+      <c r="I81" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>105</v>
+      </c>
+      <c r="B82" t="s">
+        <v>12</v>
+      </c>
       <c r="C82" s="9"/>
-      <c r="D82" s="9"/>
-      <c r="E82" s="9"/>
-      <c r="G82" s="7"/>
-    </row>
-    <row r="83" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D82" s="9">
+        <v>6110</v>
+      </c>
+      <c r="E82" s="9">
+        <v>6710</v>
+      </c>
+      <c r="F82" t="s">
+        <v>109</v>
+      </c>
+      <c r="G82" s="7">
+        <v>17</v>
+      </c>
+      <c r="H82" t="s">
+        <v>77</v>
+      </c>
+      <c r="I82" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>106</v>
+      </c>
+      <c r="B83" t="s">
+        <v>12</v>
+      </c>
       <c r="C83" s="9"/>
-      <c r="D83" s="9"/>
-      <c r="E83" s="9"/>
-      <c r="G83" s="7"/>
-    </row>
-    <row r="84" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D83" s="9">
+        <v>5980</v>
+      </c>
+      <c r="E83" s="9">
+        <v>6630</v>
+      </c>
+      <c r="F83" t="s">
+        <v>109</v>
+      </c>
+      <c r="G83" s="7">
+        <v>18</v>
+      </c>
+      <c r="H83" t="s">
+        <v>103</v>
+      </c>
+      <c r="I83" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>84</v>
+      </c>
+      <c r="B84" t="s">
+        <v>12</v>
+      </c>
       <c r="C84" s="9"/>
-      <c r="D84" s="9"/>
-      <c r="E84" s="9"/>
-      <c r="G84" s="7"/>
-    </row>
-    <row r="85" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D84" s="9">
+        <v>5980</v>
+      </c>
+      <c r="E84" s="9">
+        <v>6630</v>
+      </c>
+      <c r="F84" t="s">
+        <v>109</v>
+      </c>
+      <c r="G84" s="7">
+        <v>18</v>
+      </c>
+      <c r="H84" t="s">
+        <v>103</v>
+      </c>
+      <c r="I84" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>105</v>
+      </c>
+      <c r="B85" t="s">
+        <v>12</v>
+      </c>
       <c r="C85" s="9"/>
-      <c r="D85" s="9"/>
-      <c r="E85" s="9"/>
-      <c r="G85" s="7"/>
-    </row>
-    <row r="86" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D85" s="9">
+        <v>5980</v>
+      </c>
+      <c r="E85" s="9">
+        <v>6630</v>
+      </c>
+      <c r="F85" t="s">
+        <v>109</v>
+      </c>
+      <c r="G85" s="7">
+        <v>18</v>
+      </c>
+      <c r="H85" t="s">
+        <v>103</v>
+      </c>
+      <c r="I85" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>106</v>
+      </c>
+      <c r="B86" t="s">
+        <v>12</v>
+      </c>
       <c r="C86" s="9"/>
-      <c r="D86" s="9"/>
-      <c r="E86" s="9"/>
-      <c r="G86" s="7"/>
-    </row>
-    <row r="87" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D86" s="9">
+        <v>6190</v>
+      </c>
+      <c r="E86" s="9">
+        <v>6790</v>
+      </c>
+      <c r="F86" t="s">
+        <v>109</v>
+      </c>
+      <c r="G86" s="7">
+        <v>18</v>
+      </c>
+      <c r="H86" t="s">
+        <v>80</v>
+      </c>
+      <c r="I86" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>84</v>
+      </c>
+      <c r="B87" t="s">
+        <v>12</v>
+      </c>
       <c r="C87" s="9"/>
-      <c r="D87" s="9"/>
-      <c r="E87" s="9"/>
-      <c r="G87" s="7"/>
-    </row>
-    <row r="88" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D87" s="9">
+        <v>6190</v>
+      </c>
+      <c r="E87" s="9">
+        <v>6790</v>
+      </c>
+      <c r="F87" t="s">
+        <v>109</v>
+      </c>
+      <c r="G87" s="7">
+        <v>18</v>
+      </c>
+      <c r="H87" t="s">
+        <v>80</v>
+      </c>
+      <c r="I87" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>105</v>
+      </c>
+      <c r="B88" t="s">
+        <v>12</v>
+      </c>
       <c r="C88" s="9"/>
-      <c r="D88" s="9"/>
-      <c r="E88" s="9"/>
-      <c r="G88" s="7"/>
-    </row>
-    <row r="89" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D88" s="9">
+        <v>6190</v>
+      </c>
+      <c r="E88" s="9">
+        <v>6790</v>
+      </c>
+      <c r="F88" t="s">
+        <v>109</v>
+      </c>
+      <c r="G88" s="7">
+        <v>18</v>
+      </c>
+      <c r="H88" t="s">
+        <v>80</v>
+      </c>
+      <c r="I88" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C89" s="9"/>
       <c r="D89" s="9"/>
       <c r="E89" s="9"/>
       <c r="G89" s="7"/>
     </row>
-    <row r="90" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C90" s="9"/>
       <c r="D90" s="9"/>
       <c r="E90" s="9"/>
       <c r="G90" s="7"/>
     </row>
-    <row r="91" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C91" s="9"/>
       <c r="D91" s="9"/>
       <c r="E91" s="9"/>
       <c r="G91" s="7"/>
     </row>
-    <row r="92" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C92" s="9"/>
       <c r="D92" s="9"/>
       <c r="E92" s="9"/>
       <c r="G92" s="7"/>
     </row>
-    <row r="93" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C93" s="9"/>
       <c r="D93" s="9"/>
       <c r="E93" s="9"/>
       <c r="G93" s="7"/>
     </row>
-    <row r="94" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C94" s="9"/>
       <c r="D94" s="9"/>
       <c r="E94" s="9"/>
       <c r="G94" s="7"/>
     </row>
-    <row r="95" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C95" s="9"/>
       <c r="D95" s="9"/>
       <c r="E95" s="9"/>
       <c r="G95" s="7"/>
     </row>
-    <row r="96" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C96" s="9"/>
       <c r="D96" s="9"/>
       <c r="E96" s="9"/>
@@ -10333,18 +10507,6 @@
       <c r="D1286" s="9"/>
       <c r="E1286" s="9"/>
       <c r="G1286" s="7"/>
-    </row>
-    <row r="1287" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1287" s="9"/>
-      <c r="D1287" s="9"/>
-      <c r="E1287" s="9"/>
-      <c r="G1287" s="7"/>
-    </row>
-    <row r="1288" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1288" s="9"/>
-      <c r="D1288" s="9"/>
-      <c r="E1288" s="9"/>
-      <c r="G1288" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}"/>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DOCS EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0247A70C-45B9-4079-966B-068F73523BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23ED75F4-0555-47A6-9950-CF13E723FE72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,6 +25,7 @@
     <definedName name="Dgroup">OFFSET([1]Tariff!$J$136, 0, 0, COUNTA([1]Tariff!$J$136:$J$140),1)</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="117">
   <si>
     <t>POD</t>
   </si>
@@ -376,6 +377,24 @@
   </si>
   <si>
     <t>Z-ES</t>
+  </si>
+  <si>
+    <t>TIANJIN</t>
+  </si>
+  <si>
+    <t>NIGNBO</t>
+  </si>
+  <si>
+    <t>Z-RB</t>
+  </si>
+  <si>
+    <t>17 DRY / 15 NOR</t>
+  </si>
+  <si>
+    <t>20 DRY / 14 NOR</t>
+  </si>
+  <si>
+    <t>22 al 27 de septiembre</t>
   </si>
 </sst>
 </file>
@@ -2978,10 +2997,10 @@
       </c>
       <c r="C76" s="9"/>
       <c r="D76" s="9">
-        <v>6780</v>
+        <v>6960</v>
       </c>
       <c r="E76" s="9">
-        <v>6980</v>
+        <v>7160</v>
       </c>
       <c r="F76" t="s">
         <v>107</v>
@@ -3005,10 +3024,10 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="9">
-        <v>6780</v>
+        <v>6960</v>
       </c>
       <c r="E77" s="9">
-        <v>6980</v>
+        <v>7160</v>
       </c>
       <c r="F77" t="s">
         <v>107</v>
@@ -3032,10 +3051,10 @@
       </c>
       <c r="C78" s="9"/>
       <c r="D78" s="9">
-        <v>6780</v>
+        <v>6960</v>
       </c>
       <c r="E78" s="9">
-        <v>6980</v>
+        <v>7160</v>
       </c>
       <c r="F78" t="s">
         <v>107</v>
@@ -3059,10 +3078,10 @@
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="9">
-        <v>6780</v>
+        <v>6960</v>
       </c>
       <c r="E79" s="9">
-        <v>6980</v>
+        <v>7160</v>
       </c>
       <c r="F79" t="s">
         <v>107</v>
@@ -3086,10 +3105,10 @@
       </c>
       <c r="C80" s="9"/>
       <c r="D80" s="9">
-        <v>6780</v>
+        <v>6960</v>
       </c>
       <c r="E80" s="9">
-        <v>6980</v>
+        <v>7160</v>
       </c>
       <c r="F80" t="s">
         <v>107</v>
@@ -3248,10 +3267,10 @@
       </c>
       <c r="C86" s="9"/>
       <c r="D86" s="9">
-        <v>6190</v>
+        <v>6370</v>
       </c>
       <c r="E86" s="9">
-        <v>6790</v>
+        <v>6970</v>
       </c>
       <c r="F86" t="s">
         <v>109</v>
@@ -3275,10 +3294,10 @@
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="9">
-        <v>6190</v>
+        <v>6370</v>
       </c>
       <c r="E87" s="9">
-        <v>6790</v>
+        <v>6970</v>
       </c>
       <c r="F87" t="s">
         <v>109</v>
@@ -3302,10 +3321,10 @@
       </c>
       <c r="C88" s="9"/>
       <c r="D88" s="9">
-        <v>6190</v>
+        <v>6370</v>
       </c>
       <c r="E88" s="9">
-        <v>6790</v>
+        <v>6970</v>
       </c>
       <c r="F88" t="s">
         <v>109</v>
@@ -3321,144 +3340,535 @@
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C89" s="9"/>
-      <c r="D89" s="9"/>
-      <c r="E89" s="9"/>
-      <c r="G89" s="7"/>
+      <c r="A89" t="s">
+        <v>105</v>
+      </c>
+      <c r="B89" t="s">
+        <v>12</v>
+      </c>
+      <c r="C89" s="9">
+        <v>5810</v>
+      </c>
+      <c r="D89" s="9">
+        <v>6110</v>
+      </c>
+      <c r="E89" s="9">
+        <v>6710</v>
+      </c>
+      <c r="F89" t="s">
+        <v>109</v>
+      </c>
+      <c r="G89" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="H89" t="s">
+        <v>77</v>
+      </c>
+      <c r="I89" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C90" s="9"/>
-      <c r="D90" s="9"/>
-      <c r="E90" s="9"/>
-      <c r="G90" s="7"/>
+      <c r="A90" t="s">
+        <v>85</v>
+      </c>
+      <c r="B90" t="s">
+        <v>12</v>
+      </c>
+      <c r="C90" s="9">
+        <v>5810</v>
+      </c>
+      <c r="D90" s="9">
+        <v>6110</v>
+      </c>
+      <c r="E90" s="9">
+        <v>6710</v>
+      </c>
+      <c r="F90" t="s">
+        <v>109</v>
+      </c>
+      <c r="G90" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="H90" t="s">
+        <v>77</v>
+      </c>
+      <c r="I90" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C91" s="9"/>
-      <c r="D91" s="9"/>
-      <c r="E91" s="9"/>
-      <c r="G91" s="7"/>
+      <c r="A91" t="s">
+        <v>111</v>
+      </c>
+      <c r="B91" t="s">
+        <v>12</v>
+      </c>
+      <c r="C91" s="9">
+        <v>5810</v>
+      </c>
+      <c r="D91" s="9">
+        <v>6110</v>
+      </c>
+      <c r="E91" s="9">
+        <v>6710</v>
+      </c>
+      <c r="F91" t="s">
+        <v>109</v>
+      </c>
+      <c r="G91" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="H91" t="s">
+        <v>77</v>
+      </c>
+      <c r="I91" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C92" s="9"/>
-      <c r="D92" s="9"/>
-      <c r="E92" s="9"/>
-      <c r="G92" s="7"/>
+      <c r="A92" t="s">
+        <v>112</v>
+      </c>
+      <c r="B92" t="s">
+        <v>12</v>
+      </c>
+      <c r="C92" s="9">
+        <v>5810</v>
+      </c>
+      <c r="D92" s="9">
+        <v>6110</v>
+      </c>
+      <c r="E92" s="9">
+        <v>6710</v>
+      </c>
+      <c r="F92" t="s">
+        <v>109</v>
+      </c>
+      <c r="G92" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="H92" t="s">
+        <v>77</v>
+      </c>
+      <c r="I92" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C93" s="9"/>
-      <c r="D93" s="9"/>
-      <c r="E93" s="9"/>
-      <c r="G93" s="7"/>
+      <c r="A93" t="s">
+        <v>88</v>
+      </c>
+      <c r="B93" t="s">
+        <v>12</v>
+      </c>
+      <c r="C93" s="9">
+        <v>5610</v>
+      </c>
+      <c r="D93" s="9">
+        <v>6110</v>
+      </c>
+      <c r="E93" s="9">
+        <v>6710</v>
+      </c>
+      <c r="F93" t="s">
+        <v>109</v>
+      </c>
+      <c r="G93" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="H93" t="s">
+        <v>77</v>
+      </c>
+      <c r="I93" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C94" s="9"/>
-      <c r="D94" s="9"/>
-      <c r="E94" s="9"/>
-      <c r="G94" s="7"/>
+      <c r="A94" t="s">
+        <v>94</v>
+      </c>
+      <c r="B94" t="s">
+        <v>12</v>
+      </c>
+      <c r="C94" s="9">
+        <v>5610</v>
+      </c>
+      <c r="D94" s="9">
+        <v>6110</v>
+      </c>
+      <c r="E94" s="9">
+        <v>6710</v>
+      </c>
+      <c r="F94" t="s">
+        <v>109</v>
+      </c>
+      <c r="G94" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="H94" t="s">
+        <v>77</v>
+      </c>
+      <c r="I94" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C95" s="9"/>
-      <c r="D95" s="9"/>
-      <c r="E95" s="9"/>
-      <c r="G95" s="7"/>
+      <c r="A95" t="s">
+        <v>106</v>
+      </c>
+      <c r="B95" t="s">
+        <v>12</v>
+      </c>
+      <c r="C95" s="9">
+        <v>5810</v>
+      </c>
+      <c r="D95" s="9">
+        <v>6110</v>
+      </c>
+      <c r="E95" s="9">
+        <v>6710</v>
+      </c>
+      <c r="F95" t="s">
+        <v>109</v>
+      </c>
+      <c r="G95" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="H95" t="s">
+        <v>77</v>
+      </c>
+      <c r="I95" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C96" s="9"/>
-      <c r="D96" s="9"/>
-      <c r="E96" s="9"/>
-      <c r="G96" s="7"/>
-    </row>
-    <row r="97" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C97" s="9"/>
-      <c r="D97" s="9"/>
-      <c r="E97" s="9"/>
-      <c r="G97" s="7"/>
-    </row>
-    <row r="98" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C98" s="9"/>
-      <c r="D98" s="9"/>
-      <c r="E98" s="9"/>
-      <c r="G98" s="7"/>
-    </row>
-    <row r="99" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C99" s="9"/>
-      <c r="D99" s="9"/>
-      <c r="E99" s="9"/>
-      <c r="G99" s="7"/>
-    </row>
-    <row r="100" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C100" s="9"/>
-      <c r="D100" s="9"/>
-      <c r="E100" s="9"/>
-      <c r="G100" s="7"/>
-    </row>
-    <row r="101" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C101" s="9"/>
-      <c r="D101" s="9"/>
-      <c r="E101" s="9"/>
-      <c r="G101" s="7"/>
-    </row>
-    <row r="102" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C102" s="9"/>
-      <c r="D102" s="9"/>
-      <c r="E102" s="9"/>
-      <c r="G102" s="7"/>
-    </row>
-    <row r="103" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C103" s="9"/>
-      <c r="D103" s="9"/>
-      <c r="E103" s="9"/>
-      <c r="G103" s="7"/>
-    </row>
-    <row r="104" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C104" s="9"/>
-      <c r="D104" s="9"/>
-      <c r="E104" s="9"/>
-      <c r="G104" s="7"/>
-    </row>
-    <row r="105" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C105" s="9"/>
-      <c r="D105" s="9"/>
-      <c r="E105" s="9"/>
-      <c r="G105" s="7"/>
-    </row>
-    <row r="106" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>105</v>
+      </c>
+      <c r="B96" t="s">
+        <v>12</v>
+      </c>
+      <c r="C96" s="9">
+        <v>5570</v>
+      </c>
+      <c r="D96" s="9">
+        <v>6370</v>
+      </c>
+      <c r="E96" s="9">
+        <v>6970</v>
+      </c>
+      <c r="F96" t="s">
+        <v>109</v>
+      </c>
+      <c r="G96" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="H96" t="s">
+        <v>80</v>
+      </c>
+      <c r="I96" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>84</v>
+      </c>
+      <c r="B97" t="s">
+        <v>12</v>
+      </c>
+      <c r="C97" s="9">
+        <v>5570</v>
+      </c>
+      <c r="D97" s="9">
+        <v>6370</v>
+      </c>
+      <c r="E97" s="9">
+        <v>6970</v>
+      </c>
+      <c r="F97" t="s">
+        <v>109</v>
+      </c>
+      <c r="G97" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="H97" t="s">
+        <v>80</v>
+      </c>
+      <c r="I97" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>106</v>
+      </c>
+      <c r="B98" t="s">
+        <v>12</v>
+      </c>
+      <c r="C98" s="9">
+        <v>5570</v>
+      </c>
+      <c r="D98" s="9">
+        <v>6370</v>
+      </c>
+      <c r="E98" s="9">
+        <v>6970</v>
+      </c>
+      <c r="F98" t="s">
+        <v>109</v>
+      </c>
+      <c r="G98" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="H98" t="s">
+        <v>80</v>
+      </c>
+      <c r="I98" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>105</v>
+      </c>
+      <c r="B99" t="s">
+        <v>12</v>
+      </c>
+      <c r="C99" s="9">
+        <v>5250</v>
+      </c>
+      <c r="D99" s="9">
+        <v>6450</v>
+      </c>
+      <c r="E99" s="9">
+        <v>6650</v>
+      </c>
+      <c r="F99" t="s">
+        <v>116</v>
+      </c>
+      <c r="G99" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H99" t="s">
+        <v>75</v>
+      </c>
+      <c r="I99" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>84</v>
+      </c>
+      <c r="B100" t="s">
+        <v>12</v>
+      </c>
+      <c r="C100" s="9">
+        <v>5250</v>
+      </c>
+      <c r="D100" s="9">
+        <v>6450</v>
+      </c>
+      <c r="E100" s="9">
+        <v>6650</v>
+      </c>
+      <c r="F100" t="s">
+        <v>116</v>
+      </c>
+      <c r="G100" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H100" t="s">
+        <v>75</v>
+      </c>
+      <c r="I100" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>85</v>
+      </c>
+      <c r="B101" t="s">
+        <v>12</v>
+      </c>
+      <c r="C101" s="9">
+        <v>5250</v>
+      </c>
+      <c r="D101" s="9">
+        <v>6450</v>
+      </c>
+      <c r="E101" s="9">
+        <v>6650</v>
+      </c>
+      <c r="F101" t="s">
+        <v>116</v>
+      </c>
+      <c r="G101" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H101" t="s">
+        <v>75</v>
+      </c>
+      <c r="I101" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>87</v>
+      </c>
+      <c r="B102" t="s">
+        <v>12</v>
+      </c>
+      <c r="C102" s="9">
+        <v>5250</v>
+      </c>
+      <c r="D102" s="9">
+        <v>6450</v>
+      </c>
+      <c r="E102" s="9">
+        <v>6650</v>
+      </c>
+      <c r="F102" t="s">
+        <v>116</v>
+      </c>
+      <c r="G102" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H102" t="s">
+        <v>75</v>
+      </c>
+      <c r="I102" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>86</v>
+      </c>
+      <c r="B103" t="s">
+        <v>12</v>
+      </c>
+      <c r="C103" s="9">
+        <v>5250</v>
+      </c>
+      <c r="D103" s="9">
+        <v>6450</v>
+      </c>
+      <c r="E103" s="9">
+        <v>6650</v>
+      </c>
+      <c r="F103" t="s">
+        <v>116</v>
+      </c>
+      <c r="G103" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H103" t="s">
+        <v>75</v>
+      </c>
+      <c r="I103" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>106</v>
+      </c>
+      <c r="B104" t="s">
+        <v>12</v>
+      </c>
+      <c r="C104" s="9">
+        <v>5250</v>
+      </c>
+      <c r="D104" s="9">
+        <v>6450</v>
+      </c>
+      <c r="E104" s="9">
+        <v>6650</v>
+      </c>
+      <c r="F104" t="s">
+        <v>116</v>
+      </c>
+      <c r="G104" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H104" t="s">
+        <v>75</v>
+      </c>
+      <c r="I104" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>90</v>
+      </c>
+      <c r="B105" t="s">
+        <v>12</v>
+      </c>
+      <c r="C105" s="9">
+        <v>5450</v>
+      </c>
+      <c r="D105" s="9">
+        <v>6650</v>
+      </c>
+      <c r="E105" s="9">
+        <v>6850</v>
+      </c>
+      <c r="F105" t="s">
+        <v>116</v>
+      </c>
+      <c r="G105" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H105" t="s">
+        <v>75</v>
+      </c>
+      <c r="I105" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C106" s="9"/>
       <c r="D106" s="9"/>
       <c r="E106" s="9"/>
       <c r="G106" s="7"/>
     </row>
-    <row r="107" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C107" s="9"/>
       <c r="D107" s="9"/>
       <c r="E107" s="9"/>
       <c r="G107" s="7"/>
     </row>
-    <row r="108" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C108" s="9"/>
       <c r="D108" s="9"/>
       <c r="E108" s="9"/>
       <c r="G108" s="7"/>
     </row>
-    <row r="109" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C109" s="9"/>
       <c r="D109" s="9"/>
       <c r="E109" s="9"/>
       <c r="G109" s="7"/>
     </row>
-    <row r="110" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C110" s="9"/>
       <c r="D110" s="9"/>
       <c r="E110" s="9"/>
       <c r="G110" s="7"/>
     </row>
-    <row r="111" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C111" s="9"/>
       <c r="D111" s="9"/>
       <c r="E111" s="9"/>
       <c r="G111" s="7"/>
     </row>
-    <row r="112" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C112" s="9"/>
       <c r="D112" s="9"/>
       <c r="E112" s="9"/>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DOCS EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23ED75F4-0555-47A6-9950-CF13E723FE72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC25CEAA-49EA-4893-A1D9-9EC86B154B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,6 @@
     <definedName name="Dgroup">OFFSET([1]Tariff!$J$136, 0, 0, COUNTA([1]Tariff!$J$136:$J$140),1)</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="119">
   <si>
     <t>POD</t>
   </si>
@@ -395,6 +394,12 @@
   </si>
   <si>
     <t>22 al 27 de septiembre</t>
+  </si>
+  <si>
+    <t>BUSAN</t>
+  </si>
+  <si>
+    <t>16 al 30 de septiembre</t>
   </si>
 </sst>
 </file>
@@ -922,7 +927,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}">
-  <dimension ref="A1:I1286"/>
+  <dimension ref="A1:I1279"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
@@ -3631,532 +3636,1473 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>105</v>
+        <v>30</v>
       </c>
       <c r="B99" t="s">
         <v>12</v>
       </c>
-      <c r="C99" s="9">
-        <v>5250</v>
-      </c>
+      <c r="C99" s="9"/>
       <c r="D99" s="9">
-        <v>6450</v>
+        <v>6750</v>
       </c>
       <c r="E99" s="9">
-        <v>6650</v>
+        <v>6950</v>
       </c>
       <c r="F99" t="s">
-        <v>116</v>
-      </c>
-      <c r="G99" s="7" t="s">
-        <v>102</v>
+        <v>118</v>
+      </c>
+      <c r="G99" s="7">
+        <v>18</v>
       </c>
       <c r="H99" t="s">
         <v>75</v>
       </c>
       <c r="I99" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>84</v>
+        <v>31</v>
       </c>
       <c r="B100" t="s">
         <v>12</v>
       </c>
-      <c r="C100" s="9">
-        <v>5250</v>
-      </c>
+      <c r="C100" s="9"/>
       <c r="D100" s="9">
-        <v>6450</v>
+        <v>6950</v>
       </c>
       <c r="E100" s="9">
-        <v>6650</v>
+        <v>7350</v>
       </c>
       <c r="F100" t="s">
-        <v>116</v>
-      </c>
-      <c r="G100" s="7" t="s">
-        <v>102</v>
+        <v>118</v>
+      </c>
+      <c r="G100" s="7">
+        <v>18</v>
       </c>
       <c r="H100" t="s">
         <v>75</v>
       </c>
       <c r="I100" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="B101" t="s">
         <v>12</v>
       </c>
-      <c r="C101" s="9">
-        <v>5250</v>
-      </c>
+      <c r="C101" s="9"/>
       <c r="D101" s="9">
-        <v>6450</v>
+        <v>6750</v>
       </c>
       <c r="E101" s="9">
-        <v>6650</v>
+        <v>6950</v>
       </c>
       <c r="F101" t="s">
-        <v>116</v>
-      </c>
-      <c r="G101" s="7" t="s">
-        <v>102</v>
+        <v>118</v>
+      </c>
+      <c r="G101" s="7">
+        <v>18</v>
       </c>
       <c r="H101" t="s">
         <v>75</v>
       </c>
       <c r="I101" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="B102" t="s">
         <v>12</v>
       </c>
-      <c r="C102" s="9">
-        <v>5250</v>
-      </c>
+      <c r="C102" s="9"/>
       <c r="D102" s="9">
-        <v>6450</v>
+        <v>6750</v>
       </c>
       <c r="E102" s="9">
-        <v>6650</v>
+        <v>6950</v>
       </c>
       <c r="F102" t="s">
-        <v>116</v>
-      </c>
-      <c r="G102" s="7" t="s">
-        <v>102</v>
+        <v>118</v>
+      </c>
+      <c r="G102" s="7">
+        <v>18</v>
       </c>
       <c r="H102" t="s">
         <v>75</v>
       </c>
       <c r="I102" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="B103" t="s">
         <v>12</v>
       </c>
-      <c r="C103" s="9">
-        <v>5250</v>
-      </c>
+      <c r="C103" s="9"/>
       <c r="D103" s="9">
-        <v>6450</v>
+        <v>6750</v>
       </c>
       <c r="E103" s="9">
-        <v>6650</v>
+        <v>6950</v>
       </c>
       <c r="F103" t="s">
-        <v>116</v>
-      </c>
-      <c r="G103" s="7" t="s">
-        <v>102</v>
+        <v>118</v>
+      </c>
+      <c r="G103" s="7">
+        <v>18</v>
       </c>
       <c r="H103" t="s">
         <v>75</v>
       </c>
       <c r="I103" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>106</v>
+        <v>35</v>
       </c>
       <c r="B104" t="s">
         <v>12</v>
       </c>
-      <c r="C104" s="9">
-        <v>5250</v>
-      </c>
+      <c r="C104" s="9"/>
       <c r="D104" s="9">
-        <v>6450</v>
+        <v>5950</v>
       </c>
       <c r="E104" s="9">
         <v>6650</v>
       </c>
       <c r="F104" t="s">
-        <v>116</v>
-      </c>
-      <c r="G104" s="7" t="s">
-        <v>102</v>
+        <v>118</v>
+      </c>
+      <c r="G104" s="7">
+        <v>18</v>
       </c>
       <c r="H104" t="s">
         <v>75</v>
       </c>
       <c r="I104" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="B105" t="s">
         <v>12</v>
       </c>
-      <c r="C105" s="9">
-        <v>5450</v>
-      </c>
+      <c r="C105" s="9"/>
       <c r="D105" s="9">
+        <v>5950</v>
+      </c>
+      <c r="E105" s="9">
         <v>6650</v>
       </c>
-      <c r="E105" s="9">
-        <v>6850</v>
-      </c>
       <c r="F105" t="s">
-        <v>116</v>
-      </c>
-      <c r="G105" s="7" t="s">
-        <v>102</v>
+        <v>118</v>
+      </c>
+      <c r="G105" s="7">
+        <v>18</v>
       </c>
       <c r="H105" t="s">
         <v>75</v>
       </c>
       <c r="I105" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>37</v>
+      </c>
+      <c r="B106" t="s">
+        <v>12</v>
+      </c>
+      <c r="C106" s="9"/>
+      <c r="D106" s="9">
+        <v>6450</v>
+      </c>
+      <c r="E106" s="9">
+        <v>6950</v>
+      </c>
+      <c r="F106" t="s">
+        <v>118</v>
+      </c>
+      <c r="G106" s="7">
+        <v>18</v>
+      </c>
+      <c r="H106" t="s">
+        <v>75</v>
+      </c>
+      <c r="I106" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>38</v>
+      </c>
+      <c r="B107" t="s">
+        <v>12</v>
+      </c>
+      <c r="C107" s="9"/>
+      <c r="D107" s="9">
+        <v>5950</v>
+      </c>
+      <c r="E107" s="9">
+        <v>6650</v>
+      </c>
+      <c r="F107" t="s">
+        <v>118</v>
+      </c>
+      <c r="G107" s="7">
+        <v>18</v>
+      </c>
+      <c r="H107" t="s">
+        <v>75</v>
+      </c>
+      <c r="I107" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>39</v>
+      </c>
+      <c r="B108" t="s">
+        <v>12</v>
+      </c>
+      <c r="C108" s="9"/>
+      <c r="D108" s="9">
+        <v>5950</v>
+      </c>
+      <c r="E108" s="9">
+        <v>6650</v>
+      </c>
+      <c r="F108" t="s">
+        <v>118</v>
+      </c>
+      <c r="G108" s="7">
+        <v>18</v>
+      </c>
+      <c r="H108" t="s">
+        <v>75</v>
+      </c>
+      <c r="I108" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>40</v>
+      </c>
+      <c r="B109" t="s">
+        <v>12</v>
+      </c>
+      <c r="C109" s="9"/>
+      <c r="D109" s="9">
+        <v>5950</v>
+      </c>
+      <c r="E109" s="9">
+        <v>6650</v>
+      </c>
+      <c r="F109" t="s">
+        <v>118</v>
+      </c>
+      <c r="G109" s="7">
+        <v>18</v>
+      </c>
+      <c r="H109" t="s">
+        <v>75</v>
+      </c>
+      <c r="I109" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>41</v>
+      </c>
+      <c r="B110" t="s">
+        <v>12</v>
+      </c>
+      <c r="C110" s="9"/>
+      <c r="D110" s="9">
+        <v>5950</v>
+      </c>
+      <c r="E110" s="9">
+        <v>6650</v>
+      </c>
+      <c r="F110" t="s">
+        <v>118</v>
+      </c>
+      <c r="G110" s="7">
+        <v>18</v>
+      </c>
+      <c r="H110" t="s">
+        <v>75</v>
+      </c>
+      <c r="I110" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>42</v>
+      </c>
+      <c r="B111" t="s">
+        <v>12</v>
+      </c>
+      <c r="C111" s="9"/>
+      <c r="D111" s="9">
+        <v>5950</v>
+      </c>
+      <c r="E111" s="9">
+        <v>6650</v>
+      </c>
+      <c r="F111" t="s">
+        <v>118</v>
+      </c>
+      <c r="G111" s="7">
+        <v>18</v>
+      </c>
+      <c r="H111" t="s">
+        <v>75</v>
+      </c>
+      <c r="I111" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>43</v>
+      </c>
+      <c r="B112" t="s">
+        <v>12</v>
+      </c>
+      <c r="C112" s="9"/>
+      <c r="D112" s="9">
+        <v>5950</v>
+      </c>
+      <c r="E112" s="9">
+        <v>6650</v>
+      </c>
+      <c r="F112" t="s">
+        <v>118</v>
+      </c>
+      <c r="G112" s="7">
+        <v>18</v>
+      </c>
+      <c r="H112" t="s">
+        <v>75</v>
+      </c>
+      <c r="I112" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>44</v>
+      </c>
+      <c r="B113" t="s">
+        <v>12</v>
+      </c>
+      <c r="C113" s="9"/>
+      <c r="D113" s="9">
+        <v>5950</v>
+      </c>
+      <c r="E113" s="9">
+        <v>6650</v>
+      </c>
+      <c r="F113" t="s">
+        <v>118</v>
+      </c>
+      <c r="G113" s="7">
+        <v>18</v>
+      </c>
+      <c r="H113" t="s">
+        <v>75</v>
+      </c>
+      <c r="I113" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>45</v>
+      </c>
+      <c r="B114" t="s">
+        <v>12</v>
+      </c>
+      <c r="C114" s="9"/>
+      <c r="D114" s="9">
+        <v>5950</v>
+      </c>
+      <c r="E114" s="9">
+        <v>6650</v>
+      </c>
+      <c r="F114" t="s">
+        <v>118</v>
+      </c>
+      <c r="G114" s="7">
+        <v>18</v>
+      </c>
+      <c r="H114" t="s">
+        <v>75</v>
+      </c>
+      <c r="I114" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>46</v>
+      </c>
+      <c r="B115" t="s">
+        <v>12</v>
+      </c>
+      <c r="C115" s="9"/>
+      <c r="D115" s="9">
+        <v>5950</v>
+      </c>
+      <c r="E115" s="9">
+        <v>6650</v>
+      </c>
+      <c r="F115" t="s">
+        <v>118</v>
+      </c>
+      <c r="G115" s="7">
+        <v>18</v>
+      </c>
+      <c r="H115" t="s">
+        <v>75</v>
+      </c>
+      <c r="I115" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>47</v>
+      </c>
+      <c r="B116" t="s">
+        <v>12</v>
+      </c>
+      <c r="C116" s="9"/>
+      <c r="D116" s="9">
+        <v>6450</v>
+      </c>
+      <c r="E116" s="9">
+        <v>6950</v>
+      </c>
+      <c r="F116" t="s">
+        <v>118</v>
+      </c>
+      <c r="G116" s="7">
+        <v>18</v>
+      </c>
+      <c r="H116" t="s">
+        <v>75</v>
+      </c>
+      <c r="I116" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>43</v>
+      </c>
+      <c r="B117" t="s">
+        <v>12</v>
+      </c>
+      <c r="C117" s="9"/>
+      <c r="D117" s="9">
+        <v>5950</v>
+      </c>
+      <c r="E117" s="9">
+        <v>6650</v>
+      </c>
+      <c r="F117" t="s">
+        <v>118</v>
+      </c>
+      <c r="G117" s="7">
+        <v>18</v>
+      </c>
+      <c r="H117" t="s">
+        <v>75</v>
+      </c>
+      <c r="I117" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>46</v>
+      </c>
+      <c r="B118" t="s">
+        <v>12</v>
+      </c>
+      <c r="C118" s="9"/>
+      <c r="D118" s="9">
+        <v>5950</v>
+      </c>
+      <c r="E118" s="9">
+        <v>6650</v>
+      </c>
+      <c r="F118" t="s">
+        <v>118</v>
+      </c>
+      <c r="G118" s="7">
+        <v>18</v>
+      </c>
+      <c r="H118" t="s">
+        <v>75</v>
+      </c>
+      <c r="I118" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>48</v>
+      </c>
+      <c r="B119" t="s">
+        <v>12</v>
+      </c>
+      <c r="C119" s="9"/>
+      <c r="D119" s="9">
+        <v>5900</v>
+      </c>
+      <c r="E119" s="9">
+        <v>6350</v>
+      </c>
+      <c r="F119" t="s">
+        <v>118</v>
+      </c>
+      <c r="G119" s="7">
+        <v>18</v>
+      </c>
+      <c r="H119" t="s">
+        <v>75</v>
+      </c>
+      <c r="I119" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>49</v>
+      </c>
+      <c r="B120" t="s">
+        <v>12</v>
+      </c>
+      <c r="C120" s="9"/>
+      <c r="D120" s="9">
+        <v>5900</v>
+      </c>
+      <c r="E120" s="9">
+        <v>6350</v>
+      </c>
+      <c r="F120" t="s">
+        <v>118</v>
+      </c>
+      <c r="G120" s="7">
+        <v>18</v>
+      </c>
+      <c r="H120" t="s">
+        <v>75</v>
+      </c>
+      <c r="I120" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>50</v>
+      </c>
+      <c r="B121" t="s">
+        <v>12</v>
+      </c>
+      <c r="C121" s="9"/>
+      <c r="D121" s="9">
+        <v>5900</v>
+      </c>
+      <c r="E121" s="9">
+        <v>6350</v>
+      </c>
+      <c r="F121" t="s">
+        <v>118</v>
+      </c>
+      <c r="G121" s="7">
+        <v>18</v>
+      </c>
+      <c r="H121" t="s">
+        <v>75</v>
+      </c>
+      <c r="I121" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>51</v>
+      </c>
+      <c r="B122" t="s">
+        <v>12</v>
+      </c>
+      <c r="C122" s="9"/>
+      <c r="D122" s="9">
+        <v>5900</v>
+      </c>
+      <c r="E122" s="9">
+        <v>6350</v>
+      </c>
+      <c r="F122" t="s">
+        <v>118</v>
+      </c>
+      <c r="G122" s="7">
+        <v>18</v>
+      </c>
+      <c r="H122" t="s">
+        <v>75</v>
+      </c>
+      <c r="I122" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>52</v>
+      </c>
+      <c r="B123" t="s">
+        <v>12</v>
+      </c>
+      <c r="C123" s="9"/>
+      <c r="D123" s="9">
+        <v>5900</v>
+      </c>
+      <c r="E123" s="9">
+        <v>6350</v>
+      </c>
+      <c r="F123" t="s">
+        <v>118</v>
+      </c>
+      <c r="G123" s="7">
+        <v>18</v>
+      </c>
+      <c r="H123" t="s">
+        <v>75</v>
+      </c>
+      <c r="I123" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>53</v>
+      </c>
+      <c r="B124" t="s">
+        <v>12</v>
+      </c>
+      <c r="C124" s="9"/>
+      <c r="D124" s="9">
+        <v>6100</v>
+      </c>
+      <c r="E124" s="9">
+        <v>6650</v>
+      </c>
+      <c r="F124" t="s">
+        <v>118</v>
+      </c>
+      <c r="G124" s="7">
+        <v>18</v>
+      </c>
+      <c r="H124" t="s">
+        <v>75</v>
+      </c>
+      <c r="I124" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>54</v>
+      </c>
+      <c r="B125" t="s">
+        <v>12</v>
+      </c>
+      <c r="C125" s="9"/>
+      <c r="D125" s="9">
+        <v>6100</v>
+      </c>
+      <c r="E125" s="9">
+        <v>6650</v>
+      </c>
+      <c r="F125" t="s">
+        <v>118</v>
+      </c>
+      <c r="G125" s="7">
+        <v>18</v>
+      </c>
+      <c r="H125" t="s">
+        <v>75</v>
+      </c>
+      <c r="I125" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>117</v>
+      </c>
+      <c r="B126" t="s">
+        <v>12</v>
+      </c>
+      <c r="C126" s="9"/>
+      <c r="D126" s="9">
+        <v>5850</v>
+      </c>
+      <c r="E126" s="9">
+        <v>6150</v>
+      </c>
+      <c r="F126" t="s">
+        <v>118</v>
+      </c>
+      <c r="G126" s="7">
+        <v>18</v>
+      </c>
+      <c r="H126" t="s">
+        <v>75</v>
+      </c>
+      <c r="I126" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>55</v>
+      </c>
+      <c r="B127" t="s">
+        <v>12</v>
+      </c>
+      <c r="C127" s="9"/>
+      <c r="D127" s="9">
+        <v>6850</v>
+      </c>
+      <c r="E127" s="9">
+        <v>7050</v>
+      </c>
+      <c r="F127" t="s">
+        <v>118</v>
+      </c>
+      <c r="G127" s="7">
+        <v>18</v>
+      </c>
+      <c r="H127" t="s">
+        <v>75</v>
+      </c>
+      <c r="I127" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>56</v>
+      </c>
+      <c r="B128" t="s">
+        <v>12</v>
+      </c>
+      <c r="C128" s="9"/>
+      <c r="D128" s="9">
+        <v>6850</v>
+      </c>
+      <c r="E128" s="9">
+        <v>7050</v>
+      </c>
+      <c r="F128" t="s">
+        <v>118</v>
+      </c>
+      <c r="G128" s="7">
+        <v>18</v>
+      </c>
+      <c r="H128" t="s">
+        <v>75</v>
+      </c>
+      <c r="I128" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>57</v>
+      </c>
+      <c r="B129" t="s">
+        <v>12</v>
+      </c>
+      <c r="C129" s="9"/>
+      <c r="D129" s="9">
+        <v>6850</v>
+      </c>
+      <c r="E129" s="9">
+        <v>7050</v>
+      </c>
+      <c r="F129" t="s">
+        <v>118</v>
+      </c>
+      <c r="G129" s="7">
+        <v>18</v>
+      </c>
+      <c r="H129" t="s">
+        <v>75</v>
+      </c>
+      <c r="I129" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>58</v>
+      </c>
+      <c r="B130" t="s">
+        <v>12</v>
+      </c>
+      <c r="C130" s="9"/>
+      <c r="D130" s="9">
+        <v>7100</v>
+      </c>
+      <c r="E130" s="9">
+        <v>7550</v>
+      </c>
+      <c r="F130" t="s">
+        <v>118</v>
+      </c>
+      <c r="G130" s="7">
+        <v>18</v>
+      </c>
+      <c r="H130" t="s">
+        <v>75</v>
+      </c>
+      <c r="I130" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>59</v>
+      </c>
+      <c r="B131" t="s">
+        <v>12</v>
+      </c>
+      <c r="C131" s="9"/>
+      <c r="D131" s="9">
+        <v>7350</v>
+      </c>
+      <c r="E131" s="9">
+        <v>7450</v>
+      </c>
+      <c r="F131" t="s">
+        <v>118</v>
+      </c>
+      <c r="G131" s="7">
+        <v>18</v>
+      </c>
+      <c r="H131" t="s">
+        <v>75</v>
+      </c>
+      <c r="I131" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>60</v>
+      </c>
+      <c r="B132" t="s">
+        <v>12</v>
+      </c>
+      <c r="C132" s="9"/>
+      <c r="D132" s="9">
+        <v>6050</v>
+      </c>
+      <c r="E132" s="9">
+        <v>6450</v>
+      </c>
+      <c r="F132" t="s">
+        <v>118</v>
+      </c>
+      <c r="G132" s="7">
+        <v>18</v>
+      </c>
+      <c r="H132" t="s">
+        <v>75</v>
+      </c>
+      <c r="I132" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>61</v>
+      </c>
+      <c r="B133" t="s">
+        <v>12</v>
+      </c>
+      <c r="C133" s="9"/>
+      <c r="D133" s="9">
+        <v>6050</v>
+      </c>
+      <c r="E133" s="9">
+        <v>6450</v>
+      </c>
+      <c r="F133" t="s">
+        <v>118</v>
+      </c>
+      <c r="G133" s="7">
+        <v>18</v>
+      </c>
+      <c r="H133" t="s">
+        <v>75</v>
+      </c>
+      <c r="I133" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>62</v>
+      </c>
+      <c r="B134" t="s">
+        <v>12</v>
+      </c>
+      <c r="C134" s="9"/>
+      <c r="D134" s="9">
+        <v>6050</v>
+      </c>
+      <c r="E134" s="9">
+        <v>6450</v>
+      </c>
+      <c r="F134" t="s">
+        <v>118</v>
+      </c>
+      <c r="G134" s="7">
+        <v>18</v>
+      </c>
+      <c r="H134" t="s">
+        <v>75</v>
+      </c>
+      <c r="I134" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>63</v>
+      </c>
+      <c r="B135" t="s">
+        <v>12</v>
+      </c>
+      <c r="C135" s="9"/>
+      <c r="D135" s="9">
+        <v>6350</v>
+      </c>
+      <c r="E135" s="9">
+        <v>6650</v>
+      </c>
+      <c r="F135" t="s">
+        <v>118</v>
+      </c>
+      <c r="G135" s="7">
+        <v>18</v>
+      </c>
+      <c r="H135" t="s">
+        <v>75</v>
+      </c>
+      <c r="I135" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>64</v>
+      </c>
+      <c r="B136" t="s">
+        <v>12</v>
+      </c>
+      <c r="C136" s="9"/>
+      <c r="D136" s="9">
+        <v>6950</v>
+      </c>
+      <c r="E136" s="9">
+        <v>7350</v>
+      </c>
+      <c r="F136" t="s">
+        <v>118</v>
+      </c>
+      <c r="G136" s="7">
+        <v>18</v>
+      </c>
+      <c r="H136" t="s">
+        <v>75</v>
+      </c>
+      <c r="I136" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>65</v>
+      </c>
+      <c r="B137" t="s">
+        <v>12</v>
+      </c>
+      <c r="C137" s="9"/>
+      <c r="D137" s="9">
+        <v>6350</v>
+      </c>
+      <c r="E137" s="9">
+        <v>6650</v>
+      </c>
+      <c r="F137" t="s">
+        <v>118</v>
+      </c>
+      <c r="G137" s="7">
+        <v>18</v>
+      </c>
+      <c r="H137" t="s">
+        <v>75</v>
+      </c>
+      <c r="I137" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>66</v>
+      </c>
+      <c r="B138" t="s">
+        <v>12</v>
+      </c>
+      <c r="C138" s="9"/>
+      <c r="D138" s="9">
+        <v>6350</v>
+      </c>
+      <c r="E138" s="9">
+        <v>6650</v>
+      </c>
+      <c r="F138" t="s">
+        <v>118</v>
+      </c>
+      <c r="G138" s="7">
+        <v>18</v>
+      </c>
+      <c r="H138" t="s">
+        <v>75</v>
+      </c>
+      <c r="I138" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>67</v>
+      </c>
+      <c r="B139" t="s">
+        <v>12</v>
+      </c>
+      <c r="C139" s="9"/>
+      <c r="D139" s="9">
+        <v>6350</v>
+      </c>
+      <c r="E139" s="9">
+        <v>6650</v>
+      </c>
+      <c r="F139" t="s">
+        <v>118</v>
+      </c>
+      <c r="G139" s="7">
+        <v>18</v>
+      </c>
+      <c r="H139" t="s">
+        <v>75</v>
+      </c>
+      <c r="I139" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>68</v>
+      </c>
+      <c r="B140" t="s">
+        <v>12</v>
+      </c>
+      <c r="C140" s="9"/>
+      <c r="D140" s="9">
+        <v>6560</v>
+      </c>
+      <c r="E140" s="9">
+        <v>6860</v>
+      </c>
+      <c r="F140" t="s">
+        <v>118</v>
+      </c>
+      <c r="G140" s="7">
+        <v>18</v>
+      </c>
+      <c r="H140" t="s">
+        <v>75</v>
+      </c>
+      <c r="I140" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>69</v>
+      </c>
+      <c r="B141" t="s">
+        <v>12</v>
+      </c>
+      <c r="C141" s="9"/>
+      <c r="D141" s="9">
+        <v>6350</v>
+      </c>
+      <c r="E141" s="9">
+        <v>6650</v>
+      </c>
+      <c r="F141" t="s">
+        <v>118</v>
+      </c>
+      <c r="G141" s="7">
+        <v>18</v>
+      </c>
+      <c r="H141" t="s">
+        <v>75</v>
+      </c>
+      <c r="I141" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>70</v>
+      </c>
+      <c r="B142" t="s">
+        <v>12</v>
+      </c>
+      <c r="C142" s="9"/>
+      <c r="D142" s="9">
+        <v>6350</v>
+      </c>
+      <c r="E142" s="9">
+        <v>6650</v>
+      </c>
+      <c r="F142" t="s">
+        <v>118</v>
+      </c>
+      <c r="G142" s="7">
+        <v>18</v>
+      </c>
+      <c r="H142" t="s">
+        <v>75</v>
+      </c>
+      <c r="I142" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>71</v>
+      </c>
+      <c r="B143" t="s">
+        <v>12</v>
+      </c>
+      <c r="C143" s="9"/>
+      <c r="D143" s="9">
+        <v>5750</v>
+      </c>
+      <c r="E143" s="9">
+        <v>6450</v>
+      </c>
+      <c r="F143" t="s">
+        <v>118</v>
+      </c>
+      <c r="G143" s="7">
+        <v>18</v>
+      </c>
+      <c r="H143" t="s">
+        <v>75</v>
+      </c>
+      <c r="I143" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>72</v>
+      </c>
+      <c r="B144" t="s">
+        <v>12</v>
+      </c>
+      <c r="C144" s="9"/>
+      <c r="D144" s="9">
+        <v>5950</v>
+      </c>
+      <c r="E144" s="9">
+        <v>6450</v>
+      </c>
+      <c r="F144" t="s">
+        <v>118</v>
+      </c>
+      <c r="G144" s="7">
+        <v>18</v>
+      </c>
+      <c r="H144" t="s">
+        <v>75</v>
+      </c>
+      <c r="I144" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>73</v>
+      </c>
+      <c r="B145" t="s">
+        <v>12</v>
+      </c>
+      <c r="C145" s="9"/>
+      <c r="D145" s="9">
+        <v>5650</v>
+      </c>
+      <c r="E145" s="9">
+        <v>6150</v>
+      </c>
+      <c r="F145" t="s">
+        <v>118</v>
+      </c>
+      <c r="G145" s="7">
+        <v>18</v>
+      </c>
+      <c r="H145" t="s">
+        <v>75</v>
+      </c>
+      <c r="I145" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>105</v>
+      </c>
+      <c r="B146" t="s">
+        <v>12</v>
+      </c>
+      <c r="C146" s="9">
+        <v>4850</v>
+      </c>
+      <c r="D146" s="9">
+        <v>6050</v>
+      </c>
+      <c r="E146" s="9">
+        <v>6150</v>
+      </c>
+      <c r="F146" t="s">
+        <v>116</v>
+      </c>
+      <c r="G146" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H146" t="s">
+        <v>75</v>
+      </c>
+      <c r="I146" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C106" s="9"/>
-      <c r="D106" s="9"/>
-      <c r="E106" s="9"/>
-      <c r="G106" s="7"/>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C107" s="9"/>
-      <c r="D107" s="9"/>
-      <c r="E107" s="9"/>
-      <c r="G107" s="7"/>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C108" s="9"/>
-      <c r="D108" s="9"/>
-      <c r="E108" s="9"/>
-      <c r="G108" s="7"/>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C109" s="9"/>
-      <c r="D109" s="9"/>
-      <c r="E109" s="9"/>
-      <c r="G109" s="7"/>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C110" s="9"/>
-      <c r="D110" s="9"/>
-      <c r="E110" s="9"/>
-      <c r="G110" s="7"/>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C111" s="9"/>
-      <c r="D111" s="9"/>
-      <c r="E111" s="9"/>
-      <c r="G111" s="7"/>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C112" s="9"/>
-      <c r="D112" s="9"/>
-      <c r="E112" s="9"/>
-      <c r="G112" s="7"/>
-    </row>
-    <row r="113" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C113" s="9"/>
-      <c r="D113" s="9"/>
-      <c r="E113" s="9"/>
-      <c r="G113" s="7"/>
-    </row>
-    <row r="114" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C114" s="9"/>
-      <c r="D114" s="9"/>
-      <c r="E114" s="9"/>
-      <c r="G114" s="7"/>
-    </row>
-    <row r="115" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C115" s="9"/>
-      <c r="D115" s="9"/>
-      <c r="E115" s="9"/>
-      <c r="G115" s="7"/>
-    </row>
-    <row r="116" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C116" s="9"/>
-      <c r="D116" s="9"/>
-      <c r="E116" s="9"/>
-      <c r="G116" s="7"/>
-    </row>
-    <row r="117" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C117" s="9"/>
-      <c r="D117" s="9"/>
-      <c r="E117" s="9"/>
-      <c r="G117" s="7"/>
-    </row>
-    <row r="118" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C118" s="9"/>
-      <c r="D118" s="9"/>
-      <c r="E118" s="9"/>
-      <c r="G118" s="7"/>
-    </row>
-    <row r="119" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C119" s="9"/>
-      <c r="D119" s="9"/>
-      <c r="E119" s="9"/>
-      <c r="G119" s="7"/>
-    </row>
-    <row r="120" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C120" s="9"/>
-      <c r="D120" s="9"/>
-      <c r="E120" s="9"/>
-      <c r="G120" s="7"/>
-    </row>
-    <row r="121" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C121" s="9"/>
-      <c r="D121" s="9"/>
-      <c r="E121" s="9"/>
-      <c r="G121" s="7"/>
-    </row>
-    <row r="122" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C122" s="9"/>
-      <c r="D122" s="9"/>
-      <c r="E122" s="9"/>
-      <c r="G122" s="7"/>
-    </row>
-    <row r="123" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C123" s="9"/>
-      <c r="D123" s="9"/>
-      <c r="E123" s="9"/>
-      <c r="G123" s="7"/>
-    </row>
-    <row r="124" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C124" s="9"/>
-      <c r="D124" s="9"/>
-      <c r="E124" s="9"/>
-      <c r="G124" s="7"/>
-    </row>
-    <row r="125" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C125" s="9"/>
-      <c r="D125" s="9"/>
-      <c r="E125" s="9"/>
-      <c r="G125" s="7"/>
-    </row>
-    <row r="126" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C126" s="9"/>
-      <c r="D126" s="9"/>
-      <c r="E126" s="9"/>
-      <c r="G126" s="7"/>
-    </row>
-    <row r="127" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C127" s="9"/>
-      <c r="D127" s="9"/>
-      <c r="E127" s="9"/>
-      <c r="G127" s="7"/>
-    </row>
-    <row r="128" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C128" s="9"/>
-      <c r="D128" s="9"/>
-      <c r="E128" s="9"/>
-      <c r="G128" s="7"/>
-    </row>
-    <row r="129" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C129" s="9"/>
-      <c r="D129" s="9"/>
-      <c r="E129" s="9"/>
-      <c r="G129" s="7"/>
-    </row>
-    <row r="130" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C130" s="9"/>
-      <c r="D130" s="9"/>
-      <c r="E130" s="9"/>
-      <c r="G130" s="7"/>
-    </row>
-    <row r="131" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C131" s="9"/>
-      <c r="D131" s="9"/>
-      <c r="E131" s="9"/>
-      <c r="G131" s="7"/>
-    </row>
-    <row r="132" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C132" s="9"/>
-      <c r="D132" s="9"/>
-      <c r="E132" s="9"/>
-      <c r="G132" s="7"/>
-    </row>
-    <row r="133" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C133" s="9"/>
-      <c r="D133" s="9"/>
-      <c r="E133" s="9"/>
-      <c r="G133" s="7"/>
-    </row>
-    <row r="134" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C134" s="9"/>
-      <c r="D134" s="9"/>
-      <c r="E134" s="9"/>
-      <c r="G134" s="7"/>
-    </row>
-    <row r="135" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C135" s="9"/>
-      <c r="D135" s="9"/>
-      <c r="E135" s="9"/>
-      <c r="G135" s="7"/>
-    </row>
-    <row r="136" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C136" s="9"/>
-      <c r="D136" s="9"/>
-      <c r="E136" s="9"/>
-      <c r="G136" s="7"/>
-    </row>
-    <row r="137" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C137" s="9"/>
-      <c r="D137" s="9"/>
-      <c r="E137" s="9"/>
-      <c r="G137" s="7"/>
-    </row>
-    <row r="138" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C138" s="9"/>
-      <c r="D138" s="9"/>
-      <c r="E138" s="9"/>
-      <c r="G138" s="7"/>
-    </row>
-    <row r="139" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C139" s="9"/>
-      <c r="D139" s="9"/>
-      <c r="E139" s="9"/>
-      <c r="G139" s="7"/>
-    </row>
-    <row r="140" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C140" s="9"/>
-      <c r="D140" s="9"/>
-      <c r="E140" s="9"/>
-      <c r="G140" s="7"/>
-    </row>
-    <row r="141" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C141" s="9"/>
-      <c r="D141" s="9"/>
-      <c r="E141" s="9"/>
-      <c r="G141" s="7"/>
-    </row>
-    <row r="142" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C142" s="9"/>
-      <c r="D142" s="9"/>
-      <c r="E142" s="9"/>
-      <c r="G142" s="7"/>
-    </row>
-    <row r="143" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C143" s="9"/>
-      <c r="D143" s="9"/>
-      <c r="E143" s="9"/>
-      <c r="G143" s="7"/>
-    </row>
-    <row r="144" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C144" s="9"/>
-      <c r="D144" s="9"/>
-      <c r="E144" s="9"/>
-      <c r="G144" s="7"/>
-    </row>
-    <row r="145" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C145" s="9"/>
-      <c r="D145" s="9"/>
-      <c r="E145" s="9"/>
-      <c r="G145" s="7"/>
-    </row>
-    <row r="146" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C146" s="9"/>
-      <c r="D146" s="9"/>
-      <c r="E146" s="9"/>
-      <c r="G146" s="7"/>
-    </row>
-    <row r="147" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C147" s="9"/>
-      <c r="D147" s="9"/>
-      <c r="E147" s="9"/>
-      <c r="G147" s="7"/>
-    </row>
-    <row r="148" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C148" s="9"/>
-      <c r="D148" s="9"/>
-      <c r="E148" s="9"/>
-      <c r="G148" s="7"/>
-    </row>
-    <row r="149" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C149" s="9"/>
-      <c r="D149" s="9"/>
-      <c r="E149" s="9"/>
-      <c r="G149" s="7"/>
-    </row>
-    <row r="150" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C150" s="9"/>
-      <c r="D150" s="9"/>
-      <c r="E150" s="9"/>
-      <c r="G150" s="7"/>
-    </row>
-    <row r="151" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>84</v>
+      </c>
+      <c r="B147" t="s">
+        <v>12</v>
+      </c>
+      <c r="C147" s="9">
+        <v>4850</v>
+      </c>
+      <c r="D147" s="9">
+        <v>6050</v>
+      </c>
+      <c r="E147" s="9">
+        <v>6150</v>
+      </c>
+      <c r="F147" t="s">
+        <v>116</v>
+      </c>
+      <c r="G147" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H147" t="s">
+        <v>75</v>
+      </c>
+      <c r="I147" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>85</v>
+      </c>
+      <c r="B148" t="s">
+        <v>12</v>
+      </c>
+      <c r="C148" s="9">
+        <v>4850</v>
+      </c>
+      <c r="D148" s="9">
+        <v>6050</v>
+      </c>
+      <c r="E148" s="9">
+        <v>6150</v>
+      </c>
+      <c r="F148" t="s">
+        <v>116</v>
+      </c>
+      <c r="G148" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H148" t="s">
+        <v>75</v>
+      </c>
+      <c r="I148" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>86</v>
+      </c>
+      <c r="B149" t="s">
+        <v>12</v>
+      </c>
+      <c r="C149" s="9">
+        <v>4850</v>
+      </c>
+      <c r="D149" s="9">
+        <v>6050</v>
+      </c>
+      <c r="E149" s="9">
+        <v>6150</v>
+      </c>
+      <c r="F149" t="s">
+        <v>116</v>
+      </c>
+      <c r="G149" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H149" t="s">
+        <v>75</v>
+      </c>
+      <c r="I149" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>106</v>
+      </c>
+      <c r="B150" t="s">
+        <v>12</v>
+      </c>
+      <c r="C150" s="9">
+        <v>4850</v>
+      </c>
+      <c r="D150" s="9">
+        <v>6050</v>
+      </c>
+      <c r="E150" s="9">
+        <v>6150</v>
+      </c>
+      <c r="F150" t="s">
+        <v>116</v>
+      </c>
+      <c r="G150" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H150" t="s">
+        <v>75</v>
+      </c>
+      <c r="I150" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C151" s="9"/>
       <c r="D151" s="9"/>
       <c r="E151" s="9"/>
       <c r="G151" s="7"/>
     </row>
-    <row r="152" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C152" s="9"/>
       <c r="D152" s="9"/>
       <c r="E152" s="9"/>
       <c r="G152" s="7"/>
     </row>
-    <row r="153" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C153" s="9"/>
       <c r="D153" s="9"/>
       <c r="E153" s="9"/>
       <c r="G153" s="7"/>
     </row>
-    <row r="154" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C154" s="9"/>
       <c r="D154" s="9"/>
       <c r="E154" s="9"/>
       <c r="G154" s="7"/>
     </row>
-    <row r="155" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C155" s="9"/>
       <c r="D155" s="9"/>
       <c r="E155" s="9"/>
       <c r="G155" s="7"/>
     </row>
-    <row r="156" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C156" s="9"/>
       <c r="D156" s="9"/>
       <c r="E156" s="9"/>
       <c r="G156" s="7"/>
     </row>
-    <row r="157" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C157" s="9"/>
       <c r="D157" s="9"/>
       <c r="E157" s="9"/>
       <c r="G157" s="7"/>
     </row>
-    <row r="158" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C158" s="9"/>
       <c r="D158" s="9"/>
       <c r="E158" s="9"/>
       <c r="G158" s="7"/>
     </row>
-    <row r="159" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C159" s="9"/>
       <c r="D159" s="9"/>
       <c r="E159" s="9"/>
       <c r="G159" s="7"/>
     </row>
-    <row r="160" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C160" s="9"/>
       <c r="D160" s="9"/>
       <c r="E160" s="9"/>
@@ -10875,48 +11821,6 @@
       <c r="D1279" s="9"/>
       <c r="E1279" s="9"/>
       <c r="G1279" s="7"/>
-    </row>
-    <row r="1280" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1280" s="9"/>
-      <c r="D1280" s="9"/>
-      <c r="E1280" s="9"/>
-      <c r="G1280" s="7"/>
-    </row>
-    <row r="1281" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1281" s="9"/>
-      <c r="D1281" s="9"/>
-      <c r="E1281" s="9"/>
-      <c r="G1281" s="7"/>
-    </row>
-    <row r="1282" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1282" s="9"/>
-      <c r="D1282" s="9"/>
-      <c r="E1282" s="9"/>
-      <c r="G1282" s="7"/>
-    </row>
-    <row r="1283" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1283" s="9"/>
-      <c r="D1283" s="9"/>
-      <c r="E1283" s="9"/>
-      <c r="G1283" s="7"/>
-    </row>
-    <row r="1284" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1284" s="9"/>
-      <c r="D1284" s="9"/>
-      <c r="E1284" s="9"/>
-      <c r="G1284" s="7"/>
-    </row>
-    <row r="1285" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1285" s="9"/>
-      <c r="D1285" s="9"/>
-      <c r="E1285" s="9"/>
-      <c r="G1285" s="7"/>
-    </row>
-    <row r="1286" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1286" s="9"/>
-      <c r="D1286" s="9"/>
-      <c r="E1286" s="9"/>
-      <c r="G1286" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}"/>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DOCS EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79954A73-EBFC-41B7-ABEE-F9F9A13CEE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF4FD42-5DD8-4F92-90E1-794D9847AF11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1787" uniqueCount="162">
   <si>
     <t>POD</t>
   </si>
@@ -528,7 +528,7 @@
     <t>TAOYUAN</t>
   </si>
   <si>
-    <t>22 de sep al 11 de oct</t>
+    <t>28 de sep al 11 de oct</t>
   </si>
 </sst>
 </file>
@@ -4712,7 +4712,7 @@
         <v>5830</v>
       </c>
       <c r="F134" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G134" s="7" t="s">
         <v>91</v>
@@ -4741,7 +4741,7 @@
         <v>5830</v>
       </c>
       <c r="F135" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G135" s="7" t="s">
         <v>91</v>
@@ -4770,7 +4770,7 @@
         <v>5830</v>
       </c>
       <c r="F136" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G136" s="7" t="s">
         <v>91</v>
@@ -4799,7 +4799,7 @@
         <v>5830</v>
       </c>
       <c r="F137" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G137" s="7" t="s">
         <v>91</v>
@@ -4828,7 +4828,7 @@
         <v>5830</v>
       </c>
       <c r="F138" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G138" s="7" t="s">
         <v>91</v>
@@ -4857,7 +4857,7 @@
         <v>5830</v>
       </c>
       <c r="F139" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G139" s="7" t="s">
         <v>91</v>
@@ -4886,7 +4886,7 @@
         <v>5830</v>
       </c>
       <c r="F140" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G140" s="7" t="s">
         <v>91</v>
@@ -4915,7 +4915,7 @@
         <v>5830</v>
       </c>
       <c r="F141" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G141" s="7" t="s">
         <v>91</v>
@@ -4944,7 +4944,7 @@
         <v>6080</v>
       </c>
       <c r="F142" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G142" s="7" t="s">
         <v>91</v>
@@ -4973,7 +4973,7 @@
         <v>6030</v>
       </c>
       <c r="F143" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G143" s="7" t="s">
         <v>91</v>
@@ -5002,7 +5002,7 @@
         <v>6080</v>
       </c>
       <c r="F144" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G144" s="7" t="s">
         <v>91</v>
@@ -5031,7 +5031,7 @@
         <v>5930</v>
       </c>
       <c r="F145" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G145" s="7" t="s">
         <v>91</v>
@@ -5060,7 +5060,7 @@
         <v>5930</v>
       </c>
       <c r="F146" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G146" s="7" t="s">
         <v>91</v>
@@ -5089,7 +5089,7 @@
         <v>5930</v>
       </c>
       <c r="F147" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G147" s="7" t="s">
         <v>91</v>
@@ -5118,7 +5118,7 @@
         <v>5930</v>
       </c>
       <c r="F148" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G148" s="7" t="s">
         <v>91</v>
@@ -5147,7 +5147,7 @@
         <v>5930</v>
       </c>
       <c r="F149" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G149" s="7" t="s">
         <v>91</v>
@@ -5176,7 +5176,7 @@
         <v>5930</v>
       </c>
       <c r="F150" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G150" s="7" t="s">
         <v>91</v>
@@ -5205,7 +5205,7 @@
         <v>5930</v>
       </c>
       <c r="F151" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G151" s="7" t="s">
         <v>91</v>
@@ -5234,7 +5234,7 @@
         <v>5930</v>
       </c>
       <c r="F152" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G152" s="7" t="s">
         <v>91</v>
@@ -5263,7 +5263,7 @@
         <v>5930</v>
       </c>
       <c r="F153" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G153" s="7" t="s">
         <v>91</v>
@@ -5292,7 +5292,7 @@
         <v>5930</v>
       </c>
       <c r="F154" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G154" s="7" t="s">
         <v>91</v>
@@ -5321,7 +5321,7 @@
         <v>5930</v>
       </c>
       <c r="F155" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G155" s="7" t="s">
         <v>91</v>
@@ -5350,7 +5350,7 @@
         <v>5980</v>
       </c>
       <c r="F156" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G156" s="7" t="s">
         <v>91</v>
@@ -5379,7 +5379,7 @@
         <v>6630</v>
       </c>
       <c r="F157" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G157" s="7" t="s">
         <v>91</v>
@@ -5408,7 +5408,7 @@
         <v>6130</v>
       </c>
       <c r="F158" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G158" s="7" t="s">
         <v>91</v>
@@ -5437,7 +5437,7 @@
         <v>6330</v>
       </c>
       <c r="F159" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G159" s="7" t="s">
         <v>91</v>
@@ -5466,7 +5466,7 @@
         <v>6330</v>
       </c>
       <c r="F160" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G160" s="7" t="s">
         <v>91</v>
@@ -5495,7 +5495,7 @@
         <v>6030</v>
       </c>
       <c r="F161" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G161" s="7" t="s">
         <v>91</v>
@@ -5524,7 +5524,7 @@
         <v>6130</v>
       </c>
       <c r="F162" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G162" s="7" t="s">
         <v>91</v>
@@ -5553,7 +5553,7 @@
         <v>6130</v>
       </c>
       <c r="F163" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G163" s="7" t="s">
         <v>91</v>
@@ -5582,7 +5582,7 @@
         <v>6130</v>
       </c>
       <c r="F164" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G164" s="7" t="s">
         <v>91</v>
@@ -5611,7 +5611,7 @@
         <v>6130</v>
       </c>
       <c r="F165" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G165" s="7" t="s">
         <v>91</v>
@@ -5640,7 +5640,7 @@
         <v>6130</v>
       </c>
       <c r="F166" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G166" s="7" t="s">
         <v>91</v>
@@ -5669,7 +5669,7 @@
         <v>6130</v>
       </c>
       <c r="F167" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G167" s="7" t="s">
         <v>91</v>
@@ -5698,7 +5698,7 @@
         <v>6130</v>
       </c>
       <c r="F168" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G168" s="7" t="s">
         <v>91</v>
@@ -5727,7 +5727,7 @@
         <v>6130</v>
       </c>
       <c r="F169" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G169" s="7" t="s">
         <v>91</v>
@@ -5756,7 +5756,7 @@
         <v>6130</v>
       </c>
       <c r="F170" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G170" s="7" t="s">
         <v>91</v>
@@ -5785,7 +5785,7 @@
         <v>6280</v>
       </c>
       <c r="F171" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G171" s="7" t="s">
         <v>91</v>
@@ -5814,7 +5814,7 @@
         <v>6330</v>
       </c>
       <c r="F172" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G172" s="7" t="s">
         <v>91</v>
@@ -5843,7 +5843,7 @@
         <v>6280</v>
       </c>
       <c r="F173" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G173" s="7" t="s">
         <v>91</v>
@@ -5872,7 +5872,7 @@
         <v>6380</v>
       </c>
       <c r="F174" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G174" s="7" t="s">
         <v>91</v>
@@ -5901,7 +5901,7 @@
         <v>6820</v>
       </c>
       <c r="F175" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G175" s="7" t="s">
         <v>91</v>
@@ -5930,7 +5930,7 @@
         <v>6080</v>
       </c>
       <c r="F176" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G176" s="7" t="s">
         <v>91</v>
@@ -5959,7 +5959,7 @@
         <v>6080</v>
       </c>
       <c r="F177" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G177" s="7" t="s">
         <v>91</v>
@@ -5988,7 +5988,7 @@
         <v>6080</v>
       </c>
       <c r="F178" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G178" s="7" t="s">
         <v>91</v>
@@ -6017,7 +6017,7 @@
         <v>6240</v>
       </c>
       <c r="F179" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G179" s="7" t="s">
         <v>91</v>
@@ -6046,7 +6046,7 @@
         <v>6240</v>
       </c>
       <c r="F180" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G180" s="7" t="s">
         <v>91</v>
@@ -6075,7 +6075,7 @@
         <v>5730</v>
       </c>
       <c r="F181" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G181" s="7" t="s">
         <v>103</v>
@@ -6104,7 +6104,7 @@
         <v>5730</v>
       </c>
       <c r="F182" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G182" s="7" t="s">
         <v>103</v>
@@ -6133,7 +6133,7 @@
         <v>5730</v>
       </c>
       <c r="F183" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G183" s="7" t="s">
         <v>103</v>
@@ -6162,7 +6162,7 @@
         <v>5730</v>
       </c>
       <c r="F184" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G184" s="7" t="s">
         <v>103</v>
@@ -6191,7 +6191,7 @@
         <v>5730</v>
       </c>
       <c r="F185" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G185" s="7" t="s">
         <v>103</v>
@@ -6220,7 +6220,7 @@
         <v>5730</v>
       </c>
       <c r="F186" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G186" s="7" t="s">
         <v>103</v>
@@ -6249,7 +6249,7 @@
         <v>5730</v>
       </c>
       <c r="F187" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G187" s="7" t="s">
         <v>103</v>
@@ -6278,7 +6278,7 @@
         <v>5730</v>
       </c>
       <c r="F188" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G188" s="7" t="s">
         <v>103</v>
@@ -6307,7 +6307,7 @@
         <v>5730</v>
       </c>
       <c r="F189" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G189" s="7" t="s">
         <v>103</v>
@@ -6336,7 +6336,7 @@
         <v>5930</v>
       </c>
       <c r="F190" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G190" s="7" t="s">
         <v>103</v>
@@ -6365,7 +6365,7 @@
         <v>5730</v>
       </c>
       <c r="F191" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G191" s="7" t="s">
         <v>103</v>
@@ -6394,7 +6394,7 @@
         <v>5880</v>
       </c>
       <c r="F192" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G192" s="7" t="s">
         <v>103</v>
@@ -6423,7 +6423,7 @@
         <v>5830</v>
       </c>
       <c r="F193" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G193" s="7" t="s">
         <v>103</v>
@@ -6452,7 +6452,7 @@
         <v>5830</v>
       </c>
       <c r="F194" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G194" s="7" t="s">
         <v>103</v>
@@ -6481,7 +6481,7 @@
         <v>5830</v>
       </c>
       <c r="F195" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G195" s="7" t="s">
         <v>103</v>
@@ -6510,7 +6510,7 @@
         <v>5830</v>
       </c>
       <c r="F196" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G196" s="7" t="s">
         <v>103</v>
@@ -6539,7 +6539,7 @@
         <v>5830</v>
       </c>
       <c r="F197" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G197" s="7" t="s">
         <v>103</v>
@@ -6568,7 +6568,7 @@
         <v>5830</v>
       </c>
       <c r="F198" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G198" s="7" t="s">
         <v>103</v>
@@ -6597,7 +6597,7 @@
         <v>5830</v>
       </c>
       <c r="F199" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G199" s="7" t="s">
         <v>103</v>
@@ -6626,7 +6626,7 @@
         <v>5830</v>
       </c>
       <c r="F200" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G200" s="7" t="s">
         <v>103</v>
@@ -6655,7 +6655,7 @@
         <v>5830</v>
       </c>
       <c r="F201" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G201" s="7" t="s">
         <v>103</v>
@@ -6684,7 +6684,7 @@
         <v>5830</v>
       </c>
       <c r="F202" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G202" s="7" t="s">
         <v>103</v>
@@ -6713,7 +6713,7 @@
         <v>6030</v>
       </c>
       <c r="F203" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G203" s="7" t="s">
         <v>103</v>
@@ -6740,7 +6740,7 @@
         <v>6030</v>
       </c>
       <c r="F204" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G204" s="7">
         <v>17</v>
@@ -6767,7 +6767,7 @@
         <v>6070</v>
       </c>
       <c r="F205" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G205" s="7">
         <v>17</v>
@@ -6794,7 +6794,7 @@
         <v>6030</v>
       </c>
       <c r="F206" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G206" s="7">
         <v>17</v>
@@ -6821,7 +6821,7 @@
         <v>6160</v>
       </c>
       <c r="F207" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G207" s="7">
         <v>17</v>
@@ -6848,7 +6848,7 @@
         <v>6040</v>
       </c>
       <c r="F208" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G208" s="7">
         <v>17</v>
@@ -6875,7 +6875,7 @@
         <v>6050</v>
       </c>
       <c r="F209" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G209" s="7">
         <v>17</v>
@@ -6902,7 +6902,7 @@
         <v>5940</v>
       </c>
       <c r="F210" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G210" s="7">
         <v>17</v>
@@ -6929,7 +6929,7 @@
         <v>5940</v>
       </c>
       <c r="F211" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G211" s="7">
         <v>17</v>
@@ -6956,7 +6956,7 @@
         <v>5940</v>
       </c>
       <c r="F212" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G212" s="7">
         <v>17</v>
@@ -6983,7 +6983,7 @@
         <v>5940</v>
       </c>
       <c r="F213" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G213" s="7">
         <v>17</v>
@@ -7010,7 +7010,7 @@
         <v>5940</v>
       </c>
       <c r="F214" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G214" s="7">
         <v>17</v>
@@ -7037,7 +7037,7 @@
         <v>5940</v>
       </c>
       <c r="F215" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G215" s="7">
         <v>17</v>
@@ -7064,7 +7064,7 @@
         <v>5940</v>
       </c>
       <c r="F216" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G216" s="7">
         <v>17</v>
@@ -7091,7 +7091,7 @@
         <v>5940</v>
       </c>
       <c r="F217" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G217" s="7">
         <v>17</v>
@@ -7118,7 +7118,7 @@
         <v>6150</v>
       </c>
       <c r="F218" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G218" s="7">
         <v>17</v>
@@ -7145,7 +7145,7 @@
         <v>6120</v>
       </c>
       <c r="F219" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G219" s="7">
         <v>17</v>
@@ -7172,7 +7172,7 @@
         <v>6180</v>
       </c>
       <c r="F220" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G220" s="7">
         <v>17</v>
@@ -7199,7 +7199,7 @@
         <v>6180</v>
       </c>
       <c r="F221" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G221" s="7">
         <v>17</v>
@@ -7226,7 +7226,7 @@
         <v>6520</v>
       </c>
       <c r="F222" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G222" s="7">
         <v>17</v>
@@ -7253,7 +7253,7 @@
         <v>5880</v>
       </c>
       <c r="F223" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G223" s="7">
         <v>17</v>
@@ -7280,7 +7280,7 @@
         <v>5880</v>
       </c>
       <c r="F224" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G224" s="7">
         <v>17</v>
@@ -7307,7 +7307,7 @@
         <v>5880</v>
       </c>
       <c r="F225" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G225" s="7">
         <v>17</v>
@@ -7334,7 +7334,7 @@
         <v>6030</v>
       </c>
       <c r="F226" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G226" s="7">
         <v>17</v>
@@ -7361,7 +7361,7 @@
         <v>6180</v>
       </c>
       <c r="F227" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G227" s="7">
         <v>17</v>
@@ -7374,654 +7374,2768 @@
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C228" s="9"/>
-      <c r="D228" s="9"/>
-      <c r="E228" s="9"/>
-      <c r="G228" s="7"/>
+      <c r="A228" t="s">
+        <v>94</v>
+      </c>
+      <c r="B228" t="s">
+        <v>12</v>
+      </c>
+      <c r="C228" s="9">
+        <v>4530</v>
+      </c>
+      <c r="D228" s="9">
+        <v>5330</v>
+      </c>
+      <c r="E228" s="9">
+        <v>5530</v>
+      </c>
+      <c r="F228" t="s">
+        <v>161</v>
+      </c>
+      <c r="G228" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H228" t="s">
+        <v>72</v>
+      </c>
+      <c r="I228" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C229" s="9"/>
-      <c r="D229" s="9"/>
-      <c r="E229" s="9"/>
-      <c r="G229" s="7"/>
+      <c r="A229" t="s">
+        <v>95</v>
+      </c>
+      <c r="B229" t="s">
+        <v>12</v>
+      </c>
+      <c r="C229" s="9">
+        <v>4530</v>
+      </c>
+      <c r="D229" s="9">
+        <v>5330</v>
+      </c>
+      <c r="E229" s="9">
+        <v>5530</v>
+      </c>
+      <c r="F229" t="s">
+        <v>161</v>
+      </c>
+      <c r="G229" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H229" t="s">
+        <v>72</v>
+      </c>
+      <c r="I229" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C230" s="9"/>
-      <c r="D230" s="9"/>
-      <c r="E230" s="9"/>
-      <c r="G230" s="7"/>
+      <c r="A230" t="s">
+        <v>83</v>
+      </c>
+      <c r="B230" t="s">
+        <v>12</v>
+      </c>
+      <c r="C230" s="9">
+        <v>4530</v>
+      </c>
+      <c r="D230" s="9">
+        <v>5330</v>
+      </c>
+      <c r="E230" s="9">
+        <v>5530</v>
+      </c>
+      <c r="F230" t="s">
+        <v>161</v>
+      </c>
+      <c r="G230" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H230" t="s">
+        <v>72</v>
+      </c>
+      <c r="I230" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C231" s="9"/>
-      <c r="D231" s="9"/>
-      <c r="E231" s="9"/>
-      <c r="G231" s="7"/>
+      <c r="A231" t="s">
+        <v>82</v>
+      </c>
+      <c r="B231" t="s">
+        <v>12</v>
+      </c>
+      <c r="C231" s="9">
+        <v>4530</v>
+      </c>
+      <c r="D231" s="9">
+        <v>5330</v>
+      </c>
+      <c r="E231" s="9">
+        <v>5530</v>
+      </c>
+      <c r="F231" t="s">
+        <v>161</v>
+      </c>
+      <c r="G231" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H231" t="s">
+        <v>72</v>
+      </c>
+      <c r="I231" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C232" s="9"/>
-      <c r="D232" s="9"/>
-      <c r="E232" s="9"/>
-      <c r="G232" s="7"/>
+      <c r="A232" t="s">
+        <v>84</v>
+      </c>
+      <c r="B232" t="s">
+        <v>12</v>
+      </c>
+      <c r="C232" s="9">
+        <v>4530</v>
+      </c>
+      <c r="D232" s="9">
+        <v>5330</v>
+      </c>
+      <c r="E232" s="9">
+        <v>5530</v>
+      </c>
+      <c r="F232" t="s">
+        <v>161</v>
+      </c>
+      <c r="G232" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H232" t="s">
+        <v>72</v>
+      </c>
+      <c r="I232" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C233" s="9"/>
-      <c r="D233" s="9"/>
-      <c r="E233" s="9"/>
-      <c r="G233" s="7"/>
+      <c r="A233" t="s">
+        <v>144</v>
+      </c>
+      <c r="B233" t="s">
+        <v>12</v>
+      </c>
+      <c r="C233" s="9">
+        <v>4530</v>
+      </c>
+      <c r="D233" s="9">
+        <v>5330</v>
+      </c>
+      <c r="E233" s="9">
+        <v>5530</v>
+      </c>
+      <c r="F233" t="s">
+        <v>161</v>
+      </c>
+      <c r="G233" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H233" t="s">
+        <v>72</v>
+      </c>
+      <c r="I233" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C234" s="9"/>
-      <c r="D234" s="9"/>
-      <c r="E234" s="9"/>
-      <c r="G234" s="7"/>
+      <c r="A234" t="s">
+        <v>81</v>
+      </c>
+      <c r="B234" t="s">
+        <v>12</v>
+      </c>
+      <c r="C234" s="9">
+        <v>4530</v>
+      </c>
+      <c r="D234" s="9">
+        <v>5330</v>
+      </c>
+      <c r="E234" s="9">
+        <v>5530</v>
+      </c>
+      <c r="F234" t="s">
+        <v>161</v>
+      </c>
+      <c r="G234" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H234" t="s">
+        <v>72</v>
+      </c>
+      <c r="I234" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C235" s="9"/>
-      <c r="D235" s="9"/>
-      <c r="E235" s="9"/>
-      <c r="G235" s="7"/>
+      <c r="A235" t="s">
+        <v>80</v>
+      </c>
+      <c r="B235" t="s">
+        <v>12</v>
+      </c>
+      <c r="C235" s="9">
+        <v>4530</v>
+      </c>
+      <c r="D235" s="9">
+        <v>5330</v>
+      </c>
+      <c r="E235" s="9">
+        <v>5530</v>
+      </c>
+      <c r="F235" t="s">
+        <v>161</v>
+      </c>
+      <c r="G235" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H235" t="s">
+        <v>72</v>
+      </c>
+      <c r="I235" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C236" s="9"/>
-      <c r="D236" s="9"/>
-      <c r="E236" s="9"/>
-      <c r="G236" s="7"/>
+      <c r="A236" t="s">
+        <v>100</v>
+      </c>
+      <c r="B236" t="s">
+        <v>12</v>
+      </c>
+      <c r="C236" s="9">
+        <v>4780</v>
+      </c>
+      <c r="D236" s="9">
+        <v>5480</v>
+      </c>
+      <c r="E236" s="9">
+        <v>5780</v>
+      </c>
+      <c r="F236" t="s">
+        <v>161</v>
+      </c>
+      <c r="G236" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H236" t="s">
+        <v>72</v>
+      </c>
+      <c r="I236" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C237" s="9"/>
-      <c r="D237" s="9"/>
-      <c r="E237" s="9"/>
-      <c r="G237" s="7"/>
+      <c r="A237" t="s">
+        <v>117</v>
+      </c>
+      <c r="B237" t="s">
+        <v>12</v>
+      </c>
+      <c r="C237" s="9">
+        <v>4730</v>
+      </c>
+      <c r="D237" s="9">
+        <v>5430</v>
+      </c>
+      <c r="E237" s="9">
+        <v>5730</v>
+      </c>
+      <c r="F237" t="s">
+        <v>161</v>
+      </c>
+      <c r="G237" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H237" t="s">
+        <v>72</v>
+      </c>
+      <c r="I237" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C238" s="9"/>
-      <c r="D238" s="9"/>
-      <c r="E238" s="9"/>
-      <c r="G238" s="7"/>
+      <c r="A238" t="s">
+        <v>85</v>
+      </c>
+      <c r="B238" t="s">
+        <v>12</v>
+      </c>
+      <c r="C238" s="9">
+        <v>4780</v>
+      </c>
+      <c r="D238" s="9">
+        <v>5480</v>
+      </c>
+      <c r="E238" s="9">
+        <v>5780</v>
+      </c>
+      <c r="F238" t="s">
+        <v>161</v>
+      </c>
+      <c r="G238" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H238" t="s">
+        <v>72</v>
+      </c>
+      <c r="I238" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C239" s="9"/>
-      <c r="D239" s="9"/>
-      <c r="E239" s="9"/>
-      <c r="G239" s="7"/>
+      <c r="A239" t="s">
+        <v>90</v>
+      </c>
+      <c r="B239" t="s">
+        <v>12</v>
+      </c>
+      <c r="C239" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D239" s="9">
+        <v>5380</v>
+      </c>
+      <c r="E239" s="9">
+        <v>5630</v>
+      </c>
+      <c r="F239" t="s">
+        <v>161</v>
+      </c>
+      <c r="G239" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H239" t="s">
+        <v>72</v>
+      </c>
+      <c r="I239" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C240" s="9"/>
-      <c r="D240" s="9"/>
-      <c r="E240" s="9"/>
-      <c r="G240" s="7"/>
-    </row>
-    <row r="241" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C241" s="9"/>
-      <c r="D241" s="9"/>
-      <c r="E241" s="9"/>
-      <c r="G241" s="7"/>
-    </row>
-    <row r="242" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C242" s="9"/>
-      <c r="D242" s="9"/>
-      <c r="E242" s="9"/>
-      <c r="G242" s="7"/>
-    </row>
-    <row r="243" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C243" s="9"/>
-      <c r="D243" s="9"/>
-      <c r="E243" s="9"/>
-      <c r="G243" s="7"/>
-    </row>
-    <row r="244" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C244" s="9"/>
-      <c r="D244" s="9"/>
-      <c r="E244" s="9"/>
-      <c r="G244" s="7"/>
-    </row>
-    <row r="245" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C245" s="9"/>
-      <c r="D245" s="9"/>
-      <c r="E245" s="9"/>
-      <c r="G245" s="7"/>
-    </row>
-    <row r="246" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C246" s="9"/>
-      <c r="D246" s="9"/>
-      <c r="E246" s="9"/>
-      <c r="G246" s="7"/>
-    </row>
-    <row r="247" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C247" s="9"/>
-      <c r="D247" s="9"/>
-      <c r="E247" s="9"/>
-      <c r="G247" s="7"/>
-    </row>
-    <row r="248" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C248" s="9"/>
-      <c r="D248" s="9"/>
-      <c r="E248" s="9"/>
-      <c r="G248" s="7"/>
-    </row>
-    <row r="249" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C249" s="9"/>
-      <c r="D249" s="9"/>
-      <c r="E249" s="9"/>
-      <c r="G249" s="7"/>
-    </row>
-    <row r="250" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C250" s="9"/>
-      <c r="D250" s="9"/>
-      <c r="E250" s="9"/>
-      <c r="G250" s="7"/>
-    </row>
-    <row r="251" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C251" s="9"/>
-      <c r="D251" s="9"/>
-      <c r="E251" s="9"/>
-      <c r="G251" s="7"/>
-    </row>
-    <row r="252" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C252" s="9"/>
-      <c r="D252" s="9"/>
-      <c r="E252" s="9"/>
-      <c r="G252" s="7"/>
-    </row>
-    <row r="253" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C253" s="9"/>
-      <c r="D253" s="9"/>
-      <c r="E253" s="9"/>
-      <c r="G253" s="7"/>
-    </row>
-    <row r="254" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C254" s="9"/>
-      <c r="D254" s="9"/>
-      <c r="E254" s="9"/>
-      <c r="G254" s="7"/>
-    </row>
-    <row r="255" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C255" s="9"/>
-      <c r="D255" s="9"/>
-      <c r="E255" s="9"/>
-      <c r="G255" s="7"/>
-    </row>
-    <row r="256" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C256" s="9"/>
-      <c r="D256" s="9"/>
-      <c r="E256" s="9"/>
-      <c r="G256" s="7"/>
-    </row>
-    <row r="257" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C257" s="9"/>
-      <c r="D257" s="9"/>
-      <c r="E257" s="9"/>
-      <c r="G257" s="7"/>
-    </row>
-    <row r="258" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C258" s="9"/>
-      <c r="D258" s="9"/>
-      <c r="E258" s="9"/>
-      <c r="G258" s="7"/>
-    </row>
-    <row r="259" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C259" s="9"/>
-      <c r="D259" s="9"/>
-      <c r="E259" s="9"/>
-      <c r="G259" s="7"/>
-    </row>
-    <row r="260" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C260" s="9"/>
-      <c r="D260" s="9"/>
-      <c r="E260" s="9"/>
-      <c r="G260" s="7"/>
-    </row>
-    <row r="261" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C261" s="9"/>
-      <c r="D261" s="9"/>
-      <c r="E261" s="9"/>
-      <c r="G261" s="7"/>
-    </row>
-    <row r="262" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C262" s="9"/>
-      <c r="D262" s="9"/>
-      <c r="E262" s="9"/>
-      <c r="G262" s="7"/>
-    </row>
-    <row r="263" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C263" s="9"/>
-      <c r="D263" s="9"/>
-      <c r="E263" s="9"/>
-      <c r="G263" s="7"/>
-    </row>
-    <row r="264" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C264" s="9"/>
-      <c r="D264" s="9"/>
-      <c r="E264" s="9"/>
-      <c r="G264" s="7"/>
-    </row>
-    <row r="265" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C265" s="9"/>
-      <c r="D265" s="9"/>
-      <c r="E265" s="9"/>
-      <c r="G265" s="7"/>
-    </row>
-    <row r="266" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C266" s="9"/>
-      <c r="D266" s="9"/>
-      <c r="E266" s="9"/>
-      <c r="G266" s="7"/>
-    </row>
-    <row r="267" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C267" s="9"/>
-      <c r="D267" s="9"/>
-      <c r="E267" s="9"/>
-      <c r="G267" s="7"/>
-    </row>
-    <row r="268" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C268" s="9"/>
-      <c r="D268" s="9"/>
-      <c r="E268" s="9"/>
-      <c r="G268" s="7"/>
-    </row>
-    <row r="269" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C269" s="9"/>
-      <c r="D269" s="9"/>
-      <c r="E269" s="9"/>
-      <c r="G269" s="7"/>
-    </row>
-    <row r="270" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C270" s="9"/>
-      <c r="D270" s="9"/>
-      <c r="E270" s="9"/>
-      <c r="G270" s="7"/>
-    </row>
-    <row r="271" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C271" s="9"/>
-      <c r="D271" s="9"/>
-      <c r="E271" s="9"/>
-      <c r="G271" s="7"/>
-    </row>
-    <row r="272" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C272" s="9"/>
-      <c r="D272" s="9"/>
-      <c r="E272" s="9"/>
-      <c r="G272" s="7"/>
-    </row>
-    <row r="273" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C273" s="9"/>
-      <c r="D273" s="9"/>
-      <c r="E273" s="9"/>
-      <c r="G273" s="7"/>
-    </row>
-    <row r="274" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C274" s="9"/>
-      <c r="D274" s="9"/>
-      <c r="E274" s="9"/>
-      <c r="G274" s="7"/>
-    </row>
-    <row r="275" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C275" s="9"/>
-      <c r="D275" s="9"/>
-      <c r="E275" s="9"/>
-      <c r="G275" s="7"/>
-    </row>
-    <row r="276" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C276" s="9"/>
-      <c r="D276" s="9"/>
-      <c r="E276" s="9"/>
-      <c r="G276" s="7"/>
-    </row>
-    <row r="277" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C277" s="9"/>
-      <c r="D277" s="9"/>
-      <c r="E277" s="9"/>
-      <c r="G277" s="7"/>
-    </row>
-    <row r="278" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C278" s="9"/>
-      <c r="D278" s="9"/>
-      <c r="E278" s="9"/>
-      <c r="G278" s="7"/>
-    </row>
-    <row r="279" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C279" s="9"/>
-      <c r="D279" s="9"/>
-      <c r="E279" s="9"/>
-      <c r="G279" s="7"/>
-    </row>
-    <row r="280" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C280" s="9"/>
-      <c r="D280" s="9"/>
-      <c r="E280" s="9"/>
-      <c r="G280" s="7"/>
-    </row>
-    <row r="281" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C281" s="9"/>
-      <c r="D281" s="9"/>
-      <c r="E281" s="9"/>
-      <c r="G281" s="7"/>
-    </row>
-    <row r="282" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C282" s="9"/>
-      <c r="D282" s="9"/>
-      <c r="E282" s="9"/>
-      <c r="G282" s="7"/>
-    </row>
-    <row r="283" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C283" s="9"/>
-      <c r="D283" s="9"/>
-      <c r="E283" s="9"/>
-      <c r="G283" s="7"/>
-    </row>
-    <row r="284" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C284" s="9"/>
-      <c r="D284" s="9"/>
-      <c r="E284" s="9"/>
-      <c r="G284" s="7"/>
-    </row>
-    <row r="285" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C285" s="9"/>
-      <c r="D285" s="9"/>
-      <c r="E285" s="9"/>
-      <c r="G285" s="7"/>
-    </row>
-    <row r="286" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C286" s="9"/>
-      <c r="D286" s="9"/>
-      <c r="E286" s="9"/>
-      <c r="G286" s="7"/>
-    </row>
-    <row r="287" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C287" s="9"/>
-      <c r="D287" s="9"/>
-      <c r="E287" s="9"/>
-      <c r="G287" s="7"/>
-    </row>
-    <row r="288" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C288" s="9"/>
-      <c r="D288" s="9"/>
-      <c r="E288" s="9"/>
-      <c r="G288" s="7"/>
-    </row>
-    <row r="289" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C289" s="9"/>
-      <c r="D289" s="9"/>
-      <c r="E289" s="9"/>
-      <c r="G289" s="7"/>
-    </row>
-    <row r="290" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C290" s="9"/>
-      <c r="D290" s="9"/>
-      <c r="E290" s="9"/>
-      <c r="G290" s="7"/>
-    </row>
-    <row r="291" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C291" s="9"/>
-      <c r="D291" s="9"/>
-      <c r="E291" s="9"/>
-      <c r="G291" s="7"/>
-    </row>
-    <row r="292" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C292" s="9"/>
-      <c r="D292" s="9"/>
-      <c r="E292" s="9"/>
-      <c r="G292" s="7"/>
-    </row>
-    <row r="293" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C293" s="9"/>
-      <c r="D293" s="9"/>
-      <c r="E293" s="9"/>
-      <c r="G293" s="7"/>
-    </row>
-    <row r="294" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C294" s="9"/>
-      <c r="D294" s="9"/>
-      <c r="E294" s="9"/>
-      <c r="G294" s="7"/>
-    </row>
-    <row r="295" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C295" s="9"/>
-      <c r="D295" s="9"/>
-      <c r="E295" s="9"/>
-      <c r="G295" s="7"/>
-    </row>
-    <row r="296" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C296" s="9"/>
-      <c r="D296" s="9"/>
-      <c r="E296" s="9"/>
-      <c r="G296" s="7"/>
-    </row>
-    <row r="297" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C297" s="9"/>
-      <c r="D297" s="9"/>
-      <c r="E297" s="9"/>
-      <c r="G297" s="7"/>
-    </row>
-    <row r="298" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>87</v>
+      </c>
+      <c r="B240" t="s">
+        <v>12</v>
+      </c>
+      <c r="C240" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D240" s="9">
+        <v>5380</v>
+      </c>
+      <c r="E240" s="9">
+        <v>5630</v>
+      </c>
+      <c r="F240" t="s">
+        <v>161</v>
+      </c>
+      <c r="G240" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H240" t="s">
+        <v>72</v>
+      </c>
+      <c r="I240" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>115</v>
+      </c>
+      <c r="B241" t="s">
+        <v>12</v>
+      </c>
+      <c r="C241" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D241" s="9">
+        <v>5380</v>
+      </c>
+      <c r="E241" s="9">
+        <v>5630</v>
+      </c>
+      <c r="F241" t="s">
+        <v>161</v>
+      </c>
+      <c r="G241" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H241" t="s">
+        <v>72</v>
+      </c>
+      <c r="I241" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>86</v>
+      </c>
+      <c r="B242" t="s">
+        <v>12</v>
+      </c>
+      <c r="C242" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D242" s="9">
+        <v>5380</v>
+      </c>
+      <c r="E242" s="9">
+        <v>5630</v>
+      </c>
+      <c r="F242" t="s">
+        <v>161</v>
+      </c>
+      <c r="G242" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H242" t="s">
+        <v>72</v>
+      </c>
+      <c r="I242" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>88</v>
+      </c>
+      <c r="B243" t="s">
+        <v>12</v>
+      </c>
+      <c r="C243" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D243" s="9">
+        <v>5380</v>
+      </c>
+      <c r="E243" s="9">
+        <v>5630</v>
+      </c>
+      <c r="F243" t="s">
+        <v>161</v>
+      </c>
+      <c r="G243" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H243" t="s">
+        <v>72</v>
+      </c>
+      <c r="I243" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>121</v>
+      </c>
+      <c r="B244" t="s">
+        <v>12</v>
+      </c>
+      <c r="C244" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D244" s="9">
+        <v>5380</v>
+      </c>
+      <c r="E244" s="9">
+        <v>5630</v>
+      </c>
+      <c r="F244" t="s">
+        <v>161</v>
+      </c>
+      <c r="G244" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H244" t="s">
+        <v>72</v>
+      </c>
+      <c r="I244" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>111</v>
+      </c>
+      <c r="B245" t="s">
+        <v>12</v>
+      </c>
+      <c r="C245" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D245" s="9">
+        <v>5380</v>
+      </c>
+      <c r="E245" s="9">
+        <v>5630</v>
+      </c>
+      <c r="F245" t="s">
+        <v>161</v>
+      </c>
+      <c r="G245" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H245" t="s">
+        <v>72</v>
+      </c>
+      <c r="I245" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>124</v>
+      </c>
+      <c r="B246" t="s">
+        <v>12</v>
+      </c>
+      <c r="C246" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D246" s="9">
+        <v>5380</v>
+      </c>
+      <c r="E246" s="9">
+        <v>5630</v>
+      </c>
+      <c r="F246" t="s">
+        <v>161</v>
+      </c>
+      <c r="G246" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H246" t="s">
+        <v>72</v>
+      </c>
+      <c r="I246" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>109</v>
+      </c>
+      <c r="B247" t="s">
+        <v>12</v>
+      </c>
+      <c r="C247" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D247" s="9">
+        <v>5380</v>
+      </c>
+      <c r="E247" s="9">
+        <v>5630</v>
+      </c>
+      <c r="F247" t="s">
+        <v>161</v>
+      </c>
+      <c r="G247" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H247" t="s">
+        <v>72</v>
+      </c>
+      <c r="I247" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>130</v>
+      </c>
+      <c r="B248" t="s">
+        <v>12</v>
+      </c>
+      <c r="C248" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D248" s="9">
+        <v>5380</v>
+      </c>
+      <c r="E248" s="9">
+        <v>5630</v>
+      </c>
+      <c r="F248" t="s">
+        <v>161</v>
+      </c>
+      <c r="G248" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H248" t="s">
+        <v>72</v>
+      </c>
+      <c r="I248" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>112</v>
+      </c>
+      <c r="B249" t="s">
+        <v>12</v>
+      </c>
+      <c r="C249" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D249" s="9">
+        <v>5380</v>
+      </c>
+      <c r="E249" s="9">
+        <v>5630</v>
+      </c>
+      <c r="F249" t="s">
+        <v>161</v>
+      </c>
+      <c r="G249" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H249" t="s">
+        <v>72</v>
+      </c>
+      <c r="I249" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>145</v>
+      </c>
+      <c r="B250" t="s">
+        <v>12</v>
+      </c>
+      <c r="C250" s="9">
+        <v>4680</v>
+      </c>
+      <c r="D250" s="9">
+        <v>5430</v>
+      </c>
+      <c r="E250" s="9">
+        <v>5680</v>
+      </c>
+      <c r="F250" t="s">
+        <v>161</v>
+      </c>
+      <c r="G250" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H250" t="s">
+        <v>72</v>
+      </c>
+      <c r="I250" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>146</v>
+      </c>
+      <c r="B251" t="s">
+        <v>12</v>
+      </c>
+      <c r="C251" s="9">
+        <v>6330</v>
+      </c>
+      <c r="D251" s="9">
+        <v>5730</v>
+      </c>
+      <c r="E251" s="9">
+        <v>6330</v>
+      </c>
+      <c r="F251" t="s">
+        <v>161</v>
+      </c>
+      <c r="G251" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H251" t="s">
+        <v>72</v>
+      </c>
+      <c r="I251" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>147</v>
+      </c>
+      <c r="B252" t="s">
+        <v>12</v>
+      </c>
+      <c r="C252" s="9">
+        <v>4830</v>
+      </c>
+      <c r="D252" s="9">
+        <v>5530</v>
+      </c>
+      <c r="E252" s="9">
+        <v>5830</v>
+      </c>
+      <c r="F252" t="s">
+        <v>161</v>
+      </c>
+      <c r="G252" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H252" t="s">
+        <v>72</v>
+      </c>
+      <c r="I252" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>125</v>
+      </c>
+      <c r="B253" t="s">
+        <v>12</v>
+      </c>
+      <c r="C253" s="9">
+        <v>5030</v>
+      </c>
+      <c r="D253" s="9">
+        <v>5630</v>
+      </c>
+      <c r="E253" s="9">
+        <v>6030</v>
+      </c>
+      <c r="F253" t="s">
+        <v>161</v>
+      </c>
+      <c r="G253" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H253" t="s">
+        <v>72</v>
+      </c>
+      <c r="I253" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>148</v>
+      </c>
+      <c r="B254" t="s">
+        <v>12</v>
+      </c>
+      <c r="C254" s="9">
+        <v>5030</v>
+      </c>
+      <c r="D254" s="9">
+        <v>5630</v>
+      </c>
+      <c r="E254" s="9">
+        <v>6030</v>
+      </c>
+      <c r="F254" t="s">
+        <v>161</v>
+      </c>
+      <c r="G254" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H254" t="s">
+        <v>72</v>
+      </c>
+      <c r="I254" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>149</v>
+      </c>
+      <c r="B255" t="s">
+        <v>12</v>
+      </c>
+      <c r="C255" s="9">
+        <v>4730</v>
+      </c>
+      <c r="D255" s="9">
+        <v>5480</v>
+      </c>
+      <c r="E255" s="9">
+        <v>5730</v>
+      </c>
+      <c r="F255" t="s">
+        <v>161</v>
+      </c>
+      <c r="G255" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H255" t="s">
+        <v>72</v>
+      </c>
+      <c r="I255" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>126</v>
+      </c>
+      <c r="B256" t="s">
+        <v>12</v>
+      </c>
+      <c r="C256" s="9">
+        <v>4830</v>
+      </c>
+      <c r="D256" s="9">
+        <v>5530</v>
+      </c>
+      <c r="E256" s="9">
+        <v>5830</v>
+      </c>
+      <c r="F256" t="s">
+        <v>161</v>
+      </c>
+      <c r="G256" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H256" t="s">
+        <v>72</v>
+      </c>
+      <c r="I256" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>150</v>
+      </c>
+      <c r="B257" t="s">
+        <v>12</v>
+      </c>
+      <c r="C257" s="9">
+        <v>4830</v>
+      </c>
+      <c r="D257" s="9">
+        <v>5530</v>
+      </c>
+      <c r="E257" s="9">
+        <v>5830</v>
+      </c>
+      <c r="F257" t="s">
+        <v>161</v>
+      </c>
+      <c r="G257" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H257" t="s">
+        <v>72</v>
+      </c>
+      <c r="I257" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>151</v>
+      </c>
+      <c r="B258" t="s">
+        <v>12</v>
+      </c>
+      <c r="C258" s="9">
+        <v>4830</v>
+      </c>
+      <c r="D258" s="9">
+        <v>5530</v>
+      </c>
+      <c r="E258" s="9">
+        <v>5830</v>
+      </c>
+      <c r="F258" t="s">
+        <v>161</v>
+      </c>
+      <c r="G258" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H258" t="s">
+        <v>72</v>
+      </c>
+      <c r="I258" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>131</v>
+      </c>
+      <c r="B259" t="s">
+        <v>12</v>
+      </c>
+      <c r="C259" s="9">
+        <v>4830</v>
+      </c>
+      <c r="D259" s="9">
+        <v>5530</v>
+      </c>
+      <c r="E259" s="9">
+        <v>5830</v>
+      </c>
+      <c r="F259" t="s">
+        <v>161</v>
+      </c>
+      <c r="G259" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H259" t="s">
+        <v>72</v>
+      </c>
+      <c r="I259" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>129</v>
+      </c>
+      <c r="B260" t="s">
+        <v>12</v>
+      </c>
+      <c r="C260" s="9">
+        <v>4830</v>
+      </c>
+      <c r="D260" s="9">
+        <v>5530</v>
+      </c>
+      <c r="E260" s="9">
+        <v>5830</v>
+      </c>
+      <c r="F260" t="s">
+        <v>161</v>
+      </c>
+      <c r="G260" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H260" t="s">
+        <v>72</v>
+      </c>
+      <c r="I260" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>119</v>
+      </c>
+      <c r="B261" t="s">
+        <v>12</v>
+      </c>
+      <c r="C261" s="9">
+        <v>4830</v>
+      </c>
+      <c r="D261" s="9">
+        <v>5530</v>
+      </c>
+      <c r="E261" s="9">
+        <v>5830</v>
+      </c>
+      <c r="F261" t="s">
+        <v>161</v>
+      </c>
+      <c r="G261" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H261" t="s">
+        <v>72</v>
+      </c>
+      <c r="I261" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>122</v>
+      </c>
+      <c r="B262" t="s">
+        <v>12</v>
+      </c>
+      <c r="C262" s="9">
+        <v>4830</v>
+      </c>
+      <c r="D262" s="9">
+        <v>5530</v>
+      </c>
+      <c r="E262" s="9">
+        <v>5830</v>
+      </c>
+      <c r="F262" t="s">
+        <v>161</v>
+      </c>
+      <c r="G262" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H262" t="s">
+        <v>72</v>
+      </c>
+      <c r="I262" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>152</v>
+      </c>
+      <c r="B263" t="s">
+        <v>12</v>
+      </c>
+      <c r="C263" s="9">
+        <v>4830</v>
+      </c>
+      <c r="D263" s="9">
+        <v>5530</v>
+      </c>
+      <c r="E263" s="9">
+        <v>5830</v>
+      </c>
+      <c r="F263" t="s">
+        <v>161</v>
+      </c>
+      <c r="G263" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H263" t="s">
+        <v>72</v>
+      </c>
+      <c r="I263" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>153</v>
+      </c>
+      <c r="B264" t="s">
+        <v>12</v>
+      </c>
+      <c r="C264" s="9">
+        <v>4830</v>
+      </c>
+      <c r="D264" s="9">
+        <v>5530</v>
+      </c>
+      <c r="E264" s="9">
+        <v>5830</v>
+      </c>
+      <c r="F264" t="s">
+        <v>161</v>
+      </c>
+      <c r="G264" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H264" t="s">
+        <v>72</v>
+      </c>
+      <c r="I264" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>116</v>
+      </c>
+      <c r="B265" t="s">
+        <v>12</v>
+      </c>
+      <c r="C265" s="9">
+        <v>4980</v>
+      </c>
+      <c r="D265" s="9">
+        <v>5580</v>
+      </c>
+      <c r="E265" s="9">
+        <v>5980</v>
+      </c>
+      <c r="F265" t="s">
+        <v>161</v>
+      </c>
+      <c r="G265" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H265" t="s">
+        <v>72</v>
+      </c>
+      <c r="I265" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>120</v>
+      </c>
+      <c r="B266" t="s">
+        <v>12</v>
+      </c>
+      <c r="C266" s="9">
+        <v>5030</v>
+      </c>
+      <c r="D266" s="9">
+        <v>5630</v>
+      </c>
+      <c r="E266" s="9">
+        <v>6030</v>
+      </c>
+      <c r="F266" t="s">
+        <v>161</v>
+      </c>
+      <c r="G266" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H266" t="s">
+        <v>72</v>
+      </c>
+      <c r="I266" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>154</v>
+      </c>
+      <c r="B267" t="s">
+        <v>12</v>
+      </c>
+      <c r="C267" s="9">
+        <v>4980</v>
+      </c>
+      <c r="D267" s="9">
+        <v>5580</v>
+      </c>
+      <c r="E267" s="9">
+        <v>5980</v>
+      </c>
+      <c r="F267" t="s">
+        <v>161</v>
+      </c>
+      <c r="G267" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H267" t="s">
+        <v>72</v>
+      </c>
+      <c r="I267" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>155</v>
+      </c>
+      <c r="B268" t="s">
+        <v>12</v>
+      </c>
+      <c r="C268" s="9">
+        <v>5080</v>
+      </c>
+      <c r="D268" s="9">
+        <v>5680</v>
+      </c>
+      <c r="E268" s="9">
+        <v>6080</v>
+      </c>
+      <c r="F268" t="s">
+        <v>161</v>
+      </c>
+      <c r="G268" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H268" t="s">
+        <v>72</v>
+      </c>
+      <c r="I268" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>110</v>
+      </c>
+      <c r="B269" t="s">
+        <v>12</v>
+      </c>
+      <c r="C269" s="9">
+        <v>5330</v>
+      </c>
+      <c r="D269" s="9">
+        <v>5830</v>
+      </c>
+      <c r="E269" s="9">
+        <v>6500</v>
+      </c>
+      <c r="F269" t="s">
+        <v>161</v>
+      </c>
+      <c r="G269" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H269" t="s">
+        <v>72</v>
+      </c>
+      <c r="I269" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>156</v>
+      </c>
+      <c r="B270" t="s">
+        <v>12</v>
+      </c>
+      <c r="C270" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D270" s="9">
+        <v>5430</v>
+      </c>
+      <c r="E270" s="9">
+        <v>5770</v>
+      </c>
+      <c r="F270" t="s">
+        <v>161</v>
+      </c>
+      <c r="G270" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H270" t="s">
+        <v>72</v>
+      </c>
+      <c r="I270" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>157</v>
+      </c>
+      <c r="B271" t="s">
+        <v>12</v>
+      </c>
+      <c r="C271" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D271" s="9">
+        <v>5430</v>
+      </c>
+      <c r="E271" s="9">
+        <v>5770</v>
+      </c>
+      <c r="F271" t="s">
+        <v>161</v>
+      </c>
+      <c r="G271" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H271" t="s">
+        <v>72</v>
+      </c>
+      <c r="I271" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>158</v>
+      </c>
+      <c r="B272" t="s">
+        <v>12</v>
+      </c>
+      <c r="C272" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D272" s="9">
+        <v>5430</v>
+      </c>
+      <c r="E272" s="9">
+        <v>5770</v>
+      </c>
+      <c r="F272" t="s">
+        <v>161</v>
+      </c>
+      <c r="G272" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H272" t="s">
+        <v>72</v>
+      </c>
+      <c r="I272" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>159</v>
+      </c>
+      <c r="B273" t="s">
+        <v>12</v>
+      </c>
+      <c r="C273" s="9">
+        <v>4780</v>
+      </c>
+      <c r="D273" s="9">
+        <v>5530</v>
+      </c>
+      <c r="E273" s="9">
+        <v>5930</v>
+      </c>
+      <c r="F273" t="s">
+        <v>161</v>
+      </c>
+      <c r="G273" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H273" t="s">
+        <v>72</v>
+      </c>
+      <c r="I273" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>160</v>
+      </c>
+      <c r="B274" t="s">
+        <v>12</v>
+      </c>
+      <c r="C274" s="9">
+        <v>4780</v>
+      </c>
+      <c r="D274" s="9">
+        <v>5530</v>
+      </c>
+      <c r="E274" s="9">
+        <v>5930</v>
+      </c>
+      <c r="F274" t="s">
+        <v>161</v>
+      </c>
+      <c r="G274" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H274" t="s">
+        <v>72</v>
+      </c>
+      <c r="I274" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>94</v>
+      </c>
+      <c r="B275" t="s">
+        <v>12</v>
+      </c>
+      <c r="C275" s="9">
+        <v>4530</v>
+      </c>
+      <c r="D275" s="9">
+        <v>5130</v>
+      </c>
+      <c r="E275" s="9">
+        <v>5530</v>
+      </c>
+      <c r="F275" t="s">
+        <v>161</v>
+      </c>
+      <c r="G275" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H275" t="s">
+        <v>73</v>
+      </c>
+      <c r="I275" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>95</v>
+      </c>
+      <c r="B276" t="s">
+        <v>12</v>
+      </c>
+      <c r="C276" s="9">
+        <v>4530</v>
+      </c>
+      <c r="D276" s="9">
+        <v>5130</v>
+      </c>
+      <c r="E276" s="9">
+        <v>5530</v>
+      </c>
+      <c r="F276" t="s">
+        <v>161</v>
+      </c>
+      <c r="G276" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H276" t="s">
+        <v>73</v>
+      </c>
+      <c r="I276" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>83</v>
+      </c>
+      <c r="B277" t="s">
+        <v>12</v>
+      </c>
+      <c r="C277" s="9">
+        <v>4530</v>
+      </c>
+      <c r="D277" s="9">
+        <v>5130</v>
+      </c>
+      <c r="E277" s="9">
+        <v>5530</v>
+      </c>
+      <c r="F277" t="s">
+        <v>161</v>
+      </c>
+      <c r="G277" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H277" t="s">
+        <v>73</v>
+      </c>
+      <c r="I277" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>82</v>
+      </c>
+      <c r="B278" t="s">
+        <v>12</v>
+      </c>
+      <c r="C278" s="9">
+        <v>4530</v>
+      </c>
+      <c r="D278" s="9">
+        <v>5130</v>
+      </c>
+      <c r="E278" s="9">
+        <v>5530</v>
+      </c>
+      <c r="F278" t="s">
+        <v>161</v>
+      </c>
+      <c r="G278" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H278" t="s">
+        <v>73</v>
+      </c>
+      <c r="I278" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>84</v>
+      </c>
+      <c r="B279" t="s">
+        <v>12</v>
+      </c>
+      <c r="C279" s="9">
+        <v>4530</v>
+      </c>
+      <c r="D279" s="9">
+        <v>5130</v>
+      </c>
+      <c r="E279" s="9">
+        <v>5530</v>
+      </c>
+      <c r="F279" t="s">
+        <v>161</v>
+      </c>
+      <c r="G279" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H279" t="s">
+        <v>73</v>
+      </c>
+      <c r="I279" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>144</v>
+      </c>
+      <c r="B280" t="s">
+        <v>12</v>
+      </c>
+      <c r="C280" s="9">
+        <v>4530</v>
+      </c>
+      <c r="D280" s="9">
+        <v>5130</v>
+      </c>
+      <c r="E280" s="9">
+        <v>5530</v>
+      </c>
+      <c r="F280" t="s">
+        <v>161</v>
+      </c>
+      <c r="G280" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H280" t="s">
+        <v>73</v>
+      </c>
+      <c r="I280" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>81</v>
+      </c>
+      <c r="B281" t="s">
+        <v>12</v>
+      </c>
+      <c r="C281" s="9">
+        <v>4530</v>
+      </c>
+      <c r="D281" s="9">
+        <v>5130</v>
+      </c>
+      <c r="E281" s="9">
+        <v>5530</v>
+      </c>
+      <c r="F281" t="s">
+        <v>161</v>
+      </c>
+      <c r="G281" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H281" t="s">
+        <v>73</v>
+      </c>
+      <c r="I281" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>80</v>
+      </c>
+      <c r="B282" t="s">
+        <v>12</v>
+      </c>
+      <c r="C282" s="9">
+        <v>4530</v>
+      </c>
+      <c r="D282" s="9">
+        <v>5130</v>
+      </c>
+      <c r="E282" s="9">
+        <v>5530</v>
+      </c>
+      <c r="F282" t="s">
+        <v>161</v>
+      </c>
+      <c r="G282" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H282" t="s">
+        <v>73</v>
+      </c>
+      <c r="I282" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>100</v>
+      </c>
+      <c r="B283" t="s">
+        <v>12</v>
+      </c>
+      <c r="C283" s="9">
+        <v>4530</v>
+      </c>
+      <c r="D283" s="9">
+        <v>5130</v>
+      </c>
+      <c r="E283" s="9">
+        <v>5530</v>
+      </c>
+      <c r="F283" t="s">
+        <v>161</v>
+      </c>
+      <c r="G283" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H283" t="s">
+        <v>73</v>
+      </c>
+      <c r="I283" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>117</v>
+      </c>
+      <c r="B284" t="s">
+        <v>12</v>
+      </c>
+      <c r="C284" s="9">
+        <v>4730</v>
+      </c>
+      <c r="D284" s="9">
+        <v>5230</v>
+      </c>
+      <c r="E284" s="9">
+        <v>5730</v>
+      </c>
+      <c r="F284" t="s">
+        <v>161</v>
+      </c>
+      <c r="G284" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H284" t="s">
+        <v>73</v>
+      </c>
+      <c r="I284" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>85</v>
+      </c>
+      <c r="B285" t="s">
+        <v>12</v>
+      </c>
+      <c r="C285" s="9">
+        <v>4530</v>
+      </c>
+      <c r="D285" s="9">
+        <v>5130</v>
+      </c>
+      <c r="E285" s="9">
+        <v>5530</v>
+      </c>
+      <c r="F285" t="s">
+        <v>161</v>
+      </c>
+      <c r="G285" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H285" t="s">
+        <v>73</v>
+      </c>
+      <c r="I285" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>90</v>
+      </c>
+      <c r="B286" t="s">
+        <v>12</v>
+      </c>
+      <c r="C286" s="9">
+        <v>4680</v>
+      </c>
+      <c r="D286" s="9">
+        <v>5210</v>
+      </c>
+      <c r="E286" s="9">
+        <v>5680</v>
+      </c>
+      <c r="F286" t="s">
+        <v>161</v>
+      </c>
+      <c r="G286" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H286" t="s">
+        <v>73</v>
+      </c>
+      <c r="I286" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>87</v>
+      </c>
+      <c r="B287" t="s">
+        <v>12</v>
+      </c>
+      <c r="C287" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D287" s="9">
+        <v>5180</v>
+      </c>
+      <c r="E287" s="9">
+        <v>5630</v>
+      </c>
+      <c r="F287" t="s">
+        <v>161</v>
+      </c>
+      <c r="G287" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H287" t="s">
+        <v>73</v>
+      </c>
+      <c r="I287" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>115</v>
+      </c>
+      <c r="B288" t="s">
+        <v>12</v>
+      </c>
+      <c r="C288" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D288" s="9">
+        <v>5180</v>
+      </c>
+      <c r="E288" s="9">
+        <v>5630</v>
+      </c>
+      <c r="F288" t="s">
+        <v>161</v>
+      </c>
+      <c r="G288" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H288" t="s">
+        <v>73</v>
+      </c>
+      <c r="I288" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>86</v>
+      </c>
+      <c r="B289" t="s">
+        <v>12</v>
+      </c>
+      <c r="C289" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D289" s="9">
+        <v>5180</v>
+      </c>
+      <c r="E289" s="9">
+        <v>5630</v>
+      </c>
+      <c r="F289" t="s">
+        <v>161</v>
+      </c>
+      <c r="G289" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H289" t="s">
+        <v>73</v>
+      </c>
+      <c r="I289" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>88</v>
+      </c>
+      <c r="B290" t="s">
+        <v>12</v>
+      </c>
+      <c r="C290" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D290" s="9">
+        <v>5180</v>
+      </c>
+      <c r="E290" s="9">
+        <v>5630</v>
+      </c>
+      <c r="F290" t="s">
+        <v>161</v>
+      </c>
+      <c r="G290" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H290" t="s">
+        <v>73</v>
+      </c>
+      <c r="I290" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>121</v>
+      </c>
+      <c r="B291" t="s">
+        <v>12</v>
+      </c>
+      <c r="C291" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D291" s="9">
+        <v>5180</v>
+      </c>
+      <c r="E291" s="9">
+        <v>5630</v>
+      </c>
+      <c r="F291" t="s">
+        <v>161</v>
+      </c>
+      <c r="G291" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H291" t="s">
+        <v>73</v>
+      </c>
+      <c r="I291" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>111</v>
+      </c>
+      <c r="B292" t="s">
+        <v>12</v>
+      </c>
+      <c r="C292" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D292" s="9">
+        <v>5180</v>
+      </c>
+      <c r="E292" s="9">
+        <v>5630</v>
+      </c>
+      <c r="F292" t="s">
+        <v>161</v>
+      </c>
+      <c r="G292" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H292" t="s">
+        <v>73</v>
+      </c>
+      <c r="I292" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>124</v>
+      </c>
+      <c r="B293" t="s">
+        <v>12</v>
+      </c>
+      <c r="C293" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D293" s="9">
+        <v>5180</v>
+      </c>
+      <c r="E293" s="9">
+        <v>5630</v>
+      </c>
+      <c r="F293" t="s">
+        <v>161</v>
+      </c>
+      <c r="G293" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H293" t="s">
+        <v>73</v>
+      </c>
+      <c r="I293" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>109</v>
+      </c>
+      <c r="B294" t="s">
+        <v>12</v>
+      </c>
+      <c r="C294" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D294" s="9">
+        <v>5180</v>
+      </c>
+      <c r="E294" s="9">
+        <v>5630</v>
+      </c>
+      <c r="F294" t="s">
+        <v>161</v>
+      </c>
+      <c r="G294" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H294" t="s">
+        <v>73</v>
+      </c>
+      <c r="I294" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>130</v>
+      </c>
+      <c r="B295" t="s">
+        <v>12</v>
+      </c>
+      <c r="C295" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D295" s="9">
+        <v>5180</v>
+      </c>
+      <c r="E295" s="9">
+        <v>5630</v>
+      </c>
+      <c r="F295" t="s">
+        <v>161</v>
+      </c>
+      <c r="G295" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H295" t="s">
+        <v>73</v>
+      </c>
+      <c r="I295" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>112</v>
+      </c>
+      <c r="B296" t="s">
+        <v>12</v>
+      </c>
+      <c r="C296" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D296" s="9">
+        <v>5180</v>
+      </c>
+      <c r="E296" s="9">
+        <v>5630</v>
+      </c>
+      <c r="F296" t="s">
+        <v>161</v>
+      </c>
+      <c r="G296" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H296" t="s">
+        <v>73</v>
+      </c>
+      <c r="I296" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>145</v>
+      </c>
+      <c r="B297" t="s">
+        <v>12</v>
+      </c>
+      <c r="C297" s="9">
+        <v>4830</v>
+      </c>
+      <c r="D297" s="9">
+        <v>5340</v>
+      </c>
+      <c r="E297" s="9">
+        <v>5830</v>
+      </c>
+      <c r="F297" t="s">
+        <v>161</v>
+      </c>
+      <c r="G297" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H297" t="s">
+        <v>73</v>
+      </c>
+      <c r="I297" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>146</v>
+      </c>
+      <c r="B298" t="s">
+        <v>12</v>
+      </c>
       <c r="C298" s="9"/>
-      <c r="D298" s="9"/>
-      <c r="E298" s="9"/>
-      <c r="G298" s="7"/>
-    </row>
-    <row r="299" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D298" s="9">
+        <v>5280</v>
+      </c>
+      <c r="E298" s="9">
+        <v>5830</v>
+      </c>
+      <c r="F298" t="s">
+        <v>161</v>
+      </c>
+      <c r="G298" s="7">
+        <v>17</v>
+      </c>
+      <c r="H298" t="s">
+        <v>73</v>
+      </c>
+      <c r="I298" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>147</v>
+      </c>
+      <c r="B299" t="s">
+        <v>12</v>
+      </c>
       <c r="C299" s="9"/>
-      <c r="D299" s="9"/>
-      <c r="E299" s="9"/>
-      <c r="G299" s="7"/>
-    </row>
-    <row r="300" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D299" s="9">
+        <v>5350</v>
+      </c>
+      <c r="E299" s="9">
+        <v>5870</v>
+      </c>
+      <c r="F299" t="s">
+        <v>161</v>
+      </c>
+      <c r="G299" s="7">
+        <v>17</v>
+      </c>
+      <c r="H299" t="s">
+        <v>73</v>
+      </c>
+      <c r="I299" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>125</v>
+      </c>
+      <c r="B300" t="s">
+        <v>12</v>
+      </c>
       <c r="C300" s="9"/>
-      <c r="D300" s="9"/>
-      <c r="E300" s="9"/>
-      <c r="G300" s="7"/>
-    </row>
-    <row r="301" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D300" s="9">
+        <v>5300</v>
+      </c>
+      <c r="E300" s="9">
+        <v>5830</v>
+      </c>
+      <c r="F300" t="s">
+        <v>161</v>
+      </c>
+      <c r="G300" s="7">
+        <v>17</v>
+      </c>
+      <c r="H300" t="s">
+        <v>73</v>
+      </c>
+      <c r="I300" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>148</v>
+      </c>
+      <c r="B301" t="s">
+        <v>12</v>
+      </c>
       <c r="C301" s="9"/>
-      <c r="D301" s="9"/>
-      <c r="E301" s="9"/>
-      <c r="G301" s="7"/>
-    </row>
-    <row r="302" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D301" s="9">
+        <v>5380</v>
+      </c>
+      <c r="E301" s="9">
+        <v>5960</v>
+      </c>
+      <c r="F301" t="s">
+        <v>161</v>
+      </c>
+      <c r="G301" s="7">
+        <v>17</v>
+      </c>
+      <c r="H301" t="s">
+        <v>73</v>
+      </c>
+      <c r="I301" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>149</v>
+      </c>
+      <c r="B302" t="s">
+        <v>12</v>
+      </c>
       <c r="C302" s="9"/>
-      <c r="D302" s="9"/>
-      <c r="E302" s="9"/>
-      <c r="G302" s="7"/>
-    </row>
-    <row r="303" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D302" s="9">
+        <v>5320</v>
+      </c>
+      <c r="E302" s="9">
+        <v>5840</v>
+      </c>
+      <c r="F302" t="s">
+        <v>161</v>
+      </c>
+      <c r="G302" s="7">
+        <v>17</v>
+      </c>
+      <c r="H302" t="s">
+        <v>73</v>
+      </c>
+      <c r="I302" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>126</v>
+      </c>
+      <c r="B303" t="s">
+        <v>12</v>
+      </c>
       <c r="C303" s="9"/>
-      <c r="D303" s="9"/>
-      <c r="E303" s="9"/>
-      <c r="G303" s="7"/>
-    </row>
-    <row r="304" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D303" s="9">
+        <v>5330</v>
+      </c>
+      <c r="E303" s="9">
+        <v>5850</v>
+      </c>
+      <c r="F303" t="s">
+        <v>161</v>
+      </c>
+      <c r="G303" s="7">
+        <v>17</v>
+      </c>
+      <c r="H303" t="s">
+        <v>73</v>
+      </c>
+      <c r="I303" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>150</v>
+      </c>
+      <c r="B304" t="s">
+        <v>12</v>
+      </c>
       <c r="C304" s="9"/>
-      <c r="D304" s="9"/>
-      <c r="E304" s="9"/>
-      <c r="G304" s="7"/>
-    </row>
-    <row r="305" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D304" s="9">
+        <v>5250</v>
+      </c>
+      <c r="E304" s="9">
+        <v>5740</v>
+      </c>
+      <c r="F304" t="s">
+        <v>161</v>
+      </c>
+      <c r="G304" s="7">
+        <v>17</v>
+      </c>
+      <c r="H304" t="s">
+        <v>73</v>
+      </c>
+      <c r="I304" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>151</v>
+      </c>
+      <c r="B305" t="s">
+        <v>12</v>
+      </c>
       <c r="C305" s="9"/>
-      <c r="D305" s="9"/>
-      <c r="E305" s="9"/>
-      <c r="G305" s="7"/>
-    </row>
-    <row r="306" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D305" s="9">
+        <v>5250</v>
+      </c>
+      <c r="E305" s="9">
+        <v>5740</v>
+      </c>
+      <c r="F305" t="s">
+        <v>161</v>
+      </c>
+      <c r="G305" s="7">
+        <v>17</v>
+      </c>
+      <c r="H305" t="s">
+        <v>73</v>
+      </c>
+      <c r="I305" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>131</v>
+      </c>
+      <c r="B306" t="s">
+        <v>12</v>
+      </c>
       <c r="C306" s="9"/>
-      <c r="D306" s="9"/>
-      <c r="E306" s="9"/>
-      <c r="G306" s="7"/>
-    </row>
-    <row r="307" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D306" s="9">
+        <v>5250</v>
+      </c>
+      <c r="E306" s="9">
+        <v>5740</v>
+      </c>
+      <c r="F306" t="s">
+        <v>161</v>
+      </c>
+      <c r="G306" s="7">
+        <v>17</v>
+      </c>
+      <c r="H306" t="s">
+        <v>73</v>
+      </c>
+      <c r="I306" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>129</v>
+      </c>
+      <c r="B307" t="s">
+        <v>12</v>
+      </c>
       <c r="C307" s="9"/>
-      <c r="D307" s="9"/>
-      <c r="E307" s="9"/>
-      <c r="G307" s="7"/>
-    </row>
-    <row r="308" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D307" s="9">
+        <v>5250</v>
+      </c>
+      <c r="E307" s="9">
+        <v>5740</v>
+      </c>
+      <c r="F307" t="s">
+        <v>161</v>
+      </c>
+      <c r="G307" s="7">
+        <v>17</v>
+      </c>
+      <c r="H307" t="s">
+        <v>73</v>
+      </c>
+      <c r="I307" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>119</v>
+      </c>
+      <c r="B308" t="s">
+        <v>12</v>
+      </c>
       <c r="C308" s="9"/>
-      <c r="D308" s="9"/>
-      <c r="E308" s="9"/>
-      <c r="G308" s="7"/>
-    </row>
-    <row r="309" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D308" s="9">
+        <v>5250</v>
+      </c>
+      <c r="E308" s="9">
+        <v>5740</v>
+      </c>
+      <c r="F308" t="s">
+        <v>161</v>
+      </c>
+      <c r="G308" s="7">
+        <v>17</v>
+      </c>
+      <c r="H308" t="s">
+        <v>73</v>
+      </c>
+      <c r="I308" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>122</v>
+      </c>
+      <c r="B309" t="s">
+        <v>12</v>
+      </c>
       <c r="C309" s="9"/>
-      <c r="D309" s="9"/>
-      <c r="E309" s="9"/>
-      <c r="G309" s="7"/>
-    </row>
-    <row r="310" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D309" s="9">
+        <v>5250</v>
+      </c>
+      <c r="E309" s="9">
+        <v>5740</v>
+      </c>
+      <c r="F309" t="s">
+        <v>161</v>
+      </c>
+      <c r="G309" s="7">
+        <v>17</v>
+      </c>
+      <c r="H309" t="s">
+        <v>73</v>
+      </c>
+      <c r="I309" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>152</v>
+      </c>
+      <c r="B310" t="s">
+        <v>12</v>
+      </c>
       <c r="C310" s="9"/>
-      <c r="D310" s="9"/>
-      <c r="E310" s="9"/>
-      <c r="G310" s="7"/>
-    </row>
-    <row r="311" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D310" s="9">
+        <v>5250</v>
+      </c>
+      <c r="E310" s="9">
+        <v>5740</v>
+      </c>
+      <c r="F310" t="s">
+        <v>161</v>
+      </c>
+      <c r="G310" s="7">
+        <v>17</v>
+      </c>
+      <c r="H310" t="s">
+        <v>73</v>
+      </c>
+      <c r="I310" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>153</v>
+      </c>
+      <c r="B311" t="s">
+        <v>12</v>
+      </c>
       <c r="C311" s="9"/>
-      <c r="D311" s="9"/>
-      <c r="E311" s="9"/>
-      <c r="G311" s="7"/>
-    </row>
-    <row r="312" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D311" s="9">
+        <v>5250</v>
+      </c>
+      <c r="E311" s="9">
+        <v>5740</v>
+      </c>
+      <c r="F311" t="s">
+        <v>161</v>
+      </c>
+      <c r="G311" s="7">
+        <v>17</v>
+      </c>
+      <c r="H311" t="s">
+        <v>73</v>
+      </c>
+      <c r="I311" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>116</v>
+      </c>
+      <c r="B312" t="s">
+        <v>12</v>
+      </c>
       <c r="C312" s="9"/>
-      <c r="D312" s="9"/>
-      <c r="E312" s="9"/>
-      <c r="G312" s="7"/>
-    </row>
-    <row r="313" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D312" s="9">
+        <v>5370</v>
+      </c>
+      <c r="E312" s="9">
+        <v>5950</v>
+      </c>
+      <c r="F312" t="s">
+        <v>161</v>
+      </c>
+      <c r="G312" s="7">
+        <v>17</v>
+      </c>
+      <c r="H312" t="s">
+        <v>73</v>
+      </c>
+      <c r="I312" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>120</v>
+      </c>
+      <c r="B313" t="s">
+        <v>12</v>
+      </c>
       <c r="C313" s="9"/>
-      <c r="D313" s="9"/>
-      <c r="E313" s="9"/>
-      <c r="G313" s="7"/>
-    </row>
-    <row r="314" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D313" s="9">
+        <v>5360</v>
+      </c>
+      <c r="E313" s="9">
+        <v>5920</v>
+      </c>
+      <c r="F313" t="s">
+        <v>161</v>
+      </c>
+      <c r="G313" s="7">
+        <v>17</v>
+      </c>
+      <c r="H313" t="s">
+        <v>73</v>
+      </c>
+      <c r="I313" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>154</v>
+      </c>
+      <c r="B314" t="s">
+        <v>12</v>
+      </c>
       <c r="C314" s="9"/>
-      <c r="D314" s="9"/>
-      <c r="E314" s="9"/>
-      <c r="G314" s="7"/>
-    </row>
-    <row r="315" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D314" s="9">
+        <v>5360</v>
+      </c>
+      <c r="E314" s="9">
+        <v>5980</v>
+      </c>
+      <c r="F314" t="s">
+        <v>161</v>
+      </c>
+      <c r="G314" s="7">
+        <v>17</v>
+      </c>
+      <c r="H314" t="s">
+        <v>73</v>
+      </c>
+      <c r="I314" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>155</v>
+      </c>
+      <c r="B315" t="s">
+        <v>12</v>
+      </c>
       <c r="C315" s="9"/>
-      <c r="D315" s="9"/>
-      <c r="E315" s="9"/>
-      <c r="G315" s="7"/>
-    </row>
-    <row r="316" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D315" s="9">
+        <v>5360</v>
+      </c>
+      <c r="E315" s="9">
+        <v>5980</v>
+      </c>
+      <c r="F315" t="s">
+        <v>161</v>
+      </c>
+      <c r="G315" s="7">
+        <v>17</v>
+      </c>
+      <c r="H315" t="s">
+        <v>73</v>
+      </c>
+      <c r="I315" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>110</v>
+      </c>
+      <c r="B316" t="s">
+        <v>12</v>
+      </c>
       <c r="C316" s="9"/>
-      <c r="D316" s="9"/>
-      <c r="E316" s="9"/>
-      <c r="G316" s="7"/>
-    </row>
-    <row r="317" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D316" s="9">
+        <v>5540</v>
+      </c>
+      <c r="E316" s="9">
+        <v>6320</v>
+      </c>
+      <c r="F316" t="s">
+        <v>161</v>
+      </c>
+      <c r="G316" s="7">
+        <v>17</v>
+      </c>
+      <c r="H316" t="s">
+        <v>73</v>
+      </c>
+      <c r="I316" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>156</v>
+      </c>
+      <c r="B317" t="s">
+        <v>12</v>
+      </c>
       <c r="C317" s="9"/>
-      <c r="D317" s="9"/>
-      <c r="E317" s="9"/>
-      <c r="G317" s="7"/>
-    </row>
-    <row r="318" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D317" s="9">
+        <v>5230</v>
+      </c>
+      <c r="E317" s="9">
+        <v>5680</v>
+      </c>
+      <c r="F317" t="s">
+        <v>161</v>
+      </c>
+      <c r="G317" s="7">
+        <v>17</v>
+      </c>
+      <c r="H317" t="s">
+        <v>73</v>
+      </c>
+      <c r="I317" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>157</v>
+      </c>
+      <c r="B318" t="s">
+        <v>12</v>
+      </c>
       <c r="C318" s="9"/>
-      <c r="D318" s="9"/>
-      <c r="E318" s="9"/>
-      <c r="G318" s="7"/>
-    </row>
-    <row r="319" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D318" s="9">
+        <v>5230</v>
+      </c>
+      <c r="E318" s="9">
+        <v>5680</v>
+      </c>
+      <c r="F318" t="s">
+        <v>161</v>
+      </c>
+      <c r="G318" s="7">
+        <v>17</v>
+      </c>
+      <c r="H318" t="s">
+        <v>73</v>
+      </c>
+      <c r="I318" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>158</v>
+      </c>
+      <c r="B319" t="s">
+        <v>12</v>
+      </c>
       <c r="C319" s="9"/>
-      <c r="D319" s="9"/>
-      <c r="E319" s="9"/>
-      <c r="G319" s="7"/>
-    </row>
-    <row r="320" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D319" s="9">
+        <v>5230</v>
+      </c>
+      <c r="E319" s="9">
+        <v>5680</v>
+      </c>
+      <c r="F319" t="s">
+        <v>161</v>
+      </c>
+      <c r="G319" s="7">
+        <v>17</v>
+      </c>
+      <c r="H319" t="s">
+        <v>73</v>
+      </c>
+      <c r="I319" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>159</v>
+      </c>
+      <c r="B320" t="s">
+        <v>12</v>
+      </c>
       <c r="C320" s="9"/>
-      <c r="D320" s="9"/>
-      <c r="E320" s="9"/>
-      <c r="G320" s="7"/>
-    </row>
-    <row r="321" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D320" s="9">
+        <v>5330</v>
+      </c>
+      <c r="E320" s="9">
+        <v>5830</v>
+      </c>
+      <c r="F320" t="s">
+        <v>161</v>
+      </c>
+      <c r="G320" s="7">
+        <v>17</v>
+      </c>
+      <c r="H320" t="s">
+        <v>73</v>
+      </c>
+      <c r="I320" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>160</v>
+      </c>
+      <c r="B321" t="s">
+        <v>12</v>
+      </c>
       <c r="C321" s="9"/>
-      <c r="D321" s="9"/>
-      <c r="E321" s="9"/>
-      <c r="G321" s="7"/>
-    </row>
-    <row r="322" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D321" s="9">
+        <v>5430</v>
+      </c>
+      <c r="E321" s="9">
+        <v>5980</v>
+      </c>
+      <c r="F321" t="s">
+        <v>161</v>
+      </c>
+      <c r="G321" s="7">
+        <v>17</v>
+      </c>
+      <c r="H321" t="s">
+        <v>73</v>
+      </c>
+      <c r="I321" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C322" s="9"/>
       <c r="D322" s="9"/>
       <c r="E322" s="9"/>
       <c r="G322" s="7"/>
     </row>
-    <row r="323" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C323" s="9"/>
       <c r="D323" s="9"/>
       <c r="E323" s="9"/>
       <c r="G323" s="7"/>
     </row>
-    <row r="324" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C324" s="9"/>
       <c r="D324" s="9"/>
       <c r="E324" s="9"/>
       <c r="G324" s="7"/>
     </row>
-    <row r="325" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C325" s="9"/>
       <c r="D325" s="9"/>
       <c r="E325" s="9"/>
       <c r="G325" s="7"/>
     </row>
-    <row r="326" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C326" s="9"/>
       <c r="D326" s="9"/>
       <c r="E326" s="9"/>
       <c r="G326" s="7"/>
     </row>
-    <row r="327" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C327" s="9"/>
       <c r="D327" s="9"/>
       <c r="E327" s="9"/>
       <c r="G327" s="7"/>
     </row>
-    <row r="328" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C328" s="9"/>
       <c r="D328" s="9"/>
       <c r="E328" s="9"/>
       <c r="G328" s="7"/>
     </row>
-    <row r="329" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C329" s="9"/>
       <c r="D329" s="9"/>
       <c r="E329" s="9"/>
       <c r="G329" s="7"/>
     </row>
-    <row r="330" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C330" s="9"/>
       <c r="D330" s="9"/>
       <c r="E330" s="9"/>
       <c r="G330" s="7"/>
     </row>
-    <row r="331" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C331" s="9"/>
       <c r="D331" s="9"/>
       <c r="E331" s="9"/>
       <c r="G331" s="7"/>
     </row>
-    <row r="332" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C332" s="9"/>
       <c r="D332" s="9"/>
       <c r="E332" s="9"/>
       <c r="G332" s="7"/>
     </row>
-    <row r="333" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C333" s="9"/>
       <c r="D333" s="9"/>
       <c r="E333" s="9"/>
       <c r="G333" s="7"/>
     </row>
-    <row r="334" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C334" s="9"/>
       <c r="D334" s="9"/>
       <c r="E334" s="9"/>
       <c r="G334" s="7"/>
     </row>
-    <row r="335" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C335" s="9"/>
       <c r="D335" s="9"/>
       <c r="E335" s="9"/>
       <c r="G335" s="7"/>
     </row>
-    <row r="336" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C336" s="9"/>
       <c r="D336" s="9"/>
       <c r="E336" s="9"/>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DOCS EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF4FD42-5DD8-4F92-90E1-794D9847AF11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38DEB3BB-E8E2-4679-86F7-6D0548C6C1B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1787" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2301" uniqueCount="166">
   <si>
     <t>POD</t>
   </si>
@@ -529,6 +529,18 @@
   </si>
   <si>
     <t>28 de sep al 11 de oct</t>
+  </si>
+  <si>
+    <t>JIUJIANG, GD</t>
+  </si>
+  <si>
+    <t>XIAOLAN</t>
+  </si>
+  <si>
+    <t>GUAYAQUIL/POSORJA</t>
+  </si>
+  <si>
+    <t>1 al 11 de octubre</t>
   </si>
 </sst>
 </file>
@@ -1067,7 +1079,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}">
-  <dimension ref="A1:I1200"/>
+  <dimension ref="A1:I1161"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
@@ -10052,666 +10064,2816 @@
       </c>
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>94</v>
+      </c>
+      <c r="B322" t="s">
+        <v>12</v>
+      </c>
       <c r="C322" s="9"/>
-      <c r="D322" s="9"/>
-      <c r="E322" s="9"/>
-      <c r="G322" s="7"/>
+      <c r="D322" s="9">
+        <v>5370</v>
+      </c>
+      <c r="E322" s="9">
+        <v>5670</v>
+      </c>
+      <c r="F322" t="s">
+        <v>165</v>
+      </c>
+      <c r="G322" s="7">
+        <v>17</v>
+      </c>
+      <c r="H322" t="s">
+        <v>73</v>
+      </c>
+      <c r="I322" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>80</v>
+      </c>
+      <c r="B323" t="s">
+        <v>12</v>
+      </c>
       <c r="C323" s="9"/>
-      <c r="D323" s="9"/>
-      <c r="E323" s="9"/>
-      <c r="G323" s="7"/>
+      <c r="D323" s="9">
+        <v>5370</v>
+      </c>
+      <c r="E323" s="9">
+        <v>5670</v>
+      </c>
+      <c r="F323" t="s">
+        <v>165</v>
+      </c>
+      <c r="G323" s="7">
+        <v>17</v>
+      </c>
+      <c r="H323" t="s">
+        <v>73</v>
+      </c>
+      <c r="I323" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>108</v>
+      </c>
+      <c r="B324" t="s">
+        <v>12</v>
+      </c>
       <c r="C324" s="9"/>
-      <c r="D324" s="9"/>
-      <c r="E324" s="9"/>
-      <c r="G324" s="7"/>
+      <c r="D324" s="9">
+        <v>5370</v>
+      </c>
+      <c r="E324" s="9">
+        <v>5670</v>
+      </c>
+      <c r="F324" t="s">
+        <v>165</v>
+      </c>
+      <c r="G324" s="7">
+        <v>17</v>
+      </c>
+      <c r="H324" t="s">
+        <v>73</v>
+      </c>
+      <c r="I324" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>109</v>
+      </c>
+      <c r="B325" t="s">
+        <v>12</v>
+      </c>
       <c r="C325" s="9"/>
-      <c r="D325" s="9"/>
-      <c r="E325" s="9"/>
-      <c r="G325" s="7"/>
+      <c r="D325" s="9">
+        <v>5480</v>
+      </c>
+      <c r="E325" s="9">
+        <v>5830</v>
+      </c>
+      <c r="F325" t="s">
+        <v>165</v>
+      </c>
+      <c r="G325" s="7">
+        <v>17</v>
+      </c>
+      <c r="H325" t="s">
+        <v>73</v>
+      </c>
+      <c r="I325" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>110</v>
+      </c>
+      <c r="B326" t="s">
+        <v>12</v>
+      </c>
       <c r="C326" s="9"/>
-      <c r="D326" s="9"/>
-      <c r="E326" s="9"/>
-      <c r="G326" s="7"/>
+      <c r="D326" s="9">
+        <v>5630</v>
+      </c>
+      <c r="E326" s="9">
+        <v>6210</v>
+      </c>
+      <c r="F326" t="s">
+        <v>165</v>
+      </c>
+      <c r="G326" s="7">
+        <v>17</v>
+      </c>
+      <c r="H326" t="s">
+        <v>73</v>
+      </c>
+      <c r="I326" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>85</v>
+      </c>
+      <c r="B327" t="s">
+        <v>12</v>
+      </c>
       <c r="C327" s="9"/>
-      <c r="D327" s="9"/>
-      <c r="E327" s="9"/>
-      <c r="G327" s="7"/>
+      <c r="D327" s="9">
+        <v>5420</v>
+      </c>
+      <c r="E327" s="9">
+        <v>5770</v>
+      </c>
+      <c r="F327" t="s">
+        <v>165</v>
+      </c>
+      <c r="G327" s="7">
+        <v>17</v>
+      </c>
+      <c r="H327" t="s">
+        <v>73</v>
+      </c>
+      <c r="I327" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>111</v>
+      </c>
+      <c r="B328" t="s">
+        <v>12</v>
+      </c>
       <c r="C328" s="9"/>
-      <c r="D328" s="9"/>
-      <c r="E328" s="9"/>
-      <c r="G328" s="7"/>
+      <c r="D328" s="9">
+        <v>5480</v>
+      </c>
+      <c r="E328" s="9">
+        <v>5840</v>
+      </c>
+      <c r="F328" t="s">
+        <v>165</v>
+      </c>
+      <c r="G328" s="7">
+        <v>17</v>
+      </c>
+      <c r="H328" t="s">
+        <v>73</v>
+      </c>
+      <c r="I328" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>112</v>
+      </c>
+      <c r="B329" t="s">
+        <v>12</v>
+      </c>
       <c r="C329" s="9"/>
-      <c r="D329" s="9"/>
-      <c r="E329" s="9"/>
-      <c r="G329" s="7"/>
+      <c r="D329" s="9">
+        <v>5420</v>
+      </c>
+      <c r="E329" s="9">
+        <v>5770</v>
+      </c>
+      <c r="F329" t="s">
+        <v>165</v>
+      </c>
+      <c r="G329" s="7">
+        <v>17</v>
+      </c>
+      <c r="H329" t="s">
+        <v>73</v>
+      </c>
+      <c r="I329" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>113</v>
+      </c>
+      <c r="B330" t="s">
+        <v>12</v>
+      </c>
       <c r="C330" s="9"/>
-      <c r="D330" s="9"/>
-      <c r="E330" s="9"/>
-      <c r="G330" s="7"/>
+      <c r="D330" s="9">
+        <v>5520</v>
+      </c>
+      <c r="E330" s="9">
+        <v>5870</v>
+      </c>
+      <c r="F330" t="s">
+        <v>165</v>
+      </c>
+      <c r="G330" s="7">
+        <v>17</v>
+      </c>
+      <c r="H330" t="s">
+        <v>73</v>
+      </c>
+      <c r="I330" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>114</v>
+      </c>
+      <c r="B331" t="s">
+        <v>12</v>
+      </c>
       <c r="C331" s="9"/>
-      <c r="D331" s="9"/>
-      <c r="E331" s="9"/>
-      <c r="G331" s="7"/>
+      <c r="D331" s="9">
+        <v>5470</v>
+      </c>
+      <c r="E331" s="9">
+        <v>5850</v>
+      </c>
+      <c r="F331" t="s">
+        <v>165</v>
+      </c>
+      <c r="G331" s="7">
+        <v>17</v>
+      </c>
+      <c r="H331" t="s">
+        <v>73</v>
+      </c>
+      <c r="I331" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>115</v>
+      </c>
+      <c r="B332" t="s">
+        <v>12</v>
+      </c>
       <c r="C332" s="9"/>
-      <c r="D332" s="9"/>
-      <c r="E332" s="9"/>
-      <c r="G332" s="7"/>
+      <c r="D332" s="9">
+        <v>5470</v>
+      </c>
+      <c r="E332" s="9">
+        <v>5870</v>
+      </c>
+      <c r="F332" t="s">
+        <v>165</v>
+      </c>
+      <c r="G332" s="7">
+        <v>17</v>
+      </c>
+      <c r="H332" t="s">
+        <v>73</v>
+      </c>
+      <c r="I332" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>86</v>
+      </c>
+      <c r="B333" t="s">
+        <v>12</v>
+      </c>
       <c r="C333" s="9"/>
-      <c r="D333" s="9"/>
-      <c r="E333" s="9"/>
-      <c r="G333" s="7"/>
+      <c r="D333" s="9">
+        <v>5480</v>
+      </c>
+      <c r="E333" s="9">
+        <v>5830</v>
+      </c>
+      <c r="F333" t="s">
+        <v>165</v>
+      </c>
+      <c r="G333" s="7">
+        <v>17</v>
+      </c>
+      <c r="H333" t="s">
+        <v>73</v>
+      </c>
+      <c r="I333" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>116</v>
+      </c>
+      <c r="B334" t="s">
+        <v>12</v>
+      </c>
       <c r="C334" s="9"/>
-      <c r="D334" s="9"/>
-      <c r="E334" s="9"/>
-      <c r="G334" s="7"/>
+      <c r="D334" s="9">
+        <v>5540</v>
+      </c>
+      <c r="E334" s="9">
+        <v>5970</v>
+      </c>
+      <c r="F334" t="s">
+        <v>165</v>
+      </c>
+      <c r="G334" s="7">
+        <v>17</v>
+      </c>
+      <c r="H334" t="s">
+        <v>73</v>
+      </c>
+      <c r="I334" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>117</v>
+      </c>
+      <c r="B335" t="s">
+        <v>12</v>
+      </c>
       <c r="C335" s="9"/>
-      <c r="D335" s="9"/>
-      <c r="E335" s="9"/>
-      <c r="G335" s="7"/>
+      <c r="D335" s="9">
+        <v>5470</v>
+      </c>
+      <c r="E335" s="9">
+        <v>5870</v>
+      </c>
+      <c r="F335" t="s">
+        <v>165</v>
+      </c>
+      <c r="G335" s="7">
+        <v>17</v>
+      </c>
+      <c r="H335" t="s">
+        <v>73</v>
+      </c>
+      <c r="I335" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>118</v>
+      </c>
+      <c r="B336" t="s">
+        <v>12</v>
+      </c>
       <c r="C336" s="9"/>
-      <c r="D336" s="9"/>
-      <c r="E336" s="9"/>
-      <c r="G336" s="7"/>
-    </row>
-    <row r="337" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D336" s="9">
+        <v>5470</v>
+      </c>
+      <c r="E336" s="9">
+        <v>5840</v>
+      </c>
+      <c r="F336" t="s">
+        <v>165</v>
+      </c>
+      <c r="G336" s="7">
+        <v>17</v>
+      </c>
+      <c r="H336" t="s">
+        <v>73</v>
+      </c>
+      <c r="I336" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>119</v>
+      </c>
+      <c r="B337" t="s">
+        <v>12</v>
+      </c>
       <c r="C337" s="9"/>
-      <c r="D337" s="9"/>
-      <c r="E337" s="9"/>
-      <c r="G337" s="7"/>
-    </row>
-    <row r="338" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D337" s="9">
+        <v>5490</v>
+      </c>
+      <c r="E337" s="9">
+        <v>5820</v>
+      </c>
+      <c r="F337" t="s">
+        <v>165</v>
+      </c>
+      <c r="G337" s="7">
+        <v>17</v>
+      </c>
+      <c r="H337" t="s">
+        <v>73</v>
+      </c>
+      <c r="I337" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>120</v>
+      </c>
+      <c r="B338" t="s">
+        <v>12</v>
+      </c>
       <c r="C338" s="9"/>
-      <c r="D338" s="9"/>
-      <c r="E338" s="9"/>
-      <c r="G338" s="7"/>
-    </row>
-    <row r="339" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D338" s="9">
+        <v>5600</v>
+      </c>
+      <c r="E338" s="9">
+        <v>6070</v>
+      </c>
+      <c r="F338" t="s">
+        <v>165</v>
+      </c>
+      <c r="G338" s="7">
+        <v>17</v>
+      </c>
+      <c r="H338" t="s">
+        <v>73</v>
+      </c>
+      <c r="I338" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>121</v>
+      </c>
+      <c r="B339" t="s">
+        <v>12</v>
+      </c>
       <c r="C339" s="9"/>
-      <c r="D339" s="9"/>
-      <c r="E339" s="9"/>
-      <c r="G339" s="7"/>
-    </row>
-    <row r="340" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D339" s="9">
+        <v>5480</v>
+      </c>
+      <c r="E339" s="9">
+        <v>5840</v>
+      </c>
+      <c r="F339" t="s">
+        <v>165</v>
+      </c>
+      <c r="G339" s="7">
+        <v>17</v>
+      </c>
+      <c r="H339" t="s">
+        <v>73</v>
+      </c>
+      <c r="I339" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>122</v>
+      </c>
+      <c r="B340" t="s">
+        <v>12</v>
+      </c>
       <c r="C340" s="9"/>
-      <c r="D340" s="9"/>
-      <c r="E340" s="9"/>
-      <c r="G340" s="7"/>
-    </row>
-    <row r="341" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D340" s="9">
+        <v>5460</v>
+      </c>
+      <c r="E340" s="9">
+        <v>5820</v>
+      </c>
+      <c r="F340" t="s">
+        <v>165</v>
+      </c>
+      <c r="G340" s="7">
+        <v>17</v>
+      </c>
+      <c r="H340" t="s">
+        <v>73</v>
+      </c>
+      <c r="I340" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>81</v>
+      </c>
+      <c r="B341" t="s">
+        <v>12</v>
+      </c>
       <c r="C341" s="9"/>
-      <c r="D341" s="9"/>
-      <c r="E341" s="9"/>
-      <c r="G341" s="7"/>
-    </row>
-    <row r="342" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D341" s="9">
+        <v>5420</v>
+      </c>
+      <c r="E341" s="9">
+        <v>5770</v>
+      </c>
+      <c r="F341" t="s">
+        <v>165</v>
+      </c>
+      <c r="G341" s="7">
+        <v>17</v>
+      </c>
+      <c r="H341" t="s">
+        <v>73</v>
+      </c>
+      <c r="I341" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>89</v>
+      </c>
+      <c r="B342" t="s">
+        <v>12</v>
+      </c>
       <c r="C342" s="9"/>
-      <c r="D342" s="9"/>
-      <c r="E342" s="9"/>
-      <c r="G342" s="7"/>
-    </row>
-    <row r="343" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D342" s="9">
+        <v>5480</v>
+      </c>
+      <c r="E342" s="9">
+        <v>5840</v>
+      </c>
+      <c r="F342" t="s">
+        <v>165</v>
+      </c>
+      <c r="G342" s="7">
+        <v>17</v>
+      </c>
+      <c r="H342" t="s">
+        <v>73</v>
+      </c>
+      <c r="I342" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>123</v>
+      </c>
+      <c r="B343" t="s">
+        <v>12</v>
+      </c>
       <c r="C343" s="9"/>
-      <c r="D343" s="9"/>
-      <c r="E343" s="9"/>
-      <c r="G343" s="7"/>
-    </row>
-    <row r="344" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D343" s="9">
+        <v>5470</v>
+      </c>
+      <c r="E343" s="9">
+        <v>5830</v>
+      </c>
+      <c r="F343" t="s">
+        <v>165</v>
+      </c>
+      <c r="G343" s="7">
+        <v>17</v>
+      </c>
+      <c r="H343" t="s">
+        <v>73</v>
+      </c>
+      <c r="I343" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>90</v>
+      </c>
+      <c r="B344" t="s">
+        <v>12</v>
+      </c>
       <c r="C344" s="9"/>
-      <c r="D344" s="9"/>
-      <c r="E344" s="9"/>
-      <c r="G344" s="7"/>
-    </row>
-    <row r="345" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D344" s="9">
+        <v>5510</v>
+      </c>
+      <c r="E344" s="9">
+        <v>5930</v>
+      </c>
+      <c r="F344" t="s">
+        <v>165</v>
+      </c>
+      <c r="G344" s="7">
+        <v>17</v>
+      </c>
+      <c r="H344" t="s">
+        <v>73</v>
+      </c>
+      <c r="I344" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>82</v>
+      </c>
+      <c r="B345" t="s">
+        <v>12</v>
+      </c>
       <c r="C345" s="9"/>
-      <c r="D345" s="9"/>
-      <c r="E345" s="9"/>
-      <c r="G345" s="7"/>
-    </row>
-    <row r="346" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D345" s="9">
+        <v>5370</v>
+      </c>
+      <c r="E345" s="9">
+        <v>5670</v>
+      </c>
+      <c r="F345" t="s">
+        <v>165</v>
+      </c>
+      <c r="G345" s="7">
+        <v>17</v>
+      </c>
+      <c r="H345" t="s">
+        <v>73</v>
+      </c>
+      <c r="I345" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>95</v>
+      </c>
+      <c r="B346" t="s">
+        <v>12</v>
+      </c>
       <c r="C346" s="9"/>
-      <c r="D346" s="9"/>
-      <c r="E346" s="9"/>
-      <c r="G346" s="7"/>
-    </row>
-    <row r="347" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D346" s="9">
+        <v>5370</v>
+      </c>
+      <c r="E346" s="9">
+        <v>5670</v>
+      </c>
+      <c r="F346" t="s">
+        <v>165</v>
+      </c>
+      <c r="G346" s="7">
+        <v>17</v>
+      </c>
+      <c r="H346" t="s">
+        <v>73</v>
+      </c>
+      <c r="I346" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>124</v>
+      </c>
+      <c r="B347" t="s">
+        <v>12</v>
+      </c>
       <c r="C347" s="9"/>
-      <c r="D347" s="9"/>
-      <c r="E347" s="9"/>
-      <c r="G347" s="7"/>
-    </row>
-    <row r="348" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D347" s="9">
+        <v>5480</v>
+      </c>
+      <c r="E347" s="9">
+        <v>5840</v>
+      </c>
+      <c r="F347" t="s">
+        <v>165</v>
+      </c>
+      <c r="G347" s="7">
+        <v>17</v>
+      </c>
+      <c r="H347" t="s">
+        <v>73</v>
+      </c>
+      <c r="I347" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>125</v>
+      </c>
+      <c r="B348" t="s">
+        <v>12</v>
+      </c>
       <c r="C348" s="9"/>
-      <c r="D348" s="9"/>
-      <c r="E348" s="9"/>
-      <c r="G348" s="7"/>
-    </row>
-    <row r="349" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D348" s="9">
+        <v>5540</v>
+      </c>
+      <c r="E348" s="9">
+        <v>5950</v>
+      </c>
+      <c r="F348" t="s">
+        <v>165</v>
+      </c>
+      <c r="G348" s="7">
+        <v>17</v>
+      </c>
+      <c r="H348" t="s">
+        <v>73</v>
+      </c>
+      <c r="I348" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>126</v>
+      </c>
+      <c r="B349" t="s">
+        <v>12</v>
+      </c>
       <c r="C349" s="9"/>
-      <c r="D349" s="9"/>
-      <c r="E349" s="9"/>
-      <c r="G349" s="7"/>
-    </row>
-    <row r="350" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D349" s="9">
+        <v>5500</v>
+      </c>
+      <c r="E349" s="9">
+        <v>5870</v>
+      </c>
+      <c r="F349" t="s">
+        <v>165</v>
+      </c>
+      <c r="G349" s="7">
+        <v>17</v>
+      </c>
+      <c r="H349" t="s">
+        <v>73</v>
+      </c>
+      <c r="I349" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>84</v>
+      </c>
+      <c r="B350" t="s">
+        <v>12</v>
+      </c>
       <c r="C350" s="9"/>
-      <c r="D350" s="9"/>
-      <c r="E350" s="9"/>
-      <c r="G350" s="7"/>
-    </row>
-    <row r="351" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D350" s="9">
+        <v>5420</v>
+      </c>
+      <c r="E350" s="9">
+        <v>5770</v>
+      </c>
+      <c r="F350" t="s">
+        <v>165</v>
+      </c>
+      <c r="G350" s="7">
+        <v>17</v>
+      </c>
+      <c r="H350" t="s">
+        <v>73</v>
+      </c>
+      <c r="I350" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>100</v>
+      </c>
+      <c r="B351" t="s">
+        <v>12</v>
+      </c>
       <c r="C351" s="9"/>
-      <c r="D351" s="9"/>
-      <c r="E351" s="9"/>
-      <c r="G351" s="7"/>
-    </row>
-    <row r="352" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D351" s="9">
+        <v>5370</v>
+      </c>
+      <c r="E351" s="9">
+        <v>5670</v>
+      </c>
+      <c r="F351" t="s">
+        <v>165</v>
+      </c>
+      <c r="G351" s="7">
+        <v>17</v>
+      </c>
+      <c r="H351" t="s">
+        <v>73</v>
+      </c>
+      <c r="I351" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>127</v>
+      </c>
+      <c r="B352" t="s">
+        <v>12</v>
+      </c>
       <c r="C352" s="9"/>
-      <c r="D352" s="9"/>
-      <c r="E352" s="9"/>
-      <c r="G352" s="7"/>
-    </row>
-    <row r="353" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D352" s="9">
+        <v>5460</v>
+      </c>
+      <c r="E352" s="9">
+        <v>5820</v>
+      </c>
+      <c r="F352" t="s">
+        <v>165</v>
+      </c>
+      <c r="G352" s="7">
+        <v>17</v>
+      </c>
+      <c r="H352" t="s">
+        <v>73</v>
+      </c>
+      <c r="I352" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>83</v>
+      </c>
+      <c r="B353" t="s">
+        <v>12</v>
+      </c>
       <c r="C353" s="9"/>
-      <c r="D353" s="9"/>
-      <c r="E353" s="9"/>
-      <c r="G353" s="7"/>
-    </row>
-    <row r="354" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D353" s="9">
+        <v>5370</v>
+      </c>
+      <c r="E353" s="9">
+        <v>5670</v>
+      </c>
+      <c r="F353" t="s">
+        <v>165</v>
+      </c>
+      <c r="G353" s="7">
+        <v>17</v>
+      </c>
+      <c r="H353" t="s">
+        <v>73</v>
+      </c>
+      <c r="I353" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>128</v>
+      </c>
+      <c r="B354" t="s">
+        <v>12</v>
+      </c>
       <c r="C354" s="9"/>
-      <c r="D354" s="9"/>
-      <c r="E354" s="9"/>
-      <c r="G354" s="7"/>
-    </row>
-    <row r="355" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D354" s="9">
+        <v>5620</v>
+      </c>
+      <c r="E354" s="9">
+        <v>6130</v>
+      </c>
+      <c r="F354" t="s">
+        <v>165</v>
+      </c>
+      <c r="G354" s="7">
+        <v>17</v>
+      </c>
+      <c r="H354" t="s">
+        <v>73</v>
+      </c>
+      <c r="I354" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>129</v>
+      </c>
+      <c r="B355" t="s">
+        <v>12</v>
+      </c>
       <c r="C355" s="9"/>
-      <c r="D355" s="9"/>
-      <c r="E355" s="9"/>
-      <c r="G355" s="7"/>
-    </row>
-    <row r="356" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D355" s="9">
+        <v>5460</v>
+      </c>
+      <c r="E355" s="9">
+        <v>5820</v>
+      </c>
+      <c r="F355" t="s">
+        <v>165</v>
+      </c>
+      <c r="G355" s="7">
+        <v>17</v>
+      </c>
+      <c r="H355" t="s">
+        <v>73</v>
+      </c>
+      <c r="I355" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>130</v>
+      </c>
+      <c r="B356" t="s">
+        <v>12</v>
+      </c>
       <c r="C356" s="9"/>
-      <c r="D356" s="9"/>
-      <c r="E356" s="9"/>
-      <c r="G356" s="7"/>
-    </row>
-    <row r="357" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D356" s="9">
+        <v>5470</v>
+      </c>
+      <c r="E356" s="9">
+        <v>5870</v>
+      </c>
+      <c r="F356" t="s">
+        <v>165</v>
+      </c>
+      <c r="G356" s="7">
+        <v>17</v>
+      </c>
+      <c r="H356" t="s">
+        <v>73</v>
+      </c>
+      <c r="I356" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>131</v>
+      </c>
+      <c r="B357" t="s">
+        <v>12</v>
+      </c>
       <c r="C357" s="9"/>
-      <c r="D357" s="9"/>
-      <c r="E357" s="9"/>
-      <c r="G357" s="7"/>
-    </row>
-    <row r="358" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D357" s="9">
+        <v>5460</v>
+      </c>
+      <c r="E357" s="9">
+        <v>5820</v>
+      </c>
+      <c r="F357" t="s">
+        <v>165</v>
+      </c>
+      <c r="G357" s="7">
+        <v>17</v>
+      </c>
+      <c r="H357" t="s">
+        <v>73</v>
+      </c>
+      <c r="I357" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>87</v>
+      </c>
+      <c r="B358" t="s">
+        <v>12</v>
+      </c>
       <c r="C358" s="9"/>
-      <c r="D358" s="9"/>
-      <c r="E358" s="9"/>
-      <c r="G358" s="7"/>
-    </row>
-    <row r="359" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D358" s="9">
+        <v>5480</v>
+      </c>
+      <c r="E358" s="9">
+        <v>5840</v>
+      </c>
+      <c r="F358" t="s">
+        <v>165</v>
+      </c>
+      <c r="G358" s="7">
+        <v>17</v>
+      </c>
+      <c r="H358" t="s">
+        <v>73</v>
+      </c>
+      <c r="I358" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>88</v>
+      </c>
+      <c r="B359" t="s">
+        <v>12</v>
+      </c>
       <c r="C359" s="9"/>
-      <c r="D359" s="9"/>
-      <c r="E359" s="9"/>
-      <c r="G359" s="7"/>
-    </row>
-    <row r="360" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D359" s="9">
+        <v>5490</v>
+      </c>
+      <c r="E359" s="9">
+        <v>5840</v>
+      </c>
+      <c r="F359" t="s">
+        <v>165</v>
+      </c>
+      <c r="G359" s="7">
+        <v>17</v>
+      </c>
+      <c r="H359" t="s">
+        <v>73</v>
+      </c>
+      <c r="I359" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>94</v>
+      </c>
+      <c r="B360" t="s">
+        <v>164</v>
+      </c>
       <c r="C360" s="9"/>
-      <c r="D360" s="9"/>
-      <c r="E360" s="9"/>
-      <c r="G360" s="7"/>
-    </row>
-    <row r="361" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D360" s="9">
+        <v>5360</v>
+      </c>
+      <c r="E360" s="9">
+        <v>5560</v>
+      </c>
+      <c r="F360" t="s">
+        <v>165</v>
+      </c>
+      <c r="G360" s="7">
+        <v>18</v>
+      </c>
+      <c r="H360" t="s">
+        <v>78</v>
+      </c>
+      <c r="I360" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>80</v>
+      </c>
+      <c r="B361" t="s">
+        <v>164</v>
+      </c>
       <c r="C361" s="9"/>
-      <c r="D361" s="9"/>
-      <c r="E361" s="9"/>
-      <c r="G361" s="7"/>
-    </row>
-    <row r="362" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D361" s="9">
+        <v>5360</v>
+      </c>
+      <c r="E361" s="9">
+        <v>5560</v>
+      </c>
+      <c r="F361" t="s">
+        <v>165</v>
+      </c>
+      <c r="G361" s="7">
+        <v>18</v>
+      </c>
+      <c r="H361" t="s">
+        <v>78</v>
+      </c>
+      <c r="I361" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>108</v>
+      </c>
+      <c r="B362" t="s">
+        <v>164</v>
+      </c>
       <c r="C362" s="9"/>
-      <c r="D362" s="9"/>
-      <c r="E362" s="9"/>
-      <c r="G362" s="7"/>
-    </row>
-    <row r="363" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D362" s="9">
+        <v>5360</v>
+      </c>
+      <c r="E362" s="9">
+        <v>5560</v>
+      </c>
+      <c r="F362" t="s">
+        <v>165</v>
+      </c>
+      <c r="G362" s="7">
+        <v>18</v>
+      </c>
+      <c r="H362" t="s">
+        <v>78</v>
+      </c>
+      <c r="I362" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>144</v>
+      </c>
+      <c r="B363" t="s">
+        <v>164</v>
+      </c>
       <c r="C363" s="9"/>
-      <c r="D363" s="9"/>
-      <c r="E363" s="9"/>
-      <c r="G363" s="7"/>
-    </row>
-    <row r="364" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D363" s="9">
+        <v>5360</v>
+      </c>
+      <c r="E363" s="9">
+        <v>5560</v>
+      </c>
+      <c r="F363" t="s">
+        <v>165</v>
+      </c>
+      <c r="G363" s="7">
+        <v>18</v>
+      </c>
+      <c r="H363" t="s">
+        <v>78</v>
+      </c>
+      <c r="I363" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>106</v>
+      </c>
+      <c r="B364" t="s">
+        <v>164</v>
+      </c>
       <c r="C364" s="9"/>
-      <c r="D364" s="9"/>
-      <c r="E364" s="9"/>
-      <c r="G364" s="7"/>
-    </row>
-    <row r="365" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D364" s="9">
+        <v>5360</v>
+      </c>
+      <c r="E364" s="9">
+        <v>5560</v>
+      </c>
+      <c r="F364" t="s">
+        <v>165</v>
+      </c>
+      <c r="G364" s="7">
+        <v>18</v>
+      </c>
+      <c r="H364" t="s">
+        <v>78</v>
+      </c>
+      <c r="I364" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>109</v>
+      </c>
+      <c r="B365" t="s">
+        <v>164</v>
+      </c>
       <c r="C365" s="9"/>
-      <c r="D365" s="9"/>
-      <c r="E365" s="9"/>
-      <c r="G365" s="7"/>
-    </row>
-    <row r="366" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D365" s="9">
+        <v>5510</v>
+      </c>
+      <c r="E365" s="9">
+        <v>5810</v>
+      </c>
+      <c r="F365" t="s">
+        <v>165</v>
+      </c>
+      <c r="G365" s="7">
+        <v>18</v>
+      </c>
+      <c r="H365" t="s">
+        <v>78</v>
+      </c>
+      <c r="I365" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>110</v>
+      </c>
+      <c r="B366" t="s">
+        <v>164</v>
+      </c>
       <c r="C366" s="9"/>
-      <c r="D366" s="9"/>
-      <c r="E366" s="9"/>
-      <c r="G366" s="7"/>
-    </row>
-    <row r="367" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D366" s="9">
+        <v>5810</v>
+      </c>
+      <c r="E366" s="9">
+        <v>6460</v>
+      </c>
+      <c r="F366" t="s">
+        <v>165</v>
+      </c>
+      <c r="G366" s="7">
+        <v>18</v>
+      </c>
+      <c r="H366" t="s">
+        <v>78</v>
+      </c>
+      <c r="I366" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>85</v>
+      </c>
+      <c r="B367" t="s">
+        <v>164</v>
+      </c>
       <c r="C367" s="9"/>
-      <c r="D367" s="9"/>
-      <c r="E367" s="9"/>
-      <c r="G367" s="7"/>
-    </row>
-    <row r="368" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D367" s="9">
+        <v>5410</v>
+      </c>
+      <c r="E367" s="9">
+        <v>5660</v>
+      </c>
+      <c r="F367" t="s">
+        <v>165</v>
+      </c>
+      <c r="G367" s="7">
+        <v>18</v>
+      </c>
+      <c r="H367" t="s">
+        <v>78</v>
+      </c>
+      <c r="I367" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>111</v>
+      </c>
+      <c r="B368" t="s">
+        <v>164</v>
+      </c>
       <c r="C368" s="9"/>
-      <c r="D368" s="9"/>
-      <c r="E368" s="9"/>
-      <c r="G368" s="7"/>
-    </row>
-    <row r="369" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D368" s="9">
+        <v>5510</v>
+      </c>
+      <c r="E368" s="9">
+        <v>5810</v>
+      </c>
+      <c r="F368" t="s">
+        <v>165</v>
+      </c>
+      <c r="G368" s="7">
+        <v>18</v>
+      </c>
+      <c r="H368" t="s">
+        <v>78</v>
+      </c>
+      <c r="I368" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>112</v>
+      </c>
+      <c r="B369" t="s">
+        <v>164</v>
+      </c>
       <c r="C369" s="9"/>
-      <c r="D369" s="9"/>
-      <c r="E369" s="9"/>
-      <c r="G369" s="7"/>
-    </row>
-    <row r="370" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D369" s="9">
+        <v>5560</v>
+      </c>
+      <c r="E369" s="9">
+        <v>5960</v>
+      </c>
+      <c r="F369" t="s">
+        <v>165</v>
+      </c>
+      <c r="G369" s="7">
+        <v>18</v>
+      </c>
+      <c r="H369" t="s">
+        <v>78</v>
+      </c>
+      <c r="I369" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>115</v>
+      </c>
+      <c r="B370" t="s">
+        <v>164</v>
+      </c>
       <c r="C370" s="9"/>
-      <c r="D370" s="9"/>
-      <c r="E370" s="9"/>
-      <c r="G370" s="7"/>
-    </row>
-    <row r="371" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D370" s="9">
+        <v>5460</v>
+      </c>
+      <c r="E370" s="9">
+        <v>5760</v>
+      </c>
+      <c r="F370" t="s">
+        <v>165</v>
+      </c>
+      <c r="G370" s="7">
+        <v>18</v>
+      </c>
+      <c r="H370" t="s">
+        <v>78</v>
+      </c>
+      <c r="I370" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>86</v>
+      </c>
+      <c r="B371" t="s">
+        <v>164</v>
+      </c>
       <c r="C371" s="9"/>
-      <c r="D371" s="9"/>
-      <c r="E371" s="9"/>
-      <c r="G371" s="7"/>
-    </row>
-    <row r="372" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D371" s="9">
+        <v>5510</v>
+      </c>
+      <c r="E371" s="9">
+        <v>5810</v>
+      </c>
+      <c r="F371" t="s">
+        <v>165</v>
+      </c>
+      <c r="G371" s="7">
+        <v>18</v>
+      </c>
+      <c r="H371" t="s">
+        <v>78</v>
+      </c>
+      <c r="I371" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>116</v>
+      </c>
+      <c r="B372" t="s">
+        <v>164</v>
+      </c>
       <c r="C372" s="9"/>
-      <c r="D372" s="9"/>
-      <c r="E372" s="9"/>
-      <c r="G372" s="7"/>
-    </row>
-    <row r="373" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D372" s="9">
+        <v>5610</v>
+      </c>
+      <c r="E372" s="9">
+        <v>6060</v>
+      </c>
+      <c r="F372" t="s">
+        <v>165</v>
+      </c>
+      <c r="G372" s="7">
+        <v>18</v>
+      </c>
+      <c r="H372" t="s">
+        <v>78</v>
+      </c>
+      <c r="I372" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>162</v>
+      </c>
+      <c r="B373" t="s">
+        <v>164</v>
+      </c>
       <c r="C373" s="9"/>
-      <c r="D373" s="9"/>
-      <c r="E373" s="9"/>
-      <c r="G373" s="7"/>
-    </row>
-    <row r="374" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D373" s="9">
+        <v>5610</v>
+      </c>
+      <c r="E373" s="9">
+        <v>6060</v>
+      </c>
+      <c r="F373" t="s">
+        <v>165</v>
+      </c>
+      <c r="G373" s="7">
+        <v>18</v>
+      </c>
+      <c r="H373" t="s">
+        <v>78</v>
+      </c>
+      <c r="I373" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>117</v>
+      </c>
+      <c r="B374" t="s">
+        <v>164</v>
+      </c>
       <c r="C374" s="9"/>
-      <c r="D374" s="9"/>
-      <c r="E374" s="9"/>
-      <c r="G374" s="7"/>
-    </row>
-    <row r="375" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D374" s="9">
+        <v>5710</v>
+      </c>
+      <c r="E374" s="9">
+        <v>6260</v>
+      </c>
+      <c r="F374" t="s">
+        <v>165</v>
+      </c>
+      <c r="G374" s="7">
+        <v>18</v>
+      </c>
+      <c r="H374" t="s">
+        <v>78</v>
+      </c>
+      <c r="I374" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>119</v>
+      </c>
+      <c r="B375" t="s">
+        <v>164</v>
+      </c>
       <c r="C375" s="9"/>
-      <c r="D375" s="9"/>
-      <c r="E375" s="9"/>
-      <c r="G375" s="7"/>
-    </row>
-    <row r="376" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D375" s="9">
+        <v>5510</v>
+      </c>
+      <c r="E375" s="9">
+        <v>5860</v>
+      </c>
+      <c r="F375" t="s">
+        <v>165</v>
+      </c>
+      <c r="G375" s="7">
+        <v>18</v>
+      </c>
+      <c r="H375" t="s">
+        <v>78</v>
+      </c>
+      <c r="I375" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>121</v>
+      </c>
+      <c r="B376" t="s">
+        <v>164</v>
+      </c>
       <c r="C376" s="9"/>
-      <c r="D376" s="9"/>
-      <c r="E376" s="9"/>
-      <c r="G376" s="7"/>
-    </row>
-    <row r="377" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D376" s="9">
+        <v>5510</v>
+      </c>
+      <c r="E376" s="9">
+        <v>5810</v>
+      </c>
+      <c r="F376" t="s">
+        <v>165</v>
+      </c>
+      <c r="G376" s="7">
+        <v>18</v>
+      </c>
+      <c r="H376" t="s">
+        <v>78</v>
+      </c>
+      <c r="I376" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>122</v>
+      </c>
+      <c r="B377" t="s">
+        <v>164</v>
+      </c>
       <c r="C377" s="9"/>
-      <c r="D377" s="9"/>
-      <c r="E377" s="9"/>
-      <c r="G377" s="7"/>
-    </row>
-    <row r="378" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D377" s="9">
+        <v>5560</v>
+      </c>
+      <c r="E377" s="9">
+        <v>5960</v>
+      </c>
+      <c r="F377" t="s">
+        <v>165</v>
+      </c>
+      <c r="G377" s="7">
+        <v>18</v>
+      </c>
+      <c r="H377" t="s">
+        <v>78</v>
+      </c>
+      <c r="I377" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>81</v>
+      </c>
+      <c r="B378" t="s">
+        <v>164</v>
+      </c>
       <c r="C378" s="9"/>
-      <c r="D378" s="9"/>
-      <c r="E378" s="9"/>
-      <c r="G378" s="7"/>
-    </row>
-    <row r="379" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D378" s="9">
+        <v>5460</v>
+      </c>
+      <c r="E378" s="9">
+        <v>5760</v>
+      </c>
+      <c r="F378" t="s">
+        <v>165</v>
+      </c>
+      <c r="G378" s="7">
+        <v>18</v>
+      </c>
+      <c r="H378" t="s">
+        <v>78</v>
+      </c>
+      <c r="I378" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>89</v>
+      </c>
+      <c r="B379" t="s">
+        <v>164</v>
+      </c>
       <c r="C379" s="9"/>
-      <c r="D379" s="9"/>
-      <c r="E379" s="9"/>
-      <c r="G379" s="7"/>
-    </row>
-    <row r="380" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D379" s="9">
+        <v>5510</v>
+      </c>
+      <c r="E379" s="9">
+        <v>5810</v>
+      </c>
+      <c r="F379" t="s">
+        <v>165</v>
+      </c>
+      <c r="G379" s="7">
+        <v>18</v>
+      </c>
+      <c r="H379" t="s">
+        <v>78</v>
+      </c>
+      <c r="I379" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>90</v>
+      </c>
+      <c r="B380" t="s">
+        <v>164</v>
+      </c>
       <c r="C380" s="9"/>
-      <c r="D380" s="9"/>
-      <c r="E380" s="9"/>
-      <c r="G380" s="7"/>
-    </row>
-    <row r="381" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D380" s="9">
+        <v>5510</v>
+      </c>
+      <c r="E380" s="9">
+        <v>5810</v>
+      </c>
+      <c r="F380" t="s">
+        <v>165</v>
+      </c>
+      <c r="G380" s="7">
+        <v>18</v>
+      </c>
+      <c r="H380" t="s">
+        <v>78</v>
+      </c>
+      <c r="I380" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>82</v>
+      </c>
+      <c r="B381" t="s">
+        <v>164</v>
+      </c>
       <c r="C381" s="9"/>
-      <c r="D381" s="9"/>
-      <c r="E381" s="9"/>
-      <c r="G381" s="7"/>
-    </row>
-    <row r="382" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D381" s="9">
+        <v>5410</v>
+      </c>
+      <c r="E381" s="9">
+        <v>5660</v>
+      </c>
+      <c r="F381" t="s">
+        <v>165</v>
+      </c>
+      <c r="G381" s="7">
+        <v>18</v>
+      </c>
+      <c r="H381" t="s">
+        <v>78</v>
+      </c>
+      <c r="I381" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>95</v>
+      </c>
+      <c r="B382" t="s">
+        <v>164</v>
+      </c>
       <c r="C382" s="9"/>
-      <c r="D382" s="9"/>
-      <c r="E382" s="9"/>
-      <c r="G382" s="7"/>
-    </row>
-    <row r="383" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D382" s="9">
+        <v>5360</v>
+      </c>
+      <c r="E382" s="9">
+        <v>5560</v>
+      </c>
+      <c r="F382" t="s">
+        <v>165</v>
+      </c>
+      <c r="G382" s="7">
+        <v>18</v>
+      </c>
+      <c r="H382" t="s">
+        <v>78</v>
+      </c>
+      <c r="I382" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>124</v>
+      </c>
+      <c r="B383" t="s">
+        <v>164</v>
+      </c>
       <c r="C383" s="9"/>
-      <c r="D383" s="9"/>
-      <c r="E383" s="9"/>
-      <c r="G383" s="7"/>
-    </row>
-    <row r="384" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D383" s="9">
+        <v>5510</v>
+      </c>
+      <c r="E383" s="9">
+        <v>5810</v>
+      </c>
+      <c r="F383" t="s">
+        <v>165</v>
+      </c>
+      <c r="G383" s="7">
+        <v>18</v>
+      </c>
+      <c r="H383" t="s">
+        <v>78</v>
+      </c>
+      <c r="I383" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>125</v>
+      </c>
+      <c r="B384" t="s">
+        <v>164</v>
+      </c>
       <c r="C384" s="9"/>
-      <c r="D384" s="9"/>
-      <c r="E384" s="9"/>
-      <c r="G384" s="7"/>
-    </row>
-    <row r="385" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D384" s="9">
+        <v>5660</v>
+      </c>
+      <c r="E384" s="9">
+        <v>6160</v>
+      </c>
+      <c r="F384" t="s">
+        <v>165</v>
+      </c>
+      <c r="G384" s="7">
+        <v>18</v>
+      </c>
+      <c r="H384" t="s">
+        <v>78</v>
+      </c>
+      <c r="I384" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>163</v>
+      </c>
+      <c r="B385" t="s">
+        <v>164</v>
+      </c>
       <c r="C385" s="9"/>
-      <c r="D385" s="9"/>
-      <c r="E385" s="9"/>
-      <c r="G385" s="7"/>
-    </row>
-    <row r="386" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D385" s="9">
+        <v>5510</v>
+      </c>
+      <c r="E385" s="9">
+        <v>5810</v>
+      </c>
+      <c r="F385" t="s">
+        <v>165</v>
+      </c>
+      <c r="G385" s="7">
+        <v>18</v>
+      </c>
+      <c r="H385" t="s">
+        <v>78</v>
+      </c>
+      <c r="I385" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>84</v>
+      </c>
+      <c r="B386" t="s">
+        <v>164</v>
+      </c>
       <c r="C386" s="9"/>
-      <c r="D386" s="9"/>
-      <c r="E386" s="9"/>
-      <c r="G386" s="7"/>
-    </row>
-    <row r="387" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D386" s="9">
+        <v>5360</v>
+      </c>
+      <c r="E386" s="9">
+        <v>5560</v>
+      </c>
+      <c r="F386" t="s">
+        <v>165</v>
+      </c>
+      <c r="G386" s="7">
+        <v>18</v>
+      </c>
+      <c r="H386" t="s">
+        <v>78</v>
+      </c>
+      <c r="I386" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>100</v>
+      </c>
+      <c r="B387" t="s">
+        <v>164</v>
+      </c>
       <c r="C387" s="9"/>
-      <c r="D387" s="9"/>
-      <c r="E387" s="9"/>
-      <c r="G387" s="7"/>
-    </row>
-    <row r="388" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D387" s="9">
+        <v>5410</v>
+      </c>
+      <c r="E387" s="9">
+        <v>5660</v>
+      </c>
+      <c r="F387" t="s">
+        <v>165</v>
+      </c>
+      <c r="G387" s="7">
+        <v>18</v>
+      </c>
+      <c r="H387" t="s">
+        <v>78</v>
+      </c>
+      <c r="I387" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>83</v>
+      </c>
+      <c r="B388" t="s">
+        <v>164</v>
+      </c>
       <c r="C388" s="9"/>
-      <c r="D388" s="9"/>
-      <c r="E388" s="9"/>
-      <c r="G388" s="7"/>
-    </row>
-    <row r="389" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D388" s="9">
+        <v>5410</v>
+      </c>
+      <c r="E388" s="9">
+        <v>5660</v>
+      </c>
+      <c r="F388" t="s">
+        <v>165</v>
+      </c>
+      <c r="G388" s="7">
+        <v>18</v>
+      </c>
+      <c r="H388" t="s">
+        <v>78</v>
+      </c>
+      <c r="I388" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>129</v>
+      </c>
+      <c r="B389" t="s">
+        <v>164</v>
+      </c>
       <c r="C389" s="9"/>
-      <c r="D389" s="9"/>
-      <c r="E389" s="9"/>
-      <c r="G389" s="7"/>
-    </row>
-    <row r="390" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D389" s="9">
+        <v>5560</v>
+      </c>
+      <c r="E389" s="9">
+        <v>5960</v>
+      </c>
+      <c r="F389" t="s">
+        <v>165</v>
+      </c>
+      <c r="G389" s="7">
+        <v>18</v>
+      </c>
+      <c r="H389" t="s">
+        <v>78</v>
+      </c>
+      <c r="I389" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>147</v>
+      </c>
+      <c r="B390" t="s">
+        <v>164</v>
+      </c>
       <c r="C390" s="9"/>
-      <c r="D390" s="9"/>
-      <c r="E390" s="9"/>
-      <c r="G390" s="7"/>
-    </row>
-    <row r="391" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D390" s="9">
+        <v>5610</v>
+      </c>
+      <c r="E390" s="9">
+        <v>6060</v>
+      </c>
+      <c r="F390" t="s">
+        <v>165</v>
+      </c>
+      <c r="G390" s="7">
+        <v>18</v>
+      </c>
+      <c r="H390" t="s">
+        <v>78</v>
+      </c>
+      <c r="I390" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>131</v>
+      </c>
+      <c r="B391" t="s">
+        <v>164</v>
+      </c>
       <c r="C391" s="9"/>
-      <c r="D391" s="9"/>
-      <c r="E391" s="9"/>
-      <c r="G391" s="7"/>
-    </row>
-    <row r="392" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D391" s="9">
+        <v>5560</v>
+      </c>
+      <c r="E391" s="9">
+        <v>5960</v>
+      </c>
+      <c r="F391" t="s">
+        <v>165</v>
+      </c>
+      <c r="G391" s="7">
+        <v>18</v>
+      </c>
+      <c r="H391" t="s">
+        <v>78</v>
+      </c>
+      <c r="I391" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>87</v>
+      </c>
+      <c r="B392" t="s">
+        <v>164</v>
+      </c>
       <c r="C392" s="9"/>
-      <c r="D392" s="9"/>
-      <c r="E392" s="9"/>
-      <c r="G392" s="7"/>
-    </row>
-    <row r="393" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D392" s="9">
+        <v>5510</v>
+      </c>
+      <c r="E392" s="9">
+        <v>5810</v>
+      </c>
+      <c r="F392" t="s">
+        <v>165</v>
+      </c>
+      <c r="G392" s="7">
+        <v>18</v>
+      </c>
+      <c r="H392" t="s">
+        <v>78</v>
+      </c>
+      <c r="I392" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>88</v>
+      </c>
+      <c r="B393" t="s">
+        <v>164</v>
+      </c>
       <c r="C393" s="9"/>
-      <c r="D393" s="9"/>
-      <c r="E393" s="9"/>
-      <c r="G393" s="7"/>
-    </row>
-    <row r="394" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C394" s="9"/>
-      <c r="D394" s="9"/>
-      <c r="E394" s="9"/>
-      <c r="G394" s="7"/>
-    </row>
-    <row r="395" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C395" s="9"/>
-      <c r="D395" s="9"/>
-      <c r="E395" s="9"/>
-      <c r="G395" s="7"/>
-    </row>
-    <row r="396" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D393" s="9">
+        <v>5510</v>
+      </c>
+      <c r="E393" s="9">
+        <v>5810</v>
+      </c>
+      <c r="F393" t="s">
+        <v>165</v>
+      </c>
+      <c r="G393" s="7">
+        <v>18</v>
+      </c>
+      <c r="H393" t="s">
+        <v>78</v>
+      </c>
+      <c r="I393" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>94</v>
+      </c>
+      <c r="B394" t="s">
+        <v>12</v>
+      </c>
+      <c r="C394" s="9">
+        <v>4660</v>
+      </c>
+      <c r="D394" s="9">
+        <v>5460</v>
+      </c>
+      <c r="E394" s="9">
+        <v>5760</v>
+      </c>
+      <c r="F394" t="s">
+        <v>165</v>
+      </c>
+      <c r="G394" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="H394" t="s">
+        <v>76</v>
+      </c>
+      <c r="I394" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>80</v>
+      </c>
+      <c r="B395" t="s">
+        <v>12</v>
+      </c>
+      <c r="C395" s="9">
+        <v>4660</v>
+      </c>
+      <c r="D395" s="9">
+        <v>5460</v>
+      </c>
+      <c r="E395" s="9">
+        <v>5740</v>
+      </c>
+      <c r="F395" t="s">
+        <v>165</v>
+      </c>
+      <c r="G395" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="H395" t="s">
+        <v>76</v>
+      </c>
+      <c r="I395" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>108</v>
+      </c>
+      <c r="B396" t="s">
+        <v>12</v>
+      </c>
       <c r="C396" s="9"/>
-      <c r="D396" s="9"/>
-      <c r="E396" s="9"/>
-      <c r="G396" s="7"/>
-    </row>
-    <row r="397" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D396" s="9">
+        <v>5460</v>
+      </c>
+      <c r="E396" s="9">
+        <v>5760</v>
+      </c>
+      <c r="F396" t="s">
+        <v>165</v>
+      </c>
+      <c r="G396" s="7">
+        <v>20</v>
+      </c>
+      <c r="H396" t="s">
+        <v>76</v>
+      </c>
+      <c r="I396" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>144</v>
+      </c>
+      <c r="B397" t="s">
+        <v>12</v>
+      </c>
       <c r="C397" s="9"/>
-      <c r="D397" s="9"/>
-      <c r="E397" s="9"/>
-      <c r="G397" s="7"/>
-    </row>
-    <row r="398" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D397" s="9">
+        <v>5460</v>
+      </c>
+      <c r="E397" s="9">
+        <v>5760</v>
+      </c>
+      <c r="F397" t="s">
+        <v>165</v>
+      </c>
+      <c r="G397" s="7">
+        <v>20</v>
+      </c>
+      <c r="H397" t="s">
+        <v>76</v>
+      </c>
+      <c r="I397" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>106</v>
+      </c>
+      <c r="B398" t="s">
+        <v>12</v>
+      </c>
       <c r="C398" s="9"/>
-      <c r="D398" s="9"/>
-      <c r="E398" s="9"/>
-      <c r="G398" s="7"/>
-    </row>
-    <row r="399" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D398" s="9">
+        <v>5510</v>
+      </c>
+      <c r="E398" s="9">
+        <v>5860</v>
+      </c>
+      <c r="F398" t="s">
+        <v>165</v>
+      </c>
+      <c r="G398" s="7">
+        <v>20</v>
+      </c>
+      <c r="H398" t="s">
+        <v>76</v>
+      </c>
+      <c r="I398" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>109</v>
+      </c>
+      <c r="B399" t="s">
+        <v>12</v>
+      </c>
       <c r="C399" s="9"/>
-      <c r="D399" s="9"/>
-      <c r="E399" s="9"/>
-      <c r="G399" s="7"/>
-    </row>
-    <row r="400" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D399" s="9">
+        <v>5610</v>
+      </c>
+      <c r="E399" s="9">
+        <v>6060</v>
+      </c>
+      <c r="F399" t="s">
+        <v>165</v>
+      </c>
+      <c r="G399" s="7">
+        <v>20</v>
+      </c>
+      <c r="H399" t="s">
+        <v>76</v>
+      </c>
+      <c r="I399" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>111</v>
+      </c>
+      <c r="B400" t="s">
+        <v>12</v>
+      </c>
       <c r="C400" s="9"/>
-      <c r="D400" s="9"/>
-      <c r="E400" s="9"/>
-      <c r="G400" s="7"/>
-    </row>
-    <row r="401" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D400" s="9">
+        <v>5560</v>
+      </c>
+      <c r="E400" s="9">
+        <v>5960</v>
+      </c>
+      <c r="F400" t="s">
+        <v>165</v>
+      </c>
+      <c r="G400" s="7">
+        <v>20</v>
+      </c>
+      <c r="H400" t="s">
+        <v>76</v>
+      </c>
+      <c r="I400" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>112</v>
+      </c>
+      <c r="B401" t="s">
+        <v>12</v>
+      </c>
       <c r="C401" s="9"/>
-      <c r="D401" s="9"/>
-      <c r="E401" s="9"/>
-      <c r="G401" s="7"/>
-    </row>
-    <row r="402" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D401" s="9">
+        <v>5760</v>
+      </c>
+      <c r="E401" s="9">
+        <v>6160</v>
+      </c>
+      <c r="F401" t="s">
+        <v>165</v>
+      </c>
+      <c r="G401" s="7">
+        <v>20</v>
+      </c>
+      <c r="H401" t="s">
+        <v>76</v>
+      </c>
+      <c r="I401" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>113</v>
+      </c>
+      <c r="B402" t="s">
+        <v>12</v>
+      </c>
       <c r="C402" s="9"/>
-      <c r="D402" s="9"/>
-      <c r="E402" s="9"/>
-      <c r="G402" s="7"/>
-    </row>
-    <row r="403" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D402" s="9">
+        <v>5560</v>
+      </c>
+      <c r="E402" s="9">
+        <v>5960</v>
+      </c>
+      <c r="F402" t="s">
+        <v>165</v>
+      </c>
+      <c r="G402" s="7">
+        <v>20</v>
+      </c>
+      <c r="H402" t="s">
+        <v>76</v>
+      </c>
+      <c r="I402" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>114</v>
+      </c>
+      <c r="B403" t="s">
+        <v>12</v>
+      </c>
       <c r="C403" s="9"/>
-      <c r="D403" s="9"/>
-      <c r="E403" s="9"/>
-      <c r="G403" s="7"/>
-    </row>
-    <row r="404" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D403" s="9">
+        <v>5560</v>
+      </c>
+      <c r="E403" s="9">
+        <v>5960</v>
+      </c>
+      <c r="F403" t="s">
+        <v>165</v>
+      </c>
+      <c r="G403" s="7">
+        <v>20</v>
+      </c>
+      <c r="H403" t="s">
+        <v>76</v>
+      </c>
+      <c r="I403" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>115</v>
+      </c>
+      <c r="B404" t="s">
+        <v>12</v>
+      </c>
       <c r="C404" s="9"/>
-      <c r="D404" s="9"/>
-      <c r="E404" s="9"/>
-      <c r="G404" s="7"/>
-    </row>
-    <row r="405" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D404" s="9">
+        <v>5560</v>
+      </c>
+      <c r="E404" s="9">
+        <v>5960</v>
+      </c>
+      <c r="F404" t="s">
+        <v>165</v>
+      </c>
+      <c r="G404" s="7">
+        <v>20</v>
+      </c>
+      <c r="H404" t="s">
+        <v>76</v>
+      </c>
+      <c r="I404" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>86</v>
+      </c>
+      <c r="B405" t="s">
+        <v>12</v>
+      </c>
       <c r="C405" s="9"/>
-      <c r="D405" s="9"/>
-      <c r="E405" s="9"/>
-      <c r="G405" s="7"/>
-    </row>
-    <row r="406" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D405" s="9">
+        <v>5560</v>
+      </c>
+      <c r="E405" s="9">
+        <v>5960</v>
+      </c>
+      <c r="F405" t="s">
+        <v>165</v>
+      </c>
+      <c r="G405" s="7">
+        <v>20</v>
+      </c>
+      <c r="H405" t="s">
+        <v>76</v>
+      </c>
+      <c r="I405" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>162</v>
+      </c>
+      <c r="B406" t="s">
+        <v>12</v>
+      </c>
       <c r="C406" s="9"/>
-      <c r="D406" s="9"/>
-      <c r="E406" s="9"/>
-      <c r="G406" s="7"/>
-    </row>
-    <row r="407" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D406" s="9">
+        <v>5560</v>
+      </c>
+      <c r="E406" s="9">
+        <v>5960</v>
+      </c>
+      <c r="F406" t="s">
+        <v>165</v>
+      </c>
+      <c r="G406" s="7">
+        <v>20</v>
+      </c>
+      <c r="H406" t="s">
+        <v>76</v>
+      </c>
+      <c r="I406" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>121</v>
+      </c>
+      <c r="B407" t="s">
+        <v>12</v>
+      </c>
       <c r="C407" s="9"/>
-      <c r="D407" s="9"/>
-      <c r="E407" s="9"/>
-      <c r="G407" s="7"/>
-    </row>
-    <row r="408" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D407" s="9">
+        <v>5560</v>
+      </c>
+      <c r="E407" s="9">
+        <v>5960</v>
+      </c>
+      <c r="F407" t="s">
+        <v>165</v>
+      </c>
+      <c r="G407" s="7">
+        <v>20</v>
+      </c>
+      <c r="H407" t="s">
+        <v>76</v>
+      </c>
+      <c r="I407" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>89</v>
+      </c>
+      <c r="B408" t="s">
+        <v>12</v>
+      </c>
       <c r="C408" s="9"/>
-      <c r="D408" s="9"/>
-      <c r="E408" s="9"/>
-      <c r="G408" s="7"/>
-    </row>
-    <row r="409" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D408" s="9">
+        <v>5560</v>
+      </c>
+      <c r="E408" s="9">
+        <v>5960</v>
+      </c>
+      <c r="F408" t="s">
+        <v>165</v>
+      </c>
+      <c r="G408" s="7">
+        <v>20</v>
+      </c>
+      <c r="H408" t="s">
+        <v>76</v>
+      </c>
+      <c r="I408" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>123</v>
+      </c>
+      <c r="B409" t="s">
+        <v>12</v>
+      </c>
       <c r="C409" s="9"/>
-      <c r="D409" s="9"/>
-      <c r="E409" s="9"/>
-      <c r="G409" s="7"/>
-    </row>
-    <row r="410" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D409" s="9">
+        <v>5560</v>
+      </c>
+      <c r="E409" s="9">
+        <v>5960</v>
+      </c>
+      <c r="F409" t="s">
+        <v>165</v>
+      </c>
+      <c r="G409" s="7">
+        <v>20</v>
+      </c>
+      <c r="H409" t="s">
+        <v>76</v>
+      </c>
+      <c r="I409" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>90</v>
+      </c>
+      <c r="B410" t="s">
+        <v>12</v>
+      </c>
       <c r="C410" s="9"/>
-      <c r="D410" s="9"/>
-      <c r="E410" s="9"/>
-      <c r="G410" s="7"/>
-    </row>
-    <row r="411" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C411" s="9"/>
-      <c r="D411" s="9"/>
-      <c r="E411" s="9"/>
-      <c r="G411" s="7"/>
-    </row>
-    <row r="412" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C412" s="9"/>
-      <c r="D412" s="9"/>
-      <c r="E412" s="9"/>
-      <c r="G412" s="7"/>
-    </row>
-    <row r="413" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D410" s="9">
+        <v>5610</v>
+      </c>
+      <c r="E410" s="9">
+        <v>6060</v>
+      </c>
+      <c r="F410" t="s">
+        <v>165</v>
+      </c>
+      <c r="G410" s="7">
+        <v>20</v>
+      </c>
+      <c r="H410" t="s">
+        <v>76</v>
+      </c>
+      <c r="I410" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>82</v>
+      </c>
+      <c r="B411" t="s">
+        <v>12</v>
+      </c>
+      <c r="C411" s="9">
+        <v>4660</v>
+      </c>
+      <c r="D411" s="9">
+        <v>5460</v>
+      </c>
+      <c r="E411" s="9">
+        <v>5760</v>
+      </c>
+      <c r="F411" t="s">
+        <v>165</v>
+      </c>
+      <c r="G411" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="H411" t="s">
+        <v>76</v>
+      </c>
+      <c r="I411" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>95</v>
+      </c>
+      <c r="B412" t="s">
+        <v>12</v>
+      </c>
+      <c r="C412" s="9">
+        <v>4660</v>
+      </c>
+      <c r="D412" s="9">
+        <v>5460</v>
+      </c>
+      <c r="E412" s="9">
+        <v>5760</v>
+      </c>
+      <c r="F412" t="s">
+        <v>165</v>
+      </c>
+      <c r="G412" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="H412" t="s">
+        <v>76</v>
+      </c>
+      <c r="I412" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>124</v>
+      </c>
+      <c r="B413" t="s">
+        <v>12</v>
+      </c>
       <c r="C413" s="9"/>
-      <c r="D413" s="9"/>
-      <c r="E413" s="9"/>
-      <c r="G413" s="7"/>
-    </row>
-    <row r="414" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D413" s="9">
+        <v>5560</v>
+      </c>
+      <c r="E413" s="9">
+        <v>5960</v>
+      </c>
+      <c r="F413" t="s">
+        <v>165</v>
+      </c>
+      <c r="G413" s="7">
+        <v>20</v>
+      </c>
+      <c r="H413" t="s">
+        <v>76</v>
+      </c>
+      <c r="I413" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>163</v>
+      </c>
+      <c r="B414" t="s">
+        <v>12</v>
+      </c>
       <c r="C414" s="9"/>
-      <c r="D414" s="9"/>
-      <c r="E414" s="9"/>
-      <c r="G414" s="7"/>
-    </row>
-    <row r="415" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D414" s="9">
+        <v>5560</v>
+      </c>
+      <c r="E414" s="9">
+        <v>5960</v>
+      </c>
+      <c r="F414" t="s">
+        <v>165</v>
+      </c>
+      <c r="G414" s="7">
+        <v>20</v>
+      </c>
+      <c r="H414" t="s">
+        <v>76</v>
+      </c>
+      <c r="I414" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>84</v>
+      </c>
+      <c r="B415" t="s">
+        <v>12</v>
+      </c>
       <c r="C415" s="9"/>
-      <c r="D415" s="9"/>
-      <c r="E415" s="9"/>
-      <c r="G415" s="7"/>
-    </row>
-    <row r="416" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D415" s="9">
+        <v>5610</v>
+      </c>
+      <c r="E415" s="9">
+        <v>6060</v>
+      </c>
+      <c r="F415" t="s">
+        <v>165</v>
+      </c>
+      <c r="G415" s="7">
+        <v>20</v>
+      </c>
+      <c r="H415" t="s">
+        <v>76</v>
+      </c>
+      <c r="I415" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A416" t="s">
+        <v>87</v>
+      </c>
+      <c r="B416" t="s">
+        <v>12</v>
+      </c>
       <c r="C416" s="9"/>
-      <c r="D416" s="9"/>
-      <c r="E416" s="9"/>
-      <c r="G416" s="7"/>
-    </row>
-    <row r="417" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D416" s="9">
+        <v>5560</v>
+      </c>
+      <c r="E416" s="9">
+        <v>5960</v>
+      </c>
+      <c r="F416" t="s">
+        <v>165</v>
+      </c>
+      <c r="G416" s="7">
+        <v>20</v>
+      </c>
+      <c r="H416" t="s">
+        <v>76</v>
+      </c>
+      <c r="I416" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>88</v>
+      </c>
+      <c r="B417" t="s">
+        <v>12</v>
+      </c>
       <c r="C417" s="9"/>
-      <c r="D417" s="9"/>
-      <c r="E417" s="9"/>
-      <c r="G417" s="7"/>
-    </row>
-    <row r="418" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D417" s="9">
+        <v>5560</v>
+      </c>
+      <c r="E417" s="9">
+        <v>5960</v>
+      </c>
+      <c r="F417" t="s">
+        <v>165</v>
+      </c>
+      <c r="G417" s="7">
+        <v>20</v>
+      </c>
+      <c r="H417" t="s">
+        <v>76</v>
+      </c>
+      <c r="I417" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A418" t="s">
+        <v>94</v>
+      </c>
+      <c r="B418" t="s">
+        <v>12</v>
+      </c>
       <c r="C418" s="9"/>
-      <c r="D418" s="9"/>
-      <c r="E418" s="9"/>
-      <c r="G418" s="7"/>
-    </row>
-    <row r="419" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D418" s="9">
+        <v>5300</v>
+      </c>
+      <c r="E418" s="9">
+        <v>5600</v>
+      </c>
+      <c r="F418" t="s">
+        <v>165</v>
+      </c>
+      <c r="G418" s="7">
+        <v>21</v>
+      </c>
+      <c r="H418" t="s">
+        <v>92</v>
+      </c>
+      <c r="I418" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A419" t="s">
+        <v>80</v>
+      </c>
+      <c r="B419" t="s">
+        <v>12</v>
+      </c>
       <c r="C419" s="9"/>
-      <c r="D419" s="9"/>
-      <c r="E419" s="9"/>
-      <c r="G419" s="7"/>
-    </row>
-    <row r="420" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D419" s="9">
+        <v>5300</v>
+      </c>
+      <c r="E419" s="9">
+        <v>5600</v>
+      </c>
+      <c r="F419" t="s">
+        <v>165</v>
+      </c>
+      <c r="G419" s="7">
+        <v>21</v>
+      </c>
+      <c r="H419" t="s">
+        <v>92</v>
+      </c>
+      <c r="I419" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>81</v>
+      </c>
+      <c r="B420" t="s">
+        <v>12</v>
+      </c>
       <c r="C420" s="9"/>
-      <c r="D420" s="9"/>
-      <c r="E420" s="9"/>
-      <c r="G420" s="7"/>
-    </row>
-    <row r="421" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D420" s="9">
+        <v>5350</v>
+      </c>
+      <c r="E420" s="9">
+        <v>5650</v>
+      </c>
+      <c r="F420" t="s">
+        <v>165</v>
+      </c>
+      <c r="G420" s="7">
+        <v>21</v>
+      </c>
+      <c r="H420" t="s">
+        <v>92</v>
+      </c>
+      <c r="I420" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>100</v>
+      </c>
+      <c r="B421" t="s">
+        <v>12</v>
+      </c>
       <c r="C421" s="9"/>
-      <c r="D421" s="9"/>
-      <c r="E421" s="9"/>
-      <c r="G421" s="7"/>
-    </row>
-    <row r="422" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D421" s="9">
+        <v>5300</v>
+      </c>
+      <c r="E421" s="9">
+        <v>5600</v>
+      </c>
+      <c r="F421" t="s">
+        <v>165</v>
+      </c>
+      <c r="G421" s="7">
+        <v>21</v>
+      </c>
+      <c r="H421" t="s">
+        <v>92</v>
+      </c>
+      <c r="I421" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>117</v>
+      </c>
+      <c r="B422" t="s">
+        <v>12</v>
+      </c>
       <c r="C422" s="9"/>
-      <c r="D422" s="9"/>
-      <c r="E422" s="9"/>
-      <c r="G422" s="7"/>
-    </row>
-    <row r="423" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D422" s="9">
+        <v>5400</v>
+      </c>
+      <c r="E422" s="9">
+        <v>5800</v>
+      </c>
+      <c r="F422" t="s">
+        <v>165</v>
+      </c>
+      <c r="G422" s="7">
+        <v>21</v>
+      </c>
+      <c r="H422" t="s">
+        <v>92</v>
+      </c>
+      <c r="I422" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A423" t="s">
+        <v>85</v>
+      </c>
+      <c r="B423" t="s">
+        <v>12</v>
+      </c>
       <c r="C423" s="9"/>
-      <c r="D423" s="9"/>
-      <c r="E423" s="9"/>
-      <c r="G423" s="7"/>
-    </row>
-    <row r="424" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D423" s="9">
+        <v>5400</v>
+      </c>
+      <c r="E423" s="9">
+        <v>5700</v>
+      </c>
+      <c r="F423" t="s">
+        <v>165</v>
+      </c>
+      <c r="G423" s="7">
+        <v>21</v>
+      </c>
+      <c r="H423" t="s">
+        <v>92</v>
+      </c>
+      <c r="I423" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C424" s="9"/>
       <c r="D424" s="9"/>
       <c r="E424" s="9"/>
       <c r="G424" s="7"/>
     </row>
-    <row r="425" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C425" s="9"/>
       <c r="D425" s="9"/>
       <c r="E425" s="9"/>
       <c r="G425" s="7"/>
     </row>
-    <row r="426" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C426" s="9"/>
       <c r="D426" s="9"/>
       <c r="E426" s="9"/>
       <c r="G426" s="7"/>
     </row>
-    <row r="427" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C427" s="9"/>
       <c r="D427" s="9"/>
       <c r="E427" s="9"/>
       <c r="G427" s="7"/>
     </row>
-    <row r="428" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C428" s="9"/>
       <c r="D428" s="9"/>
       <c r="E428" s="9"/>
       <c r="G428" s="7"/>
     </row>
-    <row r="429" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C429" s="9"/>
       <c r="D429" s="9"/>
       <c r="E429" s="9"/>
       <c r="G429" s="7"/>
     </row>
-    <row r="430" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C430" s="9"/>
       <c r="D430" s="9"/>
       <c r="E430" s="9"/>
       <c r="G430" s="7"/>
     </row>
-    <row r="431" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C431" s="9"/>
       <c r="D431" s="9"/>
       <c r="E431" s="9"/>
       <c r="G431" s="7"/>
     </row>
-    <row r="432" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C432" s="9"/>
       <c r="D432" s="9"/>
       <c r="E432" s="9"/>
@@ -15090,240 +17252,6 @@
       <c r="D1161" s="9"/>
       <c r="E1161" s="9"/>
       <c r="G1161" s="7"/>
-    </row>
-    <row r="1162" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1162" s="9"/>
-      <c r="D1162" s="9"/>
-      <c r="E1162" s="9"/>
-      <c r="G1162" s="7"/>
-    </row>
-    <row r="1163" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1163" s="9"/>
-      <c r="D1163" s="9"/>
-      <c r="E1163" s="9"/>
-      <c r="G1163" s="7"/>
-    </row>
-    <row r="1164" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1164" s="9"/>
-      <c r="D1164" s="9"/>
-      <c r="E1164" s="9"/>
-      <c r="G1164" s="7"/>
-    </row>
-    <row r="1165" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1165" s="9"/>
-      <c r="D1165" s="9"/>
-      <c r="E1165" s="9"/>
-      <c r="G1165" s="7"/>
-    </row>
-    <row r="1166" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1166" s="9"/>
-      <c r="D1166" s="9"/>
-      <c r="E1166" s="9"/>
-      <c r="G1166" s="7"/>
-    </row>
-    <row r="1167" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1167" s="9"/>
-      <c r="D1167" s="9"/>
-      <c r="E1167" s="9"/>
-      <c r="G1167" s="7"/>
-    </row>
-    <row r="1168" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1168" s="9"/>
-      <c r="D1168" s="9"/>
-      <c r="E1168" s="9"/>
-      <c r="G1168" s="7"/>
-    </row>
-    <row r="1169" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1169" s="9"/>
-      <c r="D1169" s="9"/>
-      <c r="E1169" s="9"/>
-      <c r="G1169" s="7"/>
-    </row>
-    <row r="1170" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1170" s="9"/>
-      <c r="D1170" s="9"/>
-      <c r="E1170" s="9"/>
-      <c r="G1170" s="7"/>
-    </row>
-    <row r="1171" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1171" s="9"/>
-      <c r="D1171" s="9"/>
-      <c r="E1171" s="9"/>
-      <c r="G1171" s="7"/>
-    </row>
-    <row r="1172" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1172" s="9"/>
-      <c r="D1172" s="9"/>
-      <c r="E1172" s="9"/>
-      <c r="G1172" s="7"/>
-    </row>
-    <row r="1173" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1173" s="9"/>
-      <c r="D1173" s="9"/>
-      <c r="E1173" s="9"/>
-      <c r="G1173" s="7"/>
-    </row>
-    <row r="1174" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1174" s="9"/>
-      <c r="D1174" s="9"/>
-      <c r="E1174" s="9"/>
-      <c r="G1174" s="7"/>
-    </row>
-    <row r="1175" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1175" s="9"/>
-      <c r="D1175" s="9"/>
-      <c r="E1175" s="9"/>
-      <c r="G1175" s="7"/>
-    </row>
-    <row r="1176" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1176" s="9"/>
-      <c r="D1176" s="9"/>
-      <c r="E1176" s="9"/>
-      <c r="G1176" s="7"/>
-    </row>
-    <row r="1177" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1177" s="9"/>
-      <c r="D1177" s="9"/>
-      <c r="E1177" s="9"/>
-      <c r="G1177" s="7"/>
-    </row>
-    <row r="1178" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1178" s="9"/>
-      <c r="D1178" s="9"/>
-      <c r="E1178" s="9"/>
-      <c r="G1178" s="7"/>
-    </row>
-    <row r="1179" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1179" s="9"/>
-      <c r="D1179" s="9"/>
-      <c r="E1179" s="9"/>
-      <c r="G1179" s="7"/>
-    </row>
-    <row r="1180" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1180" s="9"/>
-      <c r="D1180" s="9"/>
-      <c r="E1180" s="9"/>
-      <c r="G1180" s="7"/>
-    </row>
-    <row r="1181" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1181" s="9"/>
-      <c r="D1181" s="9"/>
-      <c r="E1181" s="9"/>
-      <c r="G1181" s="7"/>
-    </row>
-    <row r="1182" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1182" s="9"/>
-      <c r="D1182" s="9"/>
-      <c r="E1182" s="9"/>
-      <c r="G1182" s="7"/>
-    </row>
-    <row r="1183" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1183" s="9"/>
-      <c r="D1183" s="9"/>
-      <c r="E1183" s="9"/>
-      <c r="G1183" s="7"/>
-    </row>
-    <row r="1184" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1184" s="9"/>
-      <c r="D1184" s="9"/>
-      <c r="E1184" s="9"/>
-      <c r="G1184" s="7"/>
-    </row>
-    <row r="1185" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1185" s="9"/>
-      <c r="D1185" s="9"/>
-      <c r="E1185" s="9"/>
-      <c r="G1185" s="7"/>
-    </row>
-    <row r="1186" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1186" s="9"/>
-      <c r="D1186" s="9"/>
-      <c r="E1186" s="9"/>
-      <c r="G1186" s="7"/>
-    </row>
-    <row r="1187" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1187" s="9"/>
-      <c r="D1187" s="9"/>
-      <c r="E1187" s="9"/>
-      <c r="G1187" s="7"/>
-    </row>
-    <row r="1188" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1188" s="9"/>
-      <c r="D1188" s="9"/>
-      <c r="E1188" s="9"/>
-      <c r="G1188" s="7"/>
-    </row>
-    <row r="1189" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1189" s="9"/>
-      <c r="D1189" s="9"/>
-      <c r="E1189" s="9"/>
-      <c r="G1189" s="7"/>
-    </row>
-    <row r="1190" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1190" s="9"/>
-      <c r="D1190" s="9"/>
-      <c r="E1190" s="9"/>
-      <c r="G1190" s="7"/>
-    </row>
-    <row r="1191" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1191" s="9"/>
-      <c r="D1191" s="9"/>
-      <c r="E1191" s="9"/>
-      <c r="G1191" s="7"/>
-    </row>
-    <row r="1192" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1192" s="9"/>
-      <c r="D1192" s="9"/>
-      <c r="E1192" s="9"/>
-      <c r="G1192" s="7"/>
-    </row>
-    <row r="1193" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1193" s="9"/>
-      <c r="D1193" s="9"/>
-      <c r="E1193" s="9"/>
-      <c r="G1193" s="7"/>
-    </row>
-    <row r="1194" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1194" s="9"/>
-      <c r="D1194" s="9"/>
-      <c r="E1194" s="9"/>
-      <c r="G1194" s="7"/>
-    </row>
-    <row r="1195" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1195" s="9"/>
-      <c r="D1195" s="9"/>
-      <c r="E1195" s="9"/>
-      <c r="G1195" s="7"/>
-    </row>
-    <row r="1196" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1196" s="9"/>
-      <c r="D1196" s="9"/>
-      <c r="E1196" s="9"/>
-      <c r="G1196" s="7"/>
-    </row>
-    <row r="1197" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1197" s="9"/>
-      <c r="D1197" s="9"/>
-      <c r="E1197" s="9"/>
-      <c r="G1197" s="7"/>
-    </row>
-    <row r="1198" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1198" s="9"/>
-      <c r="D1198" s="9"/>
-      <c r="E1198" s="9"/>
-      <c r="G1198" s="7"/>
-    </row>
-    <row r="1199" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1199" s="9"/>
-      <c r="D1199" s="9"/>
-      <c r="E1199" s="9"/>
-      <c r="G1199" s="7"/>
-    </row>
-    <row r="1200" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1200" s="9"/>
-      <c r="D1200" s="9"/>
-      <c r="E1200" s="9"/>
-      <c r="G1200" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}"/>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DOCS EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E6D781-BDA2-48E0-A3C6-968538B40142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{821FAA5F-C347-452E-85F7-4BEEA823EC41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1341" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1991" uniqueCount="150">
   <si>
     <t>POD</t>
   </si>
@@ -484,6 +484,15 @@
   </si>
   <si>
     <t>1 al 15 de octubre</t>
+  </si>
+  <si>
+    <t>15 al 21 de octubre</t>
+  </si>
+  <si>
+    <t>YML</t>
+  </si>
+  <si>
+    <t>H</t>
   </si>
 </sst>
 </file>
@@ -7878,720 +7887,3296 @@
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C249" s="9"/>
-      <c r="D249" s="9"/>
-      <c r="E249" s="9"/>
-      <c r="G249" s="7"/>
+      <c r="A249" t="s">
+        <v>88</v>
+      </c>
+      <c r="B249" t="s">
+        <v>12</v>
+      </c>
+      <c r="C249" s="9">
+        <v>5130</v>
+      </c>
+      <c r="D249" s="9">
+        <v>5930</v>
+      </c>
+      <c r="E249" s="9">
+        <v>6230</v>
+      </c>
+      <c r="F249" t="s">
+        <v>147</v>
+      </c>
+      <c r="G249" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H249" t="s">
+        <v>70</v>
+      </c>
+      <c r="I249" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C250" s="9"/>
-      <c r="D250" s="9"/>
-      <c r="E250" s="9"/>
-      <c r="G250" s="7"/>
+      <c r="A250" t="s">
+        <v>89</v>
+      </c>
+      <c r="B250" t="s">
+        <v>12</v>
+      </c>
+      <c r="C250" s="9">
+        <v>5130</v>
+      </c>
+      <c r="D250" s="9">
+        <v>5930</v>
+      </c>
+      <c r="E250" s="9">
+        <v>6230</v>
+      </c>
+      <c r="F250" t="s">
+        <v>147</v>
+      </c>
+      <c r="G250" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H250" t="s">
+        <v>70</v>
+      </c>
+      <c r="I250" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C251" s="9"/>
-      <c r="D251" s="9"/>
-      <c r="E251" s="9"/>
-      <c r="G251" s="7"/>
+      <c r="A251" t="s">
+        <v>77</v>
+      </c>
+      <c r="B251" t="s">
+        <v>12</v>
+      </c>
+      <c r="C251" s="9">
+        <v>5130</v>
+      </c>
+      <c r="D251" s="9">
+        <v>5930</v>
+      </c>
+      <c r="E251" s="9">
+        <v>6230</v>
+      </c>
+      <c r="F251" t="s">
+        <v>147</v>
+      </c>
+      <c r="G251" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H251" t="s">
+        <v>70</v>
+      </c>
+      <c r="I251" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C252" s="9"/>
-      <c r="D252" s="9"/>
-      <c r="E252" s="9"/>
-      <c r="G252" s="7"/>
+      <c r="A252" t="s">
+        <v>76</v>
+      </c>
+      <c r="B252" t="s">
+        <v>12</v>
+      </c>
+      <c r="C252" s="9">
+        <v>5130</v>
+      </c>
+      <c r="D252" s="9">
+        <v>5930</v>
+      </c>
+      <c r="E252" s="9">
+        <v>6230</v>
+      </c>
+      <c r="F252" t="s">
+        <v>147</v>
+      </c>
+      <c r="G252" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H252" t="s">
+        <v>70</v>
+      </c>
+      <c r="I252" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C253" s="9"/>
-      <c r="D253" s="9"/>
-      <c r="E253" s="9"/>
-      <c r="G253" s="7"/>
+      <c r="A253" t="s">
+        <v>78</v>
+      </c>
+      <c r="B253" t="s">
+        <v>12</v>
+      </c>
+      <c r="C253" s="9">
+        <v>5130</v>
+      </c>
+      <c r="D253" s="9">
+        <v>5930</v>
+      </c>
+      <c r="E253" s="9">
+        <v>6230</v>
+      </c>
+      <c r="F253" t="s">
+        <v>147</v>
+      </c>
+      <c r="G253" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H253" t="s">
+        <v>70</v>
+      </c>
+      <c r="I253" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C254" s="9"/>
-      <c r="D254" s="9"/>
-      <c r="E254" s="9"/>
-      <c r="G254" s="7"/>
+      <c r="A254" t="s">
+        <v>119</v>
+      </c>
+      <c r="B254" t="s">
+        <v>12</v>
+      </c>
+      <c r="C254" s="9">
+        <v>5130</v>
+      </c>
+      <c r="D254" s="9">
+        <v>5930</v>
+      </c>
+      <c r="E254" s="9">
+        <v>6230</v>
+      </c>
+      <c r="F254" t="s">
+        <v>147</v>
+      </c>
+      <c r="G254" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H254" t="s">
+        <v>70</v>
+      </c>
+      <c r="I254" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C255" s="9"/>
-      <c r="D255" s="9"/>
-      <c r="E255" s="9"/>
-      <c r="G255" s="7"/>
+      <c r="A255" t="s">
+        <v>75</v>
+      </c>
+      <c r="B255" t="s">
+        <v>12</v>
+      </c>
+      <c r="C255" s="9">
+        <v>5130</v>
+      </c>
+      <c r="D255" s="9">
+        <v>5930</v>
+      </c>
+      <c r="E255" s="9">
+        <v>6230</v>
+      </c>
+      <c r="F255" t="s">
+        <v>147</v>
+      </c>
+      <c r="G255" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H255" t="s">
+        <v>70</v>
+      </c>
+      <c r="I255" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C256" s="9"/>
-      <c r="D256" s="9"/>
-      <c r="E256" s="9"/>
-      <c r="G256" s="7"/>
-    </row>
-    <row r="257" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C257" s="9"/>
-      <c r="D257" s="9"/>
-      <c r="E257" s="9"/>
-      <c r="G257" s="7"/>
-    </row>
-    <row r="258" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C258" s="9"/>
-      <c r="D258" s="9"/>
-      <c r="E258" s="9"/>
-      <c r="G258" s="7"/>
-    </row>
-    <row r="259" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C259" s="9"/>
-      <c r="D259" s="9"/>
-      <c r="E259" s="9"/>
-      <c r="G259" s="7"/>
-    </row>
-    <row r="260" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C260" s="9"/>
-      <c r="D260" s="9"/>
-      <c r="E260" s="9"/>
-      <c r="G260" s="7"/>
-    </row>
-    <row r="261" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C261" s="9"/>
-      <c r="D261" s="9"/>
-      <c r="E261" s="9"/>
-      <c r="G261" s="7"/>
-    </row>
-    <row r="262" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C262" s="9"/>
-      <c r="D262" s="9"/>
-      <c r="E262" s="9"/>
-      <c r="G262" s="7"/>
-    </row>
-    <row r="263" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C263" s="9"/>
-      <c r="D263" s="9"/>
-      <c r="E263" s="9"/>
-      <c r="G263" s="7"/>
-    </row>
-    <row r="264" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C264" s="9"/>
-      <c r="D264" s="9"/>
-      <c r="E264" s="9"/>
-      <c r="G264" s="7"/>
-    </row>
-    <row r="265" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C265" s="9"/>
-      <c r="D265" s="9"/>
-      <c r="E265" s="9"/>
-      <c r="G265" s="7"/>
-    </row>
-    <row r="266" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C266" s="9"/>
-      <c r="D266" s="9"/>
-      <c r="E266" s="9"/>
-      <c r="G266" s="7"/>
-    </row>
-    <row r="267" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C267" s="9"/>
-      <c r="D267" s="9"/>
-      <c r="E267" s="9"/>
-      <c r="G267" s="7"/>
-    </row>
-    <row r="268" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C268" s="9"/>
-      <c r="D268" s="9"/>
-      <c r="E268" s="9"/>
-      <c r="G268" s="7"/>
-    </row>
-    <row r="269" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C269" s="9"/>
-      <c r="D269" s="9"/>
-      <c r="E269" s="9"/>
-      <c r="G269" s="7"/>
-    </row>
-    <row r="270" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C270" s="9"/>
-      <c r="D270" s="9"/>
-      <c r="E270" s="9"/>
-      <c r="G270" s="7"/>
-    </row>
-    <row r="271" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C271" s="9"/>
-      <c r="D271" s="9"/>
-      <c r="E271" s="9"/>
-      <c r="G271" s="7"/>
-    </row>
-    <row r="272" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C272" s="9"/>
-      <c r="D272" s="9"/>
-      <c r="E272" s="9"/>
-      <c r="G272" s="7"/>
-    </row>
-    <row r="273" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C273" s="9"/>
-      <c r="D273" s="9"/>
-      <c r="E273" s="9"/>
-      <c r="G273" s="7"/>
-    </row>
-    <row r="274" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C274" s="9"/>
-      <c r="D274" s="9"/>
-      <c r="E274" s="9"/>
-      <c r="G274" s="7"/>
-    </row>
-    <row r="275" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C275" s="9"/>
-      <c r="D275" s="9"/>
-      <c r="E275" s="9"/>
-      <c r="G275" s="7"/>
-    </row>
-    <row r="276" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C276" s="9"/>
-      <c r="D276" s="9"/>
-      <c r="E276" s="9"/>
-      <c r="G276" s="7"/>
-    </row>
-    <row r="277" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C277" s="9"/>
-      <c r="D277" s="9"/>
-      <c r="E277" s="9"/>
-      <c r="G277" s="7"/>
-    </row>
-    <row r="278" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C278" s="9"/>
-      <c r="D278" s="9"/>
-      <c r="E278" s="9"/>
-      <c r="G278" s="7"/>
-    </row>
-    <row r="279" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C279" s="9"/>
-      <c r="D279" s="9"/>
-      <c r="E279" s="9"/>
-      <c r="G279" s="7"/>
-    </row>
-    <row r="280" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C280" s="9"/>
-      <c r="D280" s="9"/>
-      <c r="E280" s="9"/>
-      <c r="G280" s="7"/>
-    </row>
-    <row r="281" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C281" s="9"/>
-      <c r="D281" s="9"/>
-      <c r="E281" s="9"/>
-      <c r="G281" s="7"/>
-    </row>
-    <row r="282" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C282" s="9"/>
-      <c r="D282" s="9"/>
-      <c r="E282" s="9"/>
-      <c r="G282" s="7"/>
-    </row>
-    <row r="283" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C283" s="9"/>
-      <c r="D283" s="9"/>
-      <c r="E283" s="9"/>
-      <c r="G283" s="7"/>
-    </row>
-    <row r="284" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C284" s="9"/>
-      <c r="D284" s="9"/>
-      <c r="E284" s="9"/>
-      <c r="G284" s="7"/>
-    </row>
-    <row r="285" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C285" s="9"/>
-      <c r="D285" s="9"/>
-      <c r="E285" s="9"/>
-      <c r="G285" s="7"/>
-    </row>
-    <row r="286" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C286" s="9"/>
-      <c r="D286" s="9"/>
-      <c r="E286" s="9"/>
-      <c r="G286" s="7"/>
-    </row>
-    <row r="287" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C287" s="9"/>
-      <c r="D287" s="9"/>
-      <c r="E287" s="9"/>
-      <c r="G287" s="7"/>
-    </row>
-    <row r="288" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C288" s="9"/>
-      <c r="D288" s="9"/>
-      <c r="E288" s="9"/>
-      <c r="G288" s="7"/>
-    </row>
-    <row r="289" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C289" s="9"/>
-      <c r="D289" s="9"/>
-      <c r="E289" s="9"/>
-      <c r="G289" s="7"/>
-    </row>
-    <row r="290" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C290" s="9"/>
-      <c r="D290" s="9"/>
-      <c r="E290" s="9"/>
-      <c r="G290" s="7"/>
-    </row>
-    <row r="291" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C291" s="9"/>
-      <c r="D291" s="9"/>
-      <c r="E291" s="9"/>
-      <c r="G291" s="7"/>
-    </row>
-    <row r="292" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C292" s="9"/>
-      <c r="D292" s="9"/>
-      <c r="E292" s="9"/>
-      <c r="G292" s="7"/>
-    </row>
-    <row r="293" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C293" s="9"/>
-      <c r="D293" s="9"/>
-      <c r="E293" s="9"/>
-      <c r="G293" s="7"/>
-    </row>
-    <row r="294" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C294" s="9"/>
-      <c r="D294" s="9"/>
-      <c r="E294" s="9"/>
-      <c r="G294" s="7"/>
-    </row>
-    <row r="295" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C295" s="9"/>
-      <c r="D295" s="9"/>
-      <c r="E295" s="9"/>
-      <c r="G295" s="7"/>
-    </row>
-    <row r="296" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C296" s="9"/>
-      <c r="D296" s="9"/>
-      <c r="E296" s="9"/>
-      <c r="G296" s="7"/>
-    </row>
-    <row r="297" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C297" s="9"/>
-      <c r="D297" s="9"/>
-      <c r="E297" s="9"/>
-      <c r="G297" s="7"/>
-    </row>
-    <row r="298" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C298" s="9"/>
-      <c r="D298" s="9"/>
-      <c r="E298" s="9"/>
-      <c r="G298" s="7"/>
-    </row>
-    <row r="299" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C299" s="9"/>
-      <c r="D299" s="9"/>
-      <c r="E299" s="9"/>
-      <c r="G299" s="7"/>
-    </row>
-    <row r="300" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C300" s="9"/>
-      <c r="D300" s="9"/>
-      <c r="E300" s="9"/>
-      <c r="G300" s="7"/>
-    </row>
-    <row r="301" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C301" s="9"/>
-      <c r="D301" s="9"/>
-      <c r="E301" s="9"/>
-      <c r="G301" s="7"/>
-    </row>
-    <row r="302" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C302" s="9"/>
-      <c r="D302" s="9"/>
-      <c r="E302" s="9"/>
-      <c r="G302" s="7"/>
-    </row>
-    <row r="303" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C303" s="9"/>
-      <c r="D303" s="9"/>
-      <c r="E303" s="9"/>
-      <c r="G303" s="7"/>
-    </row>
-    <row r="304" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C304" s="9"/>
-      <c r="D304" s="9"/>
-      <c r="E304" s="9"/>
-      <c r="G304" s="7"/>
-    </row>
-    <row r="305" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C305" s="9"/>
-      <c r="D305" s="9"/>
-      <c r="E305" s="9"/>
-      <c r="G305" s="7"/>
-    </row>
-    <row r="306" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C306" s="9"/>
-      <c r="D306" s="9"/>
-      <c r="E306" s="9"/>
-      <c r="G306" s="7"/>
-    </row>
-    <row r="307" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C307" s="9"/>
-      <c r="D307" s="9"/>
-      <c r="E307" s="9"/>
-      <c r="G307" s="7"/>
-    </row>
-    <row r="308" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C308" s="9"/>
-      <c r="D308" s="9"/>
-      <c r="E308" s="9"/>
-      <c r="G308" s="7"/>
-    </row>
-    <row r="309" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C309" s="9"/>
-      <c r="D309" s="9"/>
-      <c r="E309" s="9"/>
-      <c r="G309" s="7"/>
-    </row>
-    <row r="310" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C310" s="9"/>
-      <c r="D310" s="9"/>
-      <c r="E310" s="9"/>
-      <c r="G310" s="7"/>
-    </row>
-    <row r="311" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C311" s="9"/>
-      <c r="D311" s="9"/>
-      <c r="E311" s="9"/>
-      <c r="G311" s="7"/>
-    </row>
-    <row r="312" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C312" s="9"/>
-      <c r="D312" s="9"/>
-      <c r="E312" s="9"/>
-      <c r="G312" s="7"/>
-    </row>
-    <row r="313" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C313" s="9"/>
-      <c r="D313" s="9"/>
-      <c r="E313" s="9"/>
-      <c r="G313" s="7"/>
-    </row>
-    <row r="314" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C314" s="9"/>
-      <c r="D314" s="9"/>
-      <c r="E314" s="9"/>
-      <c r="G314" s="7"/>
-    </row>
-    <row r="315" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C315" s="9"/>
-      <c r="D315" s="9"/>
-      <c r="E315" s="9"/>
-      <c r="G315" s="7"/>
-    </row>
-    <row r="316" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C316" s="9"/>
-      <c r="D316" s="9"/>
-      <c r="E316" s="9"/>
-      <c r="G316" s="7"/>
-    </row>
-    <row r="317" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C317" s="9"/>
-      <c r="D317" s="9"/>
-      <c r="E317" s="9"/>
-      <c r="G317" s="7"/>
-    </row>
-    <row r="318" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C318" s="9"/>
-      <c r="D318" s="9"/>
-      <c r="E318" s="9"/>
-      <c r="G318" s="7"/>
-    </row>
-    <row r="319" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>74</v>
+      </c>
+      <c r="B256" t="s">
+        <v>12</v>
+      </c>
+      <c r="C256" s="9">
+        <v>5130</v>
+      </c>
+      <c r="D256" s="9">
+        <v>5930</v>
+      </c>
+      <c r="E256" s="9">
+        <v>6230</v>
+      </c>
+      <c r="F256" t="s">
+        <v>147</v>
+      </c>
+      <c r="G256" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H256" t="s">
+        <v>70</v>
+      </c>
+      <c r="I256" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>90</v>
+      </c>
+      <c r="B257" t="s">
+        <v>12</v>
+      </c>
+      <c r="C257" s="9">
+        <v>5380</v>
+      </c>
+      <c r="D257" s="9">
+        <v>6080</v>
+      </c>
+      <c r="E257" s="9">
+        <v>6480</v>
+      </c>
+      <c r="F257" t="s">
+        <v>147</v>
+      </c>
+      <c r="G257" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H257" t="s">
+        <v>70</v>
+      </c>
+      <c r="I257" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>103</v>
+      </c>
+      <c r="B258" t="s">
+        <v>12</v>
+      </c>
+      <c r="C258" s="9">
+        <v>5330</v>
+      </c>
+      <c r="D258" s="9">
+        <v>6030</v>
+      </c>
+      <c r="E258" s="9">
+        <v>6430</v>
+      </c>
+      <c r="F258" t="s">
+        <v>147</v>
+      </c>
+      <c r="G258" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H258" t="s">
+        <v>70</v>
+      </c>
+      <c r="I258" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>79</v>
+      </c>
+      <c r="B259" t="s">
+        <v>12</v>
+      </c>
+      <c r="C259" s="9">
+        <v>5380</v>
+      </c>
+      <c r="D259" s="9">
+        <v>6080</v>
+      </c>
+      <c r="E259" s="9">
+        <v>6480</v>
+      </c>
+      <c r="F259" t="s">
+        <v>147</v>
+      </c>
+      <c r="G259" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H259" t="s">
+        <v>70</v>
+      </c>
+      <c r="I259" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>84</v>
+      </c>
+      <c r="B260" t="s">
+        <v>12</v>
+      </c>
+      <c r="C260" s="9">
+        <v>5230</v>
+      </c>
+      <c r="D260" s="9">
+        <v>5980</v>
+      </c>
+      <c r="E260" s="9">
+        <v>6330</v>
+      </c>
+      <c r="F260" t="s">
+        <v>147</v>
+      </c>
+      <c r="G260" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H260" t="s">
+        <v>70</v>
+      </c>
+      <c r="I260" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>81</v>
+      </c>
+      <c r="B261" t="s">
+        <v>12</v>
+      </c>
+      <c r="C261" s="9">
+        <v>5230</v>
+      </c>
+      <c r="D261" s="9">
+        <v>5980</v>
+      </c>
+      <c r="E261" s="9">
+        <v>6330</v>
+      </c>
+      <c r="F261" t="s">
+        <v>147</v>
+      </c>
+      <c r="G261" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H261" t="s">
+        <v>70</v>
+      </c>
+      <c r="I261" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>101</v>
+      </c>
+      <c r="B262" t="s">
+        <v>12</v>
+      </c>
+      <c r="C262" s="9">
+        <v>5230</v>
+      </c>
+      <c r="D262" s="9">
+        <v>5980</v>
+      </c>
+      <c r="E262" s="9">
+        <v>6330</v>
+      </c>
+      <c r="F262" t="s">
+        <v>147</v>
+      </c>
+      <c r="G262" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H262" t="s">
+        <v>70</v>
+      </c>
+      <c r="I262" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>80</v>
+      </c>
+      <c r="B263" t="s">
+        <v>12</v>
+      </c>
+      <c r="C263" s="9">
+        <v>5230</v>
+      </c>
+      <c r="D263" s="9">
+        <v>5980</v>
+      </c>
+      <c r="E263" s="9">
+        <v>6330</v>
+      </c>
+      <c r="F263" t="s">
+        <v>147</v>
+      </c>
+      <c r="G263" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H263" t="s">
+        <v>70</v>
+      </c>
+      <c r="I263" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>82</v>
+      </c>
+      <c r="B264" t="s">
+        <v>12</v>
+      </c>
+      <c r="C264" s="9">
+        <v>5230</v>
+      </c>
+      <c r="D264" s="9">
+        <v>5980</v>
+      </c>
+      <c r="E264" s="9">
+        <v>6330</v>
+      </c>
+      <c r="F264" t="s">
+        <v>147</v>
+      </c>
+      <c r="G264" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H264" t="s">
+        <v>70</v>
+      </c>
+      <c r="I264" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>107</v>
+      </c>
+      <c r="B265" t="s">
+        <v>12</v>
+      </c>
+      <c r="C265" s="9">
+        <v>5230</v>
+      </c>
+      <c r="D265" s="9">
+        <v>5980</v>
+      </c>
+      <c r="E265" s="9">
+        <v>6330</v>
+      </c>
+      <c r="F265" t="s">
+        <v>147</v>
+      </c>
+      <c r="G265" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H265" t="s">
+        <v>70</v>
+      </c>
+      <c r="I265" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>97</v>
+      </c>
+      <c r="B266" t="s">
+        <v>12</v>
+      </c>
+      <c r="C266" s="9">
+        <v>5230</v>
+      </c>
+      <c r="D266" s="9">
+        <v>5980</v>
+      </c>
+      <c r="E266" s="9">
+        <v>6330</v>
+      </c>
+      <c r="F266" t="s">
+        <v>147</v>
+      </c>
+      <c r="G266" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H266" t="s">
+        <v>70</v>
+      </c>
+      <c r="I266" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>110</v>
+      </c>
+      <c r="B267" t="s">
+        <v>12</v>
+      </c>
+      <c r="C267" s="9">
+        <v>5230</v>
+      </c>
+      <c r="D267" s="9">
+        <v>5980</v>
+      </c>
+      <c r="E267" s="9">
+        <v>6330</v>
+      </c>
+      <c r="F267" t="s">
+        <v>147</v>
+      </c>
+      <c r="G267" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H267" t="s">
+        <v>70</v>
+      </c>
+      <c r="I267" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>95</v>
+      </c>
+      <c r="B268" t="s">
+        <v>12</v>
+      </c>
+      <c r="C268" s="9">
+        <v>5230</v>
+      </c>
+      <c r="D268" s="9">
+        <v>5980</v>
+      </c>
+      <c r="E268" s="9">
+        <v>6330</v>
+      </c>
+      <c r="F268" t="s">
+        <v>147</v>
+      </c>
+      <c r="G268" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H268" t="s">
+        <v>70</v>
+      </c>
+      <c r="I268" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>116</v>
+      </c>
+      <c r="B269" t="s">
+        <v>12</v>
+      </c>
+      <c r="C269" s="9">
+        <v>5230</v>
+      </c>
+      <c r="D269" s="9">
+        <v>5980</v>
+      </c>
+      <c r="E269" s="9">
+        <v>6330</v>
+      </c>
+      <c r="F269" t="s">
+        <v>147</v>
+      </c>
+      <c r="G269" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H269" t="s">
+        <v>70</v>
+      </c>
+      <c r="I269" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>98</v>
+      </c>
+      <c r="B270" t="s">
+        <v>12</v>
+      </c>
+      <c r="C270" s="9">
+        <v>5230</v>
+      </c>
+      <c r="D270" s="9">
+        <v>5980</v>
+      </c>
+      <c r="E270" s="9">
+        <v>6330</v>
+      </c>
+      <c r="F270" t="s">
+        <v>147</v>
+      </c>
+      <c r="G270" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H270" t="s">
+        <v>70</v>
+      </c>
+      <c r="I270" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>120</v>
+      </c>
+      <c r="B271" t="s">
+        <v>12</v>
+      </c>
+      <c r="C271" s="9">
+        <v>5280</v>
+      </c>
+      <c r="D271" s="9">
+        <v>6030</v>
+      </c>
+      <c r="E271" s="9">
+        <v>6380</v>
+      </c>
+      <c r="F271" t="s">
+        <v>147</v>
+      </c>
+      <c r="G271" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H271" t="s">
+        <v>70</v>
+      </c>
+      <c r="I271" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>121</v>
+      </c>
+      <c r="B272" t="s">
+        <v>12</v>
+      </c>
+      <c r="C272" s="9">
+        <v>7030</v>
+      </c>
+      <c r="D272" s="9">
+        <v>6330</v>
+      </c>
+      <c r="E272" s="9">
+        <v>7030</v>
+      </c>
+      <c r="F272" t="s">
+        <v>147</v>
+      </c>
+      <c r="G272" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H272" t="s">
+        <v>70</v>
+      </c>
+      <c r="I272" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>122</v>
+      </c>
+      <c r="B273" t="s">
+        <v>12</v>
+      </c>
+      <c r="C273" s="9">
+        <v>5430</v>
+      </c>
+      <c r="D273" s="9">
+        <v>6130</v>
+      </c>
+      <c r="E273" s="9">
+        <v>6530</v>
+      </c>
+      <c r="F273" t="s">
+        <v>147</v>
+      </c>
+      <c r="G273" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H273" t="s">
+        <v>70</v>
+      </c>
+      <c r="I273" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>111</v>
+      </c>
+      <c r="B274" t="s">
+        <v>12</v>
+      </c>
+      <c r="C274" s="9">
+        <v>5630</v>
+      </c>
+      <c r="D274" s="9">
+        <v>6230</v>
+      </c>
+      <c r="E274" s="9">
+        <v>6730</v>
+      </c>
+      <c r="F274" t="s">
+        <v>147</v>
+      </c>
+      <c r="G274" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H274" t="s">
+        <v>70</v>
+      </c>
+      <c r="I274" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>123</v>
+      </c>
+      <c r="B275" t="s">
+        <v>12</v>
+      </c>
+      <c r="C275" s="9">
+        <v>5630</v>
+      </c>
+      <c r="D275" s="9">
+        <v>6230</v>
+      </c>
+      <c r="E275" s="9">
+        <v>6730</v>
+      </c>
+      <c r="F275" t="s">
+        <v>147</v>
+      </c>
+      <c r="G275" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H275" t="s">
+        <v>70</v>
+      </c>
+      <c r="I275" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>124</v>
+      </c>
+      <c r="B276" t="s">
+        <v>12</v>
+      </c>
+      <c r="C276" s="9">
+        <v>5330</v>
+      </c>
+      <c r="D276" s="9">
+        <v>6080</v>
+      </c>
+      <c r="E276" s="9">
+        <v>6430</v>
+      </c>
+      <c r="F276" t="s">
+        <v>147</v>
+      </c>
+      <c r="G276" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H276" t="s">
+        <v>70</v>
+      </c>
+      <c r="I276" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>112</v>
+      </c>
+      <c r="B277" t="s">
+        <v>12</v>
+      </c>
+      <c r="C277" s="9">
+        <v>5430</v>
+      </c>
+      <c r="D277" s="9">
+        <v>6130</v>
+      </c>
+      <c r="E277" s="9">
+        <v>6530</v>
+      </c>
+      <c r="F277" t="s">
+        <v>147</v>
+      </c>
+      <c r="G277" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H277" t="s">
+        <v>70</v>
+      </c>
+      <c r="I277" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>125</v>
+      </c>
+      <c r="B278" t="s">
+        <v>12</v>
+      </c>
+      <c r="C278" s="9">
+        <v>5430</v>
+      </c>
+      <c r="D278" s="9">
+        <v>6130</v>
+      </c>
+      <c r="E278" s="9">
+        <v>6530</v>
+      </c>
+      <c r="F278" t="s">
+        <v>147</v>
+      </c>
+      <c r="G278" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H278" t="s">
+        <v>70</v>
+      </c>
+      <c r="I278" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>126</v>
+      </c>
+      <c r="B279" t="s">
+        <v>12</v>
+      </c>
+      <c r="C279" s="9">
+        <v>5430</v>
+      </c>
+      <c r="D279" s="9">
+        <v>6130</v>
+      </c>
+      <c r="E279" s="9">
+        <v>6530</v>
+      </c>
+      <c r="F279" t="s">
+        <v>147</v>
+      </c>
+      <c r="G279" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H279" t="s">
+        <v>70</v>
+      </c>
+      <c r="I279" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>117</v>
+      </c>
+      <c r="B280" t="s">
+        <v>12</v>
+      </c>
+      <c r="C280" s="9">
+        <v>5430</v>
+      </c>
+      <c r="D280" s="9">
+        <v>6130</v>
+      </c>
+      <c r="E280" s="9">
+        <v>6530</v>
+      </c>
+      <c r="F280" t="s">
+        <v>147</v>
+      </c>
+      <c r="G280" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H280" t="s">
+        <v>70</v>
+      </c>
+      <c r="I280" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>115</v>
+      </c>
+      <c r="B281" t="s">
+        <v>12</v>
+      </c>
+      <c r="C281" s="9">
+        <v>5430</v>
+      </c>
+      <c r="D281" s="9">
+        <v>6130</v>
+      </c>
+      <c r="E281" s="9">
+        <v>6530</v>
+      </c>
+      <c r="F281" t="s">
+        <v>147</v>
+      </c>
+      <c r="G281" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H281" t="s">
+        <v>70</v>
+      </c>
+      <c r="I281" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>105</v>
+      </c>
+      <c r="B282" t="s">
+        <v>12</v>
+      </c>
+      <c r="C282" s="9">
+        <v>5430</v>
+      </c>
+      <c r="D282" s="9">
+        <v>6130</v>
+      </c>
+      <c r="E282" s="9">
+        <v>6530</v>
+      </c>
+      <c r="F282" t="s">
+        <v>147</v>
+      </c>
+      <c r="G282" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H282" t="s">
+        <v>70</v>
+      </c>
+      <c r="I282" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>108</v>
+      </c>
+      <c r="B283" t="s">
+        <v>12</v>
+      </c>
+      <c r="C283" s="9">
+        <v>5430</v>
+      </c>
+      <c r="D283" s="9">
+        <v>6130</v>
+      </c>
+      <c r="E283" s="9">
+        <v>6530</v>
+      </c>
+      <c r="F283" t="s">
+        <v>147</v>
+      </c>
+      <c r="G283" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H283" t="s">
+        <v>70</v>
+      </c>
+      <c r="I283" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>127</v>
+      </c>
+      <c r="B284" t="s">
+        <v>12</v>
+      </c>
+      <c r="C284" s="9">
+        <v>5430</v>
+      </c>
+      <c r="D284" s="9">
+        <v>6130</v>
+      </c>
+      <c r="E284" s="9">
+        <v>6530</v>
+      </c>
+      <c r="F284" t="s">
+        <v>147</v>
+      </c>
+      <c r="G284" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H284" t="s">
+        <v>70</v>
+      </c>
+      <c r="I284" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>128</v>
+      </c>
+      <c r="B285" t="s">
+        <v>12</v>
+      </c>
+      <c r="C285" s="9">
+        <v>5430</v>
+      </c>
+      <c r="D285" s="9">
+        <v>6130</v>
+      </c>
+      <c r="E285" s="9">
+        <v>6530</v>
+      </c>
+      <c r="F285" t="s">
+        <v>147</v>
+      </c>
+      <c r="G285" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H285" t="s">
+        <v>70</v>
+      </c>
+      <c r="I285" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>102</v>
+      </c>
+      <c r="B286" t="s">
+        <v>12</v>
+      </c>
+      <c r="C286" s="9">
+        <v>5580</v>
+      </c>
+      <c r="D286" s="9">
+        <v>6180</v>
+      </c>
+      <c r="E286" s="9">
+        <v>6680</v>
+      </c>
+      <c r="F286" t="s">
+        <v>147</v>
+      </c>
+      <c r="G286" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H286" t="s">
+        <v>70</v>
+      </c>
+      <c r="I286" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>106</v>
+      </c>
+      <c r="B287" t="s">
+        <v>12</v>
+      </c>
+      <c r="C287" s="9">
+        <v>5630</v>
+      </c>
+      <c r="D287" s="9">
+        <v>6230</v>
+      </c>
+      <c r="E287" s="9">
+        <v>6730</v>
+      </c>
+      <c r="F287" t="s">
+        <v>147</v>
+      </c>
+      <c r="G287" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H287" t="s">
+        <v>70</v>
+      </c>
+      <c r="I287" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>129</v>
+      </c>
+      <c r="B288" t="s">
+        <v>12</v>
+      </c>
+      <c r="C288" s="9">
+        <v>5580</v>
+      </c>
+      <c r="D288" s="9">
+        <v>6180</v>
+      </c>
+      <c r="E288" s="9">
+        <v>6680</v>
+      </c>
+      <c r="F288" t="s">
+        <v>147</v>
+      </c>
+      <c r="G288" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H288" t="s">
+        <v>70</v>
+      </c>
+      <c r="I288" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>130</v>
+      </c>
+      <c r="B289" t="s">
+        <v>12</v>
+      </c>
+      <c r="C289" s="9">
+        <v>5680</v>
+      </c>
+      <c r="D289" s="9">
+        <v>6280</v>
+      </c>
+      <c r="E289" s="9">
+        <v>6780</v>
+      </c>
+      <c r="F289" t="s">
+        <v>147</v>
+      </c>
+      <c r="G289" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H289" t="s">
+        <v>70</v>
+      </c>
+      <c r="I289" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>96</v>
+      </c>
+      <c r="B290" t="s">
+        <v>12</v>
+      </c>
+      <c r="C290" s="9">
+        <v>5930</v>
+      </c>
+      <c r="D290" s="9">
+        <v>6430</v>
+      </c>
+      <c r="E290" s="9">
+        <v>7240</v>
+      </c>
+      <c r="F290" t="s">
+        <v>147</v>
+      </c>
+      <c r="G290" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H290" t="s">
+        <v>70</v>
+      </c>
+      <c r="I290" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>131</v>
+      </c>
+      <c r="B291" t="s">
+        <v>12</v>
+      </c>
+      <c r="C291" s="9">
+        <v>5230</v>
+      </c>
+      <c r="D291" s="9">
+        <v>6030</v>
+      </c>
+      <c r="E291" s="9">
+        <v>6500</v>
+      </c>
+      <c r="F291" t="s">
+        <v>147</v>
+      </c>
+      <c r="G291" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H291" t="s">
+        <v>70</v>
+      </c>
+      <c r="I291" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>132</v>
+      </c>
+      <c r="B292" t="s">
+        <v>12</v>
+      </c>
+      <c r="C292" s="9">
+        <v>5230</v>
+      </c>
+      <c r="D292" s="9">
+        <v>6030</v>
+      </c>
+      <c r="E292" s="9">
+        <v>6500</v>
+      </c>
+      <c r="F292" t="s">
+        <v>147</v>
+      </c>
+      <c r="G292" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H292" t="s">
+        <v>70</v>
+      </c>
+      <c r="I292" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>133</v>
+      </c>
+      <c r="B293" t="s">
+        <v>12</v>
+      </c>
+      <c r="C293" s="9">
+        <v>5230</v>
+      </c>
+      <c r="D293" s="9">
+        <v>6030</v>
+      </c>
+      <c r="E293" s="9">
+        <v>6500</v>
+      </c>
+      <c r="F293" t="s">
+        <v>147</v>
+      </c>
+      <c r="G293" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H293" t="s">
+        <v>70</v>
+      </c>
+      <c r="I293" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>134</v>
+      </c>
+      <c r="B294" t="s">
+        <v>12</v>
+      </c>
+      <c r="C294" s="9">
+        <v>5380</v>
+      </c>
+      <c r="D294" s="9">
+        <v>6130</v>
+      </c>
+      <c r="E294" s="9">
+        <v>6660</v>
+      </c>
+      <c r="F294" t="s">
+        <v>147</v>
+      </c>
+      <c r="G294" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H294" t="s">
+        <v>70</v>
+      </c>
+      <c r="I294" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>135</v>
+      </c>
+      <c r="B295" t="s">
+        <v>12</v>
+      </c>
+      <c r="C295" s="9">
+        <v>5380</v>
+      </c>
+      <c r="D295" s="9">
+        <v>6130</v>
+      </c>
+      <c r="E295" s="9">
+        <v>6660</v>
+      </c>
+      <c r="F295" t="s">
+        <v>147</v>
+      </c>
+      <c r="G295" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H295" t="s">
+        <v>70</v>
+      </c>
+      <c r="I295" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>88</v>
+      </c>
+      <c r="B296" t="s">
+        <v>12</v>
+      </c>
+      <c r="C296" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D296" s="9">
+        <v>5830</v>
+      </c>
+      <c r="E296" s="9">
+        <v>6130</v>
+      </c>
+      <c r="F296" t="s">
+        <v>147</v>
+      </c>
+      <c r="G296" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H296" t="s">
+        <v>71</v>
+      </c>
+      <c r="I296" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>89</v>
+      </c>
+      <c r="B297" t="s">
+        <v>12</v>
+      </c>
+      <c r="C297" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D297" s="9">
+        <v>5830</v>
+      </c>
+      <c r="E297" s="9">
+        <v>6130</v>
+      </c>
+      <c r="F297" t="s">
+        <v>147</v>
+      </c>
+      <c r="G297" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H297" t="s">
+        <v>71</v>
+      </c>
+      <c r="I297" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>77</v>
+      </c>
+      <c r="B298" t="s">
+        <v>12</v>
+      </c>
+      <c r="C298" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D298" s="9">
+        <v>5830</v>
+      </c>
+      <c r="E298" s="9">
+        <v>6130</v>
+      </c>
+      <c r="F298" t="s">
+        <v>147</v>
+      </c>
+      <c r="G298" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H298" t="s">
+        <v>71</v>
+      </c>
+      <c r="I298" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>76</v>
+      </c>
+      <c r="B299" t="s">
+        <v>12</v>
+      </c>
+      <c r="C299" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D299" s="9">
+        <v>5830</v>
+      </c>
+      <c r="E299" s="9">
+        <v>6130</v>
+      </c>
+      <c r="F299" t="s">
+        <v>147</v>
+      </c>
+      <c r="G299" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H299" t="s">
+        <v>71</v>
+      </c>
+      <c r="I299" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>78</v>
+      </c>
+      <c r="B300" t="s">
+        <v>12</v>
+      </c>
+      <c r="C300" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D300" s="9">
+        <v>5830</v>
+      </c>
+      <c r="E300" s="9">
+        <v>6130</v>
+      </c>
+      <c r="F300" t="s">
+        <v>147</v>
+      </c>
+      <c r="G300" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H300" t="s">
+        <v>71</v>
+      </c>
+      <c r="I300" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>119</v>
+      </c>
+      <c r="B301" t="s">
+        <v>12</v>
+      </c>
+      <c r="C301" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D301" s="9">
+        <v>5830</v>
+      </c>
+      <c r="E301" s="9">
+        <v>6130</v>
+      </c>
+      <c r="F301" t="s">
+        <v>147</v>
+      </c>
+      <c r="G301" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H301" t="s">
+        <v>71</v>
+      </c>
+      <c r="I301" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>75</v>
+      </c>
+      <c r="B302" t="s">
+        <v>12</v>
+      </c>
+      <c r="C302" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D302" s="9">
+        <v>5830</v>
+      </c>
+      <c r="E302" s="9">
+        <v>6130</v>
+      </c>
+      <c r="F302" t="s">
+        <v>147</v>
+      </c>
+      <c r="G302" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H302" t="s">
+        <v>71</v>
+      </c>
+      <c r="I302" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>74</v>
+      </c>
+      <c r="B303" t="s">
+        <v>12</v>
+      </c>
+      <c r="C303" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D303" s="9">
+        <v>5830</v>
+      </c>
+      <c r="E303" s="9">
+        <v>6130</v>
+      </c>
+      <c r="F303" t="s">
+        <v>147</v>
+      </c>
+      <c r="G303" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H303" t="s">
+        <v>71</v>
+      </c>
+      <c r="I303" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>90</v>
+      </c>
+      <c r="B304" t="s">
+        <v>12</v>
+      </c>
+      <c r="C304" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D304" s="9">
+        <v>5830</v>
+      </c>
+      <c r="E304" s="9">
+        <v>6130</v>
+      </c>
+      <c r="F304" t="s">
+        <v>147</v>
+      </c>
+      <c r="G304" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H304" t="s">
+        <v>71</v>
+      </c>
+      <c r="I304" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>103</v>
+      </c>
+      <c r="B305" t="s">
+        <v>12</v>
+      </c>
+      <c r="C305" s="9">
+        <v>4830</v>
+      </c>
+      <c r="D305" s="9">
+        <v>5930</v>
+      </c>
+      <c r="E305" s="9">
+        <v>6330</v>
+      </c>
+      <c r="F305" t="s">
+        <v>147</v>
+      </c>
+      <c r="G305" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H305" t="s">
+        <v>71</v>
+      </c>
+      <c r="I305" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>79</v>
+      </c>
+      <c r="B306" t="s">
+        <v>12</v>
+      </c>
+      <c r="C306" s="9">
+        <v>4630</v>
+      </c>
+      <c r="D306" s="9">
+        <v>5830</v>
+      </c>
+      <c r="E306" s="9">
+        <v>6130</v>
+      </c>
+      <c r="F306" t="s">
+        <v>147</v>
+      </c>
+      <c r="G306" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H306" t="s">
+        <v>71</v>
+      </c>
+      <c r="I306" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>84</v>
+      </c>
+      <c r="B307" t="s">
+        <v>12</v>
+      </c>
+      <c r="C307" s="9">
+        <v>4780</v>
+      </c>
+      <c r="D307" s="9">
+        <v>5910</v>
+      </c>
+      <c r="E307" s="9">
+        <v>6280</v>
+      </c>
+      <c r="F307" t="s">
+        <v>147</v>
+      </c>
+      <c r="G307" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H307" t="s">
+        <v>71</v>
+      </c>
+      <c r="I307" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>81</v>
+      </c>
+      <c r="B308" t="s">
+        <v>12</v>
+      </c>
+      <c r="C308" s="9">
+        <v>4730</v>
+      </c>
+      <c r="D308" s="9">
+        <v>5880</v>
+      </c>
+      <c r="E308" s="9">
+        <v>6230</v>
+      </c>
+      <c r="F308" t="s">
+        <v>147</v>
+      </c>
+      <c r="G308" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H308" t="s">
+        <v>71</v>
+      </c>
+      <c r="I308" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>101</v>
+      </c>
+      <c r="B309" t="s">
+        <v>12</v>
+      </c>
+      <c r="C309" s="9">
+        <v>4730</v>
+      </c>
+      <c r="D309" s="9">
+        <v>5880</v>
+      </c>
+      <c r="E309" s="9">
+        <v>6230</v>
+      </c>
+      <c r="F309" t="s">
+        <v>147</v>
+      </c>
+      <c r="G309" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H309" t="s">
+        <v>71</v>
+      </c>
+      <c r="I309" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>80</v>
+      </c>
+      <c r="B310" t="s">
+        <v>12</v>
+      </c>
+      <c r="C310" s="9">
+        <v>4730</v>
+      </c>
+      <c r="D310" s="9">
+        <v>5880</v>
+      </c>
+      <c r="E310" s="9">
+        <v>6230</v>
+      </c>
+      <c r="F310" t="s">
+        <v>147</v>
+      </c>
+      <c r="G310" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H310" t="s">
+        <v>71</v>
+      </c>
+      <c r="I310" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>82</v>
+      </c>
+      <c r="B311" t="s">
+        <v>12</v>
+      </c>
+      <c r="C311" s="9">
+        <v>4730</v>
+      </c>
+      <c r="D311" s="9">
+        <v>5880</v>
+      </c>
+      <c r="E311" s="9">
+        <v>6230</v>
+      </c>
+      <c r="F311" t="s">
+        <v>147</v>
+      </c>
+      <c r="G311" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H311" t="s">
+        <v>71</v>
+      </c>
+      <c r="I311" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>107</v>
+      </c>
+      <c r="B312" t="s">
+        <v>12</v>
+      </c>
+      <c r="C312" s="9">
+        <v>4730</v>
+      </c>
+      <c r="D312" s="9">
+        <v>5880</v>
+      </c>
+      <c r="E312" s="9">
+        <v>6230</v>
+      </c>
+      <c r="F312" t="s">
+        <v>147</v>
+      </c>
+      <c r="G312" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H312" t="s">
+        <v>71</v>
+      </c>
+      <c r="I312" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>97</v>
+      </c>
+      <c r="B313" t="s">
+        <v>12</v>
+      </c>
+      <c r="C313" s="9">
+        <v>4730</v>
+      </c>
+      <c r="D313" s="9">
+        <v>5880</v>
+      </c>
+      <c r="E313" s="9">
+        <v>6230</v>
+      </c>
+      <c r="F313" t="s">
+        <v>147</v>
+      </c>
+      <c r="G313" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H313" t="s">
+        <v>71</v>
+      </c>
+      <c r="I313" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>110</v>
+      </c>
+      <c r="B314" t="s">
+        <v>12</v>
+      </c>
+      <c r="C314" s="9">
+        <v>4730</v>
+      </c>
+      <c r="D314" s="9">
+        <v>5880</v>
+      </c>
+      <c r="E314" s="9">
+        <v>6230</v>
+      </c>
+      <c r="F314" t="s">
+        <v>147</v>
+      </c>
+      <c r="G314" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H314" t="s">
+        <v>71</v>
+      </c>
+      <c r="I314" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>95</v>
+      </c>
+      <c r="B315" t="s">
+        <v>12</v>
+      </c>
+      <c r="C315" s="9">
+        <v>4730</v>
+      </c>
+      <c r="D315" s="9">
+        <v>5880</v>
+      </c>
+      <c r="E315" s="9">
+        <v>6230</v>
+      </c>
+      <c r="F315" t="s">
+        <v>147</v>
+      </c>
+      <c r="G315" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H315" t="s">
+        <v>71</v>
+      </c>
+      <c r="I315" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>116</v>
+      </c>
+      <c r="B316" t="s">
+        <v>12</v>
+      </c>
+      <c r="C316" s="9">
+        <v>4730</v>
+      </c>
+      <c r="D316" s="9">
+        <v>5880</v>
+      </c>
+      <c r="E316" s="9">
+        <v>6230</v>
+      </c>
+      <c r="F316" t="s">
+        <v>147</v>
+      </c>
+      <c r="G316" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H316" t="s">
+        <v>71</v>
+      </c>
+      <c r="I316" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>98</v>
+      </c>
+      <c r="B317" t="s">
+        <v>12</v>
+      </c>
+      <c r="C317" s="9">
+        <v>4730</v>
+      </c>
+      <c r="D317" s="9">
+        <v>5880</v>
+      </c>
+      <c r="E317" s="9">
+        <v>6230</v>
+      </c>
+      <c r="F317" t="s">
+        <v>147</v>
+      </c>
+      <c r="G317" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H317" t="s">
+        <v>71</v>
+      </c>
+      <c r="I317" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>120</v>
+      </c>
+      <c r="B318" t="s">
+        <v>12</v>
+      </c>
+      <c r="C318" s="9">
+        <v>4930</v>
+      </c>
+      <c r="D318" s="9">
+        <v>6040</v>
+      </c>
+      <c r="E318" s="9">
+        <v>6430</v>
+      </c>
+      <c r="F318" t="s">
+        <v>147</v>
+      </c>
+      <c r="G318" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H318" t="s">
+        <v>71</v>
+      </c>
+      <c r="I318" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>121</v>
+      </c>
+      <c r="B319" t="s">
+        <v>12</v>
+      </c>
       <c r="C319" s="9"/>
-      <c r="D319" s="9"/>
-      <c r="E319" s="9"/>
-      <c r="G319" s="7"/>
-    </row>
-    <row r="320" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D319" s="9">
+        <v>5980</v>
+      </c>
+      <c r="E319" s="9">
+        <v>6430</v>
+      </c>
+      <c r="F319" t="s">
+        <v>147</v>
+      </c>
+      <c r="G319" s="7">
+        <v>17</v>
+      </c>
+      <c r="H319" t="s">
+        <v>71</v>
+      </c>
+      <c r="I319" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>122</v>
+      </c>
+      <c r="B320" t="s">
+        <v>12</v>
+      </c>
       <c r="C320" s="9"/>
-      <c r="D320" s="9"/>
-      <c r="E320" s="9"/>
-      <c r="G320" s="7"/>
-    </row>
-    <row r="321" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D320" s="9">
+        <v>6050</v>
+      </c>
+      <c r="E320" s="9">
+        <v>6470</v>
+      </c>
+      <c r="F320" t="s">
+        <v>147</v>
+      </c>
+      <c r="G320" s="7">
+        <v>17</v>
+      </c>
+      <c r="H320" t="s">
+        <v>71</v>
+      </c>
+      <c r="I320" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>111</v>
+      </c>
+      <c r="B321" t="s">
+        <v>12</v>
+      </c>
       <c r="C321" s="9"/>
-      <c r="D321" s="9"/>
-      <c r="E321" s="9"/>
-      <c r="G321" s="7"/>
-    </row>
-    <row r="322" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D321" s="9">
+        <v>6000</v>
+      </c>
+      <c r="E321" s="9">
+        <v>6430</v>
+      </c>
+      <c r="F321" t="s">
+        <v>147</v>
+      </c>
+      <c r="G321" s="7">
+        <v>17</v>
+      </c>
+      <c r="H321" t="s">
+        <v>71</v>
+      </c>
+      <c r="I321" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>123</v>
+      </c>
+      <c r="B322" t="s">
+        <v>12</v>
+      </c>
       <c r="C322" s="9"/>
-      <c r="D322" s="9"/>
-      <c r="E322" s="9"/>
-      <c r="G322" s="7"/>
-    </row>
-    <row r="323" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D322" s="9">
+        <v>6080</v>
+      </c>
+      <c r="E322" s="9">
+        <v>6560</v>
+      </c>
+      <c r="F322" t="s">
+        <v>147</v>
+      </c>
+      <c r="G322" s="7">
+        <v>17</v>
+      </c>
+      <c r="H322" t="s">
+        <v>71</v>
+      </c>
+      <c r="I322" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>124</v>
+      </c>
+      <c r="B323" t="s">
+        <v>12</v>
+      </c>
       <c r="C323" s="9"/>
-      <c r="D323" s="9"/>
-      <c r="E323" s="9"/>
-      <c r="G323" s="7"/>
-    </row>
-    <row r="324" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D323" s="9">
+        <v>6020</v>
+      </c>
+      <c r="E323" s="9">
+        <v>6440</v>
+      </c>
+      <c r="F323" t="s">
+        <v>147</v>
+      </c>
+      <c r="G323" s="7">
+        <v>17</v>
+      </c>
+      <c r="H323" t="s">
+        <v>71</v>
+      </c>
+      <c r="I323" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>112</v>
+      </c>
+      <c r="B324" t="s">
+        <v>12</v>
+      </c>
       <c r="C324" s="9"/>
-      <c r="D324" s="9"/>
-      <c r="E324" s="9"/>
-      <c r="G324" s="7"/>
-    </row>
-    <row r="325" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D324" s="9">
+        <v>6030</v>
+      </c>
+      <c r="E324" s="9">
+        <v>6450</v>
+      </c>
+      <c r="F324" t="s">
+        <v>147</v>
+      </c>
+      <c r="G324" s="7">
+        <v>17</v>
+      </c>
+      <c r="H324" t="s">
+        <v>71</v>
+      </c>
+      <c r="I324" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>125</v>
+      </c>
+      <c r="B325" t="s">
+        <v>12</v>
+      </c>
       <c r="C325" s="9"/>
-      <c r="D325" s="9"/>
-      <c r="E325" s="9"/>
-      <c r="G325" s="7"/>
-    </row>
-    <row r="326" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D325" s="9">
+        <v>5950</v>
+      </c>
+      <c r="E325" s="9">
+        <v>6340</v>
+      </c>
+      <c r="F325" t="s">
+        <v>147</v>
+      </c>
+      <c r="G325" s="7">
+        <v>17</v>
+      </c>
+      <c r="H325" t="s">
+        <v>71</v>
+      </c>
+      <c r="I325" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>126</v>
+      </c>
+      <c r="B326" t="s">
+        <v>12</v>
+      </c>
       <c r="C326" s="9"/>
-      <c r="D326" s="9"/>
-      <c r="E326" s="9"/>
-      <c r="G326" s="7"/>
-    </row>
-    <row r="327" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D326" s="9">
+        <v>5950</v>
+      </c>
+      <c r="E326" s="9">
+        <v>6340</v>
+      </c>
+      <c r="F326" t="s">
+        <v>147</v>
+      </c>
+      <c r="G326" s="7">
+        <v>17</v>
+      </c>
+      <c r="H326" t="s">
+        <v>71</v>
+      </c>
+      <c r="I326" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>117</v>
+      </c>
+      <c r="B327" t="s">
+        <v>12</v>
+      </c>
       <c r="C327" s="9"/>
-      <c r="D327" s="9"/>
-      <c r="E327" s="9"/>
-      <c r="G327" s="7"/>
-    </row>
-    <row r="328" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D327" s="9">
+        <v>5950</v>
+      </c>
+      <c r="E327" s="9">
+        <v>6340</v>
+      </c>
+      <c r="F327" t="s">
+        <v>147</v>
+      </c>
+      <c r="G327" s="7">
+        <v>17</v>
+      </c>
+      <c r="H327" t="s">
+        <v>71</v>
+      </c>
+      <c r="I327" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>115</v>
+      </c>
+      <c r="B328" t="s">
+        <v>12</v>
+      </c>
       <c r="C328" s="9"/>
-      <c r="D328" s="9"/>
-      <c r="E328" s="9"/>
-      <c r="G328" s="7"/>
-    </row>
-    <row r="329" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D328" s="9">
+        <v>5950</v>
+      </c>
+      <c r="E328" s="9">
+        <v>6340</v>
+      </c>
+      <c r="F328" t="s">
+        <v>147</v>
+      </c>
+      <c r="G328" s="7">
+        <v>17</v>
+      </c>
+      <c r="H328" t="s">
+        <v>71</v>
+      </c>
+      <c r="I328" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>105</v>
+      </c>
+      <c r="B329" t="s">
+        <v>12</v>
+      </c>
       <c r="C329" s="9"/>
-      <c r="D329" s="9"/>
-      <c r="E329" s="9"/>
-      <c r="G329" s="7"/>
-    </row>
-    <row r="330" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D329" s="9">
+        <v>5950</v>
+      </c>
+      <c r="E329" s="9">
+        <v>6340</v>
+      </c>
+      <c r="F329" t="s">
+        <v>147</v>
+      </c>
+      <c r="G329" s="7">
+        <v>17</v>
+      </c>
+      <c r="H329" t="s">
+        <v>71</v>
+      </c>
+      <c r="I329" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>108</v>
+      </c>
+      <c r="B330" t="s">
+        <v>12</v>
+      </c>
       <c r="C330" s="9"/>
-      <c r="D330" s="9"/>
-      <c r="E330" s="9"/>
-      <c r="G330" s="7"/>
-    </row>
-    <row r="331" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D330" s="9">
+        <v>5950</v>
+      </c>
+      <c r="E330" s="9">
+        <v>6340</v>
+      </c>
+      <c r="F330" t="s">
+        <v>147</v>
+      </c>
+      <c r="G330" s="7">
+        <v>17</v>
+      </c>
+      <c r="H330" t="s">
+        <v>71</v>
+      </c>
+      <c r="I330" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>127</v>
+      </c>
+      <c r="B331" t="s">
+        <v>12</v>
+      </c>
       <c r="C331" s="9"/>
-      <c r="D331" s="9"/>
-      <c r="E331" s="9"/>
-      <c r="G331" s="7"/>
-    </row>
-    <row r="332" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D331" s="9">
+        <v>5950</v>
+      </c>
+      <c r="E331" s="9">
+        <v>6340</v>
+      </c>
+      <c r="F331" t="s">
+        <v>147</v>
+      </c>
+      <c r="G331" s="7">
+        <v>17</v>
+      </c>
+      <c r="H331" t="s">
+        <v>71</v>
+      </c>
+      <c r="I331" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>128</v>
+      </c>
+      <c r="B332" t="s">
+        <v>12</v>
+      </c>
       <c r="C332" s="9"/>
-      <c r="D332" s="9"/>
-      <c r="E332" s="9"/>
-      <c r="G332" s="7"/>
-    </row>
-    <row r="333" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D332" s="9">
+        <v>5950</v>
+      </c>
+      <c r="E332" s="9">
+        <v>6340</v>
+      </c>
+      <c r="F332" t="s">
+        <v>147</v>
+      </c>
+      <c r="G332" s="7">
+        <v>17</v>
+      </c>
+      <c r="H332" t="s">
+        <v>71</v>
+      </c>
+      <c r="I332" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>102</v>
+      </c>
+      <c r="B333" t="s">
+        <v>12</v>
+      </c>
       <c r="C333" s="9"/>
-      <c r="D333" s="9"/>
-      <c r="E333" s="9"/>
-      <c r="G333" s="7"/>
-    </row>
-    <row r="334" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D333" s="9">
+        <v>6070</v>
+      </c>
+      <c r="E333" s="9">
+        <v>6550</v>
+      </c>
+      <c r="F333" t="s">
+        <v>147</v>
+      </c>
+      <c r="G333" s="7">
+        <v>17</v>
+      </c>
+      <c r="H333" t="s">
+        <v>71</v>
+      </c>
+      <c r="I333" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>106</v>
+      </c>
+      <c r="B334" t="s">
+        <v>12</v>
+      </c>
       <c r="C334" s="9"/>
-      <c r="D334" s="9"/>
-      <c r="E334" s="9"/>
-      <c r="G334" s="7"/>
-    </row>
-    <row r="335" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D334" s="9">
+        <v>6060</v>
+      </c>
+      <c r="E334" s="9">
+        <v>6520</v>
+      </c>
+      <c r="F334" t="s">
+        <v>147</v>
+      </c>
+      <c r="G334" s="7">
+        <v>17</v>
+      </c>
+      <c r="H334" t="s">
+        <v>71</v>
+      </c>
+      <c r="I334" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>129</v>
+      </c>
+      <c r="B335" t="s">
+        <v>12</v>
+      </c>
       <c r="C335" s="9"/>
-      <c r="D335" s="9"/>
-      <c r="E335" s="9"/>
-      <c r="G335" s="7"/>
-    </row>
-    <row r="336" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D335" s="9">
+        <v>6060</v>
+      </c>
+      <c r="E335" s="9">
+        <v>6580</v>
+      </c>
+      <c r="F335" t="s">
+        <v>147</v>
+      </c>
+      <c r="G335" s="7">
+        <v>17</v>
+      </c>
+      <c r="H335" t="s">
+        <v>71</v>
+      </c>
+      <c r="I335" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>130</v>
+      </c>
+      <c r="B336" t="s">
+        <v>12</v>
+      </c>
       <c r="C336" s="9"/>
-      <c r="D336" s="9"/>
-      <c r="E336" s="9"/>
-      <c r="G336" s="7"/>
-    </row>
-    <row r="337" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D336" s="9">
+        <v>6060</v>
+      </c>
+      <c r="E336" s="9">
+        <v>6580</v>
+      </c>
+      <c r="F336" t="s">
+        <v>147</v>
+      </c>
+      <c r="G336" s="7">
+        <v>17</v>
+      </c>
+      <c r="H336" t="s">
+        <v>71</v>
+      </c>
+      <c r="I336" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>96</v>
+      </c>
+      <c r="B337" t="s">
+        <v>12</v>
+      </c>
       <c r="C337" s="9"/>
-      <c r="D337" s="9"/>
-      <c r="E337" s="9"/>
-      <c r="G337" s="7"/>
-    </row>
-    <row r="338" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D337" s="9">
+        <v>6240</v>
+      </c>
+      <c r="E337" s="9">
+        <v>6920</v>
+      </c>
+      <c r="F337" t="s">
+        <v>147</v>
+      </c>
+      <c r="G337" s="7">
+        <v>17</v>
+      </c>
+      <c r="H337" t="s">
+        <v>71</v>
+      </c>
+      <c r="I337" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>131</v>
+      </c>
+      <c r="B338" t="s">
+        <v>12</v>
+      </c>
       <c r="C338" s="9"/>
-      <c r="D338" s="9"/>
-      <c r="E338" s="9"/>
-      <c r="G338" s="7"/>
-    </row>
-    <row r="339" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D338" s="9">
+        <v>5930</v>
+      </c>
+      <c r="E338" s="9">
+        <v>6280</v>
+      </c>
+      <c r="F338" t="s">
+        <v>147</v>
+      </c>
+      <c r="G338" s="7">
+        <v>17</v>
+      </c>
+      <c r="H338" t="s">
+        <v>71</v>
+      </c>
+      <c r="I338" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>132</v>
+      </c>
+      <c r="B339" t="s">
+        <v>12</v>
+      </c>
       <c r="C339" s="9"/>
-      <c r="D339" s="9"/>
-      <c r="E339" s="9"/>
-      <c r="G339" s="7"/>
-    </row>
-    <row r="340" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D339" s="9">
+        <v>5930</v>
+      </c>
+      <c r="E339" s="9">
+        <v>6280</v>
+      </c>
+      <c r="F339" t="s">
+        <v>147</v>
+      </c>
+      <c r="G339" s="7">
+        <v>17</v>
+      </c>
+      <c r="H339" t="s">
+        <v>71</v>
+      </c>
+      <c r="I339" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>133</v>
+      </c>
+      <c r="B340" t="s">
+        <v>12</v>
+      </c>
       <c r="C340" s="9"/>
-      <c r="D340" s="9"/>
-      <c r="E340" s="9"/>
-      <c r="G340" s="7"/>
-    </row>
-    <row r="341" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D340" s="9">
+        <v>5930</v>
+      </c>
+      <c r="E340" s="9">
+        <v>6280</v>
+      </c>
+      <c r="F340" t="s">
+        <v>147</v>
+      </c>
+      <c r="G340" s="7">
+        <v>17</v>
+      </c>
+      <c r="H340" t="s">
+        <v>71</v>
+      </c>
+      <c r="I340" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>134</v>
+      </c>
+      <c r="B341" t="s">
+        <v>12</v>
+      </c>
       <c r="C341" s="9"/>
-      <c r="D341" s="9"/>
-      <c r="E341" s="9"/>
-      <c r="G341" s="7"/>
-    </row>
-    <row r="342" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D341" s="9">
+        <v>6030</v>
+      </c>
+      <c r="E341" s="9">
+        <v>6430</v>
+      </c>
+      <c r="F341" t="s">
+        <v>147</v>
+      </c>
+      <c r="G341" s="7">
+        <v>17</v>
+      </c>
+      <c r="H341" t="s">
+        <v>71</v>
+      </c>
+      <c r="I341" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>135</v>
+      </c>
+      <c r="B342" t="s">
+        <v>12</v>
+      </c>
       <c r="C342" s="9"/>
-      <c r="D342" s="9"/>
-      <c r="E342" s="9"/>
-      <c r="G342" s="7"/>
-    </row>
-    <row r="343" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D342" s="9">
+        <v>6130</v>
+      </c>
+      <c r="E342" s="9">
+        <v>6580</v>
+      </c>
+      <c r="F342" t="s">
+        <v>147</v>
+      </c>
+      <c r="G342" s="7">
+        <v>17</v>
+      </c>
+      <c r="H342" t="s">
+        <v>71</v>
+      </c>
+      <c r="I342" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>88</v>
+      </c>
+      <c r="B343" t="s">
+        <v>12</v>
+      </c>
       <c r="C343" s="9"/>
-      <c r="D343" s="9"/>
-      <c r="E343" s="9"/>
-      <c r="G343" s="7"/>
-    </row>
-    <row r="344" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D343" s="9">
+        <v>5940</v>
+      </c>
+      <c r="E343" s="9">
+        <v>6240</v>
+      </c>
+      <c r="F343" t="s">
+        <v>147</v>
+      </c>
+      <c r="G343" s="7">
+        <v>21</v>
+      </c>
+      <c r="H343" t="s">
+        <v>73</v>
+      </c>
+      <c r="I343" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>89</v>
+      </c>
+      <c r="B344" t="s">
+        <v>12</v>
+      </c>
       <c r="C344" s="9"/>
-      <c r="D344" s="9"/>
-      <c r="E344" s="9"/>
-      <c r="G344" s="7"/>
-    </row>
-    <row r="345" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D344" s="9">
+        <v>5940</v>
+      </c>
+      <c r="E344" s="9">
+        <v>6240</v>
+      </c>
+      <c r="F344" t="s">
+        <v>147</v>
+      </c>
+      <c r="G344" s="7">
+        <v>21</v>
+      </c>
+      <c r="H344" t="s">
+        <v>73</v>
+      </c>
+      <c r="I344" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>75</v>
+      </c>
+      <c r="B345" t="s">
+        <v>12</v>
+      </c>
       <c r="C345" s="9"/>
-      <c r="D345" s="9"/>
-      <c r="E345" s="9"/>
-      <c r="G345" s="7"/>
-    </row>
-    <row r="346" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D345" s="9">
+        <v>5940</v>
+      </c>
+      <c r="E345" s="9">
+        <v>6240</v>
+      </c>
+      <c r="F345" t="s">
+        <v>147</v>
+      </c>
+      <c r="G345" s="7">
+        <v>21</v>
+      </c>
+      <c r="H345" t="s">
+        <v>73</v>
+      </c>
+      <c r="I345" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>74</v>
+      </c>
+      <c r="B346" t="s">
+        <v>12</v>
+      </c>
       <c r="C346" s="9"/>
-      <c r="D346" s="9"/>
-      <c r="E346" s="9"/>
-      <c r="G346" s="7"/>
-    </row>
-    <row r="347" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D346" s="9">
+        <v>5940</v>
+      </c>
+      <c r="E346" s="9">
+        <v>6240</v>
+      </c>
+      <c r="F346" t="s">
+        <v>147</v>
+      </c>
+      <c r="G346" s="7">
+        <v>21</v>
+      </c>
+      <c r="H346" t="s">
+        <v>73</v>
+      </c>
+      <c r="I346" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>88</v>
+      </c>
+      <c r="B347" t="s">
+        <v>12</v>
+      </c>
       <c r="C347" s="9"/>
-      <c r="D347" s="9"/>
-      <c r="E347" s="9"/>
-      <c r="G347" s="7"/>
-    </row>
-    <row r="348" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D347" s="9">
+        <v>5780</v>
+      </c>
+      <c r="E347" s="9">
+        <v>6100</v>
+      </c>
+      <c r="F347" t="s">
+        <v>147</v>
+      </c>
+      <c r="G347" s="7">
+        <v>18</v>
+      </c>
+      <c r="H347" t="s">
+        <v>86</v>
+      </c>
+      <c r="I347" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>89</v>
+      </c>
+      <c r="B348" t="s">
+        <v>12</v>
+      </c>
       <c r="C348" s="9"/>
-      <c r="D348" s="9"/>
-      <c r="E348" s="9"/>
-      <c r="G348" s="7"/>
-    </row>
-    <row r="349" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D348" s="9">
+        <v>5780</v>
+      </c>
+      <c r="E348" s="9">
+        <v>6100</v>
+      </c>
+      <c r="F348" t="s">
+        <v>147</v>
+      </c>
+      <c r="G348" s="7">
+        <v>18</v>
+      </c>
+      <c r="H348" t="s">
+        <v>86</v>
+      </c>
+      <c r="I348" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>75</v>
+      </c>
+      <c r="B349" t="s">
+        <v>12</v>
+      </c>
       <c r="C349" s="9"/>
-      <c r="D349" s="9"/>
-      <c r="E349" s="9"/>
-      <c r="G349" s="7"/>
-    </row>
-    <row r="350" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D349" s="9">
+        <v>5780</v>
+      </c>
+      <c r="E349" s="9">
+        <v>6100</v>
+      </c>
+      <c r="F349" t="s">
+        <v>147</v>
+      </c>
+      <c r="G349" s="7">
+        <v>18</v>
+      </c>
+      <c r="H349" t="s">
+        <v>86</v>
+      </c>
+      <c r="I349" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>74</v>
+      </c>
+      <c r="B350" t="s">
+        <v>12</v>
+      </c>
       <c r="C350" s="9"/>
-      <c r="D350" s="9"/>
-      <c r="E350" s="9"/>
-      <c r="G350" s="7"/>
-    </row>
-    <row r="351" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D350" s="9">
+        <v>5780</v>
+      </c>
+      <c r="E350" s="9">
+        <v>6100</v>
+      </c>
+      <c r="F350" t="s">
+        <v>147</v>
+      </c>
+      <c r="G350" s="7">
+        <v>18</v>
+      </c>
+      <c r="H350" t="s">
+        <v>86</v>
+      </c>
+      <c r="I350" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>88</v>
+      </c>
+      <c r="B351" t="s">
+        <v>12</v>
+      </c>
       <c r="C351" s="9"/>
-      <c r="D351" s="9"/>
-      <c r="E351" s="9"/>
-      <c r="G351" s="7"/>
-    </row>
-    <row r="352" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D351" s="9">
+        <v>5850</v>
+      </c>
+      <c r="E351" s="9">
+        <v>6150</v>
+      </c>
+      <c r="F351" t="s">
+        <v>147</v>
+      </c>
+      <c r="G351" s="7">
+        <v>17</v>
+      </c>
+      <c r="H351" t="s">
+        <v>71</v>
+      </c>
+      <c r="I351" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>89</v>
+      </c>
+      <c r="B352" t="s">
+        <v>12</v>
+      </c>
       <c r="C352" s="9"/>
-      <c r="D352" s="9"/>
-      <c r="E352" s="9"/>
-      <c r="G352" s="7"/>
-    </row>
-    <row r="353" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D352" s="9">
+        <v>5850</v>
+      </c>
+      <c r="E352" s="9">
+        <v>6150</v>
+      </c>
+      <c r="F352" t="s">
+        <v>147</v>
+      </c>
+      <c r="G352" s="7">
+        <v>17</v>
+      </c>
+      <c r="H352" t="s">
+        <v>71</v>
+      </c>
+      <c r="I352" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>75</v>
+      </c>
+      <c r="B353" t="s">
+        <v>12</v>
+      </c>
       <c r="C353" s="9"/>
-      <c r="D353" s="9"/>
-      <c r="E353" s="9"/>
-      <c r="G353" s="7"/>
-    </row>
-    <row r="354" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D353" s="9">
+        <v>5850</v>
+      </c>
+      <c r="E353" s="9">
+        <v>6150</v>
+      </c>
+      <c r="F353" t="s">
+        <v>147</v>
+      </c>
+      <c r="G353" s="7">
+        <v>17</v>
+      </c>
+      <c r="H353" t="s">
+        <v>71</v>
+      </c>
+      <c r="I353" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>74</v>
+      </c>
+      <c r="B354" t="s">
+        <v>12</v>
+      </c>
       <c r="C354" s="9"/>
-      <c r="D354" s="9"/>
-      <c r="E354" s="9"/>
-      <c r="G354" s="7"/>
-    </row>
-    <row r="355" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D354" s="9">
+        <v>5850</v>
+      </c>
+      <c r="E354" s="9">
+        <v>6150</v>
+      </c>
+      <c r="F354" t="s">
+        <v>147</v>
+      </c>
+      <c r="G354" s="7">
+        <v>17</v>
+      </c>
+      <c r="H354" t="s">
+        <v>71</v>
+      </c>
+      <c r="I354" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>90</v>
+      </c>
+      <c r="B355" t="s">
+        <v>12</v>
+      </c>
       <c r="C355" s="9"/>
-      <c r="D355" s="9"/>
-      <c r="E355" s="9"/>
-      <c r="G355" s="7"/>
-    </row>
-    <row r="356" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D355" s="9">
+        <v>5850</v>
+      </c>
+      <c r="E355" s="9">
+        <v>6150</v>
+      </c>
+      <c r="F355" t="s">
+        <v>147</v>
+      </c>
+      <c r="G355" s="7">
+        <v>17</v>
+      </c>
+      <c r="H355" t="s">
+        <v>71</v>
+      </c>
+      <c r="I355" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>89</v>
+      </c>
+      <c r="B356" t="s">
+        <v>12</v>
+      </c>
       <c r="C356" s="9"/>
-      <c r="D356" s="9"/>
-      <c r="E356" s="9"/>
-      <c r="G356" s="7"/>
-    </row>
-    <row r="357" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D356" s="9">
+        <v>6040</v>
+      </c>
+      <c r="E356" s="9">
+        <v>6240</v>
+      </c>
+      <c r="F356" t="s">
+        <v>147</v>
+      </c>
+      <c r="G356" s="7">
+        <v>18</v>
+      </c>
+      <c r="H356" t="s">
+        <v>72</v>
+      </c>
+      <c r="I356" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>88</v>
+      </c>
+      <c r="B357" t="s">
+        <v>12</v>
+      </c>
       <c r="C357" s="9"/>
-      <c r="D357" s="9"/>
-      <c r="E357" s="9"/>
-      <c r="G357" s="7"/>
-    </row>
-    <row r="358" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D357" s="9">
+        <v>6040</v>
+      </c>
+      <c r="E357" s="9">
+        <v>6340</v>
+      </c>
+      <c r="F357" t="s">
+        <v>147</v>
+      </c>
+      <c r="G357" s="7">
+        <v>18</v>
+      </c>
+      <c r="H357" t="s">
+        <v>72</v>
+      </c>
+      <c r="I357" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>74</v>
+      </c>
+      <c r="B358" t="s">
+        <v>12</v>
+      </c>
       <c r="C358" s="9"/>
-      <c r="D358" s="9"/>
-      <c r="E358" s="9"/>
-      <c r="G358" s="7"/>
-    </row>
-    <row r="359" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D358" s="9">
+        <v>6040</v>
+      </c>
+      <c r="E358" s="9">
+        <v>6340</v>
+      </c>
+      <c r="F358" t="s">
+        <v>147</v>
+      </c>
+      <c r="G358" s="7">
+        <v>18</v>
+      </c>
+      <c r="H358" t="s">
+        <v>72</v>
+      </c>
+      <c r="I358" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>75</v>
+      </c>
+      <c r="B359" t="s">
+        <v>12</v>
+      </c>
       <c r="C359" s="9"/>
-      <c r="D359" s="9"/>
-      <c r="E359" s="9"/>
-      <c r="G359" s="7"/>
-    </row>
-    <row r="360" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D359" s="9">
+        <v>6040</v>
+      </c>
+      <c r="E359" s="9">
+        <v>6340</v>
+      </c>
+      <c r="F359" t="s">
+        <v>147</v>
+      </c>
+      <c r="G359" s="7">
+        <v>18</v>
+      </c>
+      <c r="H359" t="s">
+        <v>72</v>
+      </c>
+      <c r="I359" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>90</v>
+      </c>
+      <c r="B360" t="s">
+        <v>12</v>
+      </c>
       <c r="C360" s="9"/>
-      <c r="D360" s="9"/>
-      <c r="E360" s="9"/>
-      <c r="G360" s="7"/>
-    </row>
-    <row r="361" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D360" s="9">
+        <v>6040</v>
+      </c>
+      <c r="E360" s="9">
+        <v>6340</v>
+      </c>
+      <c r="F360" t="s">
+        <v>147</v>
+      </c>
+      <c r="G360" s="7">
+        <v>18</v>
+      </c>
+      <c r="H360" t="s">
+        <v>72</v>
+      </c>
+      <c r="I360" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>88</v>
+      </c>
+      <c r="B361" t="s">
+        <v>12</v>
+      </c>
       <c r="C361" s="9"/>
-      <c r="D361" s="9"/>
-      <c r="E361" s="9"/>
-      <c r="G361" s="7"/>
-    </row>
-    <row r="362" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D361" s="9">
+        <v>6070</v>
+      </c>
+      <c r="E361" s="9">
+        <v>6370</v>
+      </c>
+      <c r="F361" t="s">
+        <v>147</v>
+      </c>
+      <c r="G361" s="7">
+        <v>21</v>
+      </c>
+      <c r="H361" t="s">
+        <v>148</v>
+      </c>
+      <c r="I361" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>89</v>
+      </c>
+      <c r="B362" t="s">
+        <v>12</v>
+      </c>
       <c r="C362" s="9"/>
-      <c r="D362" s="9"/>
-      <c r="E362" s="9"/>
-      <c r="G362" s="7"/>
-    </row>
-    <row r="363" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D362" s="9">
+        <v>6070</v>
+      </c>
+      <c r="E362" s="9">
+        <v>6370</v>
+      </c>
+      <c r="F362" t="s">
+        <v>147</v>
+      </c>
+      <c r="G362" s="7">
+        <v>21</v>
+      </c>
+      <c r="H362" t="s">
+        <v>148</v>
+      </c>
+      <c r="I362" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>75</v>
+      </c>
+      <c r="B363" t="s">
+        <v>12</v>
+      </c>
       <c r="C363" s="9"/>
-      <c r="D363" s="9"/>
-      <c r="E363" s="9"/>
-      <c r="G363" s="7"/>
-    </row>
-    <row r="364" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D363" s="9">
+        <v>6070</v>
+      </c>
+      <c r="E363" s="9">
+        <v>6370</v>
+      </c>
+      <c r="F363" t="s">
+        <v>147</v>
+      </c>
+      <c r="G363" s="7">
+        <v>21</v>
+      </c>
+      <c r="H363" t="s">
+        <v>148</v>
+      </c>
+      <c r="I363" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>74</v>
+      </c>
+      <c r="B364" t="s">
+        <v>12</v>
+      </c>
       <c r="C364" s="9"/>
-      <c r="D364" s="9"/>
-      <c r="E364" s="9"/>
-      <c r="G364" s="7"/>
-    </row>
-    <row r="365" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D364" s="9">
+        <v>6070</v>
+      </c>
+      <c r="E364" s="9">
+        <v>6370</v>
+      </c>
+      <c r="F364" t="s">
+        <v>147</v>
+      </c>
+      <c r="G364" s="7">
+        <v>21</v>
+      </c>
+      <c r="H364" t="s">
+        <v>148</v>
+      </c>
+      <c r="I364" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C365" s="9"/>
       <c r="D365" s="9"/>
       <c r="E365" s="9"/>
       <c r="G365" s="7"/>
     </row>
-    <row r="366" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C366" s="9"/>
       <c r="D366" s="9"/>
       <c r="E366" s="9"/>
       <c r="G366" s="7"/>
     </row>
-    <row r="367" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C367" s="9"/>
       <c r="D367" s="9"/>
       <c r="E367" s="9"/>
       <c r="G367" s="7"/>
     </row>
-    <row r="368" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C368" s="9"/>
       <c r="D368" s="9"/>
       <c r="E368" s="9"/>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DOCS EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE8FCED-794C-4DA2-BB98-9FC110EE8F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD479500-9F89-4BF9-B900-6A8436A6888C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="156">
   <si>
     <t>POD</t>
   </si>
@@ -306,9 +306,6 @@
     <t>OOCL</t>
   </si>
   <si>
-    <t>OOCL 20GP ≥ 18TN AGREGAR OWS $250</t>
-  </si>
-  <si>
     <t>SHANGHAI</t>
   </si>
   <si>
@@ -493,6 +490,27 @@
   </si>
   <si>
     <t>CMA</t>
+  </si>
+  <si>
+    <t>Z-ES</t>
+  </si>
+  <si>
+    <t>YML (Z-ES) PESO LÍMITE 20GP HASTA 16TN</t>
+  </si>
+  <si>
+    <t>OOCL (Z-HF) 20GP ≥ 18TN AGREGAR OWS $250</t>
+  </si>
+  <si>
+    <t>Z-HF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHANGHAI </t>
+  </si>
+  <si>
+    <t>KAOSHIUNG</t>
+  </si>
+  <si>
+    <t>EMC</t>
   </si>
 </sst>
 </file>
@@ -1031,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}">
-  <dimension ref="A1:I689"/>
+  <dimension ref="A1:I688"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
@@ -1084,7 +1102,7 @@
         <v>6850</v>
       </c>
       <c r="F2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G2" s="7">
         <v>18</v>
@@ -1111,7 +1129,7 @@
         <v>7250</v>
       </c>
       <c r="F3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G3" s="7">
         <v>18</v>
@@ -1138,7 +1156,7 @@
         <v>6850</v>
       </c>
       <c r="F4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G4" s="7">
         <v>18</v>
@@ -1165,7 +1183,7 @@
         <v>6850</v>
       </c>
       <c r="F5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G5" s="7">
         <v>18</v>
@@ -1192,7 +1210,7 @@
         <v>6850</v>
       </c>
       <c r="F6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G6" s="7">
         <v>18</v>
@@ -1219,7 +1237,7 @@
         <v>6650</v>
       </c>
       <c r="F7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G7" s="7">
         <v>18</v>
@@ -1246,7 +1264,7 @@
         <v>6650</v>
       </c>
       <c r="F8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G8" s="7">
         <v>18</v>
@@ -1273,7 +1291,7 @@
         <v>6950</v>
       </c>
       <c r="F9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G9" s="7">
         <v>18</v>
@@ -1300,7 +1318,7 @@
         <v>6650</v>
       </c>
       <c r="F10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G10" s="7">
         <v>18</v>
@@ -1327,7 +1345,7 @@
         <v>6650</v>
       </c>
       <c r="F11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G11" s="7">
         <v>18</v>
@@ -1354,7 +1372,7 @@
         <v>6650</v>
       </c>
       <c r="F12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G12" s="7">
         <v>18</v>
@@ -1381,7 +1399,7 @@
         <v>6650</v>
       </c>
       <c r="F13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G13" s="7">
         <v>18</v>
@@ -1408,7 +1426,7 @@
         <v>6650</v>
       </c>
       <c r="F14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G14" s="7">
         <v>18</v>
@@ -1435,7 +1453,7 @@
         <v>6650</v>
       </c>
       <c r="F15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G15" s="7">
         <v>18</v>
@@ -1462,7 +1480,7 @@
         <v>6650</v>
       </c>
       <c r="F16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G16" s="7">
         <v>18</v>
@@ -1489,7 +1507,7 @@
         <v>6650</v>
       </c>
       <c r="F17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G17" s="7">
         <v>18</v>
@@ -1516,7 +1534,7 @@
         <v>6650</v>
       </c>
       <c r="F18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G18" s="7">
         <v>18</v>
@@ -1543,7 +1561,7 @@
         <v>6650</v>
       </c>
       <c r="F19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G19" s="7">
         <v>18</v>
@@ -1570,7 +1588,7 @@
         <v>6950</v>
       </c>
       <c r="F20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G20" s="7">
         <v>18</v>
@@ -1597,7 +1615,7 @@
         <v>6650</v>
       </c>
       <c r="F21" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G21" s="7">
         <v>18</v>
@@ -1624,7 +1642,7 @@
         <v>6650</v>
       </c>
       <c r="F22" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G22" s="7">
         <v>18</v>
@@ -1638,7 +1656,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B23" t="s">
         <v>12</v>
@@ -1651,7 +1669,7 @@
         <v>7050</v>
       </c>
       <c r="F23" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G23" s="7">
         <v>18</v>
@@ -1678,7 +1696,7 @@
         <v>5650</v>
       </c>
       <c r="F24" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G24" s="7">
         <v>18</v>
@@ -1705,7 +1723,7 @@
         <v>5650</v>
       </c>
       <c r="F25" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G25" s="7">
         <v>18</v>
@@ -1732,7 +1750,7 @@
         <v>5650</v>
       </c>
       <c r="F26" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G26" s="7">
         <v>18</v>
@@ -1759,7 +1777,7 @@
         <v>5650</v>
       </c>
       <c r="F27" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G27" s="7">
         <v>18</v>
@@ -1786,7 +1804,7 @@
         <v>5650</v>
       </c>
       <c r="F28" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G28" s="7">
         <v>18</v>
@@ -1813,7 +1831,7 @@
         <v>5950</v>
       </c>
       <c r="F29" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G29" s="7">
         <v>18</v>
@@ -1840,7 +1858,7 @@
         <v>5950</v>
       </c>
       <c r="F30" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G30" s="7">
         <v>18</v>
@@ -1854,7 +1872,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B31" t="s">
         <v>12</v>
@@ -1867,7 +1885,7 @@
         <v>5650</v>
       </c>
       <c r="F31" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G31" s="7">
         <v>18</v>
@@ -1894,7 +1912,7 @@
         <v>6250</v>
       </c>
       <c r="F32" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G32" s="7">
         <v>18</v>
@@ -1908,7 +1926,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B33" t="s">
         <v>12</v>
@@ -1921,7 +1939,7 @@
         <v>6250</v>
       </c>
       <c r="F33" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G33" s="7">
         <v>18</v>
@@ -1935,7 +1953,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B34" t="s">
         <v>12</v>
@@ -1948,7 +1966,7 @@
         <v>6250</v>
       </c>
       <c r="F34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G34" s="7">
         <v>18</v>
@@ -1975,7 +1993,7 @@
         <v>6750</v>
       </c>
       <c r="F35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G35" s="7">
         <v>18</v>
@@ -2002,7 +2020,7 @@
         <v>6650</v>
       </c>
       <c r="F36" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G36" s="7">
         <v>18</v>
@@ -2029,7 +2047,7 @@
         <v>6150</v>
       </c>
       <c r="F37" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G37" s="7">
         <v>18</v>
@@ -2056,7 +2074,7 @@
         <v>6150</v>
       </c>
       <c r="F38" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G38" s="7">
         <v>18</v>
@@ -2070,7 +2088,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B39" t="s">
         <v>12</v>
@@ -2083,7 +2101,7 @@
         <v>6300</v>
       </c>
       <c r="F39" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G39" s="7">
         <v>18</v>
@@ -2110,7 +2128,7 @@
         <v>6150</v>
       </c>
       <c r="F40" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G40" s="7">
         <v>18</v>
@@ -2137,7 +2155,7 @@
         <v>5950</v>
       </c>
       <c r="F41" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G41" s="7">
         <v>18</v>
@@ -2164,7 +2182,7 @@
         <v>6650</v>
       </c>
       <c r="F42" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G42" s="7">
         <v>18</v>
@@ -2191,7 +2209,7 @@
         <v>5950</v>
       </c>
       <c r="F43" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G43" s="7">
         <v>18</v>
@@ -2218,7 +2236,7 @@
         <v>5950</v>
       </c>
       <c r="F44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G44" s="7">
         <v>18</v>
@@ -2245,7 +2263,7 @@
         <v>5950</v>
       </c>
       <c r="F45" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G45" s="7">
         <v>18</v>
@@ -2259,7 +2277,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B46" t="s">
         <v>12</v>
@@ -2272,7 +2290,7 @@
         <v>5950</v>
       </c>
       <c r="F46" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G46" s="7">
         <v>18</v>
@@ -2299,7 +2317,7 @@
         <v>6160</v>
       </c>
       <c r="F47" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G47" s="7">
         <v>18</v>
@@ -2326,7 +2344,7 @@
         <v>6350</v>
       </c>
       <c r="F48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G48" s="7">
         <v>18</v>
@@ -2353,7 +2371,7 @@
         <v>6350</v>
       </c>
       <c r="F49" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G49" s="7">
         <v>18</v>
@@ -2380,7 +2398,7 @@
         <v>6450</v>
       </c>
       <c r="F50" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G50" s="7">
         <v>18</v>
@@ -2407,7 +2425,7 @@
         <v>6450</v>
       </c>
       <c r="F51" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G51" s="7">
         <v>18</v>
@@ -2434,7 +2452,7 @@
         <v>6150</v>
       </c>
       <c r="F52" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G52" s="7">
         <v>18</v>
@@ -2448,7 +2466,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B53" t="s">
         <v>12</v>
@@ -2463,7 +2481,7 @@
         <v>6230</v>
       </c>
       <c r="F53" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>85</v>
@@ -2477,7 +2495,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B54" t="s">
         <v>12</v>
@@ -2492,7 +2510,7 @@
         <v>6230</v>
       </c>
       <c r="F54" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>85</v>
@@ -2521,7 +2539,7 @@
         <v>6230</v>
       </c>
       <c r="F55" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G55" s="7" t="s">
         <v>85</v>
@@ -2550,7 +2568,7 @@
         <v>6230</v>
       </c>
       <c r="F56" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G56" s="7" t="s">
         <v>85</v>
@@ -2579,7 +2597,7 @@
         <v>6230</v>
       </c>
       <c r="F57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G57" s="7" t="s">
         <v>85</v>
@@ -2593,7 +2611,7 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B58" t="s">
         <v>12</v>
@@ -2608,7 +2626,7 @@
         <v>6230</v>
       </c>
       <c r="F58" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G58" s="7" t="s">
         <v>85</v>
@@ -2637,7 +2655,7 @@
         <v>6230</v>
       </c>
       <c r="F59" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G59" s="7" t="s">
         <v>85</v>
@@ -2666,7 +2684,7 @@
         <v>6230</v>
       </c>
       <c r="F60" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G60" s="7" t="s">
         <v>85</v>
@@ -2680,7 +2698,7 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B61" t="s">
         <v>12</v>
@@ -2695,7 +2713,7 @@
         <v>6480</v>
       </c>
       <c r="F61" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G61" s="7" t="s">
         <v>85</v>
@@ -2709,7 +2727,7 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B62" t="s">
         <v>12</v>
@@ -2724,7 +2742,7 @@
         <v>6430</v>
       </c>
       <c r="F62" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G62" s="7" t="s">
         <v>85</v>
@@ -2753,7 +2771,7 @@
         <v>6480</v>
       </c>
       <c r="F63" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G63" s="7" t="s">
         <v>85</v>
@@ -2782,7 +2800,7 @@
         <v>6330</v>
       </c>
       <c r="F64" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G64" s="7" t="s">
         <v>85</v>
@@ -2811,7 +2829,7 @@
         <v>6330</v>
       </c>
       <c r="F65" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G65" s="7" t="s">
         <v>85</v>
@@ -2825,7 +2843,7 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B66" t="s">
         <v>12</v>
@@ -2840,7 +2858,7 @@
         <v>6330</v>
       </c>
       <c r="F66" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G66" s="7" t="s">
         <v>85</v>
@@ -2869,7 +2887,7 @@
         <v>6330</v>
       </c>
       <c r="F67" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G67" s="7" t="s">
         <v>85</v>
@@ -2898,7 +2916,7 @@
         <v>6330</v>
       </c>
       <c r="F68" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G68" s="7" t="s">
         <v>85</v>
@@ -2912,7 +2930,7 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B69" t="s">
         <v>12</v>
@@ -2927,7 +2945,7 @@
         <v>6330</v>
       </c>
       <c r="F69" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G69" s="7" t="s">
         <v>85</v>
@@ -2941,7 +2959,7 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B70" t="s">
         <v>12</v>
@@ -2956,7 +2974,7 @@
         <v>6330</v>
       </c>
       <c r="F70" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G70" s="7" t="s">
         <v>85</v>
@@ -2970,7 +2988,7 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B71" t="s">
         <v>12</v>
@@ -2985,7 +3003,7 @@
         <v>6330</v>
       </c>
       <c r="F71" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G71" s="7" t="s">
         <v>85</v>
@@ -2999,7 +3017,7 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B72" t="s">
         <v>12</v>
@@ -3014,7 +3032,7 @@
         <v>6330</v>
       </c>
       <c r="F72" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G72" s="7" t="s">
         <v>85</v>
@@ -3028,7 +3046,7 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B73" t="s">
         <v>12</v>
@@ -3043,7 +3061,7 @@
         <v>6330</v>
       </c>
       <c r="F73" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G73" s="7" t="s">
         <v>85</v>
@@ -3057,7 +3075,7 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B74" t="s">
         <v>12</v>
@@ -3072,7 +3090,7 @@
         <v>6330</v>
       </c>
       <c r="F74" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G74" s="7" t="s">
         <v>85</v>
@@ -3086,7 +3104,7 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B75" t="s">
         <v>12</v>
@@ -3101,7 +3119,7 @@
         <v>6380</v>
       </c>
       <c r="F75" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G75" s="7" t="s">
         <v>85</v>
@@ -3115,7 +3133,7 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B76" t="s">
         <v>12</v>
@@ -3130,7 +3148,7 @@
         <v>7030</v>
       </c>
       <c r="F76" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G76" s="7" t="s">
         <v>85</v>
@@ -3144,7 +3162,7 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B77" t="s">
         <v>12</v>
@@ -3159,7 +3177,7 @@
         <v>6530</v>
       </c>
       <c r="F77" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G77" s="7" t="s">
         <v>85</v>
@@ -3173,7 +3191,7 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B78" t="s">
         <v>12</v>
@@ -3188,7 +3206,7 @@
         <v>6730</v>
       </c>
       <c r="F78" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G78" s="7" t="s">
         <v>85</v>
@@ -3202,7 +3220,7 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B79" t="s">
         <v>12</v>
@@ -3217,7 +3235,7 @@
         <v>6730</v>
       </c>
       <c r="F79" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G79" s="7" t="s">
         <v>85</v>
@@ -3231,7 +3249,7 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B80" t="s">
         <v>12</v>
@@ -3246,7 +3264,7 @@
         <v>6430</v>
       </c>
       <c r="F80" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G80" s="7" t="s">
         <v>85</v>
@@ -3260,7 +3278,7 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B81" t="s">
         <v>12</v>
@@ -3275,7 +3293,7 @@
         <v>6530</v>
       </c>
       <c r="F81" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G81" s="7" t="s">
         <v>85</v>
@@ -3289,7 +3307,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B82" t="s">
         <v>12</v>
@@ -3304,7 +3322,7 @@
         <v>6530</v>
       </c>
       <c r="F82" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G82" s="7" t="s">
         <v>85</v>
@@ -3318,7 +3336,7 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B83" t="s">
         <v>12</v>
@@ -3333,7 +3351,7 @@
         <v>6530</v>
       </c>
       <c r="F83" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G83" s="7" t="s">
         <v>85</v>
@@ -3347,7 +3365,7 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B84" t="s">
         <v>12</v>
@@ -3362,7 +3380,7 @@
         <v>6530</v>
       </c>
       <c r="F84" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G84" s="7" t="s">
         <v>85</v>
@@ -3376,7 +3394,7 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B85" t="s">
         <v>12</v>
@@ -3391,7 +3409,7 @@
         <v>6530</v>
       </c>
       <c r="F85" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G85" s="7" t="s">
         <v>85</v>
@@ -3405,7 +3423,7 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B86" t="s">
         <v>12</v>
@@ -3420,7 +3438,7 @@
         <v>6530</v>
       </c>
       <c r="F86" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G86" s="7" t="s">
         <v>85</v>
@@ -3434,7 +3452,7 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B87" t="s">
         <v>12</v>
@@ -3449,7 +3467,7 @@
         <v>6530</v>
       </c>
       <c r="F87" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G87" s="7" t="s">
         <v>85</v>
@@ -3463,7 +3481,7 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B88" t="s">
         <v>12</v>
@@ -3478,7 +3496,7 @@
         <v>6530</v>
       </c>
       <c r="F88" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G88" s="7" t="s">
         <v>85</v>
@@ -3492,7 +3510,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B89" t="s">
         <v>12</v>
@@ -3507,7 +3525,7 @@
         <v>6530</v>
       </c>
       <c r="F89" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G89" s="7" t="s">
         <v>85</v>
@@ -3521,7 +3539,7 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B90" t="s">
         <v>12</v>
@@ -3536,7 +3554,7 @@
         <v>6680</v>
       </c>
       <c r="F90" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G90" s="7" t="s">
         <v>85</v>
@@ -3550,7 +3568,7 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B91" t="s">
         <v>12</v>
@@ -3565,7 +3583,7 @@
         <v>6730</v>
       </c>
       <c r="F91" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G91" s="7" t="s">
         <v>85</v>
@@ -3579,7 +3597,7 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B92" t="s">
         <v>12</v>
@@ -3594,7 +3612,7 @@
         <v>6680</v>
       </c>
       <c r="F92" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G92" s="7" t="s">
         <v>85</v>
@@ -3608,7 +3626,7 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B93" t="s">
         <v>12</v>
@@ -3623,7 +3641,7 @@
         <v>6780</v>
       </c>
       <c r="F93" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G93" s="7" t="s">
         <v>85</v>
@@ -3637,7 +3655,7 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B94" t="s">
         <v>12</v>
@@ -3652,7 +3670,7 @@
         <v>7240</v>
       </c>
       <c r="F94" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G94" s="7" t="s">
         <v>85</v>
@@ -3666,7 +3684,7 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B95" t="s">
         <v>12</v>
@@ -3681,7 +3699,7 @@
         <v>6500</v>
       </c>
       <c r="F95" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G95" s="7" t="s">
         <v>85</v>
@@ -3695,7 +3713,7 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B96" t="s">
         <v>12</v>
@@ -3710,7 +3728,7 @@
         <v>6500</v>
       </c>
       <c r="F96" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G96" s="7" t="s">
         <v>85</v>
@@ -3724,7 +3742,7 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B97" t="s">
         <v>12</v>
@@ -3739,7 +3757,7 @@
         <v>6500</v>
       </c>
       <c r="F97" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G97" s="7" t="s">
         <v>85</v>
@@ -3753,7 +3771,7 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B98" t="s">
         <v>12</v>
@@ -3768,7 +3786,7 @@
         <v>6660</v>
       </c>
       <c r="F98" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G98" s="7" t="s">
         <v>85</v>
@@ -3782,7 +3800,7 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B99" t="s">
         <v>12</v>
@@ -3797,7 +3815,7 @@
         <v>6660</v>
       </c>
       <c r="F99" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G99" s="7" t="s">
         <v>85</v>
@@ -3811,7 +3829,7 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B100" t="s">
         <v>12</v>
@@ -3826,10 +3844,10 @@
         <v>6130</v>
       </c>
       <c r="F100" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H100" t="s">
         <v>71</v>
@@ -3840,7 +3858,7 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B101" t="s">
         <v>12</v>
@@ -3855,10 +3873,10 @@
         <v>6130</v>
       </c>
       <c r="F101" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H101" t="s">
         <v>71</v>
@@ -3884,10 +3902,10 @@
         <v>6130</v>
       </c>
       <c r="F102" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H102" t="s">
         <v>71</v>
@@ -3913,10 +3931,10 @@
         <v>6130</v>
       </c>
       <c r="F103" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H103" t="s">
         <v>71</v>
@@ -3942,10 +3960,10 @@
         <v>6130</v>
       </c>
       <c r="F104" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H104" t="s">
         <v>71</v>
@@ -3956,7 +3974,7 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B105" t="s">
         <v>12</v>
@@ -3971,10 +3989,10 @@
         <v>6130</v>
       </c>
       <c r="F105" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H105" t="s">
         <v>71</v>
@@ -4000,10 +4018,10 @@
         <v>6130</v>
       </c>
       <c r="F106" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G106" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H106" t="s">
         <v>71</v>
@@ -4029,10 +4047,10 @@
         <v>6130</v>
       </c>
       <c r="F107" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G107" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H107" t="s">
         <v>71</v>
@@ -4043,7 +4061,7 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B108" t="s">
         <v>12</v>
@@ -4058,10 +4076,10 @@
         <v>6130</v>
       </c>
       <c r="F108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G108" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H108" t="s">
         <v>71</v>
@@ -4072,7 +4090,7 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B109" t="s">
         <v>12</v>
@@ -4087,10 +4105,10 @@
         <v>6330</v>
       </c>
       <c r="F109" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G109" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H109" t="s">
         <v>71</v>
@@ -4116,10 +4134,10 @@
         <v>6130</v>
       </c>
       <c r="F110" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G110" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H110" t="s">
         <v>71</v>
@@ -4145,10 +4163,10 @@
         <v>6280</v>
       </c>
       <c r="F111" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H111" t="s">
         <v>71</v>
@@ -4174,10 +4192,10 @@
         <v>6230</v>
       </c>
       <c r="F112" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G112" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H112" t="s">
         <v>71</v>
@@ -4188,7 +4206,7 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B113" t="s">
         <v>12</v>
@@ -4203,10 +4221,10 @@
         <v>6230</v>
       </c>
       <c r="F113" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G113" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H113" t="s">
         <v>71</v>
@@ -4232,10 +4250,10 @@
         <v>6230</v>
       </c>
       <c r="F114" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G114" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H114" t="s">
         <v>71</v>
@@ -4261,10 +4279,10 @@
         <v>6230</v>
       </c>
       <c r="F115" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G115" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H115" t="s">
         <v>71</v>
@@ -4275,7 +4293,7 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B116" t="s">
         <v>12</v>
@@ -4290,10 +4308,10 @@
         <v>6230</v>
       </c>
       <c r="F116" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G116" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H116" t="s">
         <v>71</v>
@@ -4304,7 +4322,7 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B117" t="s">
         <v>12</v>
@@ -4319,10 +4337,10 @@
         <v>6230</v>
       </c>
       <c r="F117" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G117" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H117" t="s">
         <v>71</v>
@@ -4333,7 +4351,7 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B118" t="s">
         <v>12</v>
@@ -4348,10 +4366,10 @@
         <v>6230</v>
       </c>
       <c r="F118" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G118" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H118" t="s">
         <v>71</v>
@@ -4362,7 +4380,7 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B119" t="s">
         <v>12</v>
@@ -4377,10 +4395,10 @@
         <v>6230</v>
       </c>
       <c r="F119" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G119" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H119" t="s">
         <v>71</v>
@@ -4391,7 +4409,7 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B120" t="s">
         <v>12</v>
@@ -4406,10 +4424,10 @@
         <v>6230</v>
       </c>
       <c r="F120" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G120" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H120" t="s">
         <v>71</v>
@@ -4420,7 +4438,7 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B121" t="s">
         <v>12</v>
@@ -4435,10 +4453,10 @@
         <v>6230</v>
       </c>
       <c r="F121" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G121" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H121" t="s">
         <v>71</v>
@@ -4449,7 +4467,7 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B122" t="s">
         <v>12</v>
@@ -4464,10 +4482,10 @@
         <v>6430</v>
       </c>
       <c r="F122" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G122" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H122" t="s">
         <v>71</v>
@@ -4478,7 +4496,7 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B123" t="s">
         <v>12</v>
@@ -4491,7 +4509,7 @@
         <v>6430</v>
       </c>
       <c r="F123" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G123" s="7">
         <v>17</v>
@@ -4505,7 +4523,7 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B124" t="s">
         <v>12</v>
@@ -4518,7 +4536,7 @@
         <v>6470</v>
       </c>
       <c r="F124" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G124" s="7">
         <v>17</v>
@@ -4532,7 +4550,7 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B125" t="s">
         <v>12</v>
@@ -4545,7 +4563,7 @@
         <v>6430</v>
       </c>
       <c r="F125" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G125" s="7">
         <v>17</v>
@@ -4559,7 +4577,7 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B126" t="s">
         <v>12</v>
@@ -4572,7 +4590,7 @@
         <v>6560</v>
       </c>
       <c r="F126" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G126" s="7">
         <v>17</v>
@@ -4586,7 +4604,7 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B127" t="s">
         <v>12</v>
@@ -4599,7 +4617,7 @@
         <v>6440</v>
       </c>
       <c r="F127" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G127" s="7">
         <v>17</v>
@@ -4613,7 +4631,7 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B128" t="s">
         <v>12</v>
@@ -4626,7 +4644,7 @@
         <v>6450</v>
       </c>
       <c r="F128" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G128" s="7">
         <v>17</v>
@@ -4640,7 +4658,7 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B129" t="s">
         <v>12</v>
@@ -4653,7 +4671,7 @@
         <v>6340</v>
       </c>
       <c r="F129" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G129" s="7">
         <v>17</v>
@@ -4667,7 +4685,7 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B130" t="s">
         <v>12</v>
@@ -4680,7 +4698,7 @@
         <v>6340</v>
       </c>
       <c r="F130" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G130" s="7">
         <v>17</v>
@@ -4694,7 +4712,7 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B131" t="s">
         <v>12</v>
@@ -4707,7 +4725,7 @@
         <v>6340</v>
       </c>
       <c r="F131" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G131" s="7">
         <v>17</v>
@@ -4721,7 +4739,7 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B132" t="s">
         <v>12</v>
@@ -4734,7 +4752,7 @@
         <v>6340</v>
       </c>
       <c r="F132" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G132" s="7">
         <v>17</v>
@@ -4748,7 +4766,7 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B133" t="s">
         <v>12</v>
@@ -4761,7 +4779,7 @@
         <v>6340</v>
       </c>
       <c r="F133" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G133" s="7">
         <v>17</v>
@@ -4775,7 +4793,7 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B134" t="s">
         <v>12</v>
@@ -4788,7 +4806,7 @@
         <v>6340</v>
       </c>
       <c r="F134" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G134" s="7">
         <v>17</v>
@@ -4802,7 +4820,7 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B135" t="s">
         <v>12</v>
@@ -4815,7 +4833,7 @@
         <v>6340</v>
       </c>
       <c r="F135" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G135" s="7">
         <v>17</v>
@@ -4829,7 +4847,7 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B136" t="s">
         <v>12</v>
@@ -4842,7 +4860,7 @@
         <v>6340</v>
       </c>
       <c r="F136" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G136" s="7">
         <v>17</v>
@@ -4856,7 +4874,7 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B137" t="s">
         <v>12</v>
@@ -4869,7 +4887,7 @@
         <v>6550</v>
       </c>
       <c r="F137" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G137" s="7">
         <v>17</v>
@@ -4883,7 +4901,7 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B138" t="s">
         <v>12</v>
@@ -4896,7 +4914,7 @@
         <v>6520</v>
       </c>
       <c r="F138" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G138" s="7">
         <v>17</v>
@@ -4910,7 +4928,7 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B139" t="s">
         <v>12</v>
@@ -4923,7 +4941,7 @@
         <v>6580</v>
       </c>
       <c r="F139" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G139" s="7">
         <v>17</v>
@@ -4937,7 +4955,7 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B140" t="s">
         <v>12</v>
@@ -4950,7 +4968,7 @@
         <v>6580</v>
       </c>
       <c r="F140" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G140" s="7">
         <v>17</v>
@@ -4964,7 +4982,7 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B141" t="s">
         <v>12</v>
@@ -4977,7 +4995,7 @@
         <v>6920</v>
       </c>
       <c r="F141" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G141" s="7">
         <v>17</v>
@@ -4991,7 +5009,7 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B142" t="s">
         <v>12</v>
@@ -5004,7 +5022,7 @@
         <v>6280</v>
       </c>
       <c r="F142" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G142" s="7">
         <v>17</v>
@@ -5018,7 +5036,7 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B143" t="s">
         <v>12</v>
@@ -5031,7 +5049,7 @@
         <v>6280</v>
       </c>
       <c r="F143" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G143" s="7">
         <v>17</v>
@@ -5045,7 +5063,7 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B144" t="s">
         <v>12</v>
@@ -5058,7 +5076,7 @@
         <v>6280</v>
       </c>
       <c r="F144" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G144" s="7">
         <v>17</v>
@@ -5072,7 +5090,7 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B145" t="s">
         <v>12</v>
@@ -5085,7 +5103,7 @@
         <v>6430</v>
       </c>
       <c r="F145" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G145" s="7">
         <v>17</v>
@@ -5099,7 +5117,7 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B146" t="s">
         <v>12</v>
@@ -5112,7 +5130,7 @@
         <v>6580</v>
       </c>
       <c r="F146" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G146" s="7">
         <v>17</v>
@@ -5126,7 +5144,7 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B147" t="s">
         <v>12</v>
@@ -5139,7 +5157,7 @@
         <v>6240</v>
       </c>
       <c r="F147" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G147" s="7">
         <v>21</v>
@@ -5148,12 +5166,12 @@
         <v>73</v>
       </c>
       <c r="I147" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B148" t="s">
         <v>12</v>
@@ -5166,7 +5184,7 @@
         <v>6240</v>
       </c>
       <c r="F148" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G148" s="7">
         <v>21</v>
@@ -5175,7 +5193,7 @@
         <v>73</v>
       </c>
       <c r="I148" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
@@ -5193,7 +5211,7 @@
         <v>6240</v>
       </c>
       <c r="F149" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G149" s="7">
         <v>21</v>
@@ -5202,7 +5220,7 @@
         <v>73</v>
       </c>
       <c r="I149" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
@@ -5220,7 +5238,7 @@
         <v>6240</v>
       </c>
       <c r="F150" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G150" s="7">
         <v>21</v>
@@ -5229,12 +5247,12 @@
         <v>73</v>
       </c>
       <c r="I150" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B151" t="s">
         <v>12</v>
@@ -5247,7 +5265,7 @@
         <v>6100</v>
       </c>
       <c r="F151" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G151" s="7">
         <v>18</v>
@@ -5256,12 +5274,12 @@
         <v>86</v>
       </c>
       <c r="I151" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B152" t="s">
         <v>12</v>
@@ -5274,7 +5292,7 @@
         <v>6100</v>
       </c>
       <c r="F152" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G152" s="7">
         <v>18</v>
@@ -5283,7 +5301,7 @@
         <v>86</v>
       </c>
       <c r="I152" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
@@ -5301,7 +5319,7 @@
         <v>6100</v>
       </c>
       <c r="F153" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G153" s="7">
         <v>18</v>
@@ -5310,7 +5328,7 @@
         <v>86</v>
       </c>
       <c r="I153" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
@@ -5328,7 +5346,7 @@
         <v>6100</v>
       </c>
       <c r="F154" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G154" s="7">
         <v>18</v>
@@ -5337,12 +5355,12 @@
         <v>86</v>
       </c>
       <c r="I154" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B155" t="s">
         <v>12</v>
@@ -5355,7 +5373,7 @@
         <v>6150</v>
       </c>
       <c r="F155" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G155" s="7">
         <v>17</v>
@@ -5364,12 +5382,12 @@
         <v>71</v>
       </c>
       <c r="I155" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B156" t="s">
         <v>12</v>
@@ -5382,7 +5400,7 @@
         <v>6150</v>
       </c>
       <c r="F156" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G156" s="7">
         <v>17</v>
@@ -5391,7 +5409,7 @@
         <v>71</v>
       </c>
       <c r="I156" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
@@ -5409,7 +5427,7 @@
         <v>6150</v>
       </c>
       <c r="F157" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G157" s="7">
         <v>17</v>
@@ -5418,7 +5436,7 @@
         <v>71</v>
       </c>
       <c r="I157" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
@@ -5436,7 +5454,7 @@
         <v>6150</v>
       </c>
       <c r="F158" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G158" s="7">
         <v>17</v>
@@ -5445,12 +5463,12 @@
         <v>71</v>
       </c>
       <c r="I158" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B159" t="s">
         <v>12</v>
@@ -5463,7 +5481,7 @@
         <v>6150</v>
       </c>
       <c r="F159" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G159" s="7">
         <v>17</v>
@@ -5472,12 +5490,12 @@
         <v>71</v>
       </c>
       <c r="I159" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B160" t="s">
         <v>12</v>
@@ -5490,7 +5508,7 @@
         <v>6240</v>
       </c>
       <c r="F160" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G160" s="7">
         <v>18</v>
@@ -5499,12 +5517,12 @@
         <v>72</v>
       </c>
       <c r="I160" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B161" t="s">
         <v>12</v>
@@ -5517,7 +5535,7 @@
         <v>6340</v>
       </c>
       <c r="F161" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G161" s="7">
         <v>18</v>
@@ -5526,7 +5544,7 @@
         <v>72</v>
       </c>
       <c r="I161" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
@@ -5544,7 +5562,7 @@
         <v>6340</v>
       </c>
       <c r="F162" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G162" s="7">
         <v>18</v>
@@ -5553,7 +5571,7 @@
         <v>72</v>
       </c>
       <c r="I162" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
@@ -5571,7 +5589,7 @@
         <v>6340</v>
       </c>
       <c r="F163" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G163" s="7">
         <v>18</v>
@@ -5580,12 +5598,12 @@
         <v>72</v>
       </c>
       <c r="I163" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B164" t="s">
         <v>12</v>
@@ -5598,7 +5616,7 @@
         <v>6340</v>
       </c>
       <c r="F164" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G164" s="7">
         <v>18</v>
@@ -5607,12 +5625,12 @@
         <v>72</v>
       </c>
       <c r="I164" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B165" t="s">
         <v>12</v>
@@ -5625,21 +5643,21 @@
         <v>6370</v>
       </c>
       <c r="F165" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G165" s="7">
         <v>21</v>
       </c>
       <c r="H165" t="s">
+        <v>145</v>
+      </c>
+      <c r="I165" t="s">
         <v>146</v>
-      </c>
-      <c r="I165" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B166" t="s">
         <v>12</v>
@@ -5652,16 +5670,16 @@
         <v>6370</v>
       </c>
       <c r="F166" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G166" s="7">
         <v>21</v>
       </c>
       <c r="H166" t="s">
+        <v>145</v>
+      </c>
+      <c r="I166" t="s">
         <v>146</v>
-      </c>
-      <c r="I166" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
@@ -5679,16 +5697,16 @@
         <v>6370</v>
       </c>
       <c r="F167" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G167" s="7">
         <v>21</v>
       </c>
       <c r="H167" t="s">
+        <v>145</v>
+      </c>
+      <c r="I167" t="s">
         <v>146</v>
-      </c>
-      <c r="I167" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
@@ -5706,24 +5724,24 @@
         <v>6370</v>
       </c>
       <c r="F168" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G168" s="7">
         <v>21</v>
       </c>
       <c r="H168" t="s">
+        <v>145</v>
+      </c>
+      <c r="I168" t="s">
         <v>146</v>
-      </c>
-      <c r="I168" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B169" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C169" s="9"/>
       <c r="D169" s="9">
@@ -5733,16 +5751,16 @@
         <v>6010</v>
       </c>
       <c r="F169" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G169" s="7">
         <v>21</v>
       </c>
       <c r="H169" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I169" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
@@ -5750,7 +5768,7 @@
         <v>74</v>
       </c>
       <c r="B170" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C170" s="9"/>
       <c r="D170" s="9">
@@ -5760,24 +5778,24 @@
         <v>6010</v>
       </c>
       <c r="F170" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G170" s="7">
         <v>21</v>
       </c>
       <c r="H170" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I170" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B171" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C171" s="9"/>
       <c r="D171" s="9">
@@ -5787,24 +5805,24 @@
         <v>6010</v>
       </c>
       <c r="F171" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G171" s="7">
         <v>21</v>
       </c>
       <c r="H171" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I171" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B172" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C172" s="9"/>
       <c r="D172" s="9">
@@ -5814,24 +5832,24 @@
         <v>6010</v>
       </c>
       <c r="F172" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G172" s="7">
         <v>21</v>
       </c>
       <c r="H172" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I172" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B173" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C173" s="9"/>
       <c r="D173" s="9">
@@ -5841,24 +5859,24 @@
         <v>6010</v>
       </c>
       <c r="F173" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G173" s="7">
         <v>21</v>
       </c>
       <c r="H173" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I173" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B174" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C174" s="9"/>
       <c r="D174" s="9">
@@ -5868,24 +5886,24 @@
         <v>6310</v>
       </c>
       <c r="F174" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G174" s="7">
         <v>21</v>
       </c>
       <c r="H174" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I174" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B175" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C175" s="9"/>
       <c r="D175" s="9">
@@ -5895,16 +5913,16 @@
         <v>6810</v>
       </c>
       <c r="F175" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G175" s="7">
         <v>21</v>
       </c>
       <c r="H175" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I175" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
@@ -5912,7 +5930,7 @@
         <v>79</v>
       </c>
       <c r="B176" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C176" s="9"/>
       <c r="D176" s="9">
@@ -5922,24 +5940,24 @@
         <v>6460</v>
       </c>
       <c r="F176" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G176" s="7">
         <v>21</v>
       </c>
       <c r="H176" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I176" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B177" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C177" s="9"/>
       <c r="D177" s="9">
@@ -5949,24 +5967,24 @@
         <v>6510</v>
       </c>
       <c r="F177" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G177" s="7">
         <v>21</v>
       </c>
       <c r="H177" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I177" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B178" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C178" s="9"/>
       <c r="D178" s="9">
@@ -5976,24 +5994,24 @@
         <v>6710</v>
       </c>
       <c r="F178" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G178" s="7">
         <v>21</v>
       </c>
       <c r="H178" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I178" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B179" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C179" s="9"/>
       <c r="D179" s="9">
@@ -6003,16 +6021,16 @@
         <v>6310</v>
       </c>
       <c r="F179" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G179" s="7">
         <v>21</v>
       </c>
       <c r="H179" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I179" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
@@ -6020,7 +6038,7 @@
         <v>80</v>
       </c>
       <c r="B180" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C180" s="9"/>
       <c r="D180" s="9">
@@ -6030,24 +6048,24 @@
         <v>6460</v>
       </c>
       <c r="F180" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G180" s="7">
         <v>21</v>
       </c>
       <c r="H180" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I180" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B181" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C181" s="9"/>
       <c r="D181" s="9">
@@ -6057,24 +6075,24 @@
         <v>6410</v>
       </c>
       <c r="F181" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G181" s="7">
         <v>21</v>
       </c>
       <c r="H181" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I181" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B182" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C182" s="9"/>
       <c r="D182" s="9">
@@ -6084,24 +6102,24 @@
         <v>6610</v>
       </c>
       <c r="F182" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G182" s="7">
         <v>21</v>
       </c>
       <c r="H182" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I182" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B183" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C183" s="9"/>
       <c r="D183" s="9">
@@ -6111,24 +6129,24 @@
         <v>6360</v>
       </c>
       <c r="F183" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G183" s="7">
         <v>21</v>
       </c>
       <c r="H183" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I183" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B184" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C184" s="9"/>
       <c r="D184" s="9">
@@ -6138,24 +6156,24 @@
         <v>6560</v>
       </c>
       <c r="F184" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G184" s="7">
         <v>21</v>
       </c>
       <c r="H184" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I184" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B185" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C185" s="9"/>
       <c r="D185" s="9">
@@ -6165,24 +6183,24 @@
         <v>6360</v>
       </c>
       <c r="F185" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G185" s="7">
         <v>21</v>
       </c>
       <c r="H185" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I185" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B186" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C186" s="9"/>
       <c r="D186" s="9">
@@ -6192,16 +6210,16 @@
         <v>6460</v>
       </c>
       <c r="F186" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G186" s="7">
         <v>21</v>
       </c>
       <c r="H186" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I186" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
@@ -6209,7 +6227,7 @@
         <v>75</v>
       </c>
       <c r="B187" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C187" s="9"/>
       <c r="D187" s="9">
@@ -6219,16 +6237,16 @@
         <v>6110</v>
       </c>
       <c r="F187" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G187" s="7">
         <v>21</v>
       </c>
       <c r="H187" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I187" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
@@ -6236,7 +6254,7 @@
         <v>83</v>
       </c>
       <c r="B188" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C188" s="9"/>
       <c r="D188" s="9">
@@ -6246,16 +6264,16 @@
         <v>6410</v>
       </c>
       <c r="F188" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G188" s="7">
         <v>21</v>
       </c>
       <c r="H188" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I188" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
@@ -6263,7 +6281,7 @@
         <v>84</v>
       </c>
       <c r="B189" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C189" s="9"/>
       <c r="D189" s="9">
@@ -6273,24 +6291,24 @@
         <v>6460</v>
       </c>
       <c r="F189" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G189" s="7">
         <v>21</v>
       </c>
       <c r="H189" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I189" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B190" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C190" s="9"/>
       <c r="D190" s="9">
@@ -6300,24 +6318,24 @@
         <v>6010</v>
       </c>
       <c r="F190" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G190" s="7">
         <v>21</v>
       </c>
       <c r="H190" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I190" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B191" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C191" s="9"/>
       <c r="D191" s="9">
@@ -6327,24 +6345,24 @@
         <v>6510</v>
       </c>
       <c r="F191" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G191" s="7">
         <v>21</v>
       </c>
       <c r="H191" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I191" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B192" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C192" s="9"/>
       <c r="D192" s="9">
@@ -6354,24 +6372,24 @@
         <v>6460</v>
       </c>
       <c r="F192" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G192" s="7">
         <v>21</v>
       </c>
       <c r="H192" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I192" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B193" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C193" s="9"/>
       <c r="D193" s="9">
@@ -6381,16 +6399,16 @@
         <v>6360</v>
       </c>
       <c r="F193" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G193" s="7">
         <v>21</v>
       </c>
       <c r="H193" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I193" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
@@ -6398,7 +6416,7 @@
         <v>78</v>
       </c>
       <c r="B194" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C194" s="9"/>
       <c r="D194" s="9">
@@ -6408,24 +6426,24 @@
         <v>6010</v>
       </c>
       <c r="F194" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G194" s="7">
         <v>21</v>
       </c>
       <c r="H194" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I194" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B195" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C195" s="9"/>
       <c r="D195" s="9">
@@ -6435,16 +6453,16 @@
         <v>6610</v>
       </c>
       <c r="F195" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G195" s="7">
         <v>21</v>
       </c>
       <c r="H195" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I195" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
@@ -6452,7 +6470,7 @@
         <v>77</v>
       </c>
       <c r="B196" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C196" s="9"/>
       <c r="D196" s="9">
@@ -6462,24 +6480,24 @@
         <v>6010</v>
       </c>
       <c r="F196" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G196" s="7">
         <v>21</v>
       </c>
       <c r="H196" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I196" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B197" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C197" s="9"/>
       <c r="D197" s="9">
@@ -6489,24 +6507,24 @@
         <v>6610</v>
       </c>
       <c r="F197" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G197" s="7">
         <v>21</v>
       </c>
       <c r="H197" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I197" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B198" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C198" s="9"/>
       <c r="D198" s="9">
@@ -6516,24 +6534,24 @@
         <v>6310</v>
       </c>
       <c r="F198" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G198" s="7">
         <v>21</v>
       </c>
       <c r="H198" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I198" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B199" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C199" s="9"/>
       <c r="D199" s="9">
@@ -6543,24 +6561,24 @@
         <v>6460</v>
       </c>
       <c r="F199" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G199" s="7">
         <v>21</v>
       </c>
       <c r="H199" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I199" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B200" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C200" s="9"/>
       <c r="D200" s="9">
@@ -6570,16 +6588,16 @@
         <v>6360</v>
       </c>
       <c r="F200" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G200" s="7">
         <v>21</v>
       </c>
       <c r="H200" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I200" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
@@ -6587,7 +6605,7 @@
         <v>81</v>
       </c>
       <c r="B201" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C201" s="9"/>
       <c r="D201" s="9">
@@ -6597,16 +6615,16 @@
         <v>6460</v>
       </c>
       <c r="F201" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G201" s="7">
         <v>21</v>
       </c>
       <c r="H201" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I201" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
@@ -6614,7 +6632,7 @@
         <v>82</v>
       </c>
       <c r="B202" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C202" s="9"/>
       <c r="D202" s="9">
@@ -6624,21 +6642,21 @@
         <v>6510</v>
       </c>
       <c r="F202" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G202" s="7">
         <v>21</v>
       </c>
       <c r="H202" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I202" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B203" t="s">
         <v>12</v>
@@ -6651,7 +6669,7 @@
         <v>6170</v>
       </c>
       <c r="F203" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G203" s="7">
         <v>17</v>
@@ -6660,7 +6678,7 @@
         <v>71</v>
       </c>
       <c r="I203" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
@@ -6678,7 +6696,7 @@
         <v>6170</v>
       </c>
       <c r="F204" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G204" s="7">
         <v>17</v>
@@ -6687,12 +6705,12 @@
         <v>71</v>
       </c>
       <c r="I204" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B205" t="s">
         <v>12</v>
@@ -6705,7 +6723,7 @@
         <v>6170</v>
       </c>
       <c r="F205" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G205" s="7">
         <v>17</v>
@@ -6714,12 +6732,12 @@
         <v>71</v>
       </c>
       <c r="I205" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B206" t="s">
         <v>12</v>
@@ -6732,7 +6750,7 @@
         <v>6330</v>
       </c>
       <c r="F206" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G206" s="7">
         <v>17</v>
@@ -6741,12 +6759,12 @@
         <v>71</v>
       </c>
       <c r="I206" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B207" t="s">
         <v>12</v>
@@ -6759,7 +6777,7 @@
         <v>6710</v>
       </c>
       <c r="F207" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G207" s="7">
         <v>17</v>
@@ -6768,7 +6786,7 @@
         <v>71</v>
       </c>
       <c r="I207" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
@@ -6786,7 +6804,7 @@
         <v>6270</v>
       </c>
       <c r="F208" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G208" s="7">
         <v>17</v>
@@ -6795,12 +6813,12 @@
         <v>71</v>
       </c>
       <c r="I208" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B209" t="s">
         <v>12</v>
@@ -6813,7 +6831,7 @@
         <v>6340</v>
       </c>
       <c r="F209" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G209" s="7">
         <v>17</v>
@@ -6822,12 +6840,12 @@
         <v>71</v>
       </c>
       <c r="I209" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B210" t="s">
         <v>12</v>
@@ -6840,7 +6858,7 @@
         <v>6270</v>
       </c>
       <c r="F210" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G210" s="7">
         <v>17</v>
@@ -6849,12 +6867,12 @@
         <v>71</v>
       </c>
       <c r="I210" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B211" t="s">
         <v>12</v>
@@ -6867,7 +6885,7 @@
         <v>6370</v>
       </c>
       <c r="F211" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G211" s="7">
         <v>17</v>
@@ -6876,12 +6894,12 @@
         <v>71</v>
       </c>
       <c r="I211" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B212" t="s">
         <v>12</v>
@@ -6894,7 +6912,7 @@
         <v>6350</v>
       </c>
       <c r="F212" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G212" s="7">
         <v>17</v>
@@ -6903,12 +6921,12 @@
         <v>71</v>
       </c>
       <c r="I212" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B213" t="s">
         <v>12</v>
@@ -6921,7 +6939,7 @@
         <v>6370</v>
       </c>
       <c r="F213" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G213" s="7">
         <v>17</v>
@@ -6930,7 +6948,7 @@
         <v>71</v>
       </c>
       <c r="I213" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
@@ -6948,7 +6966,7 @@
         <v>6330</v>
       </c>
       <c r="F214" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G214" s="7">
         <v>17</v>
@@ -6957,12 +6975,12 @@
         <v>71</v>
       </c>
       <c r="I214" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B215" t="s">
         <v>12</v>
@@ -6975,7 +6993,7 @@
         <v>6470</v>
       </c>
       <c r="F215" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G215" s="7">
         <v>17</v>
@@ -6984,12 +7002,12 @@
         <v>71</v>
       </c>
       <c r="I215" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B216" t="s">
         <v>12</v>
@@ -7002,7 +7020,7 @@
         <v>6370</v>
       </c>
       <c r="F216" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G216" s="7">
         <v>17</v>
@@ -7011,12 +7029,12 @@
         <v>71</v>
       </c>
       <c r="I216" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B217" t="s">
         <v>12</v>
@@ -7029,7 +7047,7 @@
         <v>6340</v>
       </c>
       <c r="F217" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G217" s="7">
         <v>17</v>
@@ -7038,12 +7056,12 @@
         <v>71</v>
       </c>
       <c r="I217" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B218" t="s">
         <v>12</v>
@@ -7056,7 +7074,7 @@
         <v>6320</v>
       </c>
       <c r="F218" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G218" s="7">
         <v>17</v>
@@ -7065,12 +7083,12 @@
         <v>71</v>
       </c>
       <c r="I218" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B219" t="s">
         <v>12</v>
@@ -7083,7 +7101,7 @@
         <v>6570</v>
       </c>
       <c r="F219" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G219" s="7">
         <v>17</v>
@@ -7092,12 +7110,12 @@
         <v>71</v>
       </c>
       <c r="I219" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B220" t="s">
         <v>12</v>
@@ -7110,7 +7128,7 @@
         <v>6340</v>
       </c>
       <c r="F220" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G220" s="7">
         <v>17</v>
@@ -7119,12 +7137,12 @@
         <v>71</v>
       </c>
       <c r="I220" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B221" t="s">
         <v>12</v>
@@ -7137,7 +7155,7 @@
         <v>6320</v>
       </c>
       <c r="F221" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G221" s="7">
         <v>17</v>
@@ -7146,7 +7164,7 @@
         <v>71</v>
       </c>
       <c r="I221" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
@@ -7164,7 +7182,7 @@
         <v>6270</v>
       </c>
       <c r="F222" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G222" s="7">
         <v>17</v>
@@ -7173,7 +7191,7 @@
         <v>71</v>
       </c>
       <c r="I222" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
@@ -7191,7 +7209,7 @@
         <v>6340</v>
       </c>
       <c r="F223" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G223" s="7">
         <v>17</v>
@@ -7200,12 +7218,12 @@
         <v>71</v>
       </c>
       <c r="I223" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B224" t="s">
         <v>12</v>
@@ -7218,7 +7236,7 @@
         <v>6330</v>
       </c>
       <c r="F224" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G224" s="7">
         <v>17</v>
@@ -7227,7 +7245,7 @@
         <v>71</v>
       </c>
       <c r="I224" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
@@ -7245,7 +7263,7 @@
         <v>6430</v>
       </c>
       <c r="F225" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G225" s="7">
         <v>17</v>
@@ -7254,7 +7272,7 @@
         <v>71</v>
       </c>
       <c r="I225" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
@@ -7272,7 +7290,7 @@
         <v>6170</v>
       </c>
       <c r="F226" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G226" s="7">
         <v>17</v>
@@ -7281,12 +7299,12 @@
         <v>71</v>
       </c>
       <c r="I226" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B227" t="s">
         <v>12</v>
@@ -7299,7 +7317,7 @@
         <v>6170</v>
       </c>
       <c r="F227" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G227" s="7">
         <v>17</v>
@@ -7308,12 +7326,12 @@
         <v>71</v>
       </c>
       <c r="I227" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B228" t="s">
         <v>12</v>
@@ -7326,7 +7344,7 @@
         <v>6340</v>
       </c>
       <c r="F228" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G228" s="7">
         <v>17</v>
@@ -7335,12 +7353,12 @@
         <v>71</v>
       </c>
       <c r="I228" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B229" t="s">
         <v>12</v>
@@ -7353,7 +7371,7 @@
         <v>6450</v>
       </c>
       <c r="F229" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G229" s="7">
         <v>17</v>
@@ -7362,12 +7380,12 @@
         <v>71</v>
       </c>
       <c r="I229" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B230" t="s">
         <v>12</v>
@@ -7380,7 +7398,7 @@
         <v>6370</v>
       </c>
       <c r="F230" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G230" s="7">
         <v>17</v>
@@ -7389,7 +7407,7 @@
         <v>71</v>
       </c>
       <c r="I230" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
@@ -7407,7 +7425,7 @@
         <v>6270</v>
       </c>
       <c r="F231" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G231" s="7">
         <v>17</v>
@@ -7416,12 +7434,12 @@
         <v>71</v>
       </c>
       <c r="I231" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B232" t="s">
         <v>12</v>
@@ -7434,7 +7452,7 @@
         <v>6170</v>
       </c>
       <c r="F232" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G232" s="7">
         <v>17</v>
@@ -7443,12 +7461,12 @@
         <v>71</v>
       </c>
       <c r="I232" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B233" t="s">
         <v>12</v>
@@ -7461,7 +7479,7 @@
         <v>6320</v>
       </c>
       <c r="F233" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G233" s="7">
         <v>17</v>
@@ -7470,7 +7488,7 @@
         <v>71</v>
       </c>
       <c r="I233" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
@@ -7488,7 +7506,7 @@
         <v>6170</v>
       </c>
       <c r="F234" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G234" s="7">
         <v>17</v>
@@ -7497,12 +7515,12 @@
         <v>71</v>
       </c>
       <c r="I234" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B235" t="s">
         <v>12</v>
@@ -7515,7 +7533,7 @@
         <v>6630</v>
       </c>
       <c r="F235" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G235" s="7">
         <v>17</v>
@@ -7524,12 +7542,12 @@
         <v>71</v>
       </c>
       <c r="I235" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B236" t="s">
         <v>12</v>
@@ -7542,7 +7560,7 @@
         <v>6320</v>
       </c>
       <c r="F236" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G236" s="7">
         <v>17</v>
@@ -7551,12 +7569,12 @@
         <v>71</v>
       </c>
       <c r="I236" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B237" t="s">
         <v>12</v>
@@ -7569,7 +7587,7 @@
         <v>6370</v>
       </c>
       <c r="F237" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G237" s="7">
         <v>17</v>
@@ -7578,12 +7596,12 @@
         <v>71</v>
       </c>
       <c r="I237" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B238" t="s">
         <v>12</v>
@@ -7596,7 +7614,7 @@
         <v>6320</v>
       </c>
       <c r="F238" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G238" s="7">
         <v>17</v>
@@ -7605,7 +7623,7 @@
         <v>71</v>
       </c>
       <c r="I238" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
@@ -7623,7 +7641,7 @@
         <v>6340</v>
       </c>
       <c r="F239" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G239" s="7">
         <v>17</v>
@@ -7632,7 +7650,7 @@
         <v>71</v>
       </c>
       <c r="I239" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
@@ -7650,7 +7668,7 @@
         <v>6340</v>
       </c>
       <c r="F240" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G240" s="7">
         <v>17</v>
@@ -7659,15 +7677,15 @@
         <v>71</v>
       </c>
       <c r="I240" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B241" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C241" s="9"/>
       <c r="D241" s="9">
@@ -7677,7 +7695,7 @@
         <v>6260</v>
       </c>
       <c r="F241" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G241" s="7">
         <v>18</v>
@@ -7686,7 +7704,7 @@
         <v>73</v>
       </c>
       <c r="I241" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
@@ -7694,7 +7712,7 @@
         <v>74</v>
       </c>
       <c r="B242" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C242" s="9"/>
       <c r="D242" s="9">
@@ -7704,7 +7722,7 @@
         <v>6260</v>
       </c>
       <c r="F242" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G242" s="7">
         <v>18</v>
@@ -7713,15 +7731,15 @@
         <v>73</v>
       </c>
       <c r="I242" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B243" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C243" s="9"/>
       <c r="D243" s="9">
@@ -7731,7 +7749,7 @@
         <v>6260</v>
       </c>
       <c r="F243" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G243" s="7">
         <v>18</v>
@@ -7740,15 +7758,15 @@
         <v>73</v>
       </c>
       <c r="I243" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B244" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C244" s="9"/>
       <c r="D244" s="9">
@@ -7758,7 +7776,7 @@
         <v>6260</v>
       </c>
       <c r="F244" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G244" s="7">
         <v>18</v>
@@ -7767,15 +7785,15 @@
         <v>73</v>
       </c>
       <c r="I244" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B245" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C245" s="9"/>
       <c r="D245" s="9">
@@ -7785,7 +7803,7 @@
         <v>6260</v>
       </c>
       <c r="F245" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G245" s="7">
         <v>18</v>
@@ -7794,15 +7812,15 @@
         <v>73</v>
       </c>
       <c r="I245" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B246" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C246" s="9"/>
       <c r="D246" s="9">
@@ -7812,7 +7830,7 @@
         <v>6510</v>
       </c>
       <c r="F246" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G246" s="7">
         <v>18</v>
@@ -7821,15 +7839,15 @@
         <v>73</v>
       </c>
       <c r="I246" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B247" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C247" s="9"/>
       <c r="D247" s="9">
@@ -7839,7 +7857,7 @@
         <v>7160</v>
       </c>
       <c r="F247" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G247" s="7">
         <v>18</v>
@@ -7848,7 +7866,7 @@
         <v>73</v>
       </c>
       <c r="I247" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.25">
@@ -7856,7 +7874,7 @@
         <v>79</v>
       </c>
       <c r="B248" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C248" s="9"/>
       <c r="D248" s="9">
@@ -7866,7 +7884,7 @@
         <v>6360</v>
       </c>
       <c r="F248" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G248" s="7">
         <v>18</v>
@@ -7875,15 +7893,15 @@
         <v>73</v>
       </c>
       <c r="I248" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B249" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C249" s="9"/>
       <c r="D249" s="9">
@@ -7893,7 +7911,7 @@
         <v>6510</v>
       </c>
       <c r="F249" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G249" s="7">
         <v>18</v>
@@ -7902,15 +7920,15 @@
         <v>73</v>
       </c>
       <c r="I249" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B250" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C250" s="9"/>
       <c r="D250" s="9">
@@ -7920,7 +7938,7 @@
         <v>6660</v>
       </c>
       <c r="F250" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G250" s="7">
         <v>18</v>
@@ -7929,15 +7947,15 @@
         <v>73</v>
       </c>
       <c r="I250" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B251" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C251" s="9"/>
       <c r="D251" s="9">
@@ -7947,7 +7965,7 @@
         <v>6460</v>
       </c>
       <c r="F251" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G251" s="7">
         <v>18</v>
@@ -7956,7 +7974,7 @@
         <v>73</v>
       </c>
       <c r="I251" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.25">
@@ -7964,7 +7982,7 @@
         <v>80</v>
       </c>
       <c r="B252" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C252" s="9"/>
       <c r="D252" s="9">
@@ -7974,7 +7992,7 @@
         <v>6510</v>
       </c>
       <c r="F252" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G252" s="7">
         <v>18</v>
@@ -7983,15 +8001,15 @@
         <v>73</v>
       </c>
       <c r="I252" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B253" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C253" s="9"/>
       <c r="D253" s="9">
@@ -8001,7 +8019,7 @@
         <v>6760</v>
       </c>
       <c r="F253" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G253" s="7">
         <v>18</v>
@@ -8010,15 +8028,15 @@
         <v>73</v>
       </c>
       <c r="I253" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B254" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C254" s="9"/>
       <c r="D254" s="9">
@@ -8028,7 +8046,7 @@
         <v>6760</v>
       </c>
       <c r="F254" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G254" s="7">
         <v>18</v>
@@ -8037,15 +8055,15 @@
         <v>73</v>
       </c>
       <c r="I254" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B255" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C255" s="9"/>
       <c r="D255" s="9">
@@ -8055,7 +8073,7 @@
         <v>6960</v>
       </c>
       <c r="F255" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G255" s="7">
         <v>18</v>
@@ -8064,15 +8082,15 @@
         <v>73</v>
       </c>
       <c r="I255" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B256" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C256" s="9"/>
       <c r="D256" s="9">
@@ -8082,7 +8100,7 @@
         <v>6560</v>
       </c>
       <c r="F256" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G256" s="7">
         <v>18</v>
@@ -8091,15 +8109,15 @@
         <v>73</v>
       </c>
       <c r="I256" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B257" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C257" s="9"/>
       <c r="D257" s="9">
@@ -8109,7 +8127,7 @@
         <v>6510</v>
       </c>
       <c r="F257" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G257" s="7">
         <v>18</v>
@@ -8118,15 +8136,15 @@
         <v>73</v>
       </c>
       <c r="I257" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B258" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C258" s="9"/>
       <c r="D258" s="9">
@@ -8136,7 +8154,7 @@
         <v>6660</v>
       </c>
       <c r="F258" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G258" s="7">
         <v>18</v>
@@ -8145,7 +8163,7 @@
         <v>73</v>
       </c>
       <c r="I258" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.25">
@@ -8153,7 +8171,7 @@
         <v>75</v>
       </c>
       <c r="B259" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C259" s="9"/>
       <c r="D259" s="9">
@@ -8163,7 +8181,7 @@
         <v>6460</v>
       </c>
       <c r="F259" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G259" s="7">
         <v>18</v>
@@ -8172,7 +8190,7 @@
         <v>73</v>
       </c>
       <c r="I259" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.25">
@@ -8180,7 +8198,7 @@
         <v>83</v>
       </c>
       <c r="B260" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C260" s="9"/>
       <c r="D260" s="9">
@@ -8190,7 +8208,7 @@
         <v>6510</v>
       </c>
       <c r="F260" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G260" s="7">
         <v>18</v>
@@ -8199,7 +8217,7 @@
         <v>73</v>
       </c>
       <c r="I260" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.25">
@@ -8207,7 +8225,7 @@
         <v>84</v>
       </c>
       <c r="B261" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C261" s="9"/>
       <c r="D261" s="9">
@@ -8217,7 +8235,7 @@
         <v>6510</v>
       </c>
       <c r="F261" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G261" s="7">
         <v>18</v>
@@ -8226,7 +8244,7 @@
         <v>73</v>
       </c>
       <c r="I261" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.25">
@@ -8234,7 +8252,7 @@
         <v>76</v>
       </c>
       <c r="B262" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C262" s="9"/>
       <c r="D262" s="9">
@@ -8244,7 +8262,7 @@
         <v>6360</v>
       </c>
       <c r="F262" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G262" s="7">
         <v>18</v>
@@ -8253,15 +8271,15 @@
         <v>73</v>
       </c>
       <c r="I262" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B263" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C263" s="9"/>
       <c r="D263" s="9">
@@ -8271,7 +8289,7 @@
         <v>6260</v>
       </c>
       <c r="F263" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G263" s="7">
         <v>18</v>
@@ -8280,15 +8298,15 @@
         <v>73</v>
       </c>
       <c r="I263" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B264" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C264" s="9"/>
       <c r="D264" s="9">
@@ -8298,7 +8316,7 @@
         <v>6510</v>
       </c>
       <c r="F264" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G264" s="7">
         <v>18</v>
@@ -8307,15 +8325,15 @@
         <v>73</v>
       </c>
       <c r="I264" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B265" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C265" s="9"/>
       <c r="D265" s="9">
@@ -8325,7 +8343,7 @@
         <v>6860</v>
       </c>
       <c r="F265" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G265" s="7">
         <v>18</v>
@@ -8334,15 +8352,15 @@
         <v>73</v>
       </c>
       <c r="I265" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
+        <v>136</v>
+      </c>
+      <c r="B266" t="s">
         <v>137</v>
-      </c>
-      <c r="B266" t="s">
-        <v>138</v>
       </c>
       <c r="C266" s="9"/>
       <c r="D266" s="9">
@@ -8352,7 +8370,7 @@
         <v>6510</v>
       </c>
       <c r="F266" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G266" s="7">
         <v>18</v>
@@ -8361,7 +8379,7 @@
         <v>73</v>
       </c>
       <c r="I266" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.25">
@@ -8369,7 +8387,7 @@
         <v>78</v>
       </c>
       <c r="B267" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C267" s="9"/>
       <c r="D267" s="9">
@@ -8379,7 +8397,7 @@
         <v>6260</v>
       </c>
       <c r="F267" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G267" s="7">
         <v>18</v>
@@ -8388,15 +8406,15 @@
         <v>73</v>
       </c>
       <c r="I267" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B268" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C268" s="9"/>
       <c r="D268" s="9">
@@ -8406,7 +8424,7 @@
         <v>6360</v>
       </c>
       <c r="F268" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G268" s="7">
         <v>18</v>
@@ -8415,7 +8433,7 @@
         <v>73</v>
       </c>
       <c r="I268" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.25">
@@ -8423,7 +8441,7 @@
         <v>77</v>
       </c>
       <c r="B269" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C269" s="9"/>
       <c r="D269" s="9">
@@ -8433,7 +8451,7 @@
         <v>6360</v>
       </c>
       <c r="F269" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G269" s="7">
         <v>18</v>
@@ -8442,15 +8460,15 @@
         <v>73</v>
       </c>
       <c r="I269" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B270" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C270" s="9"/>
       <c r="D270" s="9">
@@ -8460,7 +8478,7 @@
         <v>6660</v>
       </c>
       <c r="F270" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G270" s="7">
         <v>18</v>
@@ -8469,15 +8487,15 @@
         <v>73</v>
       </c>
       <c r="I270" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B271" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C271" s="9"/>
       <c r="D271" s="9">
@@ -8487,7 +8505,7 @@
         <v>6760</v>
       </c>
       <c r="F271" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G271" s="7">
         <v>18</v>
@@ -8496,15 +8514,15 @@
         <v>73</v>
       </c>
       <c r="I271" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B272" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C272" s="9"/>
       <c r="D272" s="9">
@@ -8514,7 +8532,7 @@
         <v>6660</v>
       </c>
       <c r="F272" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G272" s="7">
         <v>18</v>
@@ -8523,7 +8541,7 @@
         <v>73</v>
       </c>
       <c r="I272" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.25">
@@ -8531,7 +8549,7 @@
         <v>81</v>
       </c>
       <c r="B273" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C273" s="9"/>
       <c r="D273" s="9">
@@ -8541,7 +8559,7 @@
         <v>6510</v>
       </c>
       <c r="F273" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G273" s="7">
         <v>18</v>
@@ -8550,7 +8568,7 @@
         <v>73</v>
       </c>
       <c r="I273" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.25">
@@ -8558,7 +8576,7 @@
         <v>82</v>
       </c>
       <c r="B274" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C274" s="9"/>
       <c r="D274" s="9">
@@ -8568,7 +8586,7 @@
         <v>6510</v>
       </c>
       <c r="F274" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G274" s="7">
         <v>18</v>
@@ -8577,12 +8595,12 @@
         <v>73</v>
       </c>
       <c r="I274" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B275" t="s">
         <v>12</v>
@@ -8597,16 +8615,16 @@
         <v>6160</v>
       </c>
       <c r="F275" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G275" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H275" t="s">
         <v>72</v>
       </c>
       <c r="I275" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.25">
@@ -8626,21 +8644,21 @@
         <v>6140</v>
       </c>
       <c r="F276" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G276" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H276" t="s">
         <v>72</v>
       </c>
       <c r="I276" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B277" t="s">
         <v>12</v>
@@ -8653,7 +8671,7 @@
         <v>6160</v>
       </c>
       <c r="F277" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G277" s="7">
         <v>20</v>
@@ -8662,12 +8680,12 @@
         <v>72</v>
       </c>
       <c r="I277" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B278" t="s">
         <v>12</v>
@@ -8680,7 +8698,7 @@
         <v>6160</v>
       </c>
       <c r="F278" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G278" s="7">
         <v>20</v>
@@ -8689,12 +8707,12 @@
         <v>72</v>
       </c>
       <c r="I278" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B279" t="s">
         <v>12</v>
@@ -8707,7 +8725,7 @@
         <v>6260</v>
       </c>
       <c r="F279" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G279" s="7">
         <v>20</v>
@@ -8716,12 +8734,12 @@
         <v>72</v>
       </c>
       <c r="I279" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B280" t="s">
         <v>12</v>
@@ -8734,7 +8752,7 @@
         <v>6460</v>
       </c>
       <c r="F280" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G280" s="7">
         <v>20</v>
@@ -8743,12 +8761,12 @@
         <v>72</v>
       </c>
       <c r="I280" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B281" t="s">
         <v>12</v>
@@ -8761,7 +8779,7 @@
         <v>6360</v>
       </c>
       <c r="F281" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G281" s="7">
         <v>20</v>
@@ -8770,12 +8788,12 @@
         <v>72</v>
       </c>
       <c r="I281" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B282" t="s">
         <v>12</v>
@@ -8788,7 +8806,7 @@
         <v>6560</v>
       </c>
       <c r="F282" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G282" s="7">
         <v>20</v>
@@ -8797,12 +8815,12 @@
         <v>72</v>
       </c>
       <c r="I282" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B283" t="s">
         <v>12</v>
@@ -8815,7 +8833,7 @@
         <v>6360</v>
       </c>
       <c r="F283" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G283" s="7">
         <v>20</v>
@@ -8824,12 +8842,12 @@
         <v>72</v>
       </c>
       <c r="I283" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B284" t="s">
         <v>12</v>
@@ -8842,7 +8860,7 @@
         <v>6360</v>
       </c>
       <c r="F284" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G284" s="7">
         <v>20</v>
@@ -8851,12 +8869,12 @@
         <v>72</v>
       </c>
       <c r="I284" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B285" t="s">
         <v>12</v>
@@ -8869,7 +8887,7 @@
         <v>6360</v>
       </c>
       <c r="F285" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G285" s="7">
         <v>20</v>
@@ -8878,7 +8896,7 @@
         <v>72</v>
       </c>
       <c r="I285" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.25">
@@ -8896,7 +8914,7 @@
         <v>6360</v>
       </c>
       <c r="F286" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G286" s="7">
         <v>20</v>
@@ -8905,12 +8923,12 @@
         <v>72</v>
       </c>
       <c r="I286" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B287" t="s">
         <v>12</v>
@@ -8923,7 +8941,7 @@
         <v>6360</v>
       </c>
       <c r="F287" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G287" s="7">
         <v>20</v>
@@ -8932,12 +8950,12 @@
         <v>72</v>
       </c>
       <c r="I287" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B288" t="s">
         <v>12</v>
@@ -8950,7 +8968,7 @@
         <v>6360</v>
       </c>
       <c r="F288" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G288" s="7">
         <v>20</v>
@@ -8959,7 +8977,7 @@
         <v>72</v>
       </c>
       <c r="I288" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.25">
@@ -8977,7 +8995,7 @@
         <v>6360</v>
       </c>
       <c r="F289" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G289" s="7">
         <v>20</v>
@@ -8986,12 +9004,12 @@
         <v>72</v>
       </c>
       <c r="I289" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B290" t="s">
         <v>12</v>
@@ -9004,7 +9022,7 @@
         <v>6360</v>
       </c>
       <c r="F290" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G290" s="7">
         <v>20</v>
@@ -9013,7 +9031,7 @@
         <v>72</v>
       </c>
       <c r="I290" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.25">
@@ -9031,7 +9049,7 @@
         <v>6460</v>
       </c>
       <c r="F291" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G291" s="7">
         <v>20</v>
@@ -9040,7 +9058,7 @@
         <v>72</v>
       </c>
       <c r="I291" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.25">
@@ -9060,21 +9078,21 @@
         <v>6160</v>
       </c>
       <c r="F292" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G292" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H292" t="s">
         <v>72</v>
       </c>
       <c r="I292" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B293" t="s">
         <v>12</v>
@@ -9089,21 +9107,21 @@
         <v>6160</v>
       </c>
       <c r="F293" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G293" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H293" t="s">
         <v>72</v>
       </c>
       <c r="I293" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B294" t="s">
         <v>12</v>
@@ -9116,7 +9134,7 @@
         <v>6360</v>
       </c>
       <c r="F294" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G294" s="7">
         <v>20</v>
@@ -9125,12 +9143,12 @@
         <v>72</v>
       </c>
       <c r="I294" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B295" t="s">
         <v>12</v>
@@ -9143,7 +9161,7 @@
         <v>6360</v>
       </c>
       <c r="F295" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G295" s="7">
         <v>20</v>
@@ -9152,7 +9170,7 @@
         <v>72</v>
       </c>
       <c r="I295" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.25">
@@ -9170,7 +9188,7 @@
         <v>6460</v>
       </c>
       <c r="F296" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G296" s="7">
         <v>20</v>
@@ -9179,7 +9197,7 @@
         <v>72</v>
       </c>
       <c r="I296" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.25">
@@ -9197,7 +9215,7 @@
         <v>6360</v>
       </c>
       <c r="F297" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G297" s="7">
         <v>20</v>
@@ -9206,7 +9224,7 @@
         <v>72</v>
       </c>
       <c r="I297" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.25">
@@ -9224,7 +9242,7 @@
         <v>6360</v>
       </c>
       <c r="F298" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G298" s="7">
         <v>20</v>
@@ -9233,12 +9251,12 @@
         <v>72</v>
       </c>
       <c r="I298" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B299" t="s">
         <v>12</v>
@@ -9251,7 +9269,7 @@
         <v>6100</v>
       </c>
       <c r="F299" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G299" s="7">
         <v>18</v>
@@ -9260,7 +9278,7 @@
         <v>86</v>
       </c>
       <c r="I299" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.25">
@@ -9278,7 +9296,7 @@
         <v>6100</v>
       </c>
       <c r="F300" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G300" s="7">
         <v>18</v>
@@ -9287,7 +9305,7 @@
         <v>86</v>
       </c>
       <c r="I300" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.25">
@@ -9305,7 +9323,7 @@
         <v>6150</v>
       </c>
       <c r="F301" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G301" s="7">
         <v>18</v>
@@ -9314,12 +9332,12 @@
         <v>86</v>
       </c>
       <c r="I301" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B302" t="s">
         <v>12</v>
@@ -9332,7 +9350,7 @@
         <v>6100</v>
       </c>
       <c r="F302" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G302" s="7">
         <v>18</v>
@@ -9341,12 +9359,12 @@
         <v>86</v>
       </c>
       <c r="I302" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B303" t="s">
         <v>12</v>
@@ -9359,7 +9377,7 @@
         <v>6300</v>
       </c>
       <c r="F303" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G303" s="7">
         <v>18</v>
@@ -9368,7 +9386,7 @@
         <v>86</v>
       </c>
       <c r="I303" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.25">
@@ -9386,7 +9404,7 @@
         <v>6200</v>
       </c>
       <c r="F304" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G304" s="7">
         <v>18</v>
@@ -9395,196 +9413,811 @@
         <v>86</v>
       </c>
       <c r="I304" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="305" spans="3:7" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>88</v>
+      </c>
+      <c r="B305" t="s">
+        <v>12</v>
+      </c>
       <c r="C305" s="9"/>
-      <c r="D305" s="9"/>
-      <c r="E305" s="9"/>
-      <c r="G305" s="7"/>
-    </row>
-    <row r="306" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D305" s="9">
+        <v>5790</v>
+      </c>
+      <c r="E305" s="9">
+        <v>6090</v>
+      </c>
+      <c r="F305" t="s">
+        <v>144</v>
+      </c>
+      <c r="G305" s="7">
+        <v>17</v>
+      </c>
+      <c r="H305" t="s">
+        <v>71</v>
+      </c>
+      <c r="I305" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>76</v>
+      </c>
+      <c r="B306" t="s">
+        <v>12</v>
+      </c>
       <c r="C306" s="9"/>
-      <c r="D306" s="9"/>
-      <c r="E306" s="9"/>
-      <c r="G306" s="7"/>
-    </row>
-    <row r="307" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D306" s="9">
+        <v>5790</v>
+      </c>
+      <c r="E306" s="9">
+        <v>6090</v>
+      </c>
+      <c r="F306" t="s">
+        <v>144</v>
+      </c>
+      <c r="G306" s="7">
+        <v>17</v>
+      </c>
+      <c r="H306" t="s">
+        <v>71</v>
+      </c>
+      <c r="I306" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>87</v>
+      </c>
+      <c r="B307" t="s">
+        <v>12</v>
+      </c>
       <c r="C307" s="9"/>
-      <c r="D307" s="9"/>
-      <c r="E307" s="9"/>
-      <c r="G307" s="7"/>
-    </row>
-    <row r="308" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D307" s="9">
+        <v>5790</v>
+      </c>
+      <c r="E307" s="9">
+        <v>6090</v>
+      </c>
+      <c r="F307" t="s">
+        <v>144</v>
+      </c>
+      <c r="G307" s="7">
+        <v>17</v>
+      </c>
+      <c r="H307" t="s">
+        <v>71</v>
+      </c>
+      <c r="I307" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>75</v>
+      </c>
+      <c r="B308" t="s">
+        <v>12</v>
+      </c>
       <c r="C308" s="9"/>
-      <c r="D308" s="9"/>
-      <c r="E308" s="9"/>
-      <c r="G308" s="7"/>
-    </row>
-    <row r="309" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D308" s="9">
+        <v>5790</v>
+      </c>
+      <c r="E308" s="9">
+        <v>6090</v>
+      </c>
+      <c r="F308" t="s">
+        <v>144</v>
+      </c>
+      <c r="G308" s="7">
+        <v>17</v>
+      </c>
+      <c r="H308" t="s">
+        <v>71</v>
+      </c>
+      <c r="I308" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>74</v>
+      </c>
+      <c r="B309" t="s">
+        <v>12</v>
+      </c>
       <c r="C309" s="9"/>
-      <c r="D309" s="9"/>
-      <c r="E309" s="9"/>
-      <c r="G309" s="7"/>
-    </row>
-    <row r="310" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D309" s="9">
+        <v>5790</v>
+      </c>
+      <c r="E309" s="9">
+        <v>6090</v>
+      </c>
+      <c r="F309" t="s">
+        <v>144</v>
+      </c>
+      <c r="G309" s="7">
+        <v>17</v>
+      </c>
+      <c r="H309" t="s">
+        <v>71</v>
+      </c>
+      <c r="I309" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>88</v>
+      </c>
+      <c r="B310" t="s">
+        <v>12</v>
+      </c>
       <c r="C310" s="9"/>
-      <c r="D310" s="9"/>
-      <c r="E310" s="9"/>
-      <c r="G310" s="7"/>
-    </row>
-    <row r="311" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D310" s="9">
+        <v>5770</v>
+      </c>
+      <c r="E310" s="9">
+        <v>5970</v>
+      </c>
+      <c r="F310" t="s">
+        <v>144</v>
+      </c>
+      <c r="G310" s="7">
+        <v>21</v>
+      </c>
+      <c r="H310" t="s">
+        <v>145</v>
+      </c>
+      <c r="I310" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>76</v>
+      </c>
+      <c r="B311" t="s">
+        <v>12</v>
+      </c>
       <c r="C311" s="9"/>
-      <c r="D311" s="9"/>
-      <c r="E311" s="9"/>
-      <c r="G311" s="7"/>
-    </row>
-    <row r="312" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D311" s="9">
+        <v>5770</v>
+      </c>
+      <c r="E311" s="9">
+        <v>5970</v>
+      </c>
+      <c r="F311" t="s">
+        <v>144</v>
+      </c>
+      <c r="G311" s="7">
+        <v>21</v>
+      </c>
+      <c r="H311" t="s">
+        <v>145</v>
+      </c>
+      <c r="I311" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>87</v>
+      </c>
+      <c r="B312" t="s">
+        <v>12</v>
+      </c>
       <c r="C312" s="9"/>
-      <c r="D312" s="9"/>
-      <c r="E312" s="9"/>
-      <c r="G312" s="7"/>
-    </row>
-    <row r="313" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D312" s="9">
+        <v>5770</v>
+      </c>
+      <c r="E312" s="9">
+        <v>5970</v>
+      </c>
+      <c r="F312" t="s">
+        <v>144</v>
+      </c>
+      <c r="G312" s="7">
+        <v>21</v>
+      </c>
+      <c r="H312" t="s">
+        <v>145</v>
+      </c>
+      <c r="I312" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>75</v>
+      </c>
+      <c r="B313" t="s">
+        <v>12</v>
+      </c>
       <c r="C313" s="9"/>
-      <c r="D313" s="9"/>
-      <c r="E313" s="9"/>
-      <c r="G313" s="7"/>
-    </row>
-    <row r="314" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D313" s="9">
+        <v>5770</v>
+      </c>
+      <c r="E313" s="9">
+        <v>5970</v>
+      </c>
+      <c r="F313" t="s">
+        <v>144</v>
+      </c>
+      <c r="G313" s="7">
+        <v>21</v>
+      </c>
+      <c r="H313" t="s">
+        <v>145</v>
+      </c>
+      <c r="I313" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>74</v>
+      </c>
+      <c r="B314" t="s">
+        <v>12</v>
+      </c>
       <c r="C314" s="9"/>
-      <c r="D314" s="9"/>
-      <c r="E314" s="9"/>
-      <c r="G314" s="7"/>
-    </row>
-    <row r="315" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D314" s="9">
+        <v>5770</v>
+      </c>
+      <c r="E314" s="9">
+        <v>5970</v>
+      </c>
+      <c r="F314" t="s">
+        <v>144</v>
+      </c>
+      <c r="G314" s="7">
+        <v>21</v>
+      </c>
+      <c r="H314" t="s">
+        <v>145</v>
+      </c>
+      <c r="I314" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>74</v>
+      </c>
+      <c r="B315" t="s">
+        <v>12</v>
+      </c>
       <c r="C315" s="9"/>
-      <c r="D315" s="9"/>
-      <c r="E315" s="9"/>
-      <c r="G315" s="7"/>
-    </row>
-    <row r="316" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D315" s="9">
+        <v>5750</v>
+      </c>
+      <c r="E315" s="9">
+        <v>6050</v>
+      </c>
+      <c r="F315" t="s">
+        <v>144</v>
+      </c>
+      <c r="G315" s="7">
+        <v>21</v>
+      </c>
+      <c r="H315" t="s">
+        <v>155</v>
+      </c>
+      <c r="I315" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>153</v>
+      </c>
+      <c r="B316" t="s">
+        <v>12</v>
+      </c>
       <c r="C316" s="9"/>
-      <c r="D316" s="9"/>
-      <c r="E316" s="9"/>
-      <c r="G316" s="7"/>
-    </row>
-    <row r="317" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D316" s="9">
+        <v>5750</v>
+      </c>
+      <c r="E316" s="9">
+        <v>6050</v>
+      </c>
+      <c r="F316" t="s">
+        <v>144</v>
+      </c>
+      <c r="G316" s="7">
+        <v>21</v>
+      </c>
+      <c r="H316" t="s">
+        <v>155</v>
+      </c>
+      <c r="I316" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>75</v>
+      </c>
+      <c r="B317" t="s">
+        <v>12</v>
+      </c>
       <c r="C317" s="9"/>
-      <c r="D317" s="9"/>
-      <c r="E317" s="9"/>
-      <c r="G317" s="7"/>
-    </row>
-    <row r="318" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D317" s="9">
+        <v>5850</v>
+      </c>
+      <c r="E317" s="9">
+        <v>6150</v>
+      </c>
+      <c r="F317" t="s">
+        <v>144</v>
+      </c>
+      <c r="G317" s="7">
+        <v>21</v>
+      </c>
+      <c r="H317" t="s">
+        <v>155</v>
+      </c>
+      <c r="I317" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>76</v>
+      </c>
+      <c r="B318" t="s">
+        <v>12</v>
+      </c>
       <c r="C318" s="9"/>
-      <c r="D318" s="9"/>
-      <c r="E318" s="9"/>
-      <c r="G318" s="7"/>
-    </row>
-    <row r="319" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D318" s="9">
+        <v>5550</v>
+      </c>
+      <c r="E318" s="9">
+        <v>5750</v>
+      </c>
+      <c r="F318" t="s">
+        <v>144</v>
+      </c>
+      <c r="G318" s="7">
+        <v>21</v>
+      </c>
+      <c r="H318" t="s">
+        <v>155</v>
+      </c>
+      <c r="I318" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>77</v>
+      </c>
+      <c r="B319" t="s">
+        <v>12</v>
+      </c>
       <c r="C319" s="9"/>
-      <c r="D319" s="9"/>
-      <c r="E319" s="9"/>
-      <c r="G319" s="7"/>
-    </row>
-    <row r="320" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D319" s="9">
+        <v>5550</v>
+      </c>
+      <c r="E319" s="9">
+        <v>5750</v>
+      </c>
+      <c r="F319" t="s">
+        <v>144</v>
+      </c>
+      <c r="G319" s="7">
+        <v>21</v>
+      </c>
+      <c r="H319" t="s">
+        <v>155</v>
+      </c>
+      <c r="I319" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>78</v>
+      </c>
+      <c r="B320" t="s">
+        <v>12</v>
+      </c>
       <c r="C320" s="9"/>
-      <c r="D320" s="9"/>
-      <c r="E320" s="9"/>
-      <c r="G320" s="7"/>
-    </row>
-    <row r="321" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D320" s="9">
+        <v>5850</v>
+      </c>
+      <c r="E320" s="9">
+        <v>6150</v>
+      </c>
+      <c r="F320" t="s">
+        <v>144</v>
+      </c>
+      <c r="G320" s="7">
+        <v>21</v>
+      </c>
+      <c r="H320" t="s">
+        <v>155</v>
+      </c>
+      <c r="I320" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>154</v>
+      </c>
+      <c r="B321" t="s">
+        <v>12</v>
+      </c>
       <c r="C321" s="9"/>
-      <c r="D321" s="9"/>
-      <c r="E321" s="9"/>
-      <c r="G321" s="7"/>
-    </row>
-    <row r="322" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D321" s="9">
+        <v>5950</v>
+      </c>
+      <c r="E321" s="9">
+        <v>6250</v>
+      </c>
+      <c r="F321" t="s">
+        <v>144</v>
+      </c>
+      <c r="G321" s="7">
+        <v>21</v>
+      </c>
+      <c r="H321" t="s">
+        <v>155</v>
+      </c>
+      <c r="I321" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>92</v>
+      </c>
+      <c r="B322" t="s">
+        <v>12</v>
+      </c>
       <c r="C322" s="9"/>
-      <c r="D322" s="9"/>
-      <c r="E322" s="9"/>
-      <c r="G322" s="7"/>
-    </row>
-    <row r="323" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D322" s="9">
+        <v>5950</v>
+      </c>
+      <c r="E322" s="9">
+        <v>6250</v>
+      </c>
+      <c r="F322" t="s">
+        <v>144</v>
+      </c>
+      <c r="G322" s="7">
+        <v>21</v>
+      </c>
+      <c r="H322" t="s">
+        <v>155</v>
+      </c>
+      <c r="I322" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>89</v>
+      </c>
+      <c r="B323" t="s">
+        <v>12</v>
+      </c>
       <c r="C323" s="9"/>
-      <c r="D323" s="9"/>
-      <c r="E323" s="9"/>
-      <c r="G323" s="7"/>
-    </row>
-    <row r="324" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C324" s="9"/>
-      <c r="D324" s="9"/>
-      <c r="E324" s="9"/>
-      <c r="G324" s="7"/>
-    </row>
-    <row r="325" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C325" s="9"/>
-      <c r="D325" s="9"/>
-      <c r="E325" s="9"/>
-      <c r="G325" s="7"/>
-    </row>
-    <row r="326" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C326" s="9"/>
-      <c r="D326" s="9"/>
-      <c r="E326" s="9"/>
-      <c r="G326" s="7"/>
-    </row>
-    <row r="327" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D323" s="9">
+        <v>5950</v>
+      </c>
+      <c r="E323" s="9">
+        <v>6250</v>
+      </c>
+      <c r="F323" t="s">
+        <v>144</v>
+      </c>
+      <c r="G323" s="7">
+        <v>21</v>
+      </c>
+      <c r="H323" t="s">
+        <v>155</v>
+      </c>
+      <c r="I323" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>153</v>
+      </c>
+      <c r="B324" t="s">
+        <v>12</v>
+      </c>
+      <c r="C324" s="9">
+        <v>4350</v>
+      </c>
+      <c r="D324" s="9">
+        <v>5650</v>
+      </c>
+      <c r="E324" s="9">
+        <v>5950</v>
+      </c>
+      <c r="F324" t="s">
+        <v>144</v>
+      </c>
+      <c r="G324" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H324" t="s">
+        <v>86</v>
+      </c>
+      <c r="I324" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>75</v>
+      </c>
+      <c r="B325" t="s">
+        <v>12</v>
+      </c>
+      <c r="C325" s="9">
+        <v>4350</v>
+      </c>
+      <c r="D325" s="9">
+        <v>5650</v>
+      </c>
+      <c r="E325" s="9">
+        <v>5950</v>
+      </c>
+      <c r="F325" t="s">
+        <v>144</v>
+      </c>
+      <c r="G325" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H325" t="s">
+        <v>86</v>
+      </c>
+      <c r="I325" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>74</v>
+      </c>
+      <c r="B326" t="s">
+        <v>12</v>
+      </c>
+      <c r="C326" s="9">
+        <v>4350</v>
+      </c>
+      <c r="D326" s="9">
+        <v>5650</v>
+      </c>
+      <c r="E326" s="9">
+        <v>5950</v>
+      </c>
+      <c r="F326" t="s">
+        <v>144</v>
+      </c>
+      <c r="G326" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H326" t="s">
+        <v>86</v>
+      </c>
+      <c r="I326" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>100</v>
+      </c>
+      <c r="B327" t="s">
+        <v>12</v>
+      </c>
       <c r="C327" s="9"/>
-      <c r="D327" s="9"/>
-      <c r="E327" s="9"/>
-      <c r="G327" s="7"/>
-    </row>
-    <row r="328" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D327" s="9">
+        <v>5700</v>
+      </c>
+      <c r="E327" s="9">
+        <v>6050</v>
+      </c>
+      <c r="F327" t="s">
+        <v>144</v>
+      </c>
+      <c r="G327" s="7">
+        <v>18</v>
+      </c>
+      <c r="H327" t="s">
+        <v>86</v>
+      </c>
+      <c r="I327" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>106</v>
+      </c>
+      <c r="B328" t="s">
+        <v>12</v>
+      </c>
       <c r="C328" s="9"/>
-      <c r="D328" s="9"/>
-      <c r="E328" s="9"/>
-      <c r="G328" s="7"/>
-    </row>
-    <row r="329" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D328" s="9">
+        <v>5770</v>
+      </c>
+      <c r="E328" s="9">
+        <v>6100</v>
+      </c>
+      <c r="F328" t="s">
+        <v>144</v>
+      </c>
+      <c r="G328" s="7">
+        <v>18</v>
+      </c>
+      <c r="H328" t="s">
+        <v>86</v>
+      </c>
+      <c r="I328" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>80</v>
+      </c>
+      <c r="B329" t="s">
+        <v>12</v>
+      </c>
       <c r="C329" s="9"/>
-      <c r="D329" s="9"/>
-      <c r="E329" s="9"/>
-      <c r="G329" s="7"/>
-    </row>
-    <row r="330" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D329" s="9">
+        <v>5770</v>
+      </c>
+      <c r="E329" s="9">
+        <v>6100</v>
+      </c>
+      <c r="F329" t="s">
+        <v>144</v>
+      </c>
+      <c r="G329" s="7">
+        <v>18</v>
+      </c>
+      <c r="H329" t="s">
+        <v>86</v>
+      </c>
+      <c r="I329" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>81</v>
+      </c>
+      <c r="B330" t="s">
+        <v>12</v>
+      </c>
       <c r="C330" s="9"/>
-      <c r="D330" s="9"/>
-      <c r="E330" s="9"/>
-      <c r="G330" s="7"/>
-    </row>
-    <row r="331" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D330" s="9">
+        <v>5710</v>
+      </c>
+      <c r="E330" s="9">
+        <v>6100</v>
+      </c>
+      <c r="F330" t="s">
+        <v>144</v>
+      </c>
+      <c r="G330" s="7">
+        <v>18</v>
+      </c>
+      <c r="H330" t="s">
+        <v>86</v>
+      </c>
+      <c r="I330" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>82</v>
+      </c>
+      <c r="B331" t="s">
+        <v>12</v>
+      </c>
       <c r="C331" s="9"/>
-      <c r="D331" s="9"/>
-      <c r="E331" s="9"/>
-      <c r="G331" s="7"/>
-    </row>
-    <row r="332" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D331" s="9">
+        <v>5710</v>
+      </c>
+      <c r="E331" s="9">
+        <v>6100</v>
+      </c>
+      <c r="F331" t="s">
+        <v>144</v>
+      </c>
+      <c r="G331" s="7">
+        <v>18</v>
+      </c>
+      <c r="H331" t="s">
+        <v>86</v>
+      </c>
+      <c r="I331" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>83</v>
+      </c>
+      <c r="B332" t="s">
+        <v>12</v>
+      </c>
       <c r="C332" s="9"/>
-      <c r="D332" s="9"/>
-      <c r="E332" s="9"/>
-      <c r="G332" s="7"/>
-    </row>
-    <row r="333" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D332" s="9">
+        <v>5710</v>
+      </c>
+      <c r="E332" s="9">
+        <v>6100</v>
+      </c>
+      <c r="F332" t="s">
+        <v>144</v>
+      </c>
+      <c r="G332" s="7">
+        <v>18</v>
+      </c>
+      <c r="H332" t="s">
+        <v>86</v>
+      </c>
+      <c r="I332" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>84</v>
+      </c>
+      <c r="B333" t="s">
+        <v>12</v>
+      </c>
       <c r="C333" s="9"/>
-      <c r="D333" s="9"/>
-      <c r="E333" s="9"/>
-      <c r="G333" s="7"/>
-    </row>
-    <row r="334" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D333" s="9">
+        <v>5770</v>
+      </c>
+      <c r="E333" s="9">
+        <v>6150</v>
+      </c>
+      <c r="F333" t="s">
+        <v>144</v>
+      </c>
+      <c r="G333" s="7">
+        <v>18</v>
+      </c>
+      <c r="H333" t="s">
+        <v>86</v>
+      </c>
+      <c r="I333" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C334" s="9"/>
       <c r="D334" s="9"/>
       <c r="E334" s="9"/>
       <c r="G334" s="7"/>
     </row>
-    <row r="335" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C335" s="9"/>
       <c r="D335" s="9"/>
       <c r="E335" s="9"/>
       <c r="G335" s="7"/>
     </row>
-    <row r="336" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C336" s="9"/>
       <c r="D336" s="9"/>
       <c r="E336" s="9"/>
@@ -11701,12 +12334,6 @@
       <c r="D688" s="9"/>
       <c r="E688" s="9"/>
       <c r="G688" s="7"/>
-    </row>
-    <row r="689" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C689" s="9"/>
-      <c r="D689" s="9"/>
-      <c r="E689" s="9"/>
-      <c r="G689" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}"/>
@@ -11802,7 +12429,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3805A486-29BF-4244-AD2E-4DBCFFE9D0EA}">
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -11837,7 +12464,12 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>87</v>
+        <v>151</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DOCS EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A0161B7-8258-4995-B81D-B14CD5269140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{778DF982-90CF-4C2A-9DD2-680606C5BEE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="144">
   <si>
     <t>POD</t>
   </si>
@@ -451,6 +451,30 @@
   </si>
   <si>
     <t>17 DRY / 14 NOR</t>
+  </si>
+  <si>
+    <t>POSORJA</t>
+  </si>
+  <si>
+    <t>CMA</t>
+  </si>
+  <si>
+    <t>Z-HF</t>
+  </si>
+  <si>
+    <t>21 DRY / 14 NOR</t>
+  </si>
+  <si>
+    <t>KAOSHIUNG</t>
+  </si>
+  <si>
+    <t>XINGANG</t>
+  </si>
+  <si>
+    <t>Z-GO</t>
+  </si>
+  <si>
+    <t>18 DRY / 10 NOR</t>
   </si>
 </sst>
 </file>
@@ -5502,190 +5526,903 @@
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C162" s="9"/>
-      <c r="D162" s="9"/>
-      <c r="E162" s="9"/>
-      <c r="G162" s="7"/>
+      <c r="A162" t="s">
+        <v>71</v>
+      </c>
+      <c r="B162" t="s">
+        <v>136</v>
+      </c>
+      <c r="C162" s="9">
+        <v>5220</v>
+      </c>
+      <c r="D162" s="9">
+        <v>6420</v>
+      </c>
+      <c r="E162" s="9">
+        <v>6620</v>
+      </c>
+      <c r="F162" t="s">
+        <v>133</v>
+      </c>
+      <c r="G162" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="H162" t="s">
+        <v>137</v>
+      </c>
+      <c r="I162" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C163" s="9"/>
-      <c r="D163" s="9"/>
-      <c r="E163" s="9"/>
-      <c r="G163" s="7"/>
+      <c r="A163" t="s">
+        <v>82</v>
+      </c>
+      <c r="B163" t="s">
+        <v>136</v>
+      </c>
+      <c r="C163" s="9">
+        <v>5220</v>
+      </c>
+      <c r="D163" s="9">
+        <v>6420</v>
+      </c>
+      <c r="E163" s="9">
+        <v>6620</v>
+      </c>
+      <c r="F163" t="s">
+        <v>133</v>
+      </c>
+      <c r="G163" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="H163" t="s">
+        <v>137</v>
+      </c>
+      <c r="I163" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C164" s="9"/>
-      <c r="D164" s="9"/>
-      <c r="E164" s="9"/>
-      <c r="G164" s="7"/>
+      <c r="A164" t="s">
+        <v>72</v>
+      </c>
+      <c r="B164" t="s">
+        <v>136</v>
+      </c>
+      <c r="C164" s="9">
+        <v>5420</v>
+      </c>
+      <c r="D164" s="9">
+        <v>6520</v>
+      </c>
+      <c r="E164" s="9">
+        <v>6820</v>
+      </c>
+      <c r="F164" t="s">
+        <v>133</v>
+      </c>
+      <c r="G164" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="H164" t="s">
+        <v>137</v>
+      </c>
+      <c r="I164" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C165" s="9"/>
-      <c r="D165" s="9"/>
-      <c r="E165" s="9"/>
-      <c r="G165" s="7"/>
+      <c r="A165" t="s">
+        <v>73</v>
+      </c>
+      <c r="B165" t="s">
+        <v>136</v>
+      </c>
+      <c r="C165" s="9">
+        <v>5220</v>
+      </c>
+      <c r="D165" s="9">
+        <v>6420</v>
+      </c>
+      <c r="E165" s="9">
+        <v>6620</v>
+      </c>
+      <c r="F165" t="s">
+        <v>133</v>
+      </c>
+      <c r="G165" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="H165" t="s">
+        <v>137</v>
+      </c>
+      <c r="I165" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C166" s="9"/>
-      <c r="D166" s="9"/>
-      <c r="E166" s="9"/>
-      <c r="G166" s="7"/>
+      <c r="A166" t="s">
+        <v>74</v>
+      </c>
+      <c r="B166" t="s">
+        <v>136</v>
+      </c>
+      <c r="C166" s="9">
+        <v>5220</v>
+      </c>
+      <c r="D166" s="9">
+        <v>6420</v>
+      </c>
+      <c r="E166" s="9">
+        <v>6620</v>
+      </c>
+      <c r="F166" t="s">
+        <v>133</v>
+      </c>
+      <c r="G166" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="H166" t="s">
+        <v>137</v>
+      </c>
+      <c r="I166" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C167" s="9"/>
-      <c r="D167" s="9"/>
-      <c r="E167" s="9"/>
-      <c r="G167" s="7"/>
+      <c r="A167" t="s">
+        <v>75</v>
+      </c>
+      <c r="B167" t="s">
+        <v>136</v>
+      </c>
+      <c r="C167" s="9">
+        <v>5220</v>
+      </c>
+      <c r="D167" s="9">
+        <v>6420</v>
+      </c>
+      <c r="E167" s="9">
+        <v>6620</v>
+      </c>
+      <c r="F167" t="s">
+        <v>133</v>
+      </c>
+      <c r="G167" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="H167" t="s">
+        <v>137</v>
+      </c>
+      <c r="I167" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C168" s="9"/>
-      <c r="D168" s="9"/>
-      <c r="E168" s="9"/>
-      <c r="G168" s="7"/>
+      <c r="A168" t="s">
+        <v>84</v>
+      </c>
+      <c r="B168" t="s">
+        <v>136</v>
+      </c>
+      <c r="C168" s="9">
+        <v>5420</v>
+      </c>
+      <c r="D168" s="9">
+        <v>6520</v>
+      </c>
+      <c r="E168" s="9">
+        <v>6820</v>
+      </c>
+      <c r="F168" t="s">
+        <v>133</v>
+      </c>
+      <c r="G168" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="H168" t="s">
+        <v>137</v>
+      </c>
+      <c r="I168" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C169" s="9"/>
-      <c r="D169" s="9"/>
-      <c r="E169" s="9"/>
-      <c r="G169" s="7"/>
+      <c r="A169" t="s">
+        <v>140</v>
+      </c>
+      <c r="B169" t="s">
+        <v>136</v>
+      </c>
+      <c r="C169" s="9">
+        <v>5520</v>
+      </c>
+      <c r="D169" s="9">
+        <v>5920</v>
+      </c>
+      <c r="E169" s="9">
+        <v>7120</v>
+      </c>
+      <c r="F169" t="s">
+        <v>133</v>
+      </c>
+      <c r="G169" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="H169" t="s">
+        <v>137</v>
+      </c>
+      <c r="I169" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C170" s="9"/>
-      <c r="D170" s="9"/>
-      <c r="E170" s="9"/>
-      <c r="G170" s="7"/>
+      <c r="A170" t="s">
+        <v>86</v>
+      </c>
+      <c r="B170" t="s">
+        <v>136</v>
+      </c>
+      <c r="C170" s="9">
+        <v>5520</v>
+      </c>
+      <c r="D170" s="9">
+        <v>5920</v>
+      </c>
+      <c r="E170" s="9">
+        <v>7120</v>
+      </c>
+      <c r="F170" t="s">
+        <v>133</v>
+      </c>
+      <c r="G170" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="H170" t="s">
+        <v>137</v>
+      </c>
+      <c r="I170" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C171" s="9"/>
-      <c r="D171" s="9"/>
-      <c r="E171" s="9"/>
-      <c r="G171" s="7"/>
+      <c r="A171" t="s">
+        <v>73</v>
+      </c>
+      <c r="B171" t="s">
+        <v>12</v>
+      </c>
+      <c r="C171" s="9">
+        <v>5330</v>
+      </c>
+      <c r="D171" s="9">
+        <v>6530</v>
+      </c>
+      <c r="E171" s="9">
+        <v>6830</v>
+      </c>
+      <c r="F171" t="s">
+        <v>133</v>
+      </c>
+      <c r="G171" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H171" t="s">
+        <v>69</v>
+      </c>
+      <c r="I171" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C172" s="9"/>
-      <c r="D172" s="9"/>
-      <c r="E172" s="9"/>
-      <c r="G172" s="7"/>
+      <c r="A172" t="s">
+        <v>74</v>
+      </c>
+      <c r="B172" t="s">
+        <v>12</v>
+      </c>
+      <c r="C172" s="9">
+        <v>5330</v>
+      </c>
+      <c r="D172" s="9">
+        <v>6530</v>
+      </c>
+      <c r="E172" s="9">
+        <v>6830</v>
+      </c>
+      <c r="F172" t="s">
+        <v>133</v>
+      </c>
+      <c r="G172" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H172" t="s">
+        <v>69</v>
+      </c>
+      <c r="I172" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C173" s="9"/>
-      <c r="D173" s="9"/>
-      <c r="E173" s="9"/>
-      <c r="G173" s="7"/>
+      <c r="A173" t="s">
+        <v>83</v>
+      </c>
+      <c r="B173" t="s">
+        <v>12</v>
+      </c>
+      <c r="C173" s="9">
+        <v>5330</v>
+      </c>
+      <c r="D173" s="9">
+        <v>6530</v>
+      </c>
+      <c r="E173" s="9">
+        <v>6830</v>
+      </c>
+      <c r="F173" t="s">
+        <v>133</v>
+      </c>
+      <c r="G173" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H173" t="s">
+        <v>69</v>
+      </c>
+      <c r="I173" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C174" s="9"/>
-      <c r="D174" s="9"/>
-      <c r="E174" s="9"/>
-      <c r="G174" s="7"/>
+      <c r="A174" t="s">
+        <v>75</v>
+      </c>
+      <c r="B174" t="s">
+        <v>12</v>
+      </c>
+      <c r="C174" s="9">
+        <v>5330</v>
+      </c>
+      <c r="D174" s="9">
+        <v>6530</v>
+      </c>
+      <c r="E174" s="9">
+        <v>6830</v>
+      </c>
+      <c r="F174" t="s">
+        <v>133</v>
+      </c>
+      <c r="G174" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H174" t="s">
+        <v>69</v>
+      </c>
+      <c r="I174" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C175" s="9"/>
-      <c r="D175" s="9"/>
-      <c r="E175" s="9"/>
-      <c r="G175" s="7"/>
+      <c r="A175" t="s">
+        <v>72</v>
+      </c>
+      <c r="B175" t="s">
+        <v>12</v>
+      </c>
+      <c r="C175" s="9">
+        <v>5330</v>
+      </c>
+      <c r="D175" s="9">
+        <v>6530</v>
+      </c>
+      <c r="E175" s="9">
+        <v>6830</v>
+      </c>
+      <c r="F175" t="s">
+        <v>133</v>
+      </c>
+      <c r="G175" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H175" t="s">
+        <v>69</v>
+      </c>
+      <c r="I175" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C176" s="9"/>
-      <c r="D176" s="9"/>
-      <c r="E176" s="9"/>
-      <c r="G176" s="7"/>
-    </row>
-    <row r="177" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C177" s="9"/>
-      <c r="D177" s="9"/>
-      <c r="E177" s="9"/>
-      <c r="G177" s="7"/>
-    </row>
-    <row r="178" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C178" s="9"/>
-      <c r="D178" s="9"/>
-      <c r="E178" s="9"/>
-      <c r="G178" s="7"/>
-    </row>
-    <row r="179" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C179" s="9"/>
-      <c r="D179" s="9"/>
-      <c r="E179" s="9"/>
-      <c r="G179" s="7"/>
-    </row>
-    <row r="180" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C180" s="9"/>
-      <c r="D180" s="9"/>
-      <c r="E180" s="9"/>
-      <c r="G180" s="7"/>
-    </row>
-    <row r="181" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C181" s="9"/>
-      <c r="D181" s="9"/>
-      <c r="E181" s="9"/>
-      <c r="G181" s="7"/>
-    </row>
-    <row r="182" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C182" s="9"/>
-      <c r="D182" s="9"/>
-      <c r="E182" s="9"/>
-      <c r="G182" s="7"/>
-    </row>
-    <row r="183" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C183" s="9"/>
-      <c r="D183" s="9"/>
-      <c r="E183" s="9"/>
-      <c r="G183" s="7"/>
-    </row>
-    <row r="184" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C184" s="9"/>
-      <c r="D184" s="9"/>
-      <c r="E184" s="9"/>
-      <c r="G184" s="7"/>
-    </row>
-    <row r="185" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C185" s="9"/>
-      <c r="D185" s="9"/>
-      <c r="E185" s="9"/>
-      <c r="G185" s="7"/>
-    </row>
-    <row r="186" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C186" s="9"/>
-      <c r="D186" s="9"/>
-      <c r="E186" s="9"/>
-      <c r="G186" s="7"/>
-    </row>
-    <row r="187" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C187" s="9"/>
-      <c r="D187" s="9"/>
-      <c r="E187" s="9"/>
-      <c r="G187" s="7"/>
-    </row>
-    <row r="188" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C188" s="9"/>
-      <c r="D188" s="9"/>
-      <c r="E188" s="9"/>
-      <c r="G188" s="7"/>
-    </row>
-    <row r="189" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C189" s="9"/>
-      <c r="D189" s="9"/>
-      <c r="E189" s="9"/>
-      <c r="G189" s="7"/>
-    </row>
-    <row r="190" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C190" s="9"/>
-      <c r="D190" s="9"/>
-      <c r="E190" s="9"/>
-      <c r="G190" s="7"/>
-    </row>
-    <row r="191" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C191" s="9"/>
-      <c r="D191" s="9"/>
-      <c r="E191" s="9"/>
-      <c r="G191" s="7"/>
-    </row>
-    <row r="192" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C192" s="9"/>
-      <c r="D192" s="9"/>
-      <c r="E192" s="9"/>
-      <c r="G192" s="7"/>
+      <c r="A176" t="s">
+        <v>104</v>
+      </c>
+      <c r="B176" t="s">
+        <v>12</v>
+      </c>
+      <c r="C176" s="9">
+        <v>5330</v>
+      </c>
+      <c r="D176" s="9">
+        <v>6530</v>
+      </c>
+      <c r="E176" s="9">
+        <v>6830</v>
+      </c>
+      <c r="F176" t="s">
+        <v>133</v>
+      </c>
+      <c r="G176" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H176" t="s">
+        <v>69</v>
+      </c>
+      <c r="I176" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>84</v>
+      </c>
+      <c r="B177" t="s">
+        <v>12</v>
+      </c>
+      <c r="C177" s="9">
+        <v>5330</v>
+      </c>
+      <c r="D177" s="9">
+        <v>6530</v>
+      </c>
+      <c r="E177" s="9">
+        <v>6830</v>
+      </c>
+      <c r="F177" t="s">
+        <v>133</v>
+      </c>
+      <c r="G177" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H177" t="s">
+        <v>69</v>
+      </c>
+      <c r="I177" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>141</v>
+      </c>
+      <c r="B178" t="s">
+        <v>12</v>
+      </c>
+      <c r="C178" s="9">
+        <v>5330</v>
+      </c>
+      <c r="D178" s="9">
+        <v>6530</v>
+      </c>
+      <c r="E178" s="9">
+        <v>6830</v>
+      </c>
+      <c r="F178" t="s">
+        <v>133</v>
+      </c>
+      <c r="G178" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H178" t="s">
+        <v>69</v>
+      </c>
+      <c r="I178" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>76</v>
+      </c>
+      <c r="B179" t="s">
+        <v>12</v>
+      </c>
+      <c r="C179" s="9">
+        <v>5330</v>
+      </c>
+      <c r="D179" s="9">
+        <v>6530</v>
+      </c>
+      <c r="E179" s="9">
+        <v>6830</v>
+      </c>
+      <c r="F179" t="s">
+        <v>133</v>
+      </c>
+      <c r="G179" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H179" t="s">
+        <v>69</v>
+      </c>
+      <c r="I179" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>82</v>
+      </c>
+      <c r="B180" t="s">
+        <v>12</v>
+      </c>
+      <c r="C180" s="9">
+        <v>5330</v>
+      </c>
+      <c r="D180" s="9">
+        <v>6530</v>
+      </c>
+      <c r="E180" s="9">
+        <v>6830</v>
+      </c>
+      <c r="F180" t="s">
+        <v>133</v>
+      </c>
+      <c r="G180" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H180" t="s">
+        <v>69</v>
+      </c>
+      <c r="I180" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>71</v>
+      </c>
+      <c r="B181" t="s">
+        <v>12</v>
+      </c>
+      <c r="C181" s="9">
+        <v>5330</v>
+      </c>
+      <c r="D181" s="9">
+        <v>6530</v>
+      </c>
+      <c r="E181" s="9">
+        <v>6830</v>
+      </c>
+      <c r="F181" t="s">
+        <v>133</v>
+      </c>
+      <c r="G181" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H181" t="s">
+        <v>69</v>
+      </c>
+      <c r="I181" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>73</v>
+      </c>
+      <c r="B182" t="s">
+        <v>12</v>
+      </c>
+      <c r="C182" s="9">
+        <v>5370</v>
+      </c>
+      <c r="D182" s="9">
+        <v>6570</v>
+      </c>
+      <c r="E182" s="9">
+        <v>6870</v>
+      </c>
+      <c r="F182" t="s">
+        <v>133</v>
+      </c>
+      <c r="G182" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="H182" t="s">
+        <v>68</v>
+      </c>
+      <c r="I182" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>74</v>
+      </c>
+      <c r="B183" t="s">
+        <v>12</v>
+      </c>
+      <c r="C183" s="9">
+        <v>5370</v>
+      </c>
+      <c r="D183" s="9">
+        <v>6570</v>
+      </c>
+      <c r="E183" s="9">
+        <v>6870</v>
+      </c>
+      <c r="F183" t="s">
+        <v>133</v>
+      </c>
+      <c r="G183" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="H183" t="s">
+        <v>68</v>
+      </c>
+      <c r="I183" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>83</v>
+      </c>
+      <c r="B184" t="s">
+        <v>12</v>
+      </c>
+      <c r="C184" s="9">
+        <v>5370</v>
+      </c>
+      <c r="D184" s="9">
+        <v>6570</v>
+      </c>
+      <c r="E184" s="9">
+        <v>6870</v>
+      </c>
+      <c r="F184" t="s">
+        <v>133</v>
+      </c>
+      <c r="G184" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="H184" t="s">
+        <v>68</v>
+      </c>
+      <c r="I184" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>75</v>
+      </c>
+      <c r="B185" t="s">
+        <v>12</v>
+      </c>
+      <c r="C185" s="9">
+        <v>5370</v>
+      </c>
+      <c r="D185" s="9">
+        <v>6570</v>
+      </c>
+      <c r="E185" s="9">
+        <v>6870</v>
+      </c>
+      <c r="F185" t="s">
+        <v>133</v>
+      </c>
+      <c r="G185" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="H185" t="s">
+        <v>68</v>
+      </c>
+      <c r="I185" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>72</v>
+      </c>
+      <c r="B186" t="s">
+        <v>12</v>
+      </c>
+      <c r="C186" s="9">
+        <v>5370</v>
+      </c>
+      <c r="D186" s="9">
+        <v>6570</v>
+      </c>
+      <c r="E186" s="9">
+        <v>6870</v>
+      </c>
+      <c r="F186" t="s">
+        <v>133</v>
+      </c>
+      <c r="G186" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="H186" t="s">
+        <v>68</v>
+      </c>
+      <c r="I186" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>104</v>
+      </c>
+      <c r="B187" t="s">
+        <v>12</v>
+      </c>
+      <c r="C187" s="9">
+        <v>5370</v>
+      </c>
+      <c r="D187" s="9">
+        <v>6570</v>
+      </c>
+      <c r="E187" s="9">
+        <v>6870</v>
+      </c>
+      <c r="F187" t="s">
+        <v>133</v>
+      </c>
+      <c r="G187" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="H187" t="s">
+        <v>68</v>
+      </c>
+      <c r="I187" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>84</v>
+      </c>
+      <c r="B188" t="s">
+        <v>12</v>
+      </c>
+      <c r="C188" s="9">
+        <v>5370</v>
+      </c>
+      <c r="D188" s="9">
+        <v>6570</v>
+      </c>
+      <c r="E188" s="9">
+        <v>6870</v>
+      </c>
+      <c r="F188" t="s">
+        <v>133</v>
+      </c>
+      <c r="G188" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="H188" t="s">
+        <v>68</v>
+      </c>
+      <c r="I188" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>141</v>
+      </c>
+      <c r="B189" t="s">
+        <v>12</v>
+      </c>
+      <c r="C189" s="9">
+        <v>5370</v>
+      </c>
+      <c r="D189" s="9">
+        <v>6570</v>
+      </c>
+      <c r="E189" s="9">
+        <v>6870</v>
+      </c>
+      <c r="F189" t="s">
+        <v>133</v>
+      </c>
+      <c r="G189" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="H189" t="s">
+        <v>68</v>
+      </c>
+      <c r="I189" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>76</v>
+      </c>
+      <c r="B190" t="s">
+        <v>12</v>
+      </c>
+      <c r="C190" s="9">
+        <v>5370</v>
+      </c>
+      <c r="D190" s="9">
+        <v>6570</v>
+      </c>
+      <c r="E190" s="9">
+        <v>6870</v>
+      </c>
+      <c r="F190" t="s">
+        <v>133</v>
+      </c>
+      <c r="G190" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="H190" t="s">
+        <v>68</v>
+      </c>
+      <c r="I190" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>82</v>
+      </c>
+      <c r="B191" t="s">
+        <v>12</v>
+      </c>
+      <c r="C191" s="9">
+        <v>5370</v>
+      </c>
+      <c r="D191" s="9">
+        <v>6570</v>
+      </c>
+      <c r="E191" s="9">
+        <v>6870</v>
+      </c>
+      <c r="F191" t="s">
+        <v>133</v>
+      </c>
+      <c r="G191" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="H191" t="s">
+        <v>68</v>
+      </c>
+      <c r="I191" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>71</v>
+      </c>
+      <c r="B192" t="s">
+        <v>12</v>
+      </c>
+      <c r="C192" s="9">
+        <v>5370</v>
+      </c>
+      <c r="D192" s="9">
+        <v>6570</v>
+      </c>
+      <c r="E192" s="9">
+        <v>6870</v>
+      </c>
+      <c r="F192" t="s">
+        <v>133</v>
+      </c>
+      <c r="G192" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="H192" t="s">
+        <v>68</v>
+      </c>
+      <c r="I192" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="193" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C193" s="9"/>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DOCS EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{778DF982-90CF-4C2A-9DD2-680606C5BEE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF2A3FC9-E325-4505-946D-515C57848475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="141">
   <si>
     <t>POD</t>
   </si>
@@ -255,9 +255,6 @@
     <t>COSCO</t>
   </si>
   <si>
-    <t>PIL</t>
-  </si>
-  <si>
     <t>NINGBO</t>
   </si>
   <si>
@@ -288,9 +285,6 @@
     <t>SHANTOU</t>
   </si>
   <si>
-    <t>18 DRY / 14 NOR</t>
-  </si>
-  <si>
     <t>SHANGHAI</t>
   </si>
   <si>
@@ -417,12 +411,6 @@
     <t>PHUOC AN PORT</t>
   </si>
   <si>
-    <t>YML (Z-ES) PESO LÍMITE 20GP HASTA 16TN</t>
-  </si>
-  <si>
-    <t>OOCL (Z-HF) 20GP ≥ 18TN AGREGAR OWS $250</t>
-  </si>
-  <si>
     <t>GURGAON - GARHI HARSARU</t>
   </si>
   <si>
@@ -444,30 +432,9 @@
     <t>16 al 31 de octubre</t>
   </si>
   <si>
-    <t>22 al 28 de octubre</t>
-  </si>
-  <si>
-    <t>Z-CT</t>
-  </si>
-  <si>
-    <t>17 DRY / 14 NOR</t>
-  </si>
-  <si>
-    <t>POSORJA</t>
-  </si>
-  <si>
-    <t>CMA</t>
-  </si>
-  <si>
-    <t>Z-HF</t>
-  </si>
-  <si>
     <t>21 DRY / 14 NOR</t>
   </si>
   <si>
-    <t>KAOSHIUNG</t>
-  </si>
-  <si>
     <t>XINGANG</t>
   </si>
   <si>
@@ -475,6 +442,30 @@
   </si>
   <si>
     <t>18 DRY / 10 NOR</t>
+  </si>
+  <si>
+    <t>1 al 8 de noviembre</t>
+  </si>
+  <si>
+    <t>1 al 7 de noviembre</t>
+  </si>
+  <si>
+    <t>WENZHOU</t>
+  </si>
+  <si>
+    <t>FUQING</t>
+  </si>
+  <si>
+    <t>EMC</t>
+  </si>
+  <si>
+    <t>Z-ES</t>
+  </si>
+  <si>
+    <t>OOCL</t>
+  </si>
+  <si>
+    <t>OOCL (Z-ES) 20GP PESO MÁXIMO 16TN</t>
   </si>
 </sst>
 </file>
@@ -1013,7 +1004,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}">
-  <dimension ref="A1:I356"/>
+  <dimension ref="A1:I217"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
@@ -1066,7 +1057,7 @@
         <v>6850</v>
       </c>
       <c r="F2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G2" s="7">
         <v>18</v>
@@ -1093,7 +1084,7 @@
         <v>7250</v>
       </c>
       <c r="F3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G3" s="7">
         <v>18</v>
@@ -1120,7 +1111,7 @@
         <v>6850</v>
       </c>
       <c r="F4" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G4" s="7">
         <v>18</v>
@@ -1147,7 +1138,7 @@
         <v>6850</v>
       </c>
       <c r="F5" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G5" s="7">
         <v>18</v>
@@ -1174,7 +1165,7 @@
         <v>6850</v>
       </c>
       <c r="F6" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G6" s="7">
         <v>18</v>
@@ -1201,7 +1192,7 @@
         <v>6150</v>
       </c>
       <c r="F7" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G7" s="7">
         <v>18</v>
@@ -1228,7 +1219,7 @@
         <v>6150</v>
       </c>
       <c r="F8" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G8" s="7">
         <v>18</v>
@@ -1255,7 +1246,7 @@
         <v>6450</v>
       </c>
       <c r="F9" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G9" s="7">
         <v>18</v>
@@ -1282,7 +1273,7 @@
         <v>6150</v>
       </c>
       <c r="F10" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G10" s="7">
         <v>18</v>
@@ -1309,7 +1300,7 @@
         <v>6150</v>
       </c>
       <c r="F11" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G11" s="7">
         <v>18</v>
@@ -1323,7 +1314,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -1336,7 +1327,7 @@
         <v>6150</v>
       </c>
       <c r="F12" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G12" s="7">
         <v>18</v>
@@ -1363,7 +1354,7 @@
         <v>6150</v>
       </c>
       <c r="F13" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G13" s="7">
         <v>18</v>
@@ -1377,7 +1368,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -1390,7 +1381,7 @@
         <v>6150</v>
       </c>
       <c r="F14" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G14" s="7">
         <v>18</v>
@@ -1417,7 +1408,7 @@
         <v>6150</v>
       </c>
       <c r="F15" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G15" s="7">
         <v>18</v>
@@ -1444,7 +1435,7 @@
         <v>6150</v>
       </c>
       <c r="F16" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G16" s="7">
         <v>18</v>
@@ -1471,7 +1462,7 @@
         <v>6150</v>
       </c>
       <c r="F17" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G17" s="7">
         <v>18</v>
@@ -1498,7 +1489,7 @@
         <v>6150</v>
       </c>
       <c r="F18" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G18" s="7">
         <v>18</v>
@@ -1525,7 +1516,7 @@
         <v>6450</v>
       </c>
       <c r="F19" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G19" s="7">
         <v>18</v>
@@ -1552,7 +1543,7 @@
         <v>6150</v>
       </c>
       <c r="F20" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G20" s="7">
         <v>18</v>
@@ -1579,7 +1570,7 @@
         <v>6150</v>
       </c>
       <c r="F21" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G21" s="7">
         <v>18</v>
@@ -1593,7 +1584,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B22" t="s">
         <v>12</v>
@@ -1606,7 +1597,7 @@
         <v>6550</v>
       </c>
       <c r="F22" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G22" s="7">
         <v>18</v>
@@ -1633,7 +1624,7 @@
         <v>5850</v>
       </c>
       <c r="F23" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G23" s="7">
         <v>18</v>
@@ -1660,7 +1651,7 @@
         <v>5850</v>
       </c>
       <c r="F24" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G24" s="7">
         <v>18</v>
@@ -1687,7 +1678,7 @@
         <v>5850</v>
       </c>
       <c r="F25" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G25" s="7">
         <v>18</v>
@@ -1714,7 +1705,7 @@
         <v>5850</v>
       </c>
       <c r="F26" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G26" s="7">
         <v>18</v>
@@ -1741,7 +1732,7 @@
         <v>5850</v>
       </c>
       <c r="F27" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G27" s="7">
         <v>18</v>
@@ -1768,7 +1759,7 @@
         <v>6150</v>
       </c>
       <c r="F28" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G28" s="7">
         <v>18</v>
@@ -1795,7 +1786,7 @@
         <v>6150</v>
       </c>
       <c r="F29" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G29" s="7">
         <v>18</v>
@@ -1809,7 +1800,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B30" t="s">
         <v>12</v>
@@ -1822,7 +1813,7 @@
         <v>5850</v>
       </c>
       <c r="F30" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G30" s="7">
         <v>18</v>
@@ -1836,7 +1827,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B31" t="s">
         <v>12</v>
@@ -1849,7 +1840,7 @@
         <v>5940</v>
       </c>
       <c r="F31" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G31" s="7">
         <v>18</v>
@@ -1876,7 +1867,7 @@
         <v>6850</v>
       </c>
       <c r="F32" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G32" s="7">
         <v>18</v>
@@ -1890,7 +1881,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B33" t="s">
         <v>12</v>
@@ -1903,7 +1894,7 @@
         <v>6850</v>
       </c>
       <c r="F33" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G33" s="7">
         <v>18</v>
@@ -1917,7 +1908,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B34" t="s">
         <v>12</v>
@@ -1930,7 +1921,7 @@
         <v>6850</v>
       </c>
       <c r="F34" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G34" s="7">
         <v>18</v>
@@ -1957,7 +1948,7 @@
         <v>7350</v>
       </c>
       <c r="F35" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G35" s="7">
         <v>18</v>
@@ -1984,7 +1975,7 @@
         <v>6650</v>
       </c>
       <c r="F36" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G36" s="7">
         <v>18</v>
@@ -2011,7 +2002,7 @@
         <v>6150</v>
       </c>
       <c r="F37" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G37" s="7">
         <v>18</v>
@@ -2038,7 +2029,7 @@
         <v>6150</v>
       </c>
       <c r="F38" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G38" s="7">
         <v>18</v>
@@ -2052,7 +2043,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B39" t="s">
         <v>12</v>
@@ -2065,7 +2056,7 @@
         <v>6300</v>
       </c>
       <c r="F39" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G39" s="7">
         <v>18</v>
@@ -2092,7 +2083,7 @@
         <v>6150</v>
       </c>
       <c r="F40" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G40" s="7">
         <v>18</v>
@@ -2119,7 +2110,7 @@
         <v>5950</v>
       </c>
       <c r="F41" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G41" s="7">
         <v>18</v>
@@ -2146,7 +2137,7 @@
         <v>6650</v>
       </c>
       <c r="F42" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G42" s="7">
         <v>18</v>
@@ -2173,7 +2164,7 @@
         <v>5950</v>
       </c>
       <c r="F43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G43" s="7">
         <v>18</v>
@@ -2200,7 +2191,7 @@
         <v>5950</v>
       </c>
       <c r="F44" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G44" s="7">
         <v>18</v>
@@ -2227,7 +2218,7 @@
         <v>5950</v>
       </c>
       <c r="F45" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G45" s="7">
         <v>18</v>
@@ -2241,7 +2232,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B46" t="s">
         <v>12</v>
@@ -2254,7 +2245,7 @@
         <v>5950</v>
       </c>
       <c r="F46" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G46" s="7">
         <v>18</v>
@@ -2281,7 +2272,7 @@
         <v>6160</v>
       </c>
       <c r="F47" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G47" s="7">
         <v>18</v>
@@ -2308,7 +2299,7 @@
         <v>6350</v>
       </c>
       <c r="F48" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G48" s="7">
         <v>18</v>
@@ -2335,7 +2326,7 @@
         <v>6350</v>
       </c>
       <c r="F49" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G49" s="7">
         <v>18</v>
@@ -2362,7 +2353,7 @@
         <v>5850</v>
       </c>
       <c r="F50" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G50" s="7">
         <v>18</v>
@@ -2389,7 +2380,7 @@
         <v>6150</v>
       </c>
       <c r="F51" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G51" s="7">
         <v>18</v>
@@ -2403,7 +2394,7 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B52" t="s">
         <v>12</v>
@@ -2416,7 +2407,7 @@
         <v>6150</v>
       </c>
       <c r="F52" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G52" s="7">
         <v>18</v>
@@ -2443,7 +2434,7 @@
         <v>6150</v>
       </c>
       <c r="F53" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G53" s="7">
         <v>18</v>
@@ -2457,417 +2448,431 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B54" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="9">
-        <v>5010</v>
+        <v>4930</v>
       </c>
       <c r="D54" s="9">
-        <v>6510</v>
+        <v>6530</v>
       </c>
       <c r="E54" s="9">
-        <v>6810</v>
+        <v>6630</v>
       </c>
       <c r="F54" t="s">
         <v>133</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H54" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I54" t="s">
-        <v>134</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B55" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="9">
-        <v>5010</v>
+        <v>4930</v>
       </c>
       <c r="D55" s="9">
-        <v>6510</v>
+        <v>6530</v>
       </c>
       <c r="E55" s="9">
-        <v>6810</v>
+        <v>6630</v>
       </c>
       <c r="F55" t="s">
         <v>133</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H55" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I55" t="s">
-        <v>134</v>
+        <v>27</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B56" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="9">
-        <v>5010</v>
+        <v>4930</v>
       </c>
       <c r="D56" s="9">
-        <v>6510</v>
+        <v>6530</v>
       </c>
       <c r="E56" s="9">
-        <v>6810</v>
+        <v>6630</v>
       </c>
       <c r="F56" t="s">
         <v>133</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H56" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I56" t="s">
-        <v>134</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="B57" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="9">
-        <v>5010</v>
+        <v>4930</v>
       </c>
       <c r="D57" s="9">
-        <v>6510</v>
+        <v>6530</v>
       </c>
       <c r="E57" s="9">
-        <v>6810</v>
+        <v>6630</v>
       </c>
       <c r="F57" t="s">
         <v>133</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H57" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I57" t="s">
-        <v>134</v>
+        <v>27</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="B58" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="9">
-        <v>5010</v>
+        <v>4930</v>
       </c>
       <c r="D58" s="9">
-        <v>6510</v>
+        <v>6530</v>
       </c>
       <c r="E58" s="9">
-        <v>6810</v>
+        <v>6630</v>
       </c>
       <c r="F58" t="s">
         <v>133</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H58" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I58" t="s">
-        <v>134</v>
+        <v>27</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="B59" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="9">
-        <v>5010</v>
+        <v>4930</v>
       </c>
       <c r="D59" s="9">
-        <v>6510</v>
+        <v>6530</v>
       </c>
       <c r="E59" s="9">
-        <v>6810</v>
+        <v>6630</v>
       </c>
       <c r="F59" t="s">
         <v>133</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H59" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I59" t="s">
-        <v>134</v>
+        <v>27</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B60" t="s">
         <v>12</v>
       </c>
       <c r="C60" s="9">
-        <v>5010</v>
+        <v>4930</v>
       </c>
       <c r="D60" s="9">
-        <v>6510</v>
+        <v>6530</v>
       </c>
       <c r="E60" s="9">
-        <v>6810</v>
+        <v>6630</v>
       </c>
       <c r="F60" t="s">
         <v>133</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H60" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I60" t="s">
-        <v>134</v>
+        <v>27</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="B61" t="s">
         <v>12</v>
       </c>
-      <c r="C61" s="9"/>
+      <c r="C61" s="9">
+        <v>4930</v>
+      </c>
       <c r="D61" s="9">
-        <v>6770</v>
+        <v>6530</v>
       </c>
       <c r="E61" s="9">
-        <v>7070</v>
+        <v>6630</v>
       </c>
       <c r="F61" t="s">
         <v>133</v>
       </c>
-      <c r="G61" s="7">
-        <v>20</v>
+      <c r="G61" s="7" t="s">
+        <v>132</v>
       </c>
       <c r="H61" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I61" t="s">
-        <v>134</v>
+        <v>27</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="B62" t="s">
         <v>12</v>
       </c>
-      <c r="C62" s="9"/>
+      <c r="C62" s="9">
+        <v>5180</v>
+      </c>
       <c r="D62" s="9">
-        <v>6770</v>
+        <v>6680</v>
       </c>
       <c r="E62" s="9">
-        <v>7070</v>
+        <v>6880</v>
       </c>
       <c r="F62" t="s">
         <v>133</v>
       </c>
-      <c r="G62" s="7">
-        <v>20</v>
+      <c r="G62" s="7" t="s">
+        <v>132</v>
       </c>
       <c r="H62" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I62" t="s">
-        <v>134</v>
+        <v>27</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="B63" t="s">
         <v>12</v>
       </c>
-      <c r="C63" s="9"/>
+      <c r="C63" s="9">
+        <v>5130</v>
+      </c>
       <c r="D63" s="9">
-        <v>6770</v>
+        <v>6630</v>
       </c>
       <c r="E63" s="9">
-        <v>7070</v>
+        <v>6830</v>
       </c>
       <c r="F63" t="s">
         <v>133</v>
       </c>
-      <c r="G63" s="7">
-        <v>20</v>
+      <c r="G63" s="7" t="s">
+        <v>132</v>
       </c>
       <c r="H63" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I63" t="s">
-        <v>134</v>
+        <v>27</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B64" t="s">
         <v>12</v>
       </c>
-      <c r="C64" s="9"/>
+      <c r="C64" s="9">
+        <v>5180</v>
+      </c>
       <c r="D64" s="9">
-        <v>6770</v>
+        <v>6680</v>
       </c>
       <c r="E64" s="9">
-        <v>7070</v>
+        <v>6880</v>
       </c>
       <c r="F64" t="s">
         <v>133</v>
       </c>
-      <c r="G64" s="7">
-        <v>20</v>
+      <c r="G64" s="7" t="s">
+        <v>132</v>
       </c>
       <c r="H64" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I64" t="s">
-        <v>134</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="B65" t="s">
         <v>12</v>
       </c>
-      <c r="C65" s="9"/>
+      <c r="C65" s="9">
+        <v>5030</v>
+      </c>
       <c r="D65" s="9">
-        <v>6770</v>
+        <v>6580</v>
       </c>
       <c r="E65" s="9">
-        <v>7070</v>
+        <v>6730</v>
       </c>
       <c r="F65" t="s">
         <v>133</v>
       </c>
-      <c r="G65" s="7">
-        <v>20</v>
+      <c r="G65" s="7" t="s">
+        <v>132</v>
       </c>
       <c r="H65" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I65" t="s">
-        <v>134</v>
+        <v>27</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B66" t="s">
         <v>12</v>
       </c>
-      <c r="C66" s="9"/>
+      <c r="C66" s="9">
+        <v>5030</v>
+      </c>
       <c r="D66" s="9">
-        <v>6770</v>
+        <v>6580</v>
       </c>
       <c r="E66" s="9">
-        <v>7070</v>
+        <v>6730</v>
       </c>
       <c r="F66" t="s">
         <v>133</v>
       </c>
-      <c r="G66" s="7">
-        <v>20</v>
+      <c r="G66" s="7" t="s">
+        <v>132</v>
       </c>
       <c r="H66" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I66" t="s">
-        <v>134</v>
+        <v>27</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="B67" t="s">
         <v>12</v>
       </c>
-      <c r="C67" s="9"/>
+      <c r="C67" s="9">
+        <v>5030</v>
+      </c>
       <c r="D67" s="9">
-        <v>6770</v>
+        <v>6580</v>
       </c>
       <c r="E67" s="9">
-        <v>7070</v>
+        <v>6730</v>
       </c>
       <c r="F67" t="s">
         <v>133</v>
       </c>
-      <c r="G67" s="7">
-        <v>20</v>
+      <c r="G67" s="7" t="s">
+        <v>132</v>
       </c>
       <c r="H67" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I67" t="s">
-        <v>134</v>
+        <v>27</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B68" t="s">
         <v>12</v>
       </c>
       <c r="C68" s="9">
-        <v>5130</v>
+        <v>5030</v>
       </c>
       <c r="D68" s="9">
-        <v>6630</v>
+        <v>6580</v>
       </c>
       <c r="E68" s="9">
-        <v>6830</v>
+        <v>6730</v>
       </c>
       <c r="F68" t="s">
         <v>133</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H68" t="s">
         <v>68</v>
@@ -2878,25 +2883,25 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B69" t="s">
         <v>12</v>
       </c>
       <c r="C69" s="9">
-        <v>5130</v>
+        <v>5030</v>
       </c>
       <c r="D69" s="9">
-        <v>6630</v>
+        <v>6580</v>
       </c>
       <c r="E69" s="9">
-        <v>6830</v>
+        <v>6730</v>
       </c>
       <c r="F69" t="s">
         <v>133</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H69" t="s">
         <v>68</v>
@@ -2907,25 +2912,25 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="B70" t="s">
         <v>12</v>
       </c>
       <c r="C70" s="9">
-        <v>5130</v>
+        <v>5030</v>
       </c>
       <c r="D70" s="9">
-        <v>6630</v>
+        <v>6580</v>
       </c>
       <c r="E70" s="9">
-        <v>6830</v>
+        <v>6730</v>
       </c>
       <c r="F70" t="s">
         <v>133</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H70" t="s">
         <v>68</v>
@@ -2936,25 +2941,25 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="B71" t="s">
         <v>12</v>
       </c>
       <c r="C71" s="9">
-        <v>5130</v>
+        <v>5030</v>
       </c>
       <c r="D71" s="9">
-        <v>6630</v>
+        <v>6580</v>
       </c>
       <c r="E71" s="9">
-        <v>6830</v>
+        <v>6730</v>
       </c>
       <c r="F71" t="s">
         <v>133</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H71" t="s">
         <v>68</v>
@@ -2965,25 +2970,25 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="B72" t="s">
         <v>12</v>
       </c>
       <c r="C72" s="9">
-        <v>5130</v>
+        <v>5030</v>
       </c>
       <c r="D72" s="9">
-        <v>6630</v>
+        <v>6580</v>
       </c>
       <c r="E72" s="9">
-        <v>6830</v>
+        <v>6730</v>
       </c>
       <c r="F72" t="s">
         <v>133</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H72" t="s">
         <v>68</v>
@@ -2994,25 +2999,25 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="B73" t="s">
         <v>12</v>
       </c>
       <c r="C73" s="9">
-        <v>5130</v>
+        <v>5030</v>
       </c>
       <c r="D73" s="9">
-        <v>6630</v>
+        <v>6580</v>
       </c>
       <c r="E73" s="9">
-        <v>6830</v>
+        <v>6730</v>
       </c>
       <c r="F73" t="s">
         <v>133</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H73" t="s">
         <v>68</v>
@@ -3023,25 +3028,25 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="B74" t="s">
         <v>12</v>
       </c>
       <c r="C74" s="9">
-        <v>5130</v>
+        <v>5030</v>
       </c>
       <c r="D74" s="9">
-        <v>6630</v>
+        <v>6580</v>
       </c>
       <c r="E74" s="9">
-        <v>6830</v>
+        <v>6730</v>
       </c>
       <c r="F74" t="s">
         <v>133</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H74" t="s">
         <v>68</v>
@@ -3052,25 +3057,25 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="B75" t="s">
         <v>12</v>
       </c>
       <c r="C75" s="9">
-        <v>5130</v>
+        <v>5030</v>
       </c>
       <c r="D75" s="9">
-        <v>6630</v>
+        <v>6580</v>
       </c>
       <c r="E75" s="9">
-        <v>6830</v>
+        <v>6730</v>
       </c>
       <c r="F75" t="s">
         <v>133</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H75" t="s">
         <v>68</v>
@@ -3081,25 +3086,25 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="B76" t="s">
         <v>12</v>
       </c>
       <c r="C76" s="9">
-        <v>5380</v>
+        <v>5080</v>
       </c>
       <c r="D76" s="9">
+        <v>6630</v>
+      </c>
+      <c r="E76" s="9">
         <v>6780</v>
       </c>
-      <c r="E76" s="9">
-        <v>7080</v>
-      </c>
       <c r="F76" t="s">
         <v>133</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H76" t="s">
         <v>68</v>
@@ -3110,25 +3115,25 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="B77" t="s">
         <v>12</v>
       </c>
       <c r="C77" s="9">
-        <v>5330</v>
+        <v>7430</v>
       </c>
       <c r="D77" s="9">
-        <v>6730</v>
+        <v>6930</v>
       </c>
       <c r="E77" s="9">
-        <v>7030</v>
+        <v>7430</v>
       </c>
       <c r="F77" t="s">
         <v>133</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H77" t="s">
         <v>68</v>
@@ -3139,25 +3144,25 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="B78" t="s">
         <v>12</v>
       </c>
       <c r="C78" s="9">
-        <v>5380</v>
+        <v>5230</v>
       </c>
       <c r="D78" s="9">
-        <v>6780</v>
+        <v>6730</v>
       </c>
       <c r="E78" s="9">
-        <v>7080</v>
+        <v>6930</v>
       </c>
       <c r="F78" t="s">
         <v>133</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H78" t="s">
         <v>68</v>
@@ -3168,25 +3173,25 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="B79" t="s">
         <v>12</v>
       </c>
       <c r="C79" s="9">
-        <v>5230</v>
+        <v>5430</v>
       </c>
       <c r="D79" s="9">
-        <v>6680</v>
+        <v>6830</v>
       </c>
       <c r="E79" s="9">
-        <v>6930</v>
+        <v>7130</v>
       </c>
       <c r="F79" t="s">
         <v>133</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H79" t="s">
         <v>68</v>
@@ -3197,25 +3202,25 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="B80" t="s">
         <v>12</v>
       </c>
       <c r="C80" s="9">
-        <v>5230</v>
+        <v>5430</v>
       </c>
       <c r="D80" s="9">
-        <v>6680</v>
+        <v>6830</v>
       </c>
       <c r="E80" s="9">
-        <v>6930</v>
+        <v>7130</v>
       </c>
       <c r="F80" t="s">
         <v>133</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H80" t="s">
         <v>68</v>
@@ -3226,25 +3231,25 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="B81" t="s">
         <v>12</v>
       </c>
       <c r="C81" s="9">
-        <v>5230</v>
+        <v>5130</v>
       </c>
       <c r="D81" s="9">
         <v>6680</v>
       </c>
       <c r="E81" s="9">
-        <v>6930</v>
+        <v>6830</v>
       </c>
       <c r="F81" t="s">
         <v>133</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H81" t="s">
         <v>68</v>
@@ -3255,7 +3260,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="B82" t="s">
         <v>12</v>
@@ -3264,7 +3269,7 @@
         <v>5230</v>
       </c>
       <c r="D82" s="9">
-        <v>6680</v>
+        <v>6730</v>
       </c>
       <c r="E82" s="9">
         <v>6930</v>
@@ -3273,7 +3278,7 @@
         <v>133</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H82" t="s">
         <v>68</v>
@@ -3284,7 +3289,7 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="B83" t="s">
         <v>12</v>
@@ -3293,7 +3298,7 @@
         <v>5230</v>
       </c>
       <c r="D83" s="9">
-        <v>6680</v>
+        <v>6730</v>
       </c>
       <c r="E83" s="9">
         <v>6930</v>
@@ -3302,7 +3307,7 @@
         <v>133</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H83" t="s">
         <v>68</v>
@@ -3313,7 +3318,7 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="B84" t="s">
         <v>12</v>
@@ -3322,7 +3327,7 @@
         <v>5230</v>
       </c>
       <c r="D84" s="9">
-        <v>6680</v>
+        <v>6730</v>
       </c>
       <c r="E84" s="9">
         <v>6930</v>
@@ -3331,7 +3336,7 @@
         <v>133</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H84" t="s">
         <v>68</v>
@@ -3342,7 +3347,7 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B85" t="s">
         <v>12</v>
@@ -3351,7 +3356,7 @@
         <v>5230</v>
       </c>
       <c r="D85" s="9">
-        <v>6680</v>
+        <v>6730</v>
       </c>
       <c r="E85" s="9">
         <v>6930</v>
@@ -3360,7 +3365,7 @@
         <v>133</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H85" t="s">
         <v>68</v>
@@ -3371,7 +3376,7 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B86" t="s">
         <v>12</v>
@@ -3380,7 +3385,7 @@
         <v>5230</v>
       </c>
       <c r="D86" s="9">
-        <v>6680</v>
+        <v>6730</v>
       </c>
       <c r="E86" s="9">
         <v>6930</v>
@@ -3389,7 +3394,7 @@
         <v>133</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H86" t="s">
         <v>68</v>
@@ -3400,7 +3405,7 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B87" t="s">
         <v>12</v>
@@ -3409,7 +3414,7 @@
         <v>5230</v>
       </c>
       <c r="D87" s="9">
-        <v>6680</v>
+        <v>6730</v>
       </c>
       <c r="E87" s="9">
         <v>6930</v>
@@ -3418,7 +3423,7 @@
         <v>133</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H87" t="s">
         <v>68</v>
@@ -3429,7 +3434,7 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="B88" t="s">
         <v>12</v>
@@ -3438,7 +3443,7 @@
         <v>5230</v>
       </c>
       <c r="D88" s="9">
-        <v>6680</v>
+        <v>6730</v>
       </c>
       <c r="E88" s="9">
         <v>6930</v>
@@ -3447,7 +3452,7 @@
         <v>133</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H88" t="s">
         <v>68</v>
@@ -3458,7 +3463,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="B89" t="s">
         <v>12</v>
@@ -3467,7 +3472,7 @@
         <v>5230</v>
       </c>
       <c r="D89" s="9">
-        <v>6680</v>
+        <v>6730</v>
       </c>
       <c r="E89" s="9">
         <v>6930</v>
@@ -3476,7 +3481,7 @@
         <v>133</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H89" t="s">
         <v>68</v>
@@ -3487,25 +3492,25 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B90" t="s">
         <v>12</v>
       </c>
       <c r="C90" s="9">
-        <v>5280</v>
+        <v>5230</v>
       </c>
       <c r="D90" s="9">
         <v>6730</v>
       </c>
       <c r="E90" s="9">
-        <v>6980</v>
+        <v>6930</v>
       </c>
       <c r="F90" t="s">
         <v>133</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H90" t="s">
         <v>68</v>
@@ -3516,25 +3521,25 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="B91" t="s">
         <v>12</v>
       </c>
       <c r="C91" s="9">
-        <v>7630</v>
+        <v>5380</v>
       </c>
       <c r="D91" s="9">
-        <v>7030</v>
+        <v>6780</v>
       </c>
       <c r="E91" s="9">
-        <v>7630</v>
+        <v>7080</v>
       </c>
       <c r="F91" t="s">
         <v>133</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H91" t="s">
         <v>68</v>
@@ -3545,7 +3550,7 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="B92" t="s">
         <v>12</v>
@@ -3563,7 +3568,7 @@
         <v>133</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H92" t="s">
         <v>68</v>
@@ -3574,25 +3579,25 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="B93" t="s">
         <v>12</v>
       </c>
       <c r="C93" s="9">
-        <v>5630</v>
+        <v>5380</v>
       </c>
       <c r="D93" s="9">
-        <v>6930</v>
+        <v>6780</v>
       </c>
       <c r="E93" s="9">
-        <v>7330</v>
+        <v>7080</v>
       </c>
       <c r="F93" t="s">
         <v>133</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H93" t="s">
         <v>68</v>
@@ -3603,25 +3608,25 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B94" t="s">
         <v>12</v>
       </c>
       <c r="C94" s="9">
-        <v>5630</v>
+        <v>5480</v>
       </c>
       <c r="D94" s="9">
-        <v>6930</v>
+        <v>6880</v>
       </c>
       <c r="E94" s="9">
-        <v>7330</v>
+        <v>7180</v>
       </c>
       <c r="F94" t="s">
         <v>133</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H94" t="s">
         <v>68</v>
@@ -3632,25 +3637,25 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="B95" t="s">
         <v>12</v>
       </c>
       <c r="C95" s="9">
-        <v>5330</v>
+        <v>5730</v>
       </c>
       <c r="D95" s="9">
-        <v>6780</v>
+        <v>7030</v>
       </c>
       <c r="E95" s="9">
-        <v>7030</v>
+        <v>7660</v>
       </c>
       <c r="F95" t="s">
         <v>133</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H95" t="s">
         <v>68</v>
@@ -3661,25 +3666,25 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="B96" t="s">
         <v>12</v>
       </c>
       <c r="C96" s="9">
-        <v>5430</v>
+        <v>5030</v>
       </c>
       <c r="D96" s="9">
-        <v>6830</v>
+        <v>6630</v>
       </c>
       <c r="E96" s="9">
-        <v>7130</v>
+        <v>6920</v>
       </c>
       <c r="F96" t="s">
         <v>133</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H96" t="s">
         <v>68</v>
@@ -3690,25 +3695,25 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B97" t="s">
         <v>12</v>
       </c>
       <c r="C97" s="9">
-        <v>5430</v>
+        <v>5030</v>
       </c>
       <c r="D97" s="9">
-        <v>6830</v>
+        <v>6630</v>
       </c>
       <c r="E97" s="9">
-        <v>7130</v>
+        <v>6920</v>
       </c>
       <c r="F97" t="s">
         <v>133</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H97" t="s">
         <v>68</v>
@@ -3719,25 +3724,25 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B98" t="s">
         <v>12</v>
       </c>
       <c r="C98" s="9">
-        <v>5430</v>
+        <v>5030</v>
       </c>
       <c r="D98" s="9">
-        <v>6830</v>
+        <v>6630</v>
       </c>
       <c r="E98" s="9">
-        <v>7130</v>
+        <v>6920</v>
       </c>
       <c r="F98" t="s">
         <v>133</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H98" t="s">
         <v>68</v>
@@ -3748,25 +3753,25 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="B99" t="s">
         <v>12</v>
       </c>
       <c r="C99" s="9">
-        <v>5430</v>
+        <v>5180</v>
       </c>
       <c r="D99" s="9">
-        <v>6830</v>
+        <v>6730</v>
       </c>
       <c r="E99" s="9">
-        <v>7130</v>
+        <v>7080</v>
       </c>
       <c r="F99" t="s">
         <v>133</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H99" t="s">
         <v>68</v>
@@ -3777,25 +3782,25 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="B100" t="s">
         <v>12</v>
       </c>
       <c r="C100" s="9">
-        <v>5430</v>
+        <v>5180</v>
       </c>
       <c r="D100" s="9">
-        <v>6830</v>
+        <v>6730</v>
       </c>
       <c r="E100" s="9">
-        <v>7130</v>
+        <v>7080</v>
       </c>
       <c r="F100" t="s">
         <v>133</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H100" t="s">
         <v>68</v>
@@ -3806,28 +3811,28 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="B101" t="s">
         <v>12</v>
       </c>
       <c r="C101" s="9">
-        <v>5430</v>
+        <v>4830</v>
       </c>
       <c r="D101" s="9">
-        <v>6830</v>
+        <v>6430</v>
       </c>
       <c r="E101" s="9">
-        <v>7130</v>
+        <v>6530</v>
       </c>
       <c r="F101" t="s">
         <v>133</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H101" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I101" t="s">
         <v>27</v>
@@ -3835,28 +3840,28 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="B102" t="s">
         <v>12</v>
       </c>
       <c r="C102" s="9">
-        <v>5430</v>
+        <v>4830</v>
       </c>
       <c r="D102" s="9">
-        <v>6830</v>
+        <v>6430</v>
       </c>
       <c r="E102" s="9">
-        <v>7130</v>
+        <v>6530</v>
       </c>
       <c r="F102" t="s">
         <v>133</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H102" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I102" t="s">
         <v>27</v>
@@ -3864,28 +3869,28 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="B103" t="s">
         <v>12</v>
       </c>
       <c r="C103" s="9">
-        <v>5430</v>
+        <v>4830</v>
       </c>
       <c r="D103" s="9">
-        <v>6830</v>
+        <v>6430</v>
       </c>
       <c r="E103" s="9">
-        <v>7130</v>
+        <v>6530</v>
       </c>
       <c r="F103" t="s">
         <v>133</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H103" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I103" t="s">
         <v>27</v>
@@ -3893,28 +3898,28 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="B104" t="s">
         <v>12</v>
       </c>
       <c r="C104" s="9">
-        <v>5430</v>
+        <v>4830</v>
       </c>
       <c r="D104" s="9">
-        <v>6830</v>
+        <v>6430</v>
       </c>
       <c r="E104" s="9">
-        <v>7130</v>
+        <v>6530</v>
       </c>
       <c r="F104" t="s">
         <v>133</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H104" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I104" t="s">
         <v>27</v>
@@ -3922,28 +3927,28 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="B105" t="s">
         <v>12</v>
       </c>
       <c r="C105" s="9">
-        <v>5580</v>
+        <v>4830</v>
       </c>
       <c r="D105" s="9">
-        <v>6880</v>
+        <v>6430</v>
       </c>
       <c r="E105" s="9">
-        <v>7280</v>
+        <v>6530</v>
       </c>
       <c r="F105" t="s">
         <v>133</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H105" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I105" t="s">
         <v>27</v>
@@ -3951,28 +3956,28 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="B106" t="s">
         <v>12</v>
       </c>
       <c r="C106" s="9">
-        <v>5630</v>
+        <v>4830</v>
       </c>
       <c r="D106" s="9">
-        <v>6930</v>
+        <v>6430</v>
       </c>
       <c r="E106" s="9">
-        <v>7330</v>
+        <v>6530</v>
       </c>
       <c r="F106" t="s">
         <v>133</v>
       </c>
       <c r="G106" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H106" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I106" t="s">
         <v>27</v>
@@ -3980,28 +3985,28 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="B107" t="s">
         <v>12</v>
       </c>
       <c r="C107" s="9">
-        <v>5580</v>
+        <v>4830</v>
       </c>
       <c r="D107" s="9">
-        <v>6880</v>
+        <v>6430</v>
       </c>
       <c r="E107" s="9">
-        <v>7280</v>
+        <v>6530</v>
       </c>
       <c r="F107" t="s">
         <v>133</v>
       </c>
       <c r="G107" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H107" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I107" t="s">
         <v>27</v>
@@ -4009,28 +4014,28 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="B108" t="s">
         <v>12</v>
       </c>
       <c r="C108" s="9">
-        <v>5680</v>
+        <v>4830</v>
       </c>
       <c r="D108" s="9">
-        <v>6980</v>
+        <v>6430</v>
       </c>
       <c r="E108" s="9">
-        <v>7380</v>
+        <v>6530</v>
       </c>
       <c r="F108" t="s">
         <v>133</v>
       </c>
       <c r="G108" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H108" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I108" t="s">
         <v>27</v>
@@ -4038,28 +4043,28 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B109" t="s">
         <v>12</v>
       </c>
       <c r="C109" s="9">
-        <v>5930</v>
+        <v>4830</v>
       </c>
       <c r="D109" s="9">
-        <v>7130</v>
+        <v>6430</v>
       </c>
       <c r="E109" s="9">
-        <v>7870</v>
+        <v>6530</v>
       </c>
       <c r="F109" t="s">
         <v>133</v>
       </c>
       <c r="G109" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H109" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I109" t="s">
         <v>27</v>
@@ -4067,28 +4072,28 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="B110" t="s">
         <v>12</v>
       </c>
       <c r="C110" s="9">
-        <v>5230</v>
+        <v>5030</v>
       </c>
       <c r="D110" s="9">
+        <v>6530</v>
+      </c>
+      <c r="E110" s="9">
         <v>6730</v>
       </c>
-      <c r="E110" s="9">
-        <v>7130</v>
-      </c>
       <c r="F110" t="s">
         <v>133</v>
       </c>
       <c r="G110" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H110" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I110" t="s">
         <v>27</v>
@@ -4096,28 +4101,28 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="B111" t="s">
         <v>12</v>
       </c>
       <c r="C111" s="9">
-        <v>5230</v>
+        <v>4830</v>
       </c>
       <c r="D111" s="9">
-        <v>6730</v>
+        <v>6430</v>
       </c>
       <c r="E111" s="9">
-        <v>7130</v>
+        <v>6530</v>
       </c>
       <c r="F111" t="s">
         <v>133</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H111" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I111" t="s">
         <v>27</v>
@@ -4125,28 +4130,28 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="B112" t="s">
         <v>12</v>
       </c>
       <c r="C112" s="9">
-        <v>5230</v>
+        <v>4980</v>
       </c>
       <c r="D112" s="9">
-        <v>6730</v>
+        <v>6510</v>
       </c>
       <c r="E112" s="9">
-        <v>7130</v>
+        <v>6680</v>
       </c>
       <c r="F112" t="s">
         <v>133</v>
       </c>
       <c r="G112" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H112" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I112" t="s">
         <v>27</v>
@@ -4154,28 +4159,28 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="B113" t="s">
         <v>12</v>
       </c>
       <c r="C113" s="9">
-        <v>5380</v>
+        <v>4930</v>
       </c>
       <c r="D113" s="9">
-        <v>6830</v>
+        <v>6480</v>
       </c>
       <c r="E113" s="9">
-        <v>7290</v>
+        <v>6630</v>
       </c>
       <c r="F113" t="s">
         <v>133</v>
       </c>
       <c r="G113" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H113" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I113" t="s">
         <v>27</v>
@@ -4183,28 +4188,28 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="B114" t="s">
         <v>12</v>
       </c>
       <c r="C114" s="9">
-        <v>5380</v>
+        <v>4930</v>
       </c>
       <c r="D114" s="9">
-        <v>6830</v>
+        <v>6480</v>
       </c>
       <c r="E114" s="9">
-        <v>7290</v>
+        <v>6630</v>
       </c>
       <c r="F114" t="s">
         <v>133</v>
       </c>
       <c r="G114" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H114" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I114" t="s">
         <v>27</v>
@@ -4212,25 +4217,25 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B115" t="s">
         <v>12</v>
       </c>
       <c r="C115" s="9">
-        <v>5030</v>
+        <v>4930</v>
       </c>
       <c r="D115" s="9">
-        <v>6530</v>
+        <v>6480</v>
       </c>
       <c r="E115" s="9">
-        <v>6830</v>
+        <v>6630</v>
       </c>
       <c r="F115" t="s">
         <v>133</v>
       </c>
       <c r="G115" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H115" t="s">
         <v>69</v>
@@ -4241,25 +4246,25 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>78</v>
+      </c>
+      <c r="B116" t="s">
+        <v>12</v>
+      </c>
+      <c r="C116" s="9">
+        <v>4930</v>
+      </c>
+      <c r="D116" s="9">
+        <v>6480</v>
+      </c>
+      <c r="E116" s="9">
+        <v>6630</v>
+      </c>
+      <c r="F116" t="s">
+        <v>133</v>
+      </c>
+      <c r="G116" s="7" t="s">
         <v>83</v>
-      </c>
-      <c r="B116" t="s">
-        <v>12</v>
-      </c>
-      <c r="C116" s="9">
-        <v>5030</v>
-      </c>
-      <c r="D116" s="9">
-        <v>6530</v>
-      </c>
-      <c r="E116" s="9">
-        <v>6830</v>
-      </c>
-      <c r="F116" t="s">
-        <v>133</v>
-      </c>
-      <c r="G116" s="7" t="s">
-        <v>85</v>
       </c>
       <c r="H116" t="s">
         <v>69</v>
@@ -4270,25 +4275,25 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="B117" t="s">
         <v>12</v>
       </c>
       <c r="C117" s="9">
-        <v>5030</v>
+        <v>4930</v>
       </c>
       <c r="D117" s="9">
-        <v>6530</v>
+        <v>6480</v>
       </c>
       <c r="E117" s="9">
-        <v>6830</v>
+        <v>6630</v>
       </c>
       <c r="F117" t="s">
         <v>133</v>
       </c>
       <c r="G117" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H117" t="s">
         <v>69</v>
@@ -4299,25 +4304,25 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="B118" t="s">
         <v>12</v>
       </c>
       <c r="C118" s="9">
-        <v>5030</v>
+        <v>4930</v>
       </c>
       <c r="D118" s="9">
-        <v>6530</v>
+        <v>6480</v>
       </c>
       <c r="E118" s="9">
-        <v>6830</v>
+        <v>6630</v>
       </c>
       <c r="F118" t="s">
         <v>133</v>
       </c>
       <c r="G118" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H118" t="s">
         <v>69</v>
@@ -4328,25 +4333,25 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="B119" t="s">
         <v>12</v>
       </c>
       <c r="C119" s="9">
-        <v>5030</v>
+        <v>4930</v>
       </c>
       <c r="D119" s="9">
-        <v>6530</v>
+        <v>6480</v>
       </c>
       <c r="E119" s="9">
-        <v>6830</v>
+        <v>6630</v>
       </c>
       <c r="F119" t="s">
         <v>133</v>
       </c>
       <c r="G119" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H119" t="s">
         <v>69</v>
@@ -4357,25 +4362,25 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="B120" t="s">
         <v>12</v>
       </c>
       <c r="C120" s="9">
-        <v>5030</v>
+        <v>4930</v>
       </c>
       <c r="D120" s="9">
-        <v>6530</v>
+        <v>6480</v>
       </c>
       <c r="E120" s="9">
-        <v>6830</v>
+        <v>6630</v>
       </c>
       <c r="F120" t="s">
         <v>133</v>
       </c>
       <c r="G120" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H120" t="s">
         <v>69</v>
@@ -4386,25 +4391,25 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="B121" t="s">
         <v>12</v>
       </c>
       <c r="C121" s="9">
-        <v>5030</v>
+        <v>4930</v>
       </c>
       <c r="D121" s="9">
-        <v>6530</v>
+        <v>6480</v>
       </c>
       <c r="E121" s="9">
-        <v>6830</v>
+        <v>6630</v>
       </c>
       <c r="F121" t="s">
         <v>133</v>
       </c>
       <c r="G121" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H121" t="s">
         <v>69</v>
@@ -4415,25 +4420,25 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="B122" t="s">
         <v>12</v>
       </c>
       <c r="C122" s="9">
-        <v>5030</v>
+        <v>4930</v>
       </c>
       <c r="D122" s="9">
-        <v>6530</v>
+        <v>6480</v>
       </c>
       <c r="E122" s="9">
-        <v>6830</v>
+        <v>6630</v>
       </c>
       <c r="F122" t="s">
         <v>133</v>
       </c>
       <c r="G122" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H122" t="s">
         <v>69</v>
@@ -4444,16 +4449,16 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="B123" t="s">
         <v>12</v>
       </c>
       <c r="C123" s="9">
-        <v>5030</v>
+        <v>5130</v>
       </c>
       <c r="D123" s="9">
-        <v>6530</v>
+        <v>6640</v>
       </c>
       <c r="E123" s="9">
         <v>6830</v>
@@ -4462,7 +4467,7 @@
         <v>133</v>
       </c>
       <c r="G123" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H123" t="s">
         <v>69</v>
@@ -4473,25 +4478,23 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="B124" t="s">
         <v>12</v>
       </c>
-      <c r="C124" s="9">
-        <v>5230</v>
-      </c>
+      <c r="C124" s="9"/>
       <c r="D124" s="9">
-        <v>6630</v>
+        <v>6580</v>
       </c>
       <c r="E124" s="9">
-        <v>7030</v>
+        <v>6830</v>
       </c>
       <c r="F124" t="s">
         <v>133</v>
       </c>
       <c r="G124" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H124" t="s">
         <v>69</v>
@@ -4502,25 +4505,23 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="B125" t="s">
         <v>12</v>
       </c>
-      <c r="C125" s="9">
-        <v>5030</v>
-      </c>
+      <c r="C125" s="9"/>
       <c r="D125" s="9">
-        <v>6530</v>
+        <v>6650</v>
       </c>
       <c r="E125" s="9">
-        <v>6830</v>
+        <v>6870</v>
       </c>
       <c r="F125" t="s">
         <v>133</v>
       </c>
       <c r="G125" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H125" t="s">
         <v>69</v>
@@ -4531,25 +4532,23 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="B126" t="s">
         <v>12</v>
       </c>
-      <c r="C126" s="9">
-        <v>5180</v>
-      </c>
+      <c r="C126" s="9"/>
       <c r="D126" s="9">
-        <v>6610</v>
+        <v>6600</v>
       </c>
       <c r="E126" s="9">
-        <v>6980</v>
+        <v>6830</v>
       </c>
       <c r="F126" t="s">
         <v>133</v>
       </c>
       <c r="G126" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H126" t="s">
         <v>69</v>
@@ -4560,25 +4559,23 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="B127" t="s">
         <v>12</v>
       </c>
-      <c r="C127" s="9">
-        <v>5130</v>
-      </c>
+      <c r="C127" s="9"/>
       <c r="D127" s="9">
-        <v>6580</v>
+        <v>6680</v>
       </c>
       <c r="E127" s="9">
-        <v>6930</v>
+        <v>6960</v>
       </c>
       <c r="F127" t="s">
         <v>133</v>
       </c>
       <c r="G127" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H127" t="s">
         <v>69</v>
@@ -4589,25 +4586,23 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="B128" t="s">
         <v>12</v>
       </c>
-      <c r="C128" s="9">
-        <v>5130</v>
-      </c>
+      <c r="C128" s="9"/>
       <c r="D128" s="9">
-        <v>6580</v>
+        <v>6620</v>
       </c>
       <c r="E128" s="9">
-        <v>6930</v>
+        <v>6840</v>
       </c>
       <c r="F128" t="s">
         <v>133</v>
       </c>
       <c r="G128" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H128" t="s">
         <v>69</v>
@@ -4618,25 +4613,23 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="B129" t="s">
         <v>12</v>
       </c>
-      <c r="C129" s="9">
-        <v>5130</v>
-      </c>
+      <c r="C129" s="9"/>
       <c r="D129" s="9">
-        <v>6580</v>
+        <v>6630</v>
       </c>
       <c r="E129" s="9">
-        <v>6930</v>
+        <v>6850</v>
       </c>
       <c r="F129" t="s">
         <v>133</v>
       </c>
       <c r="G129" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H129" t="s">
         <v>69</v>
@@ -4647,25 +4640,23 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="B130" t="s">
         <v>12</v>
       </c>
-      <c r="C130" s="9">
-        <v>5130</v>
-      </c>
+      <c r="C130" s="9"/>
       <c r="D130" s="9">
-        <v>6580</v>
+        <v>6550</v>
       </c>
       <c r="E130" s="9">
-        <v>6930</v>
+        <v>6740</v>
       </c>
       <c r="F130" t="s">
         <v>133</v>
       </c>
       <c r="G130" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H130" t="s">
         <v>69</v>
@@ -4676,25 +4667,23 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="B131" t="s">
         <v>12</v>
       </c>
-      <c r="C131" s="9">
-        <v>5130</v>
-      </c>
+      <c r="C131" s="9"/>
       <c r="D131" s="9">
-        <v>6580</v>
+        <v>6550</v>
       </c>
       <c r="E131" s="9">
-        <v>6930</v>
+        <v>6740</v>
       </c>
       <c r="F131" t="s">
         <v>133</v>
       </c>
       <c r="G131" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H131" t="s">
         <v>69</v>
@@ -4705,25 +4694,23 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B132" t="s">
         <v>12</v>
       </c>
-      <c r="C132" s="9">
-        <v>5130</v>
-      </c>
+      <c r="C132" s="9"/>
       <c r="D132" s="9">
-        <v>6580</v>
+        <v>6550</v>
       </c>
       <c r="E132" s="9">
-        <v>6930</v>
+        <v>6740</v>
       </c>
       <c r="F132" t="s">
         <v>133</v>
       </c>
       <c r="G132" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H132" t="s">
         <v>69</v>
@@ -4734,25 +4721,23 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B133" t="s">
         <v>12</v>
       </c>
-      <c r="C133" s="9">
-        <v>5130</v>
-      </c>
+      <c r="C133" s="9"/>
       <c r="D133" s="9">
-        <v>6580</v>
+        <v>6550</v>
       </c>
       <c r="E133" s="9">
-        <v>6930</v>
+        <v>6740</v>
       </c>
       <c r="F133" t="s">
         <v>133</v>
       </c>
       <c r="G133" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H133" t="s">
         <v>69</v>
@@ -4763,25 +4748,23 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B134" t="s">
         <v>12</v>
       </c>
-      <c r="C134" s="9">
-        <v>5130</v>
-      </c>
+      <c r="C134" s="9"/>
       <c r="D134" s="9">
-        <v>6580</v>
+        <v>6550</v>
       </c>
       <c r="E134" s="9">
-        <v>6930</v>
+        <v>6740</v>
       </c>
       <c r="F134" t="s">
         <v>133</v>
       </c>
       <c r="G134" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H134" t="s">
         <v>69</v>
@@ -4792,25 +4775,23 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="B135" t="s">
         <v>12</v>
       </c>
-      <c r="C135" s="9">
-        <v>5130</v>
-      </c>
+      <c r="C135" s="9"/>
       <c r="D135" s="9">
-        <v>6580</v>
+        <v>6550</v>
       </c>
       <c r="E135" s="9">
-        <v>6930</v>
+        <v>6740</v>
       </c>
       <c r="F135" t="s">
         <v>133</v>
       </c>
       <c r="G135" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H135" t="s">
         <v>69</v>
@@ -4821,25 +4802,23 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="B136" t="s">
         <v>12</v>
       </c>
-      <c r="C136" s="9">
-        <v>5130</v>
-      </c>
+      <c r="C136" s="9"/>
       <c r="D136" s="9">
-        <v>6580</v>
+        <v>6550</v>
       </c>
       <c r="E136" s="9">
-        <v>6930</v>
+        <v>6740</v>
       </c>
       <c r="F136" t="s">
         <v>133</v>
       </c>
       <c r="G136" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H136" t="s">
         <v>69</v>
@@ -4850,25 +4829,23 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B137" t="s">
         <v>12</v>
       </c>
-      <c r="C137" s="9">
-        <v>5330</v>
-      </c>
+      <c r="C137" s="9"/>
       <c r="D137" s="9">
+        <v>6550</v>
+      </c>
+      <c r="E137" s="9">
         <v>6740</v>
       </c>
-      <c r="E137" s="9">
-        <v>7130</v>
-      </c>
       <c r="F137" t="s">
         <v>133</v>
       </c>
       <c r="G137" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H137" t="s">
         <v>69</v>
@@ -4879,23 +4856,23 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="B138" t="s">
         <v>12</v>
       </c>
       <c r="C138" s="9"/>
       <c r="D138" s="9">
-        <v>6680</v>
+        <v>6670</v>
       </c>
       <c r="E138" s="9">
-        <v>7130</v>
+        <v>6950</v>
       </c>
       <c r="F138" t="s">
         <v>133</v>
       </c>
-      <c r="G138" s="7">
-        <v>17</v>
+      <c r="G138" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="H138" t="s">
         <v>69</v>
@@ -4906,23 +4883,23 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="B139" t="s">
         <v>12</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="9">
-        <v>6750</v>
+        <v>6660</v>
       </c>
       <c r="E139" s="9">
-        <v>7170</v>
+        <v>6920</v>
       </c>
       <c r="F139" t="s">
         <v>133</v>
       </c>
-      <c r="G139" s="7">
-        <v>17</v>
+      <c r="G139" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="H139" t="s">
         <v>69</v>
@@ -4933,23 +4910,23 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="B140" t="s">
         <v>12</v>
       </c>
       <c r="C140" s="9"/>
       <c r="D140" s="9">
-        <v>6700</v>
+        <v>6660</v>
       </c>
       <c r="E140" s="9">
-        <v>7130</v>
+        <v>6980</v>
       </c>
       <c r="F140" t="s">
         <v>133</v>
       </c>
-      <c r="G140" s="7">
-        <v>17</v>
+      <c r="G140" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="H140" t="s">
         <v>69</v>
@@ -4960,23 +4937,23 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B141" t="s">
         <v>12</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="9">
-        <v>6780</v>
+        <v>6660</v>
       </c>
       <c r="E141" s="9">
-        <v>7260</v>
+        <v>6980</v>
       </c>
       <c r="F141" t="s">
         <v>133</v>
       </c>
-      <c r="G141" s="7">
-        <v>17</v>
+      <c r="G141" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="H141" t="s">
         <v>69</v>
@@ -4987,23 +4964,23 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="B142" t="s">
         <v>12</v>
       </c>
       <c r="C142" s="9"/>
       <c r="D142" s="9">
-        <v>6720</v>
+        <v>6840</v>
       </c>
       <c r="E142" s="9">
-        <v>7140</v>
+        <v>7320</v>
       </c>
       <c r="F142" t="s">
         <v>133</v>
       </c>
-      <c r="G142" s="7">
-        <v>17</v>
+      <c r="G142" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="H142" t="s">
         <v>69</v>
@@ -5014,23 +4991,23 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="B143" t="s">
         <v>12</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="9">
-        <v>6730</v>
+        <v>6530</v>
       </c>
       <c r="E143" s="9">
-        <v>7150</v>
+        <v>6680</v>
       </c>
       <c r="F143" t="s">
         <v>133</v>
       </c>
-      <c r="G143" s="7">
-        <v>17</v>
+      <c r="G143" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="H143" t="s">
         <v>69</v>
@@ -5041,23 +5018,23 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B144" t="s">
         <v>12</v>
       </c>
       <c r="C144" s="9"/>
       <c r="D144" s="9">
-        <v>6650</v>
+        <v>6530</v>
       </c>
       <c r="E144" s="9">
-        <v>7040</v>
+        <v>6680</v>
       </c>
       <c r="F144" t="s">
         <v>133</v>
       </c>
-      <c r="G144" s="7">
-        <v>17</v>
+      <c r="G144" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="H144" t="s">
         <v>69</v>
@@ -5068,23 +5045,23 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B145" t="s">
         <v>12</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="9">
-        <v>6650</v>
+        <v>6530</v>
       </c>
       <c r="E145" s="9">
-        <v>7040</v>
+        <v>6680</v>
       </c>
       <c r="F145" t="s">
         <v>133</v>
       </c>
-      <c r="G145" s="7">
-        <v>17</v>
+      <c r="G145" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="H145" t="s">
         <v>69</v>
@@ -5095,23 +5072,23 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="B146" t="s">
         <v>12</v>
       </c>
       <c r="C146" s="9"/>
       <c r="D146" s="9">
-        <v>6650</v>
+        <v>6630</v>
       </c>
       <c r="E146" s="9">
-        <v>7040</v>
+        <v>6830</v>
       </c>
       <c r="F146" t="s">
         <v>133</v>
       </c>
-      <c r="G146" s="7">
-        <v>17</v>
+      <c r="G146" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="H146" t="s">
         <v>69</v>
@@ -5122,23 +5099,23 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="B147" t="s">
         <v>12</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="9">
-        <v>6650</v>
+        <v>6730</v>
       </c>
       <c r="E147" s="9">
-        <v>7040</v>
+        <v>6980</v>
       </c>
       <c r="F147" t="s">
         <v>133</v>
       </c>
-      <c r="G147" s="7">
-        <v>17</v>
+      <c r="G147" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="H147" t="s">
         <v>69</v>
@@ -5149,380 +5126,408 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="B148" t="s">
         <v>12</v>
       </c>
-      <c r="C148" s="9"/>
+      <c r="C148" s="9">
+        <v>4830</v>
+      </c>
       <c r="D148" s="9">
-        <v>6650</v>
+        <v>6330</v>
       </c>
       <c r="E148" s="9">
-        <v>7040</v>
+        <v>6630</v>
       </c>
       <c r="F148" t="s">
-        <v>133</v>
-      </c>
-      <c r="G148" s="7">
-        <v>17</v>
+        <v>134</v>
+      </c>
+      <c r="G148" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="H148" t="s">
         <v>69</v>
       </c>
       <c r="I148" t="s">
-        <v>27</v>
+        <v>131</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="B149" t="s">
         <v>12</v>
       </c>
-      <c r="C149" s="9"/>
+      <c r="C149" s="9">
+        <v>4830</v>
+      </c>
       <c r="D149" s="9">
-        <v>6650</v>
+        <v>6330</v>
       </c>
       <c r="E149" s="9">
-        <v>7040</v>
+        <v>6630</v>
       </c>
       <c r="F149" t="s">
-        <v>133</v>
-      </c>
-      <c r="G149" s="7">
-        <v>17</v>
+        <v>134</v>
+      </c>
+      <c r="G149" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="H149" t="s">
         <v>69</v>
       </c>
       <c r="I149" t="s">
-        <v>27</v>
+        <v>131</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="B150" t="s">
         <v>12</v>
       </c>
-      <c r="C150" s="9"/>
+      <c r="C150" s="9">
+        <v>4830</v>
+      </c>
       <c r="D150" s="9">
-        <v>6650</v>
+        <v>6330</v>
       </c>
       <c r="E150" s="9">
-        <v>7040</v>
+        <v>6630</v>
       </c>
       <c r="F150" t="s">
-        <v>133</v>
-      </c>
-      <c r="G150" s="7">
-        <v>17</v>
+        <v>134</v>
+      </c>
+      <c r="G150" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="H150" t="s">
         <v>69</v>
       </c>
       <c r="I150" t="s">
-        <v>27</v>
+        <v>131</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="B151" t="s">
         <v>12</v>
       </c>
-      <c r="C151" s="9"/>
+      <c r="C151" s="9">
+        <v>4830</v>
+      </c>
       <c r="D151" s="9">
-        <v>6650</v>
+        <v>6330</v>
       </c>
       <c r="E151" s="9">
-        <v>7040</v>
+        <v>6630</v>
       </c>
       <c r="F151" t="s">
-        <v>133</v>
-      </c>
-      <c r="G151" s="7">
-        <v>17</v>
+        <v>134</v>
+      </c>
+      <c r="G151" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="H151" t="s">
         <v>69</v>
       </c>
       <c r="I151" t="s">
-        <v>27</v>
+        <v>131</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="B152" t="s">
         <v>12</v>
       </c>
-      <c r="C152" s="9"/>
+      <c r="C152" s="9">
+        <v>4830</v>
+      </c>
       <c r="D152" s="9">
-        <v>6770</v>
+        <v>6330</v>
       </c>
       <c r="E152" s="9">
-        <v>7250</v>
+        <v>6630</v>
       </c>
       <c r="F152" t="s">
-        <v>133</v>
-      </c>
-      <c r="G152" s="7">
-        <v>17</v>
+        <v>134</v>
+      </c>
+      <c r="G152" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="H152" t="s">
         <v>69</v>
       </c>
       <c r="I152" t="s">
-        <v>27</v>
+        <v>131</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="B153" t="s">
         <v>12</v>
       </c>
-      <c r="C153" s="9"/>
+      <c r="C153" s="9">
+        <v>4830</v>
+      </c>
       <c r="D153" s="9">
-        <v>6760</v>
+        <v>6330</v>
       </c>
       <c r="E153" s="9">
-        <v>7220</v>
+        <v>6630</v>
       </c>
       <c r="F153" t="s">
-        <v>133</v>
-      </c>
-      <c r="G153" s="7">
-        <v>17</v>
+        <v>134</v>
+      </c>
+      <c r="G153" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="H153" t="s">
         <v>69</v>
       </c>
       <c r="I153" t="s">
-        <v>27</v>
+        <v>131</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="B154" t="s">
         <v>12</v>
       </c>
-      <c r="C154" s="9"/>
+      <c r="C154" s="9">
+        <v>4830</v>
+      </c>
       <c r="D154" s="9">
-        <v>6760</v>
+        <v>6330</v>
       </c>
       <c r="E154" s="9">
-        <v>7280</v>
+        <v>6630</v>
       </c>
       <c r="F154" t="s">
-        <v>133</v>
-      </c>
-      <c r="G154" s="7">
-        <v>17</v>
+        <v>134</v>
+      </c>
+      <c r="G154" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="H154" t="s">
         <v>69</v>
       </c>
       <c r="I154" t="s">
-        <v>27</v>
+        <v>131</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="B155" t="s">
         <v>12</v>
       </c>
-      <c r="C155" s="9"/>
+      <c r="C155" s="9">
+        <v>4830</v>
+      </c>
       <c r="D155" s="9">
-        <v>6760</v>
+        <v>6330</v>
       </c>
       <c r="E155" s="9">
-        <v>7280</v>
+        <v>6630</v>
       </c>
       <c r="F155" t="s">
-        <v>133</v>
-      </c>
-      <c r="G155" s="7">
-        <v>17</v>
+        <v>134</v>
+      </c>
+      <c r="G155" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="H155" t="s">
         <v>69</v>
       </c>
       <c r="I155" t="s">
-        <v>27</v>
+        <v>131</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="B156" t="s">
         <v>12</v>
       </c>
-      <c r="C156" s="9"/>
+      <c r="C156" s="9">
+        <v>4830</v>
+      </c>
       <c r="D156" s="9">
-        <v>6940</v>
+        <v>6330</v>
       </c>
       <c r="E156" s="9">
-        <v>7620</v>
+        <v>6630</v>
       </c>
       <c r="F156" t="s">
-        <v>133</v>
-      </c>
-      <c r="G156" s="7">
-        <v>17</v>
+        <v>134</v>
+      </c>
+      <c r="G156" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="H156" t="s">
         <v>69</v>
       </c>
       <c r="I156" t="s">
-        <v>27</v>
+        <v>131</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="B157" t="s">
         <v>12</v>
       </c>
-      <c r="C157" s="9"/>
+      <c r="C157" s="9">
+        <v>4830</v>
+      </c>
       <c r="D157" s="9">
+        <v>6330</v>
+      </c>
+      <c r="E157" s="9">
         <v>6630</v>
       </c>
-      <c r="E157" s="9">
-        <v>6980</v>
-      </c>
       <c r="F157" t="s">
-        <v>133</v>
-      </c>
-      <c r="G157" s="7">
-        <v>17</v>
+        <v>134</v>
+      </c>
+      <c r="G157" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="H157" t="s">
         <v>69</v>
       </c>
       <c r="I157" t="s">
-        <v>27</v>
+        <v>131</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="B158" t="s">
         <v>12</v>
       </c>
-      <c r="C158" s="9"/>
+      <c r="C158" s="9">
+        <v>4830</v>
+      </c>
       <c r="D158" s="9">
+        <v>6330</v>
+      </c>
+      <c r="E158" s="9">
         <v>6630</v>
       </c>
-      <c r="E158" s="9">
-        <v>6980</v>
-      </c>
       <c r="F158" t="s">
-        <v>133</v>
-      </c>
-      <c r="G158" s="7">
-        <v>17</v>
+        <v>134</v>
+      </c>
+      <c r="G158" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="H158" t="s">
         <v>69</v>
       </c>
       <c r="I158" t="s">
-        <v>27</v>
+        <v>131</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>118</v>
+        <v>72</v>
       </c>
       <c r="B159" t="s">
         <v>12</v>
       </c>
-      <c r="C159" s="9"/>
+      <c r="C159" s="9">
+        <v>4880</v>
+      </c>
       <c r="D159" s="9">
-        <v>6630</v>
+        <v>6480</v>
       </c>
       <c r="E159" s="9">
-        <v>6980</v>
+        <v>6580</v>
       </c>
       <c r="F159" t="s">
-        <v>133</v>
-      </c>
-      <c r="G159" s="7">
-        <v>17</v>
+        <v>134</v>
+      </c>
+      <c r="G159" s="7" t="s">
+        <v>132</v>
       </c>
       <c r="H159" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I159" t="s">
-        <v>27</v>
+        <v>131</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="B160" t="s">
         <v>12</v>
       </c>
-      <c r="C160" s="9"/>
+      <c r="C160" s="9">
+        <v>4880</v>
+      </c>
       <c r="D160" s="9">
-        <v>6730</v>
+        <v>6480</v>
       </c>
       <c r="E160" s="9">
-        <v>7130</v>
+        <v>6580</v>
       </c>
       <c r="F160" t="s">
-        <v>133</v>
-      </c>
-      <c r="G160" s="7">
-        <v>17</v>
+        <v>134</v>
+      </c>
+      <c r="G160" s="7" t="s">
+        <v>132</v>
       </c>
       <c r="H160" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I160" t="s">
-        <v>27</v>
+        <v>131</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="B161" t="s">
         <v>12</v>
       </c>
-      <c r="C161" s="9"/>
+      <c r="C161" s="9">
+        <v>4880</v>
+      </c>
       <c r="D161" s="9">
-        <v>6830</v>
+        <v>6480</v>
       </c>
       <c r="E161" s="9">
-        <v>7280</v>
+        <v>6580</v>
       </c>
       <c r="F161" t="s">
-        <v>133</v>
-      </c>
-      <c r="G161" s="7">
-        <v>17</v>
+        <v>134</v>
+      </c>
+      <c r="G161" s="7" t="s">
+        <v>132</v>
       </c>
       <c r="H161" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I161" t="s">
-        <v>27</v>
+        <v>131</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
@@ -5530,115 +5535,115 @@
         <v>71</v>
       </c>
       <c r="B162" t="s">
-        <v>136</v>
+        <v>12</v>
       </c>
       <c r="C162" s="9">
-        <v>5220</v>
+        <v>4880</v>
       </c>
       <c r="D162" s="9">
-        <v>6420</v>
+        <v>6480</v>
       </c>
       <c r="E162" s="9">
-        <v>6620</v>
+        <v>6580</v>
       </c>
       <c r="F162" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G162" s="7" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H162" t="s">
-        <v>137</v>
+        <v>68</v>
       </c>
       <c r="I162" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="B163" t="s">
-        <v>136</v>
+        <v>12</v>
       </c>
       <c r="C163" s="9">
-        <v>5220</v>
+        <v>4880</v>
       </c>
       <c r="D163" s="9">
-        <v>6420</v>
+        <v>6480</v>
       </c>
       <c r="E163" s="9">
-        <v>6620</v>
+        <v>6580</v>
       </c>
       <c r="F163" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G163" s="7" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H163" t="s">
-        <v>137</v>
+        <v>68</v>
       </c>
       <c r="I163" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B164" t="s">
-        <v>136</v>
+        <v>12</v>
       </c>
       <c r="C164" s="9">
-        <v>5420</v>
+        <v>4880</v>
       </c>
       <c r="D164" s="9">
-        <v>6520</v>
+        <v>6480</v>
       </c>
       <c r="E164" s="9">
-        <v>6820</v>
+        <v>6580</v>
       </c>
       <c r="F164" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G164" s="7" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H164" t="s">
-        <v>137</v>
+        <v>68</v>
       </c>
       <c r="I164" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B165" t="s">
-        <v>136</v>
+        <v>12</v>
       </c>
       <c r="C165" s="9">
-        <v>5220</v>
+        <v>4880</v>
       </c>
       <c r="D165" s="9">
-        <v>6420</v>
+        <v>6480</v>
       </c>
       <c r="E165" s="9">
-        <v>6620</v>
+        <v>6580</v>
       </c>
       <c r="F165" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G165" s="7" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H165" t="s">
-        <v>137</v>
+        <v>68</v>
       </c>
       <c r="I165" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
@@ -5646,144 +5651,144 @@
         <v>74</v>
       </c>
       <c r="B166" t="s">
-        <v>136</v>
+        <v>12</v>
       </c>
       <c r="C166" s="9">
-        <v>5220</v>
+        <v>4880</v>
       </c>
       <c r="D166" s="9">
-        <v>6420</v>
+        <v>6480</v>
       </c>
       <c r="E166" s="9">
-        <v>6620</v>
+        <v>6580</v>
       </c>
       <c r="F166" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G166" s="7" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H166" t="s">
-        <v>137</v>
+        <v>68</v>
       </c>
       <c r="I166" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="B167" t="s">
-        <v>136</v>
+        <v>12</v>
       </c>
       <c r="C167" s="9">
-        <v>5220</v>
+        <v>5130</v>
       </c>
       <c r="D167" s="9">
-        <v>6420</v>
+        <v>6630</v>
       </c>
       <c r="E167" s="9">
-        <v>6620</v>
+        <v>6830</v>
       </c>
       <c r="F167" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G167" s="7" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H167" t="s">
-        <v>137</v>
+        <v>68</v>
       </c>
       <c r="I167" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="B168" t="s">
-        <v>136</v>
+        <v>12</v>
       </c>
       <c r="C168" s="9">
-        <v>5420</v>
+        <v>5130</v>
       </c>
       <c r="D168" s="9">
-        <v>6520</v>
+        <v>6630</v>
       </c>
       <c r="E168" s="9">
-        <v>6820</v>
+        <v>6830</v>
       </c>
       <c r="F168" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G168" s="7" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H168" t="s">
-        <v>137</v>
+        <v>68</v>
       </c>
       <c r="I168" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="B169" t="s">
-        <v>136</v>
+        <v>12</v>
       </c>
       <c r="C169" s="9">
-        <v>5520</v>
+        <v>5130</v>
       </c>
       <c r="D169" s="9">
-        <v>5920</v>
+        <v>6630</v>
       </c>
       <c r="E169" s="9">
-        <v>7120</v>
+        <v>6830</v>
       </c>
       <c r="F169" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G169" s="7" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H169" t="s">
-        <v>137</v>
+        <v>68</v>
       </c>
       <c r="I169" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="B170" t="s">
-        <v>136</v>
+        <v>12</v>
       </c>
       <c r="C170" s="9">
-        <v>5520</v>
+        <v>5130</v>
       </c>
       <c r="D170" s="9">
-        <v>5920</v>
+        <v>6630</v>
       </c>
       <c r="E170" s="9">
-        <v>7120</v>
+        <v>6830</v>
       </c>
       <c r="F170" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G170" s="7" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H170" t="s">
-        <v>137</v>
+        <v>68</v>
       </c>
       <c r="I170" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
@@ -5794,727 +5799,881 @@
         <v>12</v>
       </c>
       <c r="C171" s="9">
-        <v>5330</v>
+        <v>6660</v>
       </c>
       <c r="D171" s="9">
-        <v>6530</v>
+        <v>6360</v>
       </c>
       <c r="E171" s="9">
-        <v>6830</v>
+        <v>6660</v>
       </c>
       <c r="F171" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G171" s="7" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="H171" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="I171" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B172" t="s">
         <v>12</v>
       </c>
       <c r="C172" s="9">
-        <v>5330</v>
+        <v>6660</v>
       </c>
       <c r="D172" s="9">
-        <v>6530</v>
+        <v>6360</v>
       </c>
       <c r="E172" s="9">
-        <v>6830</v>
+        <v>6660</v>
       </c>
       <c r="F172" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G172" s="7" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="H172" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="I172" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="B173" t="s">
         <v>12</v>
       </c>
       <c r="C173" s="9">
-        <v>5330</v>
+        <v>6660</v>
       </c>
       <c r="D173" s="9">
-        <v>6530</v>
+        <v>6360</v>
       </c>
       <c r="E173" s="9">
-        <v>6830</v>
+        <v>6660</v>
       </c>
       <c r="F173" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G173" s="7" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="H173" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="I173" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B174" t="s">
         <v>12</v>
       </c>
       <c r="C174" s="9">
-        <v>5330</v>
+        <v>6660</v>
       </c>
       <c r="D174" s="9">
-        <v>6530</v>
+        <v>6360</v>
       </c>
       <c r="E174" s="9">
-        <v>6830</v>
+        <v>6660</v>
       </c>
       <c r="F174" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G174" s="7" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="H174" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="I174" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="B175" t="s">
         <v>12</v>
       </c>
       <c r="C175" s="9">
-        <v>5330</v>
+        <v>6660</v>
       </c>
       <c r="D175" s="9">
-        <v>6530</v>
+        <v>6360</v>
       </c>
       <c r="E175" s="9">
-        <v>6830</v>
+        <v>6660</v>
       </c>
       <c r="F175" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G175" s="7" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="H175" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="I175" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="B176" t="s">
         <v>12</v>
       </c>
       <c r="C176" s="9">
-        <v>5330</v>
+        <v>6660</v>
       </c>
       <c r="D176" s="9">
-        <v>6530</v>
+        <v>6360</v>
       </c>
       <c r="E176" s="9">
-        <v>6830</v>
+        <v>6660</v>
       </c>
       <c r="F176" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G176" s="7" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="H176" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="I176" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="B177" t="s">
         <v>12</v>
       </c>
       <c r="C177" s="9">
-        <v>5330</v>
+        <v>6660</v>
       </c>
       <c r="D177" s="9">
-        <v>6530</v>
+        <v>6360</v>
       </c>
       <c r="E177" s="9">
-        <v>6830</v>
+        <v>6660</v>
       </c>
       <c r="F177" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G177" s="7" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="H177" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="I177" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>141</v>
+        <v>75</v>
       </c>
       <c r="B178" t="s">
         <v>12</v>
       </c>
       <c r="C178" s="9">
-        <v>5330</v>
+        <v>6760</v>
       </c>
       <c r="D178" s="9">
-        <v>6530</v>
+        <v>6410</v>
       </c>
       <c r="E178" s="9">
-        <v>6830</v>
+        <v>6760</v>
       </c>
       <c r="F178" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G178" s="7" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="H178" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="I178" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="B179" t="s">
         <v>12</v>
       </c>
       <c r="C179" s="9">
-        <v>5330</v>
+        <v>6760</v>
       </c>
       <c r="D179" s="9">
-        <v>6530</v>
+        <v>6410</v>
       </c>
       <c r="E179" s="9">
-        <v>6830</v>
+        <v>6760</v>
       </c>
       <c r="F179" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G179" s="7" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="H179" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="I179" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B180" t="s">
         <v>12</v>
       </c>
       <c r="C180" s="9">
-        <v>5330</v>
+        <v>6760</v>
       </c>
       <c r="D180" s="9">
-        <v>6530</v>
+        <v>6410</v>
       </c>
       <c r="E180" s="9">
-        <v>6830</v>
+        <v>6760</v>
       </c>
       <c r="F180" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G180" s="7" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="H180" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="I180" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
       <c r="B181" t="s">
         <v>12</v>
       </c>
       <c r="C181" s="9">
-        <v>5330</v>
+        <v>6760</v>
       </c>
       <c r="D181" s="9">
-        <v>6530</v>
+        <v>6410</v>
       </c>
       <c r="E181" s="9">
-        <v>6830</v>
+        <v>6760</v>
       </c>
       <c r="F181" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G181" s="7" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="H181" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="I181" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B182" t="s">
         <v>12</v>
       </c>
       <c r="C182" s="9">
-        <v>5370</v>
+        <v>6760</v>
       </c>
       <c r="D182" s="9">
-        <v>6570</v>
+        <v>6410</v>
       </c>
       <c r="E182" s="9">
-        <v>6870</v>
+        <v>6760</v>
       </c>
       <c r="F182" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G182" s="7" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="H182" t="s">
-        <v>68</v>
+        <v>137</v>
       </c>
       <c r="I182" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="B183" t="s">
         <v>12</v>
       </c>
       <c r="C183" s="9">
-        <v>5370</v>
+        <v>6760</v>
       </c>
       <c r="D183" s="9">
-        <v>6570</v>
+        <v>6410</v>
       </c>
       <c r="E183" s="9">
-        <v>6870</v>
+        <v>6760</v>
       </c>
       <c r="F183" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G183" s="7" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="H183" t="s">
-        <v>68</v>
+        <v>137</v>
       </c>
       <c r="I183" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B184" t="s">
         <v>12</v>
       </c>
       <c r="C184" s="9">
-        <v>5370</v>
+        <v>6760</v>
       </c>
       <c r="D184" s="9">
-        <v>6570</v>
+        <v>6410</v>
       </c>
       <c r="E184" s="9">
-        <v>6870</v>
+        <v>6760</v>
       </c>
       <c r="F184" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G184" s="7" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="H184" t="s">
-        <v>68</v>
+        <v>137</v>
       </c>
       <c r="I184" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="B185" t="s">
         <v>12</v>
       </c>
       <c r="C185" s="9">
-        <v>5370</v>
+        <v>6760</v>
       </c>
       <c r="D185" s="9">
-        <v>6570</v>
+        <v>6410</v>
       </c>
       <c r="E185" s="9">
-        <v>6870</v>
+        <v>6760</v>
       </c>
       <c r="F185" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G185" s="7" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="H185" t="s">
-        <v>68</v>
+        <v>137</v>
       </c>
       <c r="I185" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B186" t="s">
         <v>12</v>
       </c>
-      <c r="C186" s="9">
-        <v>5370</v>
-      </c>
+      <c r="C186" s="9"/>
       <c r="D186" s="9">
-        <v>6570</v>
+        <v>6310</v>
       </c>
       <c r="E186" s="9">
-        <v>6870</v>
+        <v>6510</v>
       </c>
       <c r="F186" t="s">
-        <v>133</v>
-      </c>
-      <c r="G186" s="7" t="s">
-        <v>143</v>
+        <v>134</v>
+      </c>
+      <c r="G186" s="7">
+        <v>17</v>
       </c>
       <c r="H186" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I186" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="B187" t="s">
         <v>12</v>
       </c>
-      <c r="C187" s="9">
-        <v>5370</v>
-      </c>
+      <c r="C187" s="9"/>
       <c r="D187" s="9">
-        <v>6570</v>
+        <v>6310</v>
       </c>
       <c r="E187" s="9">
-        <v>6870</v>
+        <v>6510</v>
       </c>
       <c r="F187" t="s">
-        <v>133</v>
-      </c>
-      <c r="G187" s="7" t="s">
-        <v>143</v>
+        <v>134</v>
+      </c>
+      <c r="G187" s="7">
+        <v>17</v>
       </c>
       <c r="H187" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I187" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B188" t="s">
         <v>12</v>
       </c>
-      <c r="C188" s="9">
-        <v>5370</v>
-      </c>
+      <c r="C188" s="9"/>
       <c r="D188" s="9">
-        <v>6570</v>
+        <v>6310</v>
       </c>
       <c r="E188" s="9">
-        <v>6870</v>
+        <v>6510</v>
       </c>
       <c r="F188" t="s">
-        <v>133</v>
-      </c>
-      <c r="G188" s="7" t="s">
-        <v>143</v>
+        <v>134</v>
+      </c>
+      <c r="G188" s="7">
+        <v>17</v>
       </c>
       <c r="H188" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I188" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>141</v>
+        <v>71</v>
       </c>
       <c r="B189" t="s">
         <v>12</v>
       </c>
-      <c r="C189" s="9">
-        <v>5370</v>
-      </c>
+      <c r="C189" s="9"/>
       <c r="D189" s="9">
-        <v>6570</v>
+        <v>6310</v>
       </c>
       <c r="E189" s="9">
-        <v>6870</v>
+        <v>6510</v>
       </c>
       <c r="F189" t="s">
-        <v>133</v>
-      </c>
-      <c r="G189" s="7" t="s">
-        <v>143</v>
+        <v>134</v>
+      </c>
+      <c r="G189" s="7">
+        <v>17</v>
       </c>
       <c r="H189" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I189" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B190" t="s">
         <v>12</v>
       </c>
-      <c r="C190" s="9">
-        <v>5370</v>
-      </c>
+      <c r="C190" s="9"/>
       <c r="D190" s="9">
-        <v>6570</v>
+        <v>6310</v>
       </c>
       <c r="E190" s="9">
-        <v>6870</v>
+        <v>6510</v>
       </c>
       <c r="F190" t="s">
-        <v>133</v>
-      </c>
-      <c r="G190" s="7" t="s">
-        <v>143</v>
+        <v>134</v>
+      </c>
+      <c r="G190" s="7">
+        <v>17</v>
       </c>
       <c r="H190" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I190" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B191" t="s">
         <v>12</v>
       </c>
-      <c r="C191" s="9">
-        <v>5370</v>
-      </c>
+      <c r="C191" s="9"/>
       <c r="D191" s="9">
-        <v>6570</v>
+        <v>6350</v>
       </c>
       <c r="E191" s="9">
-        <v>6870</v>
+        <v>6550</v>
       </c>
       <c r="F191" t="s">
-        <v>133</v>
-      </c>
-      <c r="G191" s="7" t="s">
-        <v>143</v>
+        <v>134</v>
+      </c>
+      <c r="G191" s="7">
+        <v>18</v>
       </c>
       <c r="H191" t="s">
-        <v>68</v>
+        <v>139</v>
       </c>
       <c r="I191" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
+        <v>72</v>
+      </c>
+      <c r="B192" t="s">
+        <v>12</v>
+      </c>
+      <c r="C192" s="9"/>
+      <c r="D192" s="9">
+        <v>6350</v>
+      </c>
+      <c r="E192" s="9">
+        <v>6550</v>
+      </c>
+      <c r="F192" t="s">
+        <v>134</v>
+      </c>
+      <c r="G192" s="7">
+        <v>18</v>
+      </c>
+      <c r="H192" t="s">
+        <v>139</v>
+      </c>
+      <c r="I192" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>80</v>
+      </c>
+      <c r="B193" t="s">
+        <v>12</v>
+      </c>
+      <c r="C193" s="9"/>
+      <c r="D193" s="9">
+        <v>6350</v>
+      </c>
+      <c r="E193" s="9">
+        <v>6550</v>
+      </c>
+      <c r="F193" t="s">
+        <v>134</v>
+      </c>
+      <c r="G193" s="7">
+        <v>18</v>
+      </c>
+      <c r="H193" t="s">
+        <v>139</v>
+      </c>
+      <c r="I193" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
         <v>71</v>
       </c>
-      <c r="B192" t="s">
-        <v>12</v>
-      </c>
-      <c r="C192" s="9">
-        <v>5370</v>
-      </c>
-      <c r="D192" s="9">
-        <v>6570</v>
-      </c>
-      <c r="E192" s="9">
-        <v>6870</v>
-      </c>
-      <c r="F192" t="s">
-        <v>133</v>
-      </c>
-      <c r="G192" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="H192" t="s">
-        <v>68</v>
-      </c>
-      <c r="I192" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="193" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C193" s="9"/>
-      <c r="D193" s="9"/>
-      <c r="E193" s="9"/>
-      <c r="G193" s="7"/>
-    </row>
-    <row r="194" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="B194" t="s">
+        <v>12</v>
+      </c>
       <c r="C194" s="9"/>
-      <c r="D194" s="9"/>
-      <c r="E194" s="9"/>
-      <c r="G194" s="7"/>
-    </row>
-    <row r="195" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D194" s="9">
+        <v>6350</v>
+      </c>
+      <c r="E194" s="9">
+        <v>6550</v>
+      </c>
+      <c r="F194" t="s">
+        <v>134</v>
+      </c>
+      <c r="G194" s="7">
+        <v>18</v>
+      </c>
+      <c r="H194" t="s">
+        <v>139</v>
+      </c>
+      <c r="I194" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>70</v>
+      </c>
+      <c r="B195" t="s">
+        <v>12</v>
+      </c>
       <c r="C195" s="9"/>
-      <c r="D195" s="9"/>
-      <c r="E195" s="9"/>
-      <c r="G195" s="7"/>
-    </row>
-    <row r="196" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D195" s="9">
+        <v>6350</v>
+      </c>
+      <c r="E195" s="9">
+        <v>6550</v>
+      </c>
+      <c r="F195" t="s">
+        <v>134</v>
+      </c>
+      <c r="G195" s="7">
+        <v>18</v>
+      </c>
+      <c r="H195" t="s">
+        <v>139</v>
+      </c>
+      <c r="I195" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>81</v>
+      </c>
+      <c r="B196" t="s">
+        <v>12</v>
+      </c>
       <c r="C196" s="9"/>
-      <c r="D196" s="9"/>
-      <c r="E196" s="9"/>
-      <c r="G196" s="7"/>
-    </row>
-    <row r="197" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D196" s="9">
+        <v>6430</v>
+      </c>
+      <c r="E196" s="9">
+        <v>6730</v>
+      </c>
+      <c r="F196" t="s">
+        <v>134</v>
+      </c>
+      <c r="G196" s="7">
+        <v>21</v>
+      </c>
+      <c r="H196" t="s">
+        <v>137</v>
+      </c>
+      <c r="I196" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>72</v>
+      </c>
+      <c r="B197" t="s">
+        <v>12</v>
+      </c>
       <c r="C197" s="9"/>
-      <c r="D197" s="9"/>
-      <c r="E197" s="9"/>
-      <c r="G197" s="7"/>
-    </row>
-    <row r="198" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D197" s="9">
+        <v>6430</v>
+      </c>
+      <c r="E197" s="9">
+        <v>6730</v>
+      </c>
+      <c r="F197" t="s">
+        <v>134</v>
+      </c>
+      <c r="G197" s="7">
+        <v>21</v>
+      </c>
+      <c r="H197" t="s">
+        <v>137</v>
+      </c>
+      <c r="I197" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>80</v>
+      </c>
+      <c r="B198" t="s">
+        <v>12</v>
+      </c>
       <c r="C198" s="9"/>
-      <c r="D198" s="9"/>
-      <c r="E198" s="9"/>
-      <c r="G198" s="7"/>
-    </row>
-    <row r="199" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D198" s="9">
+        <v>6430</v>
+      </c>
+      <c r="E198" s="9">
+        <v>6730</v>
+      </c>
+      <c r="F198" t="s">
+        <v>134</v>
+      </c>
+      <c r="G198" s="7">
+        <v>21</v>
+      </c>
+      <c r="H198" t="s">
+        <v>137</v>
+      </c>
+      <c r="I198" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>71</v>
+      </c>
+      <c r="B199" t="s">
+        <v>12</v>
+      </c>
       <c r="C199" s="9"/>
-      <c r="D199" s="9"/>
-      <c r="E199" s="9"/>
-      <c r="G199" s="7"/>
-    </row>
-    <row r="200" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D199" s="9">
+        <v>6430</v>
+      </c>
+      <c r="E199" s="9">
+        <v>6730</v>
+      </c>
+      <c r="F199" t="s">
+        <v>134</v>
+      </c>
+      <c r="G199" s="7">
+        <v>21</v>
+      </c>
+      <c r="H199" t="s">
+        <v>137</v>
+      </c>
+      <c r="I199" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>70</v>
+      </c>
+      <c r="B200" t="s">
+        <v>12</v>
+      </c>
       <c r="C200" s="9"/>
-      <c r="D200" s="9"/>
-      <c r="E200" s="9"/>
-      <c r="G200" s="7"/>
-    </row>
-    <row r="201" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D200" s="9">
+        <v>6430</v>
+      </c>
+      <c r="E200" s="9">
+        <v>6730</v>
+      </c>
+      <c r="F200" t="s">
+        <v>134</v>
+      </c>
+      <c r="G200" s="7">
+        <v>21</v>
+      </c>
+      <c r="H200" t="s">
+        <v>137</v>
+      </c>
+      <c r="I200" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C201" s="9"/>
       <c r="D201" s="9"/>
       <c r="E201" s="9"/>
       <c r="G201" s="7"/>
     </row>
-    <row r="202" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C202" s="9"/>
       <c r="D202" s="9"/>
       <c r="E202" s="9"/>
       <c r="G202" s="7"/>
     </row>
-    <row r="203" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C203" s="9"/>
       <c r="D203" s="9"/>
       <c r="E203" s="9"/>
       <c r="G203" s="7"/>
     </row>
-    <row r="204" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C204" s="9"/>
       <c r="D204" s="9"/>
       <c r="E204" s="9"/>
       <c r="G204" s="7"/>
     </row>
-    <row r="205" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C205" s="9"/>
       <c r="D205" s="9"/>
       <c r="E205" s="9"/>
       <c r="G205" s="7"/>
     </row>
-    <row r="206" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C206" s="9"/>
       <c r="D206" s="9"/>
       <c r="E206" s="9"/>
       <c r="G206" s="7"/>
     </row>
-    <row r="207" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C207" s="9"/>
       <c r="D207" s="9"/>
       <c r="E207" s="9"/>
       <c r="G207" s="7"/>
     </row>
-    <row r="208" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C208" s="9"/>
       <c r="D208" s="9"/>
       <c r="E208" s="9"/>
@@ -6573,840 +6732,6 @@
       <c r="D217" s="9"/>
       <c r="E217" s="9"/>
       <c r="G217" s="7"/>
-    </row>
-    <row r="218" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C218" s="9"/>
-      <c r="D218" s="9"/>
-      <c r="E218" s="9"/>
-      <c r="G218" s="7"/>
-    </row>
-    <row r="219" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C219" s="9"/>
-      <c r="D219" s="9"/>
-      <c r="E219" s="9"/>
-      <c r="G219" s="7"/>
-    </row>
-    <row r="220" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C220" s="9"/>
-      <c r="D220" s="9"/>
-      <c r="E220" s="9"/>
-      <c r="G220" s="7"/>
-    </row>
-    <row r="221" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C221" s="9"/>
-      <c r="D221" s="9"/>
-      <c r="E221" s="9"/>
-      <c r="G221" s="7"/>
-    </row>
-    <row r="222" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C222" s="9"/>
-      <c r="D222" s="9"/>
-      <c r="E222" s="9"/>
-      <c r="G222" s="7"/>
-    </row>
-    <row r="223" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C223" s="9"/>
-      <c r="D223" s="9"/>
-      <c r="E223" s="9"/>
-      <c r="G223" s="7"/>
-    </row>
-    <row r="224" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C224" s="9"/>
-      <c r="D224" s="9"/>
-      <c r="E224" s="9"/>
-      <c r="G224" s="7"/>
-    </row>
-    <row r="225" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C225" s="9"/>
-      <c r="D225" s="9"/>
-      <c r="E225" s="9"/>
-      <c r="G225" s="7"/>
-    </row>
-    <row r="226" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C226" s="9"/>
-      <c r="D226" s="9"/>
-      <c r="E226" s="9"/>
-      <c r="G226" s="7"/>
-    </row>
-    <row r="227" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C227" s="9"/>
-      <c r="D227" s="9"/>
-      <c r="E227" s="9"/>
-      <c r="G227" s="7"/>
-    </row>
-    <row r="228" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C228" s="9"/>
-      <c r="D228" s="9"/>
-      <c r="E228" s="9"/>
-      <c r="G228" s="7"/>
-    </row>
-    <row r="229" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C229" s="9"/>
-      <c r="D229" s="9"/>
-      <c r="E229" s="9"/>
-      <c r="G229" s="7"/>
-    </row>
-    <row r="230" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C230" s="9"/>
-      <c r="D230" s="9"/>
-      <c r="E230" s="9"/>
-      <c r="G230" s="7"/>
-    </row>
-    <row r="231" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C231" s="9"/>
-      <c r="D231" s="9"/>
-      <c r="E231" s="9"/>
-      <c r="G231" s="7"/>
-    </row>
-    <row r="232" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C232" s="9"/>
-      <c r="D232" s="9"/>
-      <c r="E232" s="9"/>
-      <c r="G232" s="7"/>
-    </row>
-    <row r="233" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C233" s="9"/>
-      <c r="D233" s="9"/>
-      <c r="E233" s="9"/>
-      <c r="G233" s="7"/>
-    </row>
-    <row r="234" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C234" s="9"/>
-      <c r="D234" s="9"/>
-      <c r="E234" s="9"/>
-      <c r="G234" s="7"/>
-    </row>
-    <row r="235" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C235" s="9"/>
-      <c r="D235" s="9"/>
-      <c r="E235" s="9"/>
-      <c r="G235" s="7"/>
-    </row>
-    <row r="236" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C236" s="9"/>
-      <c r="D236" s="9"/>
-      <c r="E236" s="9"/>
-      <c r="G236" s="7"/>
-    </row>
-    <row r="237" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C237" s="9"/>
-      <c r="D237" s="9"/>
-      <c r="E237" s="9"/>
-      <c r="G237" s="7"/>
-    </row>
-    <row r="238" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C238" s="9"/>
-      <c r="D238" s="9"/>
-      <c r="E238" s="9"/>
-      <c r="G238" s="7"/>
-    </row>
-    <row r="239" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C239" s="9"/>
-      <c r="D239" s="9"/>
-      <c r="E239" s="9"/>
-      <c r="G239" s="7"/>
-    </row>
-    <row r="240" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C240" s="9"/>
-      <c r="D240" s="9"/>
-      <c r="E240" s="9"/>
-      <c r="G240" s="7"/>
-    </row>
-    <row r="241" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C241" s="9"/>
-      <c r="D241" s="9"/>
-      <c r="E241" s="9"/>
-      <c r="G241" s="7"/>
-    </row>
-    <row r="242" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C242" s="9"/>
-      <c r="D242" s="9"/>
-      <c r="E242" s="9"/>
-      <c r="G242" s="7"/>
-    </row>
-    <row r="243" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C243" s="9"/>
-      <c r="D243" s="9"/>
-      <c r="E243" s="9"/>
-      <c r="G243" s="7"/>
-    </row>
-    <row r="244" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C244" s="9"/>
-      <c r="D244" s="9"/>
-      <c r="E244" s="9"/>
-      <c r="G244" s="7"/>
-    </row>
-    <row r="245" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C245" s="9"/>
-      <c r="D245" s="9"/>
-      <c r="E245" s="9"/>
-      <c r="G245" s="7"/>
-    </row>
-    <row r="246" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C246" s="9"/>
-      <c r="D246" s="9"/>
-      <c r="E246" s="9"/>
-      <c r="G246" s="7"/>
-    </row>
-    <row r="247" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C247" s="9"/>
-      <c r="D247" s="9"/>
-      <c r="E247" s="9"/>
-      <c r="G247" s="7"/>
-    </row>
-    <row r="248" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C248" s="9"/>
-      <c r="D248" s="9"/>
-      <c r="E248" s="9"/>
-      <c r="G248" s="7"/>
-    </row>
-    <row r="249" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C249" s="9"/>
-      <c r="D249" s="9"/>
-      <c r="E249" s="9"/>
-      <c r="G249" s="7"/>
-    </row>
-    <row r="250" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C250" s="9"/>
-      <c r="D250" s="9"/>
-      <c r="E250" s="9"/>
-      <c r="G250" s="7"/>
-    </row>
-    <row r="251" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C251" s="9"/>
-      <c r="D251" s="9"/>
-      <c r="E251" s="9"/>
-      <c r="G251" s="7"/>
-    </row>
-    <row r="252" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C252" s="9"/>
-      <c r="D252" s="9"/>
-      <c r="E252" s="9"/>
-      <c r="G252" s="7"/>
-    </row>
-    <row r="253" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C253" s="9"/>
-      <c r="D253" s="9"/>
-      <c r="E253" s="9"/>
-      <c r="G253" s="7"/>
-    </row>
-    <row r="254" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C254" s="9"/>
-      <c r="D254" s="9"/>
-      <c r="E254" s="9"/>
-      <c r="G254" s="7"/>
-    </row>
-    <row r="255" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C255" s="9"/>
-      <c r="D255" s="9"/>
-      <c r="E255" s="9"/>
-      <c r="G255" s="7"/>
-    </row>
-    <row r="256" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C256" s="9"/>
-      <c r="D256" s="9"/>
-      <c r="E256" s="9"/>
-      <c r="G256" s="7"/>
-    </row>
-    <row r="257" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C257" s="9"/>
-      <c r="D257" s="9"/>
-      <c r="E257" s="9"/>
-      <c r="G257" s="7"/>
-    </row>
-    <row r="258" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C258" s="9"/>
-      <c r="D258" s="9"/>
-      <c r="E258" s="9"/>
-      <c r="G258" s="7"/>
-    </row>
-    <row r="259" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C259" s="9"/>
-      <c r="D259" s="9"/>
-      <c r="E259" s="9"/>
-      <c r="G259" s="7"/>
-    </row>
-    <row r="260" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C260" s="9"/>
-      <c r="D260" s="9"/>
-      <c r="E260" s="9"/>
-      <c r="G260" s="7"/>
-    </row>
-    <row r="261" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C261" s="9"/>
-      <c r="D261" s="9"/>
-      <c r="E261" s="9"/>
-      <c r="G261" s="7"/>
-    </row>
-    <row r="262" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C262" s="9"/>
-      <c r="D262" s="9"/>
-      <c r="E262" s="9"/>
-      <c r="G262" s="7"/>
-    </row>
-    <row r="263" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C263" s="9"/>
-      <c r="D263" s="9"/>
-      <c r="E263" s="9"/>
-      <c r="G263" s="7"/>
-    </row>
-    <row r="264" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C264" s="9"/>
-      <c r="D264" s="9"/>
-      <c r="E264" s="9"/>
-      <c r="G264" s="7"/>
-    </row>
-    <row r="265" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C265" s="9"/>
-      <c r="D265" s="9"/>
-      <c r="E265" s="9"/>
-      <c r="G265" s="7"/>
-    </row>
-    <row r="266" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C266" s="9"/>
-      <c r="D266" s="9"/>
-      <c r="E266" s="9"/>
-      <c r="G266" s="7"/>
-    </row>
-    <row r="267" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C267" s="9"/>
-      <c r="D267" s="9"/>
-      <c r="E267" s="9"/>
-      <c r="G267" s="7"/>
-    </row>
-    <row r="268" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C268" s="9"/>
-      <c r="D268" s="9"/>
-      <c r="E268" s="9"/>
-      <c r="G268" s="7"/>
-    </row>
-    <row r="269" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C269" s="9"/>
-      <c r="D269" s="9"/>
-      <c r="E269" s="9"/>
-      <c r="G269" s="7"/>
-    </row>
-    <row r="270" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C270" s="9"/>
-      <c r="D270" s="9"/>
-      <c r="E270" s="9"/>
-      <c r="G270" s="7"/>
-    </row>
-    <row r="271" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C271" s="9"/>
-      <c r="D271" s="9"/>
-      <c r="E271" s="9"/>
-      <c r="G271" s="7"/>
-    </row>
-    <row r="272" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C272" s="9"/>
-      <c r="D272" s="9"/>
-      <c r="E272" s="9"/>
-      <c r="G272" s="7"/>
-    </row>
-    <row r="273" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C273" s="9"/>
-      <c r="D273" s="9"/>
-      <c r="E273" s="9"/>
-      <c r="G273" s="7"/>
-    </row>
-    <row r="274" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C274" s="9"/>
-      <c r="D274" s="9"/>
-      <c r="E274" s="9"/>
-      <c r="G274" s="7"/>
-    </row>
-    <row r="275" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C275" s="9"/>
-      <c r="D275" s="9"/>
-      <c r="E275" s="9"/>
-      <c r="G275" s="7"/>
-    </row>
-    <row r="276" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C276" s="9"/>
-      <c r="D276" s="9"/>
-      <c r="E276" s="9"/>
-      <c r="G276" s="7"/>
-    </row>
-    <row r="277" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C277" s="9"/>
-      <c r="D277" s="9"/>
-      <c r="E277" s="9"/>
-      <c r="G277" s="7"/>
-    </row>
-    <row r="278" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C278" s="9"/>
-      <c r="D278" s="9"/>
-      <c r="E278" s="9"/>
-      <c r="G278" s="7"/>
-    </row>
-    <row r="279" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C279" s="9"/>
-      <c r="D279" s="9"/>
-      <c r="E279" s="9"/>
-      <c r="G279" s="7"/>
-    </row>
-    <row r="280" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C280" s="9"/>
-      <c r="D280" s="9"/>
-      <c r="E280" s="9"/>
-      <c r="G280" s="7"/>
-    </row>
-    <row r="281" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C281" s="9"/>
-      <c r="D281" s="9"/>
-      <c r="E281" s="9"/>
-      <c r="G281" s="7"/>
-    </row>
-    <row r="282" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C282" s="9"/>
-      <c r="D282" s="9"/>
-      <c r="E282" s="9"/>
-      <c r="G282" s="7"/>
-    </row>
-    <row r="283" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C283" s="9"/>
-      <c r="D283" s="9"/>
-      <c r="E283" s="9"/>
-      <c r="G283" s="7"/>
-    </row>
-    <row r="284" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C284" s="9"/>
-      <c r="D284" s="9"/>
-      <c r="E284" s="9"/>
-      <c r="G284" s="7"/>
-    </row>
-    <row r="285" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C285" s="9"/>
-      <c r="D285" s="9"/>
-      <c r="E285" s="9"/>
-      <c r="G285" s="7"/>
-    </row>
-    <row r="286" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C286" s="9"/>
-      <c r="D286" s="9"/>
-      <c r="E286" s="9"/>
-      <c r="G286" s="7"/>
-    </row>
-    <row r="287" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C287" s="9"/>
-      <c r="D287" s="9"/>
-      <c r="E287" s="9"/>
-      <c r="G287" s="7"/>
-    </row>
-    <row r="288" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C288" s="9"/>
-      <c r="D288" s="9"/>
-      <c r="E288" s="9"/>
-      <c r="G288" s="7"/>
-    </row>
-    <row r="289" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C289" s="9"/>
-      <c r="D289" s="9"/>
-      <c r="E289" s="9"/>
-      <c r="G289" s="7"/>
-    </row>
-    <row r="290" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C290" s="9"/>
-      <c r="D290" s="9"/>
-      <c r="E290" s="9"/>
-      <c r="G290" s="7"/>
-    </row>
-    <row r="291" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C291" s="9"/>
-      <c r="D291" s="9"/>
-      <c r="E291" s="9"/>
-      <c r="G291" s="7"/>
-    </row>
-    <row r="292" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C292" s="9"/>
-      <c r="D292" s="9"/>
-      <c r="E292" s="9"/>
-      <c r="G292" s="7"/>
-    </row>
-    <row r="293" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C293" s="9"/>
-      <c r="D293" s="9"/>
-      <c r="E293" s="9"/>
-      <c r="G293" s="7"/>
-    </row>
-    <row r="294" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C294" s="9"/>
-      <c r="D294" s="9"/>
-      <c r="E294" s="9"/>
-      <c r="G294" s="7"/>
-    </row>
-    <row r="295" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C295" s="9"/>
-      <c r="D295" s="9"/>
-      <c r="E295" s="9"/>
-      <c r="G295" s="7"/>
-    </row>
-    <row r="296" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C296" s="9"/>
-      <c r="D296" s="9"/>
-      <c r="E296" s="9"/>
-      <c r="G296" s="7"/>
-    </row>
-    <row r="297" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C297" s="9"/>
-      <c r="D297" s="9"/>
-      <c r="E297" s="9"/>
-      <c r="G297" s="7"/>
-    </row>
-    <row r="298" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C298" s="9"/>
-      <c r="D298" s="9"/>
-      <c r="E298" s="9"/>
-      <c r="G298" s="7"/>
-    </row>
-    <row r="299" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C299" s="9"/>
-      <c r="D299" s="9"/>
-      <c r="E299" s="9"/>
-      <c r="G299" s="7"/>
-    </row>
-    <row r="300" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C300" s="9"/>
-      <c r="D300" s="9"/>
-      <c r="E300" s="9"/>
-      <c r="G300" s="7"/>
-    </row>
-    <row r="301" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C301" s="9"/>
-      <c r="D301" s="9"/>
-      <c r="E301" s="9"/>
-      <c r="G301" s="7"/>
-    </row>
-    <row r="302" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C302" s="9"/>
-      <c r="D302" s="9"/>
-      <c r="E302" s="9"/>
-      <c r="G302" s="7"/>
-    </row>
-    <row r="303" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C303" s="9"/>
-      <c r="D303" s="9"/>
-      <c r="E303" s="9"/>
-      <c r="G303" s="7"/>
-    </row>
-    <row r="304" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C304" s="9"/>
-      <c r="D304" s="9"/>
-      <c r="E304" s="9"/>
-      <c r="G304" s="7"/>
-    </row>
-    <row r="305" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C305" s="9"/>
-      <c r="D305" s="9"/>
-      <c r="E305" s="9"/>
-      <c r="G305" s="7"/>
-    </row>
-    <row r="306" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C306" s="9"/>
-      <c r="D306" s="9"/>
-      <c r="E306" s="9"/>
-      <c r="G306" s="7"/>
-    </row>
-    <row r="307" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C307" s="9"/>
-      <c r="D307" s="9"/>
-      <c r="E307" s="9"/>
-      <c r="G307" s="7"/>
-    </row>
-    <row r="308" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C308" s="9"/>
-      <c r="D308" s="9"/>
-      <c r="E308" s="9"/>
-      <c r="G308" s="7"/>
-    </row>
-    <row r="309" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C309" s="9"/>
-      <c r="D309" s="9"/>
-      <c r="E309" s="9"/>
-      <c r="G309" s="7"/>
-    </row>
-    <row r="310" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C310" s="9"/>
-      <c r="D310" s="9"/>
-      <c r="E310" s="9"/>
-      <c r="G310" s="7"/>
-    </row>
-    <row r="311" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C311" s="9"/>
-      <c r="D311" s="9"/>
-      <c r="E311" s="9"/>
-      <c r="G311" s="7"/>
-    </row>
-    <row r="312" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C312" s="9"/>
-      <c r="D312" s="9"/>
-      <c r="E312" s="9"/>
-      <c r="G312" s="7"/>
-    </row>
-    <row r="313" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C313" s="9"/>
-      <c r="D313" s="9"/>
-      <c r="E313" s="9"/>
-      <c r="G313" s="7"/>
-    </row>
-    <row r="314" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C314" s="9"/>
-      <c r="D314" s="9"/>
-      <c r="E314" s="9"/>
-      <c r="G314" s="7"/>
-    </row>
-    <row r="315" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C315" s="9"/>
-      <c r="D315" s="9"/>
-      <c r="E315" s="9"/>
-      <c r="G315" s="7"/>
-    </row>
-    <row r="316" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C316" s="9"/>
-      <c r="D316" s="9"/>
-      <c r="E316" s="9"/>
-      <c r="G316" s="7"/>
-    </row>
-    <row r="317" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C317" s="9"/>
-      <c r="D317" s="9"/>
-      <c r="E317" s="9"/>
-      <c r="G317" s="7"/>
-    </row>
-    <row r="318" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C318" s="9"/>
-      <c r="D318" s="9"/>
-      <c r="E318" s="9"/>
-      <c r="G318" s="7"/>
-    </row>
-    <row r="319" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C319" s="9"/>
-      <c r="D319" s="9"/>
-      <c r="E319" s="9"/>
-      <c r="G319" s="7"/>
-    </row>
-    <row r="320" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C320" s="9"/>
-      <c r="D320" s="9"/>
-      <c r="E320" s="9"/>
-      <c r="G320" s="7"/>
-    </row>
-    <row r="321" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C321" s="9"/>
-      <c r="D321" s="9"/>
-      <c r="E321" s="9"/>
-      <c r="G321" s="7"/>
-    </row>
-    <row r="322" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C322" s="9"/>
-      <c r="D322" s="9"/>
-      <c r="E322" s="9"/>
-      <c r="G322" s="7"/>
-    </row>
-    <row r="323" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C323" s="9"/>
-      <c r="D323" s="9"/>
-      <c r="E323" s="9"/>
-      <c r="G323" s="7"/>
-    </row>
-    <row r="324" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C324" s="9"/>
-      <c r="D324" s="9"/>
-      <c r="E324" s="9"/>
-      <c r="G324" s="7"/>
-    </row>
-    <row r="325" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C325" s="9"/>
-      <c r="D325" s="9"/>
-      <c r="E325" s="9"/>
-      <c r="G325" s="7"/>
-    </row>
-    <row r="326" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C326" s="9"/>
-      <c r="D326" s="9"/>
-      <c r="E326" s="9"/>
-      <c r="G326" s="7"/>
-    </row>
-    <row r="327" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C327" s="9"/>
-      <c r="D327" s="9"/>
-      <c r="E327" s="9"/>
-      <c r="G327" s="7"/>
-    </row>
-    <row r="328" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C328" s="9"/>
-      <c r="D328" s="9"/>
-      <c r="E328" s="9"/>
-      <c r="G328" s="7"/>
-    </row>
-    <row r="329" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C329" s="9"/>
-      <c r="D329" s="9"/>
-      <c r="E329" s="9"/>
-      <c r="G329" s="7"/>
-    </row>
-    <row r="330" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C330" s="9"/>
-      <c r="D330" s="9"/>
-      <c r="E330" s="9"/>
-      <c r="G330" s="7"/>
-    </row>
-    <row r="331" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C331" s="9"/>
-      <c r="D331" s="9"/>
-      <c r="E331" s="9"/>
-      <c r="G331" s="7"/>
-    </row>
-    <row r="332" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C332" s="9"/>
-      <c r="D332" s="9"/>
-      <c r="E332" s="9"/>
-      <c r="G332" s="7"/>
-    </row>
-    <row r="333" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C333" s="9"/>
-      <c r="D333" s="9"/>
-      <c r="E333" s="9"/>
-      <c r="G333" s="7"/>
-    </row>
-    <row r="334" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C334" s="9"/>
-      <c r="D334" s="9"/>
-      <c r="E334" s="9"/>
-      <c r="G334" s="7"/>
-    </row>
-    <row r="335" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C335" s="9"/>
-      <c r="D335" s="9"/>
-      <c r="E335" s="9"/>
-      <c r="G335" s="7"/>
-    </row>
-    <row r="336" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C336" s="9"/>
-      <c r="D336" s="9"/>
-      <c r="E336" s="9"/>
-      <c r="G336" s="7"/>
-    </row>
-    <row r="337" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C337" s="9"/>
-      <c r="D337" s="9"/>
-      <c r="E337" s="9"/>
-      <c r="G337" s="7"/>
-    </row>
-    <row r="338" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C338" s="9"/>
-      <c r="D338" s="9"/>
-      <c r="E338" s="9"/>
-      <c r="G338" s="7"/>
-    </row>
-    <row r="339" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C339" s="9"/>
-      <c r="D339" s="9"/>
-      <c r="E339" s="9"/>
-      <c r="G339" s="7"/>
-    </row>
-    <row r="340" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C340" s="9"/>
-      <c r="D340" s="9"/>
-      <c r="E340" s="9"/>
-      <c r="G340" s="7"/>
-    </row>
-    <row r="341" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C341" s="9"/>
-      <c r="D341" s="9"/>
-      <c r="E341" s="9"/>
-      <c r="G341" s="7"/>
-    </row>
-    <row r="342" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C342" s="9"/>
-      <c r="D342" s="9"/>
-      <c r="E342" s="9"/>
-      <c r="G342" s="7"/>
-    </row>
-    <row r="343" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C343" s="9"/>
-      <c r="D343" s="9"/>
-      <c r="E343" s="9"/>
-      <c r="G343" s="7"/>
-    </row>
-    <row r="344" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C344" s="9"/>
-      <c r="D344" s="9"/>
-      <c r="E344" s="9"/>
-      <c r="G344" s="7"/>
-    </row>
-    <row r="345" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C345" s="9"/>
-      <c r="D345" s="9"/>
-      <c r="E345" s="9"/>
-      <c r="G345" s="7"/>
-    </row>
-    <row r="346" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C346" s="9"/>
-      <c r="D346" s="9"/>
-      <c r="E346" s="9"/>
-      <c r="G346" s="7"/>
-    </row>
-    <row r="347" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C347" s="9"/>
-      <c r="D347" s="9"/>
-      <c r="E347" s="9"/>
-      <c r="G347" s="7"/>
-    </row>
-    <row r="348" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C348" s="9"/>
-      <c r="D348" s="9"/>
-      <c r="E348" s="9"/>
-      <c r="G348" s="7"/>
-    </row>
-    <row r="349" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C349" s="9"/>
-      <c r="D349" s="9"/>
-      <c r="E349" s="9"/>
-      <c r="G349" s="7"/>
-    </row>
-    <row r="350" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C350" s="9"/>
-      <c r="D350" s="9"/>
-      <c r="E350" s="9"/>
-      <c r="G350" s="7"/>
-    </row>
-    <row r="351" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C351" s="9"/>
-      <c r="D351" s="9"/>
-      <c r="E351" s="9"/>
-      <c r="G351" s="7"/>
-    </row>
-    <row r="352" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C352" s="9"/>
-      <c r="D352" s="9"/>
-      <c r="E352" s="9"/>
-      <c r="G352" s="7"/>
-    </row>
-    <row r="353" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C353" s="9"/>
-      <c r="D353" s="9"/>
-      <c r="E353" s="9"/>
-      <c r="G353" s="7"/>
-    </row>
-    <row r="354" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C354" s="9"/>
-      <c r="D354" s="9"/>
-      <c r="E354" s="9"/>
-      <c r="G354" s="7"/>
-    </row>
-    <row r="355" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C355" s="9"/>
-      <c r="D355" s="9"/>
-      <c r="E355" s="9"/>
-      <c r="G355" s="7"/>
-    </row>
-    <row r="356" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C356" s="9"/>
-      <c r="D356" s="9"/>
-      <c r="E356" s="9"/>
-      <c r="G356" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}"/>
@@ -7502,7 +6827,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3805A486-29BF-4244-AD2E-4DBCFFE9D0EA}">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -7537,12 +6862,7 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DOCS EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF2A3FC9-E325-4505-946D-515C57848475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD0C9728-7E14-4F9D-8EB8-0DFB04949693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5798,9 +5798,7 @@
       <c r="B171" t="s">
         <v>12</v>
       </c>
-      <c r="C171" s="9">
-        <v>6660</v>
-      </c>
+      <c r="C171" s="9"/>
       <c r="D171" s="9">
         <v>6360</v>
       </c>
@@ -5827,9 +5825,7 @@
       <c r="B172" t="s">
         <v>12</v>
       </c>
-      <c r="C172" s="9">
-        <v>6660</v>
-      </c>
+      <c r="C172" s="9"/>
       <c r="D172" s="9">
         <v>6360</v>
       </c>
@@ -5856,9 +5852,7 @@
       <c r="B173" t="s">
         <v>12</v>
       </c>
-      <c r="C173" s="9">
-        <v>6660</v>
-      </c>
+      <c r="C173" s="9"/>
       <c r="D173" s="9">
         <v>6360</v>
       </c>
@@ -5885,9 +5879,7 @@
       <c r="B174" t="s">
         <v>12</v>
       </c>
-      <c r="C174" s="9">
-        <v>6660</v>
-      </c>
+      <c r="C174" s="9"/>
       <c r="D174" s="9">
         <v>6360</v>
       </c>
@@ -5914,9 +5906,7 @@
       <c r="B175" t="s">
         <v>12</v>
       </c>
-      <c r="C175" s="9">
-        <v>6660</v>
-      </c>
+      <c r="C175" s="9"/>
       <c r="D175" s="9">
         <v>6360</v>
       </c>
@@ -5943,9 +5933,7 @@
       <c r="B176" t="s">
         <v>12</v>
       </c>
-      <c r="C176" s="9">
-        <v>6660</v>
-      </c>
+      <c r="C176" s="9"/>
       <c r="D176" s="9">
         <v>6360</v>
       </c>
@@ -5972,9 +5960,7 @@
       <c r="B177" t="s">
         <v>12</v>
       </c>
-      <c r="C177" s="9">
-        <v>6660</v>
-      </c>
+      <c r="C177" s="9"/>
       <c r="D177" s="9">
         <v>6360</v>
       </c>
@@ -6001,9 +5987,7 @@
       <c r="B178" t="s">
         <v>12</v>
       </c>
-      <c r="C178" s="9">
-        <v>6760</v>
-      </c>
+      <c r="C178" s="9"/>
       <c r="D178" s="9">
         <v>6410</v>
       </c>
@@ -6030,9 +6014,7 @@
       <c r="B179" t="s">
         <v>12</v>
       </c>
-      <c r="C179" s="9">
-        <v>6760</v>
-      </c>
+      <c r="C179" s="9"/>
       <c r="D179" s="9">
         <v>6410</v>
       </c>
@@ -6059,9 +6041,7 @@
       <c r="B180" t="s">
         <v>12</v>
       </c>
-      <c r="C180" s="9">
-        <v>6760</v>
-      </c>
+      <c r="C180" s="9"/>
       <c r="D180" s="9">
         <v>6410</v>
       </c>
@@ -6088,9 +6068,7 @@
       <c r="B181" t="s">
         <v>12</v>
       </c>
-      <c r="C181" s="9">
-        <v>6760</v>
-      </c>
+      <c r="C181" s="9"/>
       <c r="D181" s="9">
         <v>6410</v>
       </c>
@@ -6117,9 +6095,7 @@
       <c r="B182" t="s">
         <v>12</v>
       </c>
-      <c r="C182" s="9">
-        <v>6760</v>
-      </c>
+      <c r="C182" s="9"/>
       <c r="D182" s="9">
         <v>6410</v>
       </c>
@@ -6146,9 +6122,7 @@
       <c r="B183" t="s">
         <v>12</v>
       </c>
-      <c r="C183" s="9">
-        <v>6760</v>
-      </c>
+      <c r="C183" s="9"/>
       <c r="D183" s="9">
         <v>6410</v>
       </c>
@@ -6175,9 +6149,7 @@
       <c r="B184" t="s">
         <v>12</v>
       </c>
-      <c r="C184" s="9">
-        <v>6760</v>
-      </c>
+      <c r="C184" s="9"/>
       <c r="D184" s="9">
         <v>6410</v>
       </c>
@@ -6204,9 +6176,7 @@
       <c r="B185" t="s">
         <v>12</v>
       </c>
-      <c r="C185" s="9">
-        <v>6760</v>
-      </c>
+      <c r="C185" s="9"/>
       <c r="D185" s="9">
         <v>6410</v>
       </c>
